--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://desenvolvimentocartaodetodo-my.sharepoint.com/personal/peopleanalytics_cartaodetodos_com/Documents/People Analytics/PEPO 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{3C106086-31EC-41F0-8AB6-DE03ED0B0AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{2E15DFB4-E428-4DE4-88DA-4CA6BE165C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
-    <sheet name="Respostas_Gestores" sheetId="2" r:id="rId2"/>
-    <sheet name="Validacoes_Gestores_PEPO2026" sheetId="3" r:id="rId3"/>
+    <sheet name="Respostas" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="867">
   <si>
     <t>Gestor Avaliador</t>
   </si>
@@ -1996,18 +1995,6 @@
     <t>ALTAIR DE JESUS VILAR GUIMARAES</t>
   </si>
   <si>
-    <t>1641891</t>
-  </si>
-  <si>
-    <t>LUIGGI DELA MURA PASQUARELLI</t>
-  </si>
-  <si>
-    <t>PILOTO COMERCIAL DE HELICOPTERO</t>
-  </si>
-  <si>
-    <t>25 - PRESIDENCIA - ALTAIR</t>
-  </si>
-  <si>
     <t>985260</t>
   </si>
   <si>
@@ -2269,18 +2256,6 @@
     <t>HENDRIC CAVALCANTE DE OLIVEIRA ANDRADE</t>
   </si>
   <si>
-    <t>365535</t>
-  </si>
-  <si>
-    <t>M01</t>
-  </si>
-  <si>
-    <t>COORDENADORA ADMINISTRATIVA FINANCEIRA (M.I)</t>
-  </si>
-  <si>
-    <t>25 - MARA - COORDENADOR</t>
-  </si>
-  <si>
     <t>331800</t>
   </si>
   <si>
@@ -2407,15 +2382,6 @@
     <t>25 - OPERACOES - DIRETORIA</t>
   </si>
   <si>
-    <t>94726</t>
-  </si>
-  <si>
-    <t>IC02</t>
-  </si>
-  <si>
-    <t>25 - INCUBADORA - DIRETORIA</t>
-  </si>
-  <si>
     <t>2180921</t>
   </si>
   <si>
@@ -2437,18 +2403,6 @@
     <t>JULIA ALVES PINHEIRO GONCALVES MENEZES</t>
   </si>
   <si>
-    <t>70320</t>
-  </si>
-  <si>
-    <t>PJ24</t>
-  </si>
-  <si>
-    <t>DIRETOR REGIONAL</t>
-  </si>
-  <si>
-    <t>REGIONAL SÃO PAULO - MINAS - DIRETORIA</t>
-  </si>
-  <si>
     <t>ANDRE NADEO</t>
   </si>
   <si>
@@ -2461,45 +2415,9 @@
     <t>ASSISTENTE ADMINISTRATIVO PLANETA DE TODOS</t>
   </si>
   <si>
-    <t>13154</t>
-  </si>
-  <si>
-    <t>PJ16</t>
-  </si>
-  <si>
     <t>BRUNO CASTRO METZKER</t>
   </si>
   <si>
-    <t>REGIONAL EQUATORIAL - DIRETORIA</t>
-  </si>
-  <si>
-    <t>70319</t>
-  </si>
-  <si>
-    <t>PJ17</t>
-  </si>
-  <si>
-    <t>REGIONAL CENTRO SUL - DIRETORIA</t>
-  </si>
-  <si>
-    <t>70338</t>
-  </si>
-  <si>
-    <t>PJ23</t>
-  </si>
-  <si>
-    <t>REGIONAL COSTA LESTE - DIRETORIA</t>
-  </si>
-  <si>
-    <t>70327</t>
-  </si>
-  <si>
-    <t>PJ26</t>
-  </si>
-  <si>
-    <t>REGIONAL INTERIOR - DIRETORIA</t>
-  </si>
-  <si>
     <t>70234</t>
   </si>
   <si>
@@ -2530,15 +2448,6 @@
     <t>SERGIO LUIZ PACHECO</t>
   </si>
   <si>
-    <t>15018</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>VICE PRESIDENTE GLOBAL</t>
-  </si>
-  <si>
     <t>236385</t>
   </si>
   <si>
@@ -2650,15 +2559,6 @@
     <t>SERVICOS DE MANUTENCAO E EDIFICACOES</t>
   </si>
   <si>
-    <t>13203</t>
-  </si>
-  <si>
-    <t>SAMARA DOS REIS FERREIRA</t>
-  </si>
-  <si>
-    <t>SECRETÁRIA EXECUTIVA</t>
-  </si>
-  <si>
     <t>13199</t>
   </si>
   <si>
@@ -2671,24 +2571,12 @@
     <t>25 - FINANCAS - GERENCIA 1</t>
   </si>
   <si>
-    <t>13205</t>
-  </si>
-  <si>
-    <t>ASSESSOR DA PRESIDENCIA</t>
-  </si>
-  <si>
     <t>13151</t>
   </si>
   <si>
     <t>ALINE BASSO DE AZEVEDO</t>
   </si>
   <si>
-    <t>13213</t>
-  </si>
-  <si>
-    <t>UARLAS BONFIM</t>
-  </si>
-  <si>
     <t>15020</t>
   </si>
   <si>
@@ -2701,27 +2589,9 @@
     <t>25 - PRESIDENCIA</t>
   </si>
   <si>
-    <t>15019</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>13709</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Data e hora do Envio</t>
-  </si>
-  <si>
     <t>Nome do Gestor</t>
   </si>
   <si>
-    <t>Selecionar do Funcionário Avaliado</t>
-  </si>
-  <si>
     <t>Gestor Correto?</t>
   </si>
   <si>
@@ -2734,18 +2604,6 @@
     <t>Departamento Correto?</t>
   </si>
   <si>
-    <t>Selecione o Primeiro Par para Avaliação:</t>
-  </si>
-  <si>
-    <t>Legibilidade Par 1</t>
-  </si>
-  <si>
-    <t>Selecione o Segundo Par para Avaliação:</t>
-  </si>
-  <si>
-    <t>Legibilidade Par 2</t>
-  </si>
-  <si>
     <t>Momento do Envio</t>
   </si>
   <si>
@@ -2774,6 +2632,9 @@
   </si>
   <si>
     <t>E-mail gestor validador</t>
+  </si>
+  <si>
+    <t>status_resposta</t>
   </si>
 </sst>
 </file>
@@ -2783,7 +2644,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2814,33 +2675,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -2874,35 +2708,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Hiperlink" xfId="3" builtinId="8"/>
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2931,44 +2795,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2982,11 +2808,15 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:J306" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:J306" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I306">
-    <sortCondition descending="1" ref="I1:I306"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:J292" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:J292" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I292">
+    <sortCondition descending="1" ref="I1:I292"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador"/>
@@ -2997,7 +2827,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="0"/>
     <tableColumn id="10" xr3:uid="{924CDE42-02DE-4EFB-A383-D6819D596AFA}" name="E-mail gestor validador" dataCellStyle="Hiperlink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3005,9 +2835,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:J2" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
-  <autoFilter ref="A1:J2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:K2" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:K2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{CFF5932B-854B-4B23-A01A-04BA6982E294}" name="Momento do Envio"/>
     <tableColumn id="2" xr3:uid="{9A82702E-3CB5-486A-B49B-3CBF2D1B5744}" name="Nome do Gestor"/>
     <tableColumn id="3" xr3:uid="{15330415-ADF2-4758-8694-FD7A376B81D4}" name="Funcionário Avaliado"/>
@@ -3018,6 +2848,7 @@
     <tableColumn id="8" xr3:uid="{2FF534DC-1CF1-4C48-B7C4-CAF3960253B8}" name="Departamento Correto?"/>
     <tableColumn id="9" xr3:uid="{D960B0AB-147E-49C9-81F6-3A62815C92D5}" name="Par 1"/>
     <tableColumn id="10" xr3:uid="{A24B24E4-1150-4A03-93C9-672C68A1D0C8}" name="Par 2"/>
+    <tableColumn id="11" xr3:uid="{5AFF58B5-A998-4A5A-9F0A-A92C2CDE82B2}" name="status_resposta"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3310,7 +3141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J306"/>
+  <dimension ref="A1:J292"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.88671875" bestFit="1" customWidth="1"/>
@@ -3326,35 +3157,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>912</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3362,7 +3193,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>910</v>
+        <v>863</v>
       </c>
       <c r="C2">
         <v>2701261</v>
@@ -3386,7 +3217,7 @@
         <v>46053</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3418,7 +3249,7 @@
         <v>46053</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -3450,7 +3281,7 @@
         <v>46043</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -3482,7 +3313,7 @@
         <v>46041</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -3514,7 +3345,7 @@
         <v>46027</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -3546,7 +3377,7 @@
         <v>46027</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -3578,7 +3409,7 @@
         <v>46006</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -3610,7 +3441,7 @@
         <v>46006</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -3642,7 +3473,7 @@
         <v>46006</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -3674,7 +3505,7 @@
         <v>46006</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -3706,7 +3537,7 @@
         <v>45992</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -3738,7 +3569,7 @@
         <v>45992</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -3770,7 +3601,7 @@
         <v>45992</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -3802,7 +3633,7 @@
         <v>45992</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -3834,7 +3665,7 @@
         <v>45978</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -3866,7 +3697,7 @@
         <v>45978</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -3898,7 +3729,7 @@
         <v>45978</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -3930,7 +3761,7 @@
         <v>45978</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -3962,7 +3793,7 @@
         <v>45978</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -3994,7 +3825,7 @@
         <v>45978</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -4026,7 +3857,7 @@
         <v>45978</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -4058,7 +3889,7 @@
         <v>45978</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -4090,7 +3921,7 @@
         <v>45978</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -4122,7 +3953,7 @@
         <v>45978</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -4154,7 +3985,7 @@
         <v>45966</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -4186,7 +4017,7 @@
         <v>45964</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -4218,7 +4049,7 @@
         <v>45964</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -4250,7 +4081,7 @@
         <v>45964</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -4282,7 +4113,7 @@
         <v>45964</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -4314,7 +4145,7 @@
         <v>45964</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -4346,7 +4177,7 @@
         <v>45964</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -4378,7 +4209,7 @@
         <v>45950</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -4410,7 +4241,7 @@
         <v>45950</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -4442,7 +4273,7 @@
         <v>45936</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -4474,7 +4305,7 @@
         <v>45936</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -4506,7 +4337,7 @@
         <v>45936</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -4538,7 +4369,7 @@
         <v>45936</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -4570,7 +4401,7 @@
         <v>45936</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -4602,7 +4433,7 @@
         <v>45915</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -4634,7 +4465,7 @@
         <v>45915</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -4666,7 +4497,7 @@
         <v>45915</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -4698,7 +4529,7 @@
         <v>45915</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -4730,7 +4561,7 @@
         <v>45915</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -4762,7 +4593,7 @@
         <v>45915</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -4794,7 +4625,7 @@
         <v>45901</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
@@ -4826,7 +4657,7 @@
         <v>45901</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -4858,7 +4689,7 @@
         <v>45887</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
@@ -4890,7 +4721,7 @@
         <v>45887</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -4922,7 +4753,7 @@
         <v>45887</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -4954,7 +4785,7 @@
         <v>45887</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -4986,7 +4817,7 @@
         <v>45887</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -5018,7 +4849,7 @@
         <v>45873</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -5050,7 +4881,7 @@
         <v>45873</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -5082,7 +4913,7 @@
         <v>45873</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -5114,7 +4945,7 @@
         <v>45873</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -5146,7 +4977,7 @@
         <v>45873</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
@@ -5178,7 +5009,7 @@
         <v>45873</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
@@ -5210,7 +5041,7 @@
         <v>45873</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
@@ -5242,7 +5073,7 @@
         <v>45873</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
@@ -5274,7 +5105,7 @@
         <v>45873</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -5306,7 +5137,7 @@
         <v>45861</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -5338,7 +5169,7 @@
         <v>45852</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
@@ -5370,7 +5201,7 @@
         <v>45852</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
@@ -5402,7 +5233,7 @@
         <v>45845</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
@@ -5434,7 +5265,7 @@
         <v>45845</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
@@ -5466,7 +5297,7 @@
         <v>45839</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
@@ -5498,7 +5329,7 @@
         <v>45824</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
@@ -5530,7 +5361,7 @@
         <v>45824</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
@@ -5562,7 +5393,7 @@
         <v>45824</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
@@ -5594,7 +5425,7 @@
         <v>45824</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
@@ -5626,7 +5457,7 @@
         <v>45817</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
@@ -5658,7 +5489,7 @@
         <v>45810</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
@@ -5690,7 +5521,7 @@
         <v>45810</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
@@ -5722,7 +5553,7 @@
         <v>45810</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
@@ -5754,7 +5585,7 @@
         <v>45810</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
@@ -5786,7 +5617,7 @@
         <v>45810</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
@@ -5818,7 +5649,7 @@
         <v>45796</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
@@ -5850,7 +5681,7 @@
         <v>45789</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
@@ -5882,7 +5713,7 @@
         <v>45789</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
@@ -5914,7 +5745,7 @@
         <v>45789</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
@@ -5946,7 +5777,7 @@
         <v>45789</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
@@ -5978,7 +5809,7 @@
         <v>45782</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
@@ -6010,7 +5841,7 @@
         <v>45782</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
@@ -6042,7 +5873,7 @@
         <v>45782</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
@@ -6074,7 +5905,7 @@
         <v>45782</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
@@ -6106,7 +5937,7 @@
         <v>45782</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
@@ -6138,7 +5969,7 @@
         <v>45761</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
@@ -6170,7 +6001,7 @@
         <v>45761</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
@@ -6202,7 +6033,7 @@
         <v>45761</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
@@ -6234,7 +6065,7 @@
         <v>45761</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
@@ -6266,7 +6097,7 @@
         <v>45761</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
@@ -6298,7 +6129,7 @@
         <v>45761</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
@@ -6330,7 +6161,7 @@
         <v>45761</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
@@ -6362,7 +6193,7 @@
         <v>45761</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
@@ -6394,7 +6225,7 @@
         <v>45761</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
@@ -6426,7 +6257,7 @@
         <v>45761</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
@@ -6458,7 +6289,7 @@
         <v>45761</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
@@ -6490,7 +6321,7 @@
         <v>45758</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
@@ -6522,7 +6353,7 @@
         <v>45757</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
@@ -6554,7 +6385,7 @@
         <v>45754</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
@@ -6586,7 +6417,7 @@
         <v>45733</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
@@ -6618,7 +6449,7 @@
         <v>45722</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
@@ -6650,7 +6481,7 @@
         <v>45722</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
@@ -6682,7 +6513,7 @@
         <v>45722</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
@@ -6714,7 +6545,7 @@
         <v>45722</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
@@ -6746,7 +6577,7 @@
         <v>45722</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
@@ -6778,7 +6609,7 @@
         <v>45722</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
@@ -6810,7 +6641,7 @@
         <v>45722</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
@@ -6842,7 +6673,7 @@
         <v>45722</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
@@ -6874,7 +6705,7 @@
         <v>45721</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
@@ -6906,7 +6737,7 @@
         <v>45705</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
@@ -6938,7 +6769,7 @@
         <v>45705</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
@@ -6970,7 +6801,7 @@
         <v>45705</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
@@ -7002,7 +6833,7 @@
         <v>45705</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
@@ -7034,7 +6865,7 @@
         <v>45705</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
@@ -7066,7 +6897,7 @@
         <v>45705</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
@@ -7098,7 +6929,7 @@
         <v>45705</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
@@ -7130,7 +6961,7 @@
         <v>45705</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
@@ -7162,7 +6993,7 @@
         <v>45691</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
@@ -7194,7 +7025,7 @@
         <v>45691</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
@@ -7226,7 +7057,7 @@
         <v>45691</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
@@ -7258,7 +7089,7 @@
         <v>45691</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
@@ -7290,7 +7121,7 @@
         <v>45691</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
@@ -7322,7 +7153,7 @@
         <v>45691</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
@@ -7354,7 +7185,7 @@
         <v>45690</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
@@ -7386,7 +7217,7 @@
         <v>45684</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
@@ -7418,7 +7249,7 @@
         <v>45684</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
@@ -7450,7 +7281,7 @@
         <v>45680</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
@@ -7482,7 +7313,7 @@
         <v>45677</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
@@ -7514,7 +7345,7 @@
         <v>45677</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
@@ -7546,7 +7377,7 @@
         <v>45663</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
@@ -7578,7 +7409,7 @@
         <v>45659</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
@@ -7610,7 +7441,7 @@
         <v>45642</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
@@ -7642,7 +7473,7 @@
         <v>45628</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
@@ -7674,7 +7505,7 @@
         <v>45628</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
@@ -7706,7 +7537,7 @@
         <v>45628</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
@@ -7738,7 +7569,7 @@
         <v>45628</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
@@ -7770,7 +7601,7 @@
         <v>45614</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
@@ -7802,7 +7633,7 @@
         <v>45614</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
@@ -7834,7 +7665,7 @@
         <v>45600</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
@@ -7866,7 +7697,7 @@
         <v>45600</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
@@ -7898,7 +7729,7 @@
         <v>45600</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
@@ -7930,7 +7761,7 @@
         <v>45600</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
@@ -7962,7 +7793,7 @@
         <v>45600</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
@@ -7994,7 +7825,7 @@
         <v>45586</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
@@ -8026,7 +7857,7 @@
         <v>45580</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
@@ -8058,7 +7889,7 @@
         <v>45566</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
@@ -8090,7 +7921,7 @@
         <v>45566</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
@@ -8122,7 +7953,7 @@
         <v>45566</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
@@ -8154,7 +7985,7 @@
         <v>45566</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
@@ -8186,7 +8017,7 @@
         <v>45564</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
@@ -8218,7 +8049,7 @@
         <v>45551</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
@@ -8250,7 +8081,7 @@
         <v>45551</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
@@ -8282,7 +8113,7 @@
         <v>45545</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
@@ -8314,7 +8145,7 @@
         <v>45537</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
@@ -8346,7 +8177,7 @@
         <v>45520</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
@@ -8378,7 +8209,7 @@
         <v>45520</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
@@ -8410,7 +8241,7 @@
         <v>45520</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
@@ -8442,7 +8273,7 @@
         <v>45516</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
@@ -8474,7 +8305,7 @@
         <v>45505</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
@@ -8506,7 +8337,7 @@
         <v>45505</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
@@ -8538,7 +8369,7 @@
         <v>45488</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
@@ -8570,7 +8401,7 @@
         <v>45481</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
@@ -8602,7 +8433,7 @@
         <v>45474</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
@@ -8634,7 +8465,7 @@
         <v>45474</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
@@ -8666,7 +8497,7 @@
         <v>45460</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
@@ -8698,7 +8529,7 @@
         <v>45460</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
@@ -8730,7 +8561,7 @@
         <v>45460</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
@@ -8762,7 +8593,7 @@
         <v>45453</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
@@ -8794,7 +8625,7 @@
         <v>45446</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
@@ -8826,7 +8657,7 @@
         <v>45446</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
@@ -8858,7 +8689,7 @@
         <v>45446</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
@@ -8890,7 +8721,7 @@
         <v>45446</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
@@ -8922,7 +8753,7 @@
         <v>45439</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
@@ -8954,7 +8785,7 @@
         <v>45414</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
@@ -8986,7 +8817,7 @@
         <v>45390</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
@@ -9018,7 +8849,7 @@
         <v>45386</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
@@ -9050,7 +8881,7 @@
         <v>45383</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
@@ -9082,7 +8913,7 @@
         <v>45366</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
@@ -9114,7 +8945,7 @@
         <v>45357</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
@@ -9146,7 +8977,7 @@
         <v>45357</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
@@ -9178,7 +9009,7 @@
         <v>45355</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
@@ -9210,7 +9041,7 @@
         <v>45337</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
@@ -9242,7 +9073,7 @@
         <v>45323</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
@@ -9274,7 +9105,7 @@
         <v>45323</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
@@ -9306,7 +9137,7 @@
         <v>45313</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
@@ -9338,7 +9169,7 @@
         <v>45306</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
@@ -9370,7 +9201,7 @@
         <v>45306</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
@@ -9402,7 +9233,7 @@
         <v>45275</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
@@ -9434,7 +9265,7 @@
         <v>45275</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
@@ -9466,7 +9297,7 @@
         <v>45275</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
@@ -9498,7 +9329,7 @@
         <v>45275</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
@@ -9530,7 +9361,7 @@
         <v>45244</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
@@ -9562,7 +9393,7 @@
         <v>45233</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
@@ -9594,7 +9425,7 @@
         <v>45219</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
@@ -9626,7 +9457,7 @@
         <v>45215</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
@@ -9658,7 +9489,7 @@
         <v>45201</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
@@ -9690,7 +9521,7 @@
         <v>45194</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
@@ -9722,7 +9553,7 @@
         <v>45170</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
@@ -9754,7 +9585,7 @@
         <v>45170</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
@@ -9786,7 +9617,7 @@
         <v>45170</v>
       </c>
       <c r="J202" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
@@ -9818,7 +9649,7 @@
         <v>45154</v>
       </c>
       <c r="J203" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
@@ -9850,7 +9681,7 @@
         <v>45154</v>
       </c>
       <c r="J204" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
@@ -9882,7 +9713,7 @@
         <v>45152</v>
       </c>
       <c r="J205" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
@@ -9914,7 +9745,7 @@
         <v>45117</v>
       </c>
       <c r="J206" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
@@ -9946,7 +9777,7 @@
         <v>45110</v>
       </c>
       <c r="J207" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
@@ -9978,7 +9809,7 @@
         <v>45098</v>
       </c>
       <c r="J208" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
@@ -10010,7 +9841,7 @@
         <v>45089</v>
       </c>
       <c r="J209" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
@@ -10042,7 +9873,7 @@
         <v>45082</v>
       </c>
       <c r="J210" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
@@ -10074,7 +9905,7 @@
         <v>45082</v>
       </c>
       <c r="J211" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
@@ -10106,7 +9937,7 @@
         <v>45068</v>
       </c>
       <c r="J212" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
@@ -10138,7 +9969,7 @@
         <v>45063</v>
       </c>
       <c r="J213" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
@@ -10170,7 +10001,7 @@
         <v>45061</v>
       </c>
       <c r="J214" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
@@ -10202,7 +10033,7 @@
         <v>45041</v>
       </c>
       <c r="J215" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
@@ -10234,504 +10065,504 @@
         <v>45041</v>
       </c>
       <c r="J216" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>652</v>
+        <v>145</v>
       </c>
       <c r="B217" t="s">
-        <v>652</v>
+        <v>145</v>
       </c>
       <c r="C217" t="s">
         <v>653</v>
       </c>
       <c r="D217">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E217" t="s">
-        <v>654</v>
+        <v>144</v>
       </c>
       <c r="F217" t="s">
-        <v>655</v>
+        <v>457</v>
       </c>
       <c r="G217" t="s">
         <v>15</v>
       </c>
       <c r="H217" t="s">
-        <v>656</v>
+        <v>571</v>
       </c>
       <c r="I217" s="2">
-        <v>45022</v>
+        <v>45019</v>
       </c>
       <c r="J217" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="B218" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="C218" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D218">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="E218" t="s">
-        <v>144</v>
+        <v>655</v>
       </c>
       <c r="F218" t="s">
-        <v>457</v>
+        <v>57</v>
       </c>
       <c r="G218" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="H218" t="s">
-        <v>571</v>
+        <v>58</v>
       </c>
       <c r="I218" s="2">
-        <v>45019</v>
+        <v>44979</v>
       </c>
       <c r="J218" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>52</v>
+        <v>283</v>
       </c>
       <c r="B219" t="s">
-        <v>53</v>
+        <v>283</v>
       </c>
       <c r="C219" t="s">
+        <v>656</v>
+      </c>
+      <c r="D219">
+        <v>578</v>
+      </c>
+      <c r="E219" t="s">
+        <v>657</v>
+      </c>
+      <c r="F219" t="s">
         <v>658</v>
       </c>
-      <c r="D219">
-        <v>589</v>
-      </c>
-      <c r="E219" t="s">
-        <v>659</v>
-      </c>
-      <c r="F219" t="s">
-        <v>57</v>
-      </c>
       <c r="G219" t="s">
-        <v>346</v>
+        <v>15</v>
       </c>
       <c r="H219" t="s">
-        <v>58</v>
+        <v>317</v>
       </c>
       <c r="I219" s="2">
-        <v>44979</v>
+        <v>44958</v>
       </c>
       <c r="J219" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>283</v>
+        <v>48</v>
       </c>
       <c r="B220" t="s">
-        <v>283</v>
+        <v>30</v>
       </c>
       <c r="C220" t="s">
+        <v>659</v>
+      </c>
+      <c r="D220">
+        <v>674</v>
+      </c>
+      <c r="E220" t="s">
         <v>660</v>
       </c>
-      <c r="D220">
-        <v>578</v>
-      </c>
-      <c r="E220" t="s">
-        <v>661</v>
-      </c>
       <c r="F220" t="s">
-        <v>662</v>
+        <v>51</v>
       </c>
       <c r="G220" t="s">
         <v>15</v>
       </c>
       <c r="H220" t="s">
-        <v>317</v>
+        <v>47</v>
       </c>
       <c r="I220" s="2">
         <v>44958</v>
       </c>
       <c r="J220" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>48</v>
+        <v>206</v>
       </c>
       <c r="B221" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="C221" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D221">
-        <v>674</v>
+        <v>579</v>
       </c>
       <c r="E221" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F221" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="G221" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H221" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="I221" s="2">
         <v>44958</v>
       </c>
       <c r="J221" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>206</v>
+        <v>35</v>
       </c>
       <c r="B222" t="s">
-        <v>206</v>
+        <v>35</v>
       </c>
       <c r="C222" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D222">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="E222" t="s">
-        <v>666</v>
+        <v>44</v>
       </c>
       <c r="F222" t="s">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="G222" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H222" t="s">
-        <v>104</v>
+        <v>664</v>
       </c>
       <c r="I222" s="2">
-        <v>44958</v>
+        <v>44951</v>
       </c>
       <c r="J222" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="B223" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C223" t="s">
+        <v>665</v>
+      </c>
+      <c r="D223">
+        <v>572</v>
+      </c>
+      <c r="E223" t="s">
+        <v>666</v>
+      </c>
+      <c r="F223" t="s">
         <v>667</v>
       </c>
-      <c r="D223">
-        <v>575</v>
-      </c>
-      <c r="E223" t="s">
-        <v>44</v>
-      </c>
-      <c r="F223" t="s">
-        <v>371</v>
-      </c>
       <c r="G223" t="s">
         <v>15</v>
       </c>
       <c r="H223" t="s">
-        <v>668</v>
+        <v>73</v>
       </c>
       <c r="I223" s="2">
-        <v>44951</v>
+        <v>44949</v>
       </c>
       <c r="J223" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>69</v>
+        <v>197</v>
       </c>
       <c r="B224" t="s">
-        <v>24</v>
+        <v>197</v>
       </c>
       <c r="C224" t="s">
+        <v>668</v>
+      </c>
+      <c r="D224">
+        <v>553</v>
+      </c>
+      <c r="E224" t="s">
         <v>669</v>
       </c>
-      <c r="D224">
-        <v>572</v>
-      </c>
-      <c r="E224" t="s">
-        <v>670</v>
-      </c>
       <c r="F224" t="s">
-        <v>671</v>
+        <v>82</v>
       </c>
       <c r="G224" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H224" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="I224" s="2">
-        <v>44949</v>
+        <v>44921</v>
       </c>
       <c r="J224" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>197</v>
+        <v>383</v>
       </c>
       <c r="B225" t="s">
-        <v>197</v>
+        <v>383</v>
       </c>
       <c r="C225" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D225">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E225" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F225" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="G225" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H225" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="I225" s="2">
         <v>44921</v>
       </c>
       <c r="J225" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>383</v>
+        <v>44</v>
       </c>
       <c r="B226" t="s">
-        <v>383</v>
+        <v>35</v>
       </c>
       <c r="C226" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D226">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E226" t="s">
-        <v>675</v>
+        <v>193</v>
       </c>
       <c r="F226" t="s">
-        <v>14</v>
+        <v>673</v>
       </c>
       <c r="G226" t="s">
         <v>15</v>
       </c>
       <c r="H226" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="I226" s="2">
-        <v>44921</v>
+        <v>44909</v>
       </c>
       <c r="J226" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="B227" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="C227" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D227">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>193</v>
+        <v>675</v>
       </c>
       <c r="F227" t="s">
-        <v>677</v>
+        <v>328</v>
       </c>
       <c r="G227" t="s">
         <v>15</v>
       </c>
       <c r="H227" t="s">
-        <v>508</v>
+        <v>93</v>
       </c>
       <c r="I227" s="2">
         <v>44909</v>
       </c>
       <c r="J227" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="B228" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="C228" t="s">
+        <v>676</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="E228" t="s">
         <v>678</v>
       </c>
-      <c r="D228">
-        <v>547</v>
-      </c>
-      <c r="E228" t="s">
-        <v>679</v>
-      </c>
       <c r="F228" t="s">
-        <v>328</v>
+        <v>648</v>
       </c>
       <c r="G228" t="s">
         <v>15</v>
       </c>
       <c r="H228" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="I228" s="2">
-        <v>44909</v>
+        <v>44907</v>
       </c>
       <c r="J228" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
+        <v>48</v>
+      </c>
+      <c r="B229" t="s">
+        <v>30</v>
+      </c>
+      <c r="C229" t="s">
+        <v>679</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="E229" t="s">
         <v>178</v>
       </c>
-      <c r="B229" t="s">
-        <v>178</v>
-      </c>
-      <c r="C229" t="s">
-        <v>680</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="E229" t="s">
-        <v>682</v>
-      </c>
       <c r="F229" t="s">
-        <v>648</v>
+        <v>371</v>
       </c>
       <c r="G229" t="s">
         <v>15</v>
       </c>
       <c r="H229" t="s">
-        <v>47</v>
+        <v>641</v>
       </c>
       <c r="I229" s="2">
-        <v>44907</v>
+        <v>44902</v>
       </c>
       <c r="J229" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>48</v>
+        <v>383</v>
       </c>
       <c r="B230" t="s">
-        <v>30</v>
+        <v>383</v>
       </c>
       <c r="C230" t="s">
-        <v>683</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>684</v>
+        <v>681</v>
+      </c>
+      <c r="D230">
+        <v>545</v>
       </c>
       <c r="E230" t="s">
-        <v>178</v>
+        <v>682</v>
       </c>
       <c r="F230" t="s">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="G230" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H230" t="s">
-        <v>641</v>
+        <v>16</v>
       </c>
       <c r="I230" s="2">
-        <v>44902</v>
+        <v>44900</v>
       </c>
       <c r="J230" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>383</v>
+        <v>48</v>
       </c>
       <c r="B231" t="s">
-        <v>383</v>
+        <v>30</v>
       </c>
       <c r="C231" t="s">
-        <v>685</v>
-      </c>
-      <c r="D231">
-        <v>545</v>
+        <v>683</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>684</v>
       </c>
       <c r="E231" t="s">
-        <v>686</v>
+        <v>96</v>
       </c>
       <c r="F231" t="s">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="G231" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H231" t="s">
-        <v>16</v>
+        <v>641</v>
       </c>
       <c r="I231" s="2">
         <v>44900</v>
       </c>
       <c r="J231" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>48</v>
+        <v>178</v>
       </c>
       <c r="B232" t="s">
-        <v>30</v>
+        <v>178</v>
       </c>
       <c r="C232" t="s">
+        <v>685</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="E232" t="s">
         <v>687</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="E232" t="s">
-        <v>96</v>
       </c>
       <c r="F232" t="s">
         <v>648</v>
@@ -10740,318 +10571,318 @@
         <v>15</v>
       </c>
       <c r="H232" t="s">
-        <v>641</v>
+        <v>47</v>
       </c>
       <c r="I232" s="2">
-        <v>44900</v>
+        <v>44894</v>
       </c>
       <c r="J232" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B233" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="C233" t="s">
+        <v>688</v>
+      </c>
+      <c r="D233">
+        <v>539</v>
+      </c>
+      <c r="E233" t="s">
         <v>689</v>
       </c>
-      <c r="D233" s="3" t="s">
+      <c r="F233" t="s">
         <v>690</v>
       </c>
-      <c r="E233" t="s">
-        <v>691</v>
-      </c>
-      <c r="F233" t="s">
-        <v>648</v>
-      </c>
       <c r="G233" t="s">
         <v>15</v>
       </c>
       <c r="H233" t="s">
-        <v>47</v>
+        <v>458</v>
       </c>
       <c r="I233" s="2">
-        <v>44894</v>
+        <v>44874</v>
       </c>
       <c r="J233" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="B234" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C234" t="s">
+        <v>691</v>
+      </c>
+      <c r="D234">
+        <v>538</v>
+      </c>
+      <c r="E234" t="s">
         <v>692</v>
       </c>
-      <c r="D234">
-        <v>539</v>
-      </c>
-      <c r="E234" t="s">
-        <v>693</v>
-      </c>
       <c r="F234" t="s">
-        <v>694</v>
+        <v>446</v>
       </c>
       <c r="G234" t="s">
         <v>15</v>
       </c>
       <c r="H234" t="s">
-        <v>458</v>
+        <v>47</v>
       </c>
       <c r="I234" s="2">
         <v>44874</v>
       </c>
       <c r="J234" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>44</v>
+        <v>472</v>
       </c>
       <c r="B235" t="s">
-        <v>35</v>
+        <v>330</v>
       </c>
       <c r="C235" t="s">
+        <v>693</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="E235" t="s">
+        <v>48</v>
+      </c>
+      <c r="F235" t="s">
         <v>695</v>
       </c>
-      <c r="D235">
-        <v>538</v>
-      </c>
-      <c r="E235" t="s">
+      <c r="G235" t="s">
+        <v>15</v>
+      </c>
+      <c r="H235" t="s">
         <v>696</v>
       </c>
-      <c r="F235" t="s">
-        <v>446</v>
-      </c>
-      <c r="G235" t="s">
-        <v>15</v>
-      </c>
-      <c r="H235" t="s">
-        <v>47</v>
-      </c>
       <c r="I235" s="2">
-        <v>44874</v>
+        <v>44866</v>
       </c>
       <c r="J235" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>472</v>
+        <v>578</v>
       </c>
       <c r="B236" t="s">
-        <v>330</v>
+        <v>35</v>
       </c>
       <c r="C236" t="s">
         <v>697</v>
       </c>
-      <c r="D236" s="3" t="s">
+      <c r="D236">
+        <v>533</v>
+      </c>
+      <c r="E236" t="s">
         <v>698</v>
       </c>
-      <c r="E236" t="s">
-        <v>48</v>
-      </c>
       <c r="F236" t="s">
+        <v>61</v>
+      </c>
+      <c r="G236" t="s">
+        <v>15</v>
+      </c>
+      <c r="H236" t="s">
         <v>699</v>
       </c>
-      <c r="G236" t="s">
-        <v>15</v>
-      </c>
-      <c r="H236" t="s">
-        <v>700</v>
-      </c>
       <c r="I236" s="2">
-        <v>44866</v>
+        <v>44851</v>
       </c>
       <c r="J236" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>578</v>
+        <v>700</v>
       </c>
       <c r="B237" t="s">
-        <v>35</v>
+        <v>700</v>
       </c>
       <c r="C237" t="s">
         <v>701</v>
       </c>
-      <c r="D237">
-        <v>533</v>
+      <c r="D237" s="3" t="s">
+        <v>702</v>
       </c>
       <c r="E237" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F237" t="s">
-        <v>61</v>
+        <v>704</v>
       </c>
       <c r="G237" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H237" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I237" s="2">
-        <v>44851</v>
+        <v>44840</v>
       </c>
       <c r="J237" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>704</v>
+        <v>206</v>
       </c>
       <c r="B238" t="s">
-        <v>704</v>
+        <v>206</v>
       </c>
       <c r="C238" t="s">
-        <v>705</v>
-      </c>
-      <c r="D238" s="3" t="s">
         <v>706</v>
+      </c>
+      <c r="D238">
+        <v>528</v>
       </c>
       <c r="E238" t="s">
         <v>707</v>
       </c>
       <c r="F238" t="s">
-        <v>708</v>
+        <v>82</v>
       </c>
       <c r="G238" t="s">
         <v>176</v>
       </c>
       <c r="H238" t="s">
-        <v>709</v>
+        <v>104</v>
       </c>
       <c r="I238" s="2">
-        <v>44840</v>
+        <v>44830</v>
       </c>
       <c r="J238" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>206</v>
+        <v>472</v>
       </c>
       <c r="B239" t="s">
-        <v>206</v>
+        <v>330</v>
       </c>
       <c r="C239" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D239">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E239" t="s">
-        <v>711</v>
+        <v>35</v>
       </c>
       <c r="F239" t="s">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="G239" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H239" t="s">
-        <v>104</v>
+        <v>709</v>
       </c>
       <c r="I239" s="2">
-        <v>44830</v>
+        <v>44823</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>472</v>
+        <v>358</v>
       </c>
       <c r="B240" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="C240" t="s">
+        <v>710</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="E240" t="s">
         <v>712</v>
       </c>
-      <c r="D240">
-        <v>523</v>
-      </c>
-      <c r="E240" t="s">
-        <v>35</v>
-      </c>
       <c r="F240" t="s">
-        <v>474</v>
+        <v>713</v>
       </c>
       <c r="G240" t="s">
-        <v>15</v>
+        <v>363</v>
       </c>
       <c r="H240" t="s">
-        <v>713</v>
+        <v>364</v>
       </c>
       <c r="I240" s="2">
-        <v>44823</v>
+        <v>44774</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>358</v>
+        <v>197</v>
       </c>
       <c r="B241" t="s">
-        <v>358</v>
+        <v>197</v>
       </c>
       <c r="C241" t="s">
         <v>714</v>
       </c>
-      <c r="D241" s="3" t="s">
+      <c r="D241">
+        <v>919</v>
+      </c>
+      <c r="E241" t="s">
         <v>715</v>
       </c>
-      <c r="E241" t="s">
-        <v>716</v>
-      </c>
       <c r="F241" t="s">
-        <v>717</v>
+        <v>82</v>
       </c>
       <c r="G241" t="s">
-        <v>363</v>
+        <v>15</v>
       </c>
       <c r="H241" t="s">
-        <v>364</v>
+        <v>200</v>
       </c>
       <c r="I241" s="2">
-        <v>44774</v>
+        <v>44746</v>
       </c>
       <c r="J241" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="B242" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="C242" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D242">
-        <v>919</v>
+        <v>495</v>
       </c>
       <c r="E242" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F242" t="s">
         <v>82</v>
@@ -11060,109 +10891,109 @@
         <v>15</v>
       </c>
       <c r="H242" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="I242" s="2">
-        <v>44746</v>
+        <v>44720</v>
       </c>
       <c r="J242" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>79</v>
+        <v>689</v>
       </c>
       <c r="B243" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="C243" t="s">
+        <v>718</v>
+      </c>
+      <c r="D243">
+        <v>493</v>
+      </c>
+      <c r="E243" t="s">
+        <v>719</v>
+      </c>
+      <c r="F243" t="s">
         <v>720</v>
       </c>
-      <c r="D243">
-        <v>495</v>
-      </c>
-      <c r="E243" t="s">
+      <c r="G243" t="s">
+        <v>15</v>
+      </c>
+      <c r="H243" t="s">
         <v>721</v>
       </c>
-      <c r="F243" t="s">
-        <v>82</v>
-      </c>
-      <c r="G243" t="s">
-        <v>15</v>
-      </c>
-      <c r="H243" t="s">
-        <v>83</v>
-      </c>
       <c r="I243" s="2">
-        <v>44720</v>
+        <v>44718</v>
       </c>
       <c r="J243" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>693</v>
+        <v>17</v>
       </c>
       <c r="B244" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="C244" t="s">
         <v>722</v>
       </c>
-      <c r="D244">
-        <v>493</v>
+      <c r="D244" s="3" t="s">
+        <v>723</v>
       </c>
       <c r="E244" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F244" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G244" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H244" t="s">
-        <v>725</v>
+        <v>22</v>
       </c>
       <c r="I244" s="2">
-        <v>44718</v>
+        <v>44714</v>
       </c>
       <c r="J244" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="B245" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="C245" t="s">
         <v>726</v>
       </c>
-      <c r="D245" s="3" t="s">
+      <c r="D245">
+        <v>491</v>
+      </c>
+      <c r="E245" t="s">
         <v>727</v>
       </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>728</v>
       </c>
-      <c r="F245" t="s">
-        <v>729</v>
-      </c>
       <c r="G245" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H245" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="I245" s="2">
-        <v>44714</v>
+        <v>44713</v>
       </c>
       <c r="J245" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
@@ -11173,16 +11004,16 @@
         <v>89</v>
       </c>
       <c r="C246" t="s">
+        <v>729</v>
+      </c>
+      <c r="D246">
+        <v>489</v>
+      </c>
+      <c r="E246" t="s">
         <v>730</v>
       </c>
-      <c r="D246">
-        <v>491</v>
-      </c>
-      <c r="E246" t="s">
-        <v>731</v>
-      </c>
       <c r="F246" t="s">
-        <v>732</v>
+        <v>328</v>
       </c>
       <c r="G246" t="s">
         <v>15</v>
@@ -11191,1930 +11022,1482 @@
         <v>93</v>
       </c>
       <c r="I246" s="2">
-        <v>44713</v>
+        <v>44692</v>
       </c>
       <c r="J246" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="B247" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="C247" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D247">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E247" t="s">
-        <v>734</v>
+        <v>62</v>
       </c>
       <c r="F247" t="s">
-        <v>328</v>
+        <v>260</v>
       </c>
       <c r="G247" t="s">
         <v>15</v>
       </c>
       <c r="H247" t="s">
-        <v>93</v>
+        <v>261</v>
       </c>
       <c r="I247" s="2">
-        <v>44692</v>
+        <v>44690</v>
       </c>
       <c r="J247" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B248" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C248" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D248">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E248" t="s">
-        <v>62</v>
+        <v>733</v>
       </c>
       <c r="F248" t="s">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="G248" t="s">
         <v>15</v>
       </c>
       <c r="H248" t="s">
-        <v>261</v>
+        <v>58</v>
       </c>
       <c r="I248" s="2">
-        <v>44690</v>
+        <v>44671</v>
       </c>
       <c r="J248" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>52</v>
+        <v>302</v>
       </c>
       <c r="B249" t="s">
-        <v>53</v>
+        <v>302</v>
       </c>
       <c r="C249" t="s">
+        <v>734</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="E249" t="s">
         <v>736</v>
       </c>
-      <c r="D249">
-        <v>483</v>
-      </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>737</v>
       </c>
-      <c r="F249" t="s">
-        <v>20</v>
-      </c>
       <c r="G249" t="s">
         <v>15</v>
       </c>
       <c r="H249" t="s">
-        <v>58</v>
+        <v>501</v>
       </c>
       <c r="I249" s="2">
-        <v>44671</v>
+        <v>44652</v>
       </c>
       <c r="J249" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>302</v>
+        <v>383</v>
       </c>
       <c r="B250" t="s">
-        <v>302</v>
+        <v>383</v>
       </c>
       <c r="C250" t="s">
         <v>738</v>
       </c>
-      <c r="D250" s="3" t="s">
+      <c r="D250">
+        <v>474</v>
+      </c>
+      <c r="E250" t="s">
         <v>739</v>
       </c>
-      <c r="E250" t="s">
-        <v>740</v>
-      </c>
       <c r="F250" t="s">
-        <v>741</v>
+        <v>82</v>
       </c>
       <c r="G250" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H250" t="s">
-        <v>501</v>
+        <v>16</v>
       </c>
       <c r="I250" s="2">
-        <v>44652</v>
+        <v>44641</v>
       </c>
       <c r="J250" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>383</v>
+        <v>144</v>
       </c>
       <c r="B251" t="s">
-        <v>383</v>
+        <v>145</v>
       </c>
       <c r="C251" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D251">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E251" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="F251" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="G251" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H251" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="I251" s="2">
-        <v>44641</v>
+        <v>44630</v>
       </c>
       <c r="J251" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>652</v>
+        <v>89</v>
       </c>
       <c r="B252" t="s">
-        <v>652</v>
+        <v>89</v>
       </c>
       <c r="C252" t="s">
-        <v>744</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>745</v>
+        <v>742</v>
+      </c>
+      <c r="D252">
+        <v>451</v>
       </c>
       <c r="E252" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="F252" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="G252" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="H252" t="s">
-        <v>747</v>
+        <v>121</v>
       </c>
       <c r="I252" s="2">
-        <v>44636</v>
+        <v>44573</v>
       </c>
       <c r="J252" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="B253" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="C253" t="s">
-        <v>748</v>
-      </c>
-      <c r="D253">
-        <v>469</v>
+        <v>744</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>745</v>
       </c>
       <c r="E253" t="s">
-        <v>749</v>
+        <v>29</v>
       </c>
       <c r="F253" t="s">
-        <v>43</v>
+        <v>371</v>
       </c>
       <c r="G253" t="s">
         <v>15</v>
       </c>
       <c r="H253" t="s">
-        <v>148</v>
+        <v>641</v>
       </c>
       <c r="I253" s="2">
-        <v>44630</v>
+        <v>44562</v>
       </c>
       <c r="J253" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B254" t="s">
         <v>89</v>
       </c>
       <c r="C254" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="D254">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E254" t="s">
-        <v>88</v>
+        <v>747</v>
       </c>
       <c r="F254" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="G254" t="s">
         <v>15</v>
       </c>
       <c r="H254" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="I254" s="2">
-        <v>44573</v>
+        <v>44550</v>
       </c>
       <c r="J254" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="B255" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="C255" t="s">
-        <v>752</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
+      </c>
+      <c r="D255">
+        <v>441</v>
       </c>
       <c r="E255" t="s">
-        <v>29</v>
+        <v>750</v>
       </c>
       <c r="F255" t="s">
-        <v>371</v>
+        <v>751</v>
       </c>
       <c r="G255" t="s">
         <v>15</v>
       </c>
       <c r="H255" t="s">
-        <v>641</v>
+        <v>252</v>
       </c>
       <c r="I255" s="2">
-        <v>44562</v>
+        <v>44546</v>
       </c>
       <c r="J255" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="B256" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="C256" t="s">
+        <v>752</v>
+      </c>
+      <c r="D256">
+        <v>439</v>
+      </c>
+      <c r="E256" t="s">
+        <v>753</v>
+      </c>
+      <c r="F256" t="s">
         <v>754</v>
       </c>
-      <c r="D256">
-        <v>447</v>
-      </c>
-      <c r="E256" t="s">
-        <v>755</v>
-      </c>
-      <c r="F256" t="s">
-        <v>756</v>
-      </c>
       <c r="G256" t="s">
         <v>15</v>
       </c>
       <c r="H256" t="s">
-        <v>93</v>
+        <v>252</v>
       </c>
       <c r="I256" s="2">
-        <v>44550</v>
+        <v>44543</v>
       </c>
       <c r="J256" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="B257" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="C257" t="s">
+        <v>755</v>
+      </c>
+      <c r="D257">
+        <v>434</v>
+      </c>
+      <c r="E257" t="s">
+        <v>756</v>
+      </c>
+      <c r="F257" t="s">
         <v>757</v>
       </c>
-      <c r="D257">
-        <v>441</v>
-      </c>
-      <c r="E257" t="s">
-        <v>758</v>
-      </c>
-      <c r="F257" t="s">
-        <v>759</v>
-      </c>
       <c r="G257" t="s">
         <v>15</v>
       </c>
       <c r="H257" t="s">
-        <v>252</v>
+        <v>186</v>
       </c>
       <c r="I257" s="2">
-        <v>44546</v>
+        <v>44531</v>
       </c>
       <c r="J257" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>131</v>
+        <v>506</v>
       </c>
       <c r="B258" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C258" t="s">
+        <v>758</v>
+      </c>
+      <c r="D258">
+        <v>433</v>
+      </c>
+      <c r="E258" t="s">
+        <v>759</v>
+      </c>
+      <c r="F258" t="s">
+        <v>61</v>
+      </c>
+      <c r="G258" t="s">
+        <v>15</v>
+      </c>
+      <c r="H258" t="s">
         <v>760</v>
       </c>
-      <c r="D258">
-        <v>439</v>
-      </c>
-      <c r="E258" t="s">
-        <v>761</v>
-      </c>
-      <c r="F258" t="s">
-        <v>762</v>
-      </c>
-      <c r="G258" t="s">
-        <v>15</v>
-      </c>
-      <c r="H258" t="s">
-        <v>252</v>
-      </c>
       <c r="I258" s="2">
-        <v>44543</v>
+        <v>44522</v>
       </c>
       <c r="J258" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>182</v>
+        <v>283</v>
       </c>
       <c r="B259" t="s">
-        <v>24</v>
+        <v>283</v>
       </c>
       <c r="C259" t="s">
+        <v>761</v>
+      </c>
+      <c r="D259">
+        <v>431</v>
+      </c>
+      <c r="E259" t="s">
+        <v>762</v>
+      </c>
+      <c r="F259" t="s">
         <v>763</v>
       </c>
-      <c r="D259">
-        <v>434</v>
-      </c>
-      <c r="E259" t="s">
+      <c r="G259" t="s">
+        <v>15</v>
+      </c>
+      <c r="H259" t="s">
         <v>764</v>
       </c>
-      <c r="F259" t="s">
-        <v>765</v>
-      </c>
-      <c r="G259" t="s">
-        <v>15</v>
-      </c>
-      <c r="H259" t="s">
-        <v>186</v>
-      </c>
       <c r="I259" s="2">
-        <v>44531</v>
+        <v>44522</v>
       </c>
       <c r="J259" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>506</v>
+        <v>101</v>
       </c>
       <c r="B260" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="C260" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D260">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E260" t="s">
-        <v>767</v>
+        <v>206</v>
       </c>
       <c r="F260" t="s">
-        <v>61</v>
+        <v>413</v>
       </c>
       <c r="G260" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H260" t="s">
-        <v>768</v>
+        <v>104</v>
       </c>
       <c r="I260" s="2">
-        <v>44522</v>
+        <v>44501</v>
       </c>
       <c r="J260" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>283</v>
+        <v>17</v>
       </c>
       <c r="B261" t="s">
-        <v>283</v>
+        <v>17</v>
       </c>
       <c r="C261" t="s">
-        <v>769</v>
-      </c>
-      <c r="D261">
-        <v>431</v>
+        <v>766</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>767</v>
       </c>
       <c r="E261" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="F261" t="s">
-        <v>771</v>
+        <v>436</v>
       </c>
       <c r="G261" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H261" t="s">
-        <v>772</v>
+        <v>22</v>
       </c>
       <c r="I261" s="2">
-        <v>44522</v>
+        <v>44494</v>
       </c>
       <c r="J261" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="B262" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="C262" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="D262">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E262" t="s">
-        <v>206</v>
+        <v>770</v>
       </c>
       <c r="F262" t="s">
-        <v>413</v>
+        <v>636</v>
       </c>
       <c r="G262" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H262" t="s">
-        <v>104</v>
+        <v>447</v>
       </c>
       <c r="I262" s="2">
-        <v>44501</v>
+        <v>44482</v>
       </c>
       <c r="J262" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>17</v>
+        <v>630</v>
       </c>
       <c r="B263" t="s">
-        <v>17</v>
+        <v>630</v>
       </c>
       <c r="C263" t="s">
-        <v>774</v>
-      </c>
-      <c r="D263" s="3" t="s">
-        <v>775</v>
+        <v>771</v>
+      </c>
+      <c r="D263">
+        <v>414</v>
       </c>
       <c r="E263" t="s">
-        <v>776</v>
+        <v>472</v>
       </c>
       <c r="F263" t="s">
-        <v>436</v>
+        <v>772</v>
       </c>
       <c r="G263" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H263" t="s">
-        <v>22</v>
+        <v>773</v>
       </c>
       <c r="I263" s="2">
-        <v>44494</v>
+        <v>44470</v>
       </c>
       <c r="J263" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B264" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C264" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D264">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="E264" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="F264" t="s">
-        <v>636</v>
+        <v>57</v>
       </c>
       <c r="G264" t="s">
         <v>15</v>
       </c>
       <c r="H264" t="s">
-        <v>447</v>
+        <v>58</v>
       </c>
       <c r="I264" s="2">
-        <v>44482</v>
+        <v>44391</v>
       </c>
       <c r="J264" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>630</v>
+        <v>283</v>
       </c>
       <c r="B265" t="s">
-        <v>630</v>
+        <v>283</v>
       </c>
       <c r="C265" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D265">
-        <v>414</v>
+        <v>388</v>
       </c>
       <c r="E265" t="s">
-        <v>472</v>
+        <v>777</v>
       </c>
       <c r="F265" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G265" t="s">
         <v>15</v>
       </c>
       <c r="H265" t="s">
-        <v>781</v>
+        <v>764</v>
       </c>
       <c r="I265" s="2">
-        <v>44470</v>
+        <v>44348</v>
       </c>
       <c r="J265" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>52</v>
+        <v>514</v>
       </c>
       <c r="B266" t="s">
-        <v>53</v>
+        <v>514</v>
       </c>
       <c r="C266" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D266">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="E266" t="s">
-        <v>783</v>
+        <v>329</v>
       </c>
       <c r="F266" t="s">
-        <v>57</v>
+        <v>780</v>
       </c>
       <c r="G266" t="s">
         <v>15</v>
       </c>
       <c r="H266" t="s">
-        <v>58</v>
+        <v>781</v>
       </c>
       <c r="I266" s="2">
-        <v>44391</v>
+        <v>44342</v>
       </c>
       <c r="J266" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="B267" t="s">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="C267" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D267">
-        <v>388</v>
+        <v>841</v>
       </c>
       <c r="E267" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F267" t="s">
-        <v>786</v>
+        <v>14</v>
       </c>
       <c r="G267" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="H267" t="s">
-        <v>772</v>
+        <v>104</v>
       </c>
       <c r="I267" s="2">
-        <v>44348</v>
+        <v>44292</v>
       </c>
       <c r="J267" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>514</v>
+        <v>111</v>
       </c>
       <c r="B268" t="s">
-        <v>514</v>
+        <v>111</v>
       </c>
       <c r="C268" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D268">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="E268" t="s">
-        <v>329</v>
+        <v>785</v>
       </c>
       <c r="F268" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G268" t="s">
         <v>15</v>
       </c>
       <c r="H268" t="s">
-        <v>789</v>
+        <v>115</v>
       </c>
       <c r="I268" s="2">
-        <v>44342</v>
+        <v>44259</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>652</v>
+        <v>206</v>
       </c>
       <c r="B269" t="s">
-        <v>652</v>
+        <v>206</v>
       </c>
       <c r="C269" t="s">
-        <v>790</v>
-      </c>
-      <c r="D269" s="3" t="s">
-        <v>791</v>
+        <v>787</v>
+      </c>
+      <c r="D269">
+        <v>373</v>
       </c>
       <c r="E269" t="s">
-        <v>358</v>
+        <v>788</v>
       </c>
       <c r="F269" t="s">
-        <v>708</v>
+        <v>82</v>
       </c>
       <c r="G269" t="s">
-        <v>363</v>
+        <v>176</v>
       </c>
       <c r="H269" t="s">
-        <v>792</v>
+        <v>104</v>
       </c>
       <c r="I269" s="2">
-        <v>44322</v>
+        <v>44249</v>
       </c>
       <c r="J269" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>206</v>
+        <v>601</v>
       </c>
       <c r="B270" t="s">
-        <v>206</v>
+        <v>789</v>
       </c>
       <c r="C270" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D270">
-        <v>841</v>
+        <v>370</v>
       </c>
       <c r="E270" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F270" t="s">
-        <v>14</v>
+        <v>792</v>
       </c>
       <c r="G270" t="s">
-        <v>346</v>
+        <v>15</v>
       </c>
       <c r="H270" t="s">
-        <v>104</v>
+        <v>604</v>
       </c>
       <c r="I270" s="2">
-        <v>44292</v>
+        <v>44228</v>
       </c>
       <c r="J270" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>111</v>
+        <v>700</v>
       </c>
       <c r="B271" t="s">
-        <v>111</v>
+        <v>700</v>
       </c>
       <c r="C271" t="s">
+        <v>794</v>
+      </c>
+      <c r="D271" s="3" t="s">
         <v>795</v>
-      </c>
-      <c r="D271">
-        <v>376</v>
       </c>
       <c r="E271" t="s">
         <v>796</v>
       </c>
       <c r="F271" t="s">
-        <v>797</v>
+        <v>704</v>
       </c>
       <c r="G271" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H271" t="s">
-        <v>115</v>
+        <v>705</v>
       </c>
       <c r="I271" s="2">
-        <v>44259</v>
+        <v>44197</v>
       </c>
       <c r="J271" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>206</v>
+        <v>607</v>
       </c>
       <c r="B272" t="s">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="C272" t="s">
+        <v>797</v>
+      </c>
+      <c r="D272">
+        <v>356</v>
+      </c>
+      <c r="E272" t="s">
         <v>798</v>
       </c>
-      <c r="D272">
-        <v>373</v>
-      </c>
-      <c r="E272" t="s">
-        <v>799</v>
-      </c>
       <c r="F272" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="G272" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H272" t="s">
-        <v>104</v>
+        <v>610</v>
       </c>
       <c r="I272" s="2">
-        <v>44249</v>
+        <v>44097</v>
       </c>
       <c r="J272" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>652</v>
+        <v>88</v>
       </c>
       <c r="B273" t="s">
-        <v>652</v>
+        <v>89</v>
       </c>
       <c r="C273" t="s">
+        <v>799</v>
+      </c>
+      <c r="D273">
+        <v>349</v>
+      </c>
+      <c r="E273" t="s">
         <v>800</v>
       </c>
-      <c r="D273" s="3" t="s">
+      <c r="F273" t="s">
         <v>801</v>
       </c>
-      <c r="E273" t="s">
-        <v>10</v>
-      </c>
-      <c r="F273" t="s">
-        <v>802</v>
-      </c>
       <c r="G273" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H273" t="s">
-        <v>803</v>
+        <v>93</v>
       </c>
       <c r="I273" s="2">
-        <v>44246</v>
+        <v>43985</v>
       </c>
       <c r="J273" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>601</v>
+        <v>178</v>
       </c>
       <c r="B274" t="s">
-        <v>804</v>
+        <v>178</v>
       </c>
       <c r="C274" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D274">
-        <v>370</v>
+        <v>343</v>
       </c>
       <c r="E274" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="F274" t="s">
-        <v>807</v>
+        <v>99</v>
       </c>
       <c r="G274" t="s">
         <v>15</v>
       </c>
       <c r="H274" t="s">
-        <v>604</v>
+        <v>47</v>
       </c>
       <c r="I274" s="2">
-        <v>44228</v>
+        <v>43888</v>
       </c>
       <c r="J274" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>652</v>
+        <v>137</v>
       </c>
       <c r="B275" t="s">
-        <v>652</v>
+        <v>137</v>
       </c>
       <c r="C275" t="s">
-        <v>808</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>809</v>
+        <v>804</v>
+      </c>
+      <c r="D275">
+        <v>329</v>
       </c>
       <c r="E275" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="F275" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="G275" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H275" t="s">
-        <v>811</v>
+        <v>141</v>
       </c>
       <c r="I275" s="2">
-        <v>44197</v>
+        <v>43682</v>
       </c>
       <c r="J275" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>652</v>
+        <v>264</v>
       </c>
       <c r="B276" t="s">
-        <v>652</v>
+        <v>53</v>
       </c>
       <c r="C276" t="s">
-        <v>812</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>813</v>
+        <v>807</v>
+      </c>
+      <c r="D276">
+        <v>314</v>
       </c>
       <c r="E276" t="s">
-        <v>411</v>
+        <v>52</v>
       </c>
       <c r="F276" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="G276" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H276" t="s">
-        <v>814</v>
+        <v>269</v>
       </c>
       <c r="I276" s="2">
-        <v>44197</v>
+        <v>43605</v>
       </c>
       <c r="J276" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>652</v>
+        <v>630</v>
       </c>
       <c r="B277" t="s">
-        <v>652</v>
+        <v>630</v>
       </c>
       <c r="C277" t="s">
-        <v>815</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>816</v>
+        <v>809</v>
+      </c>
+      <c r="D277">
+        <v>627</v>
       </c>
       <c r="E277" t="s">
-        <v>101</v>
+        <v>343</v>
       </c>
       <c r="F277" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="G277" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H277" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="I277" s="2">
-        <v>44197</v>
+        <v>43587</v>
       </c>
       <c r="J277" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>652</v>
+        <v>283</v>
       </c>
       <c r="B278" t="s">
-        <v>652</v>
+        <v>283</v>
       </c>
       <c r="C278" t="s">
-        <v>818</v>
-      </c>
-      <c r="D278" s="3" t="s">
-        <v>819</v>
+        <v>812</v>
+      </c>
+      <c r="D278">
+        <v>292</v>
       </c>
       <c r="E278" t="s">
-        <v>197</v>
+        <v>813</v>
       </c>
       <c r="F278" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="G278" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H278" t="s">
-        <v>820</v>
+        <v>764</v>
       </c>
       <c r="I278" s="2">
-        <v>44197</v>
+        <v>43556</v>
       </c>
       <c r="J278" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>704</v>
+        <v>145</v>
       </c>
       <c r="B279" t="s">
-        <v>704</v>
+        <v>145</v>
       </c>
       <c r="C279" t="s">
-        <v>821</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>822</v>
+        <v>815</v>
+      </c>
+      <c r="D279">
+        <v>283</v>
       </c>
       <c r="E279" t="s">
-        <v>823</v>
+        <v>607</v>
       </c>
       <c r="F279" t="s">
-        <v>708</v>
+        <v>457</v>
       </c>
       <c r="G279" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H279" t="s">
-        <v>709</v>
+        <v>571</v>
       </c>
       <c r="I279" s="2">
-        <v>44197</v>
+        <v>43509</v>
       </c>
       <c r="J279" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>607</v>
+        <v>700</v>
       </c>
       <c r="B280" t="s">
-        <v>145</v>
+        <v>700</v>
       </c>
       <c r="C280" t="s">
-        <v>824</v>
-      </c>
-      <c r="D280">
-        <v>356</v>
+        <v>816</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>817</v>
       </c>
       <c r="E280" t="s">
-        <v>825</v>
+        <v>17</v>
       </c>
       <c r="F280" t="s">
-        <v>43</v>
+        <v>818</v>
       </c>
       <c r="G280" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H280" t="s">
-        <v>610</v>
+        <v>819</v>
       </c>
       <c r="I280" s="2">
-        <v>44097</v>
+        <v>43500</v>
       </c>
       <c r="J280" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>88</v>
+        <v>329</v>
       </c>
       <c r="B281" t="s">
-        <v>89</v>
+        <v>330</v>
       </c>
       <c r="C281" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="D281">
-        <v>349</v>
+        <v>274</v>
       </c>
       <c r="E281" t="s">
-        <v>827</v>
+        <v>283</v>
       </c>
       <c r="F281" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="G281" t="s">
         <v>15</v>
       </c>
       <c r="H281" t="s">
-        <v>93</v>
+        <v>822</v>
       </c>
       <c r="I281" s="2">
-        <v>43985</v>
+        <v>43416</v>
       </c>
       <c r="J281" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>178</v>
+        <v>578</v>
       </c>
       <c r="B282" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="C282" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="D282">
-        <v>343</v>
+        <v>272</v>
       </c>
       <c r="E282" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="F282" t="s">
-        <v>99</v>
+        <v>825</v>
       </c>
       <c r="G282" t="s">
         <v>15</v>
       </c>
       <c r="H282" t="s">
-        <v>47</v>
+        <v>699</v>
       </c>
       <c r="I282" s="2">
-        <v>43888</v>
+        <v>43416</v>
       </c>
       <c r="J282" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>652</v>
+        <v>44</v>
       </c>
       <c r="B283" t="s">
-        <v>652</v>
+        <v>35</v>
       </c>
       <c r="C283" t="s">
-        <v>831</v>
-      </c>
-      <c r="D283" s="3" t="s">
-        <v>832</v>
+        <v>826</v>
+      </c>
+      <c r="D283">
+        <v>261</v>
       </c>
       <c r="E283" t="s">
-        <v>514</v>
+        <v>827</v>
       </c>
       <c r="F283" t="s">
-        <v>833</v>
+        <v>636</v>
       </c>
       <c r="G283" t="s">
         <v>15</v>
       </c>
       <c r="H283" t="s">
-        <v>656</v>
+        <v>47</v>
       </c>
       <c r="I283" s="2">
-        <v>43823</v>
+        <v>43313</v>
       </c>
       <c r="J283" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>137</v>
+        <v>793</v>
       </c>
       <c r="B284" t="s">
-        <v>137</v>
+        <v>828</v>
       </c>
       <c r="C284" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="D284">
-        <v>329</v>
+        <v>409</v>
       </c>
       <c r="E284" t="s">
-        <v>835</v>
+        <v>173</v>
       </c>
       <c r="F284" t="s">
-        <v>836</v>
+        <v>413</v>
       </c>
       <c r="G284" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H284" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="I284" s="2">
-        <v>43682</v>
+        <v>43243</v>
       </c>
       <c r="J284" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>53</v>
+        <v>283</v>
       </c>
       <c r="C285" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="D285">
-        <v>314</v>
+        <v>244</v>
       </c>
       <c r="E285" t="s">
-        <v>52</v>
+        <v>831</v>
       </c>
       <c r="F285" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="G285" t="s">
         <v>15</v>
       </c>
       <c r="H285" t="s">
-        <v>269</v>
+        <v>833</v>
       </c>
       <c r="I285" s="2">
-        <v>43605</v>
+        <v>43160</v>
       </c>
       <c r="J285" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>630</v>
+        <v>178</v>
       </c>
       <c r="B286" t="s">
-        <v>630</v>
+        <v>178</v>
       </c>
       <c r="C286" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="D286">
-        <v>627</v>
+        <v>236</v>
       </c>
       <c r="E286" t="s">
-        <v>343</v>
+        <v>835</v>
       </c>
       <c r="F286" t="s">
-        <v>840</v>
+        <v>33</v>
       </c>
       <c r="G286" t="s">
         <v>15</v>
       </c>
       <c r="H286" t="s">
-        <v>841</v>
+        <v>47</v>
       </c>
       <c r="I286" s="2">
-        <v>43587</v>
+        <v>43028</v>
       </c>
       <c r="J286" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>283</v>
+        <v>137</v>
       </c>
       <c r="B287" t="s">
-        <v>283</v>
+        <v>137</v>
       </c>
       <c r="C287" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="D287">
-        <v>292</v>
+        <v>213</v>
       </c>
       <c r="E287" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="F287" t="s">
-        <v>844</v>
+        <v>806</v>
       </c>
       <c r="G287" t="s">
         <v>15</v>
       </c>
       <c r="H287" t="s">
-        <v>772</v>
+        <v>141</v>
       </c>
       <c r="I287" s="2">
-        <v>43556</v>
+        <v>42751</v>
       </c>
       <c r="J287" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B288" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C288" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="D288">
-        <v>283</v>
+        <v>208</v>
       </c>
       <c r="E288" t="s">
-        <v>607</v>
+        <v>839</v>
       </c>
       <c r="F288" t="s">
-        <v>457</v>
+        <v>840</v>
       </c>
       <c r="G288" t="s">
         <v>15</v>
       </c>
       <c r="H288" t="s">
-        <v>571</v>
+        <v>141</v>
       </c>
       <c r="I288" s="2">
-        <v>43509</v>
+        <v>42614</v>
       </c>
       <c r="J288" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>704</v>
+        <v>264</v>
       </c>
       <c r="B289" t="s">
-        <v>704</v>
+        <v>53</v>
       </c>
       <c r="C289" t="s">
-        <v>846</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>847</v>
+        <v>841</v>
+      </c>
+      <c r="D289">
+        <v>180</v>
       </c>
       <c r="E289" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="F289" t="s">
-        <v>848</v>
+        <v>268</v>
       </c>
       <c r="G289" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H289" t="s">
-        <v>849</v>
+        <v>269</v>
       </c>
       <c r="I289" s="2">
-        <v>43500</v>
+        <v>42381</v>
       </c>
       <c r="J289" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>329</v>
+        <v>452</v>
       </c>
       <c r="B290" t="s">
-        <v>330</v>
+        <v>452</v>
       </c>
       <c r="C290" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="D290">
-        <v>274</v>
+        <v>169</v>
       </c>
       <c r="E290" t="s">
-        <v>283</v>
+        <v>89</v>
       </c>
       <c r="F290" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="G290" t="s">
         <v>15</v>
       </c>
       <c r="H290" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="I290" s="2">
-        <v>43416</v>
+        <v>42248</v>
       </c>
       <c r="J290" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>578</v>
+        <v>168</v>
       </c>
       <c r="B291" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="C291" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="D291">
-        <v>272</v>
+        <v>131</v>
       </c>
       <c r="E291" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="F291" t="s">
-        <v>855</v>
+        <v>185</v>
       </c>
       <c r="G291" t="s">
         <v>15</v>
       </c>
       <c r="H291" t="s">
-        <v>703</v>
+        <v>172</v>
       </c>
       <c r="I291" s="2">
-        <v>43416</v>
+        <v>41255</v>
       </c>
       <c r="J291" s="2" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="B292" t="s">
-        <v>35</v>
+        <v>346</v>
       </c>
       <c r="C292" t="s">
-        <v>856</v>
-      </c>
-      <c r="D292">
-        <v>261</v>
+        <v>847</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>848</v>
       </c>
       <c r="E292" t="s">
-        <v>857</v>
+        <v>652</v>
       </c>
       <c r="F292" t="s">
-        <v>636</v>
+        <v>849</v>
       </c>
       <c r="G292" t="s">
         <v>15</v>
       </c>
       <c r="H292" t="s">
-        <v>47</v>
+        <v>850</v>
       </c>
       <c r="I292" s="2">
-        <v>43313</v>
+        <v>37163</v>
       </c>
       <c r="J292" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>810</v>
-      </c>
-      <c r="B293" t="s">
-        <v>858</v>
-      </c>
-      <c r="C293" t="s">
-        <v>859</v>
-      </c>
-      <c r="D293">
-        <v>409</v>
-      </c>
-      <c r="E293" t="s">
-        <v>173</v>
-      </c>
-      <c r="F293" t="s">
-        <v>413</v>
-      </c>
-      <c r="G293" t="s">
-        <v>176</v>
-      </c>
-      <c r="H293" t="s">
-        <v>177</v>
-      </c>
-      <c r="I293" s="2">
-        <v>43243</v>
-      </c>
-      <c r="J293" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>283</v>
-      </c>
-      <c r="B294" t="s">
-        <v>283</v>
-      </c>
-      <c r="C294" t="s">
-        <v>860</v>
-      </c>
-      <c r="D294">
-        <v>244</v>
-      </c>
-      <c r="E294" t="s">
-        <v>861</v>
-      </c>
-      <c r="F294" t="s">
-        <v>862</v>
-      </c>
-      <c r="G294" t="s">
-        <v>15</v>
-      </c>
-      <c r="H294" t="s">
-        <v>863</v>
-      </c>
-      <c r="I294" s="2">
-        <v>43160</v>
-      </c>
-      <c r="J294" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>178</v>
-      </c>
-      <c r="B295" t="s">
-        <v>178</v>
-      </c>
-      <c r="C295" t="s">
-        <v>864</v>
-      </c>
-      <c r="D295">
-        <v>236</v>
-      </c>
-      <c r="E295" t="s">
-        <v>865</v>
-      </c>
-      <c r="F295" t="s">
-        <v>33</v>
-      </c>
-      <c r="G295" t="s">
-        <v>15</v>
-      </c>
-      <c r="H295" t="s">
-        <v>47</v>
-      </c>
-      <c r="I295" s="2">
-        <v>43028</v>
-      </c>
-      <c r="J295" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
-        <v>137</v>
-      </c>
-      <c r="B296" t="s">
-        <v>137</v>
-      </c>
-      <c r="C296" t="s">
-        <v>866</v>
-      </c>
-      <c r="D296">
-        <v>213</v>
-      </c>
-      <c r="E296" t="s">
-        <v>867</v>
-      </c>
-      <c r="F296" t="s">
-        <v>836</v>
-      </c>
-      <c r="G296" t="s">
-        <v>15</v>
-      </c>
-      <c r="H296" t="s">
-        <v>141</v>
-      </c>
-      <c r="I296" s="2">
-        <v>42751</v>
-      </c>
-      <c r="J296" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>137</v>
-      </c>
-      <c r="B297" t="s">
-        <v>137</v>
-      </c>
-      <c r="C297" t="s">
-        <v>868</v>
-      </c>
-      <c r="D297">
-        <v>208</v>
-      </c>
-      <c r="E297" t="s">
-        <v>869</v>
-      </c>
-      <c r="F297" t="s">
-        <v>870</v>
-      </c>
-      <c r="G297" t="s">
-        <v>15</v>
-      </c>
-      <c r="H297" t="s">
-        <v>141</v>
-      </c>
-      <c r="I297" s="2">
-        <v>42614</v>
-      </c>
-      <c r="J297" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>652</v>
-      </c>
-      <c r="B298" t="s">
-        <v>652</v>
-      </c>
-      <c r="C298" t="s">
-        <v>871</v>
-      </c>
-      <c r="D298">
-        <v>207</v>
-      </c>
-      <c r="E298" t="s">
-        <v>872</v>
-      </c>
-      <c r="F298" t="s">
-        <v>873</v>
-      </c>
-      <c r="G298" t="s">
-        <v>15</v>
-      </c>
-      <c r="H298" t="s">
-        <v>656</v>
-      </c>
-      <c r="I298" s="2">
-        <v>42522</v>
-      </c>
-      <c r="J298" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
-        <v>264</v>
-      </c>
-      <c r="B299" t="s">
-        <v>53</v>
-      </c>
-      <c r="C299" t="s">
-        <v>874</v>
-      </c>
-      <c r="D299">
-        <v>180</v>
-      </c>
-      <c r="E299" t="s">
-        <v>209</v>
-      </c>
-      <c r="F299" t="s">
-        <v>268</v>
-      </c>
-      <c r="G299" t="s">
-        <v>15</v>
-      </c>
-      <c r="H299" t="s">
-        <v>269</v>
-      </c>
-      <c r="I299" s="2">
-        <v>42381</v>
-      </c>
-      <c r="J299" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A300" t="s">
-        <v>452</v>
-      </c>
-      <c r="B300" t="s">
-        <v>452</v>
-      </c>
-      <c r="C300" t="s">
-        <v>875</v>
-      </c>
-      <c r="D300">
-        <v>169</v>
-      </c>
-      <c r="E300" t="s">
-        <v>89</v>
-      </c>
-      <c r="F300" t="s">
-        <v>876</v>
-      </c>
-      <c r="G300" t="s">
-        <v>15</v>
-      </c>
-      <c r="H300" t="s">
-        <v>877</v>
-      </c>
-      <c r="I300" s="2">
-        <v>42248</v>
-      </c>
-      <c r="J300" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A301" t="s">
-        <v>652</v>
-      </c>
-      <c r="B301" t="s">
-        <v>652</v>
-      </c>
-      <c r="C301" t="s">
-        <v>878</v>
-      </c>
-      <c r="D301">
-        <v>139</v>
-      </c>
-      <c r="E301" t="s">
-        <v>137</v>
-      </c>
-      <c r="F301" t="s">
-        <v>879</v>
-      </c>
-      <c r="G301" t="s">
-        <v>15</v>
-      </c>
-      <c r="H301" t="s">
-        <v>656</v>
-      </c>
-      <c r="I301" s="2">
-        <v>41582</v>
-      </c>
-      <c r="J301" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>168</v>
-      </c>
-      <c r="B302" t="s">
-        <v>168</v>
-      </c>
-      <c r="C302" t="s">
-        <v>880</v>
-      </c>
-      <c r="D302">
-        <v>131</v>
-      </c>
-      <c r="E302" t="s">
-        <v>881</v>
-      </c>
-      <c r="F302" t="s">
-        <v>185</v>
-      </c>
-      <c r="G302" t="s">
-        <v>15</v>
-      </c>
-      <c r="H302" t="s">
-        <v>172</v>
-      </c>
-      <c r="I302" s="2">
-        <v>41255</v>
-      </c>
-      <c r="J302" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
-        <v>652</v>
-      </c>
-      <c r="B303" t="s">
-        <v>652</v>
-      </c>
-      <c r="C303" t="s">
-        <v>882</v>
-      </c>
-      <c r="D303">
-        <v>101</v>
-      </c>
-      <c r="E303" t="s">
-        <v>883</v>
-      </c>
-      <c r="F303" t="s">
-        <v>879</v>
-      </c>
-      <c r="G303" t="s">
-        <v>15</v>
-      </c>
-      <c r="H303" t="s">
-        <v>656</v>
-      </c>
-      <c r="I303" s="2">
-        <v>39203</v>
-      </c>
-      <c r="J303" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>346</v>
-      </c>
-      <c r="B304" t="s">
-        <v>346</v>
-      </c>
-      <c r="C304" t="s">
-        <v>884</v>
-      </c>
-      <c r="D304" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="E304" t="s">
-        <v>652</v>
-      </c>
-      <c r="F304" t="s">
-        <v>886</v>
-      </c>
-      <c r="G304" t="s">
-        <v>15</v>
-      </c>
-      <c r="H304" t="s">
-        <v>887</v>
-      </c>
-      <c r="I304" s="2">
-        <v>37163</v>
-      </c>
-      <c r="J304" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
-        <v>652</v>
-      </c>
-      <c r="B305" t="s">
-        <v>652</v>
-      </c>
-      <c r="C305" t="s">
-        <v>888</v>
-      </c>
-      <c r="D305" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="E305" t="s">
-        <v>704</v>
-      </c>
-      <c r="F305" t="s">
-        <v>833</v>
-      </c>
-      <c r="G305" t="s">
-        <v>15</v>
-      </c>
-      <c r="H305" t="s">
-        <v>656</v>
-      </c>
-      <c r="I305" s="2">
-        <v>37163</v>
-      </c>
-      <c r="J305" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
-        <v>652</v>
-      </c>
-      <c r="B306" t="s">
-        <v>652</v>
-      </c>
-      <c r="C306" t="s">
-        <v>890</v>
-      </c>
-      <c r="D306" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="E306" t="s">
-        <v>630</v>
-      </c>
-      <c r="F306" t="s">
-        <v>833</v>
-      </c>
-      <c r="G306" t="s">
-        <v>15</v>
-      </c>
-      <c r="H306" t="s">
-        <v>656</v>
-      </c>
-      <c r="I306" s="2">
-        <v>36527</v>
-      </c>
-      <c r="J306" s="8" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -13127,68 +12510,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="38.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>892</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>894</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>895</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>896</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>897</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>898</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>899</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>900</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>901</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>902</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
@@ -13201,43 +12524,47 @@
     <col min="8" max="8" width="22.77734375" customWidth="1"/>
     <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>903</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>893</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>904</v>
-      </c>
-      <c r="D1" s="9" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>895</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>896</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>897</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>898</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>905</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E1" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>907</v>
+        <v>860</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -13246,16 +12573,16 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>908</v>
+        <v>861</v>
       </c>
       <c r="F2" t="s">
-        <v>909</v>
+        <v>862</v>
       </c>
       <c r="G2" t="s">
-        <v>908</v>
+        <v>861</v>
       </c>
       <c r="H2" t="s">
-        <v>908</v>
+        <v>861</v>
       </c>
       <c r="I2" t="s">
         <v>332</v>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://desenvolvimentocartaodetodo-my.sharepoint.com/personal/peopleanalytics_cartaodetodos_com/Documents/People Analytics/PEPO 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{2E15DFB4-E428-4DE4-88DA-4CA6BE165C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="14_{2E15DFB4-E428-4DE4-88DA-4CA6BE165C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72443148-EC40-4C9A-B642-E69598456F49}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="859">
   <si>
     <t>Gestor Avaliador</t>
   </si>
@@ -1992,9 +1992,6 @@
     <t>ANALISTA DE PROCESSOS JR</t>
   </si>
   <si>
-    <t>ALTAIR DE JESUS VILAR GUIMARAES</t>
-  </si>
-  <si>
     <t>985260</t>
   </si>
   <si>
@@ -2463,15 +2460,6 @@
     <t>COORDENADOR DE PROJETOS</t>
   </si>
   <si>
-    <t>13200</t>
-  </si>
-  <si>
-    <t>CPCO  CHIEF PEOPLE AND CULTURE OFFICER</t>
-  </si>
-  <si>
-    <t>25 - P&amp;C - DIRETORIA</t>
-  </si>
-  <si>
     <t>13198</t>
   </si>
   <si>
@@ -2575,18 +2563,6 @@
   </si>
   <si>
     <t>ALINE BASSO DE AZEVEDO</t>
-  </si>
-  <si>
-    <t>15020</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>PRESIDENTE</t>
-  </si>
-  <si>
-    <t>25 - PRESIDENCIA</t>
   </si>
   <si>
     <t>Nome do Gestor</t>
@@ -2730,30 +2706,6 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color auto="1"/>
@@ -2795,6 +2747,30 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2808,15 +2784,11 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:J292" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:J292" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I292">
-    <sortCondition descending="1" ref="I1:I292"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:J290" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:J290" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I290">
+    <sortCondition descending="1" ref="I1:I290"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador"/>
@@ -2827,15 +2799,15 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{924CDE42-02DE-4EFB-A383-D6819D596AFA}" name="E-mail gestor validador" dataCellStyle="Hiperlink"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{924CDE42-02DE-4EFB-A383-D6819D596AFA}" name="E-mail gestor validador"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:K2" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:K2" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:K2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{CFF5932B-854B-4B23-A01A-04BA6982E294}" name="Momento do Envio"/>
@@ -3141,7 +3113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J292"/>
+  <dimension ref="A1:J290"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.88671875" bestFit="1" customWidth="1"/>
@@ -3185,7 +3157,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3193,7 +3165,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="C2">
         <v>2701261</v>
@@ -3217,7 +3189,7 @@
         <v>46053</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3249,7 +3221,7 @@
         <v>46053</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -3281,7 +3253,7 @@
         <v>46043</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -3313,7 +3285,7 @@
         <v>46041</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -3345,7 +3317,7 @@
         <v>46027</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -3377,7 +3349,7 @@
         <v>46027</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -3409,7 +3381,7 @@
         <v>46006</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -3441,7 +3413,7 @@
         <v>46006</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -3473,7 +3445,7 @@
         <v>46006</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -3505,7 +3477,7 @@
         <v>46006</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -3537,7 +3509,7 @@
         <v>45992</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -3569,7 +3541,7 @@
         <v>45992</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -3601,7 +3573,7 @@
         <v>45992</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -3633,7 +3605,7 @@
         <v>45992</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -3665,7 +3637,7 @@
         <v>45978</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -3697,7 +3669,7 @@
         <v>45978</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -3729,7 +3701,7 @@
         <v>45978</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -3761,7 +3733,7 @@
         <v>45978</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -3793,7 +3765,7 @@
         <v>45978</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -3825,7 +3797,7 @@
         <v>45978</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -3857,7 +3829,7 @@
         <v>45978</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -3889,7 +3861,7 @@
         <v>45978</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -3921,7 +3893,7 @@
         <v>45978</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -3953,7 +3925,7 @@
         <v>45978</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -3985,7 +3957,7 @@
         <v>45966</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -4017,7 +3989,7 @@
         <v>45964</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -4049,7 +4021,7 @@
         <v>45964</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -4081,7 +4053,7 @@
         <v>45964</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -4113,7 +4085,7 @@
         <v>45964</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -4145,7 +4117,7 @@
         <v>45964</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -4177,7 +4149,7 @@
         <v>45964</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -4209,7 +4181,7 @@
         <v>45950</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -4241,7 +4213,7 @@
         <v>45950</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -4273,7 +4245,7 @@
         <v>45936</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -4305,7 +4277,7 @@
         <v>45936</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -4337,7 +4309,7 @@
         <v>45936</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -4369,7 +4341,7 @@
         <v>45936</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -4401,7 +4373,7 @@
         <v>45936</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -4433,7 +4405,7 @@
         <v>45915</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -4465,7 +4437,7 @@
         <v>45915</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -4497,7 +4469,7 @@
         <v>45915</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -4529,7 +4501,7 @@
         <v>45915</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -4561,7 +4533,7 @@
         <v>45915</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -4593,7 +4565,7 @@
         <v>45915</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -4625,7 +4597,7 @@
         <v>45901</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
@@ -4657,7 +4629,7 @@
         <v>45901</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -4689,7 +4661,7 @@
         <v>45887</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
@@ -4721,7 +4693,7 @@
         <v>45887</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -4753,7 +4725,7 @@
         <v>45887</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -4785,7 +4757,7 @@
         <v>45887</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -4817,7 +4789,7 @@
         <v>45887</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -4849,7 +4821,7 @@
         <v>45873</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -4881,7 +4853,7 @@
         <v>45873</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -4913,7 +4885,7 @@
         <v>45873</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -4945,7 +4917,7 @@
         <v>45873</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -4977,7 +4949,7 @@
         <v>45873</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
@@ -5009,7 +4981,7 @@
         <v>45873</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
@@ -5041,7 +5013,7 @@
         <v>45873</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
@@ -5073,7 +5045,7 @@
         <v>45873</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
@@ -5105,7 +5077,7 @@
         <v>45873</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -5137,7 +5109,7 @@
         <v>45861</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -5169,7 +5141,7 @@
         <v>45852</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
@@ -5201,7 +5173,7 @@
         <v>45852</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
@@ -5233,7 +5205,7 @@
         <v>45845</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
@@ -5265,7 +5237,7 @@
         <v>45845</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
@@ -5297,7 +5269,7 @@
         <v>45839</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
@@ -5329,7 +5301,7 @@
         <v>45824</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
@@ -5361,7 +5333,7 @@
         <v>45824</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
@@ -5393,7 +5365,7 @@
         <v>45824</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
@@ -5425,7 +5397,7 @@
         <v>45824</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
@@ -5457,7 +5429,7 @@
         <v>45817</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
@@ -5489,7 +5461,7 @@
         <v>45810</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
@@ -5521,7 +5493,7 @@
         <v>45810</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
@@ -5553,7 +5525,7 @@
         <v>45810</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
@@ -5585,7 +5557,7 @@
         <v>45810</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
@@ -5617,7 +5589,7 @@
         <v>45810</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
@@ -5649,7 +5621,7 @@
         <v>45796</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
@@ -5681,7 +5653,7 @@
         <v>45789</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
@@ -5713,7 +5685,7 @@
         <v>45789</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
@@ -5745,7 +5717,7 @@
         <v>45789</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
@@ -5777,7 +5749,7 @@
         <v>45789</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
@@ -5809,7 +5781,7 @@
         <v>45782</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
@@ -5841,7 +5813,7 @@
         <v>45782</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
@@ -5873,7 +5845,7 @@
         <v>45782</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
@@ -5905,7 +5877,7 @@
         <v>45782</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
@@ -5937,7 +5909,7 @@
         <v>45782</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
@@ -5969,7 +5941,7 @@
         <v>45761</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
@@ -6001,7 +5973,7 @@
         <v>45761</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
@@ -6033,7 +6005,7 @@
         <v>45761</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
@@ -6065,7 +6037,7 @@
         <v>45761</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
@@ -6097,7 +6069,7 @@
         <v>45761</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
@@ -6129,7 +6101,7 @@
         <v>45761</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
@@ -6161,7 +6133,7 @@
         <v>45761</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
@@ -6193,7 +6165,7 @@
         <v>45761</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
@@ -6225,7 +6197,7 @@
         <v>45761</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
@@ -6257,7 +6229,7 @@
         <v>45761</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
@@ -6289,7 +6261,7 @@
         <v>45761</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
@@ -6321,7 +6293,7 @@
         <v>45758</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
@@ -6353,7 +6325,7 @@
         <v>45757</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
@@ -6385,7 +6357,7 @@
         <v>45754</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
@@ -6417,7 +6389,7 @@
         <v>45733</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
@@ -6449,7 +6421,7 @@
         <v>45722</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
@@ -6481,7 +6453,7 @@
         <v>45722</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
@@ -6513,7 +6485,7 @@
         <v>45722</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
@@ -6545,7 +6517,7 @@
         <v>45722</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
@@ -6577,7 +6549,7 @@
         <v>45722</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
@@ -6609,7 +6581,7 @@
         <v>45722</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
@@ -6641,7 +6613,7 @@
         <v>45722</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
@@ -6673,7 +6645,7 @@
         <v>45722</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
@@ -6705,7 +6677,7 @@
         <v>45721</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
@@ -6737,7 +6709,7 @@
         <v>45705</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
@@ -6769,7 +6741,7 @@
         <v>45705</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
@@ -6801,7 +6773,7 @@
         <v>45705</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
@@ -6833,7 +6805,7 @@
         <v>45705</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
@@ -6865,7 +6837,7 @@
         <v>45705</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
@@ -6897,7 +6869,7 @@
         <v>45705</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
@@ -6929,7 +6901,7 @@
         <v>45705</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
@@ -6961,7 +6933,7 @@
         <v>45705</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
@@ -6993,7 +6965,7 @@
         <v>45691</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
@@ -7025,7 +6997,7 @@
         <v>45691</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
@@ -7057,7 +7029,7 @@
         <v>45691</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
@@ -7089,7 +7061,7 @@
         <v>45691</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
@@ -7121,7 +7093,7 @@
         <v>45691</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
@@ -7153,7 +7125,7 @@
         <v>45691</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
@@ -7185,7 +7157,7 @@
         <v>45690</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
@@ -7217,7 +7189,7 @@
         <v>45684</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
@@ -7249,7 +7221,7 @@
         <v>45684</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
@@ -7281,7 +7253,7 @@
         <v>45680</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
@@ -7313,7 +7285,7 @@
         <v>45677</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
@@ -7345,7 +7317,7 @@
         <v>45677</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
@@ -7377,7 +7349,7 @@
         <v>45663</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
@@ -7409,7 +7381,7 @@
         <v>45659</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
@@ -7441,7 +7413,7 @@
         <v>45642</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
@@ -7473,7 +7445,7 @@
         <v>45628</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
@@ -7505,7 +7477,7 @@
         <v>45628</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
@@ -7537,7 +7509,7 @@
         <v>45628</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
@@ -7569,7 +7541,7 @@
         <v>45628</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
@@ -7601,7 +7573,7 @@
         <v>45614</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
@@ -7633,7 +7605,7 @@
         <v>45614</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
@@ -7665,7 +7637,7 @@
         <v>45600</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
@@ -7697,7 +7669,7 @@
         <v>45600</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
@@ -7729,7 +7701,7 @@
         <v>45600</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
@@ -7761,7 +7733,7 @@
         <v>45600</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
@@ -7793,7 +7765,7 @@
         <v>45600</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
@@ -7825,7 +7797,7 @@
         <v>45586</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
@@ -7857,7 +7829,7 @@
         <v>45580</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
@@ -7889,7 +7861,7 @@
         <v>45566</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
@@ -7921,7 +7893,7 @@
         <v>45566</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
@@ -7953,7 +7925,7 @@
         <v>45566</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
@@ -7985,7 +7957,7 @@
         <v>45566</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
@@ -8017,7 +7989,7 @@
         <v>45564</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
@@ -8049,7 +8021,7 @@
         <v>45551</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
@@ -8081,7 +8053,7 @@
         <v>45551</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
@@ -8113,7 +8085,7 @@
         <v>45545</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
@@ -8145,7 +8117,7 @@
         <v>45537</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
@@ -8177,7 +8149,7 @@
         <v>45520</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
@@ -8209,7 +8181,7 @@
         <v>45520</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
@@ -8241,7 +8213,7 @@
         <v>45520</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
@@ -8273,7 +8245,7 @@
         <v>45516</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
@@ -8305,7 +8277,7 @@
         <v>45505</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
@@ -8337,7 +8309,7 @@
         <v>45505</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
@@ -8369,7 +8341,7 @@
         <v>45488</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
@@ -8401,7 +8373,7 @@
         <v>45481</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
@@ -8433,7 +8405,7 @@
         <v>45474</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
@@ -8465,7 +8437,7 @@
         <v>45474</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
@@ -8497,7 +8469,7 @@
         <v>45460</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
@@ -8529,7 +8501,7 @@
         <v>45460</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
@@ -8561,7 +8533,7 @@
         <v>45460</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
@@ -8593,7 +8565,7 @@
         <v>45453</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
@@ -8625,7 +8597,7 @@
         <v>45446</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
@@ -8657,7 +8629,7 @@
         <v>45446</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
@@ -8689,7 +8661,7 @@
         <v>45446</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
@@ -8721,7 +8693,7 @@
         <v>45446</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
@@ -8753,7 +8725,7 @@
         <v>45439</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
@@ -8785,7 +8757,7 @@
         <v>45414</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
@@ -8817,7 +8789,7 @@
         <v>45390</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
@@ -8849,7 +8821,7 @@
         <v>45386</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
@@ -8881,7 +8853,7 @@
         <v>45383</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
@@ -8913,7 +8885,7 @@
         <v>45366</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
@@ -8945,7 +8917,7 @@
         <v>45357</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
@@ -8977,7 +8949,7 @@
         <v>45357</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
@@ -9009,7 +8981,7 @@
         <v>45355</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
@@ -9041,7 +9013,7 @@
         <v>45337</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
@@ -9073,7 +9045,7 @@
         <v>45323</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
@@ -9105,7 +9077,7 @@
         <v>45323</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
@@ -9137,7 +9109,7 @@
         <v>45313</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
@@ -9169,7 +9141,7 @@
         <v>45306</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
@@ -9201,7 +9173,7 @@
         <v>45306</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
@@ -9233,7 +9205,7 @@
         <v>45275</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
@@ -9265,7 +9237,7 @@
         <v>45275</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
@@ -9297,7 +9269,7 @@
         <v>45275</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
@@ -9329,7 +9301,7 @@
         <v>45275</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
@@ -9361,7 +9333,7 @@
         <v>45244</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
@@ -9393,7 +9365,7 @@
         <v>45233</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
@@ -9425,7 +9397,7 @@
         <v>45219</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
@@ -9457,7 +9429,7 @@
         <v>45215</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
@@ -9489,7 +9461,7 @@
         <v>45201</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
@@ -9521,7 +9493,7 @@
         <v>45194</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
@@ -9553,7 +9525,7 @@
         <v>45170</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
@@ -9585,7 +9557,7 @@
         <v>45170</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
@@ -9617,7 +9589,7 @@
         <v>45170</v>
       </c>
       <c r="J202" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
@@ -9649,7 +9621,7 @@
         <v>45154</v>
       </c>
       <c r="J203" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
@@ -9681,7 +9653,7 @@
         <v>45154</v>
       </c>
       <c r="J204" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
@@ -9713,7 +9685,7 @@
         <v>45152</v>
       </c>
       <c r="J205" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
@@ -9745,7 +9717,7 @@
         <v>45117</v>
       </c>
       <c r="J206" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
@@ -9777,7 +9749,7 @@
         <v>45110</v>
       </c>
       <c r="J207" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
@@ -9809,7 +9781,7 @@
         <v>45098</v>
       </c>
       <c r="J208" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
@@ -9841,7 +9813,7 @@
         <v>45089</v>
       </c>
       <c r="J209" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
@@ -9873,7 +9845,7 @@
         <v>45082</v>
       </c>
       <c r="J210" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
@@ -9905,7 +9877,7 @@
         <v>45082</v>
       </c>
       <c r="J211" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
@@ -9937,7 +9909,7 @@
         <v>45068</v>
       </c>
       <c r="J212" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
@@ -9969,7 +9941,7 @@
         <v>45063</v>
       </c>
       <c r="J213" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
@@ -10001,7 +9973,7 @@
         <v>45061</v>
       </c>
       <c r="J214" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
@@ -10033,7 +10005,7 @@
         <v>45041</v>
       </c>
       <c r="J215" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
@@ -10065,7 +10037,7 @@
         <v>45041</v>
       </c>
       <c r="J216" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
@@ -10076,7 +10048,7 @@
         <v>145</v>
       </c>
       <c r="C217" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D217">
         <v>596</v>
@@ -10097,7 +10069,7 @@
         <v>45019</v>
       </c>
       <c r="J217" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
@@ -10108,13 +10080,13 @@
         <v>53</v>
       </c>
       <c r="C218" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D218">
         <v>589</v>
       </c>
       <c r="E218" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F218" t="s">
         <v>57</v>
@@ -10129,7 +10101,7 @@
         <v>44979</v>
       </c>
       <c r="J218" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
@@ -10140,16 +10112,16 @@
         <v>283</v>
       </c>
       <c r="C219" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D219">
         <v>578</v>
       </c>
       <c r="E219" t="s">
+        <v>656</v>
+      </c>
+      <c r="F219" t="s">
         <v>657</v>
-      </c>
-      <c r="F219" t="s">
-        <v>658</v>
       </c>
       <c r="G219" t="s">
         <v>15</v>
@@ -10161,7 +10133,7 @@
         <v>44958</v>
       </c>
       <c r="J219" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
@@ -10172,13 +10144,13 @@
         <v>30</v>
       </c>
       <c r="C220" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D220">
         <v>674</v>
       </c>
       <c r="E220" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F220" t="s">
         <v>51</v>
@@ -10193,7 +10165,7 @@
         <v>44958</v>
       </c>
       <c r="J220" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
@@ -10204,13 +10176,13 @@
         <v>206</v>
       </c>
       <c r="C221" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D221">
         <v>579</v>
       </c>
       <c r="E221" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F221" t="s">
         <v>82</v>
@@ -10225,7 +10197,7 @@
         <v>44958</v>
       </c>
       <c r="J221" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
@@ -10236,7 +10208,7 @@
         <v>35</v>
       </c>
       <c r="C222" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D222">
         <v>575</v>
@@ -10251,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="H222" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I222" s="2">
         <v>44951</v>
       </c>
       <c r="J222" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
@@ -10268,16 +10240,16 @@
         <v>24</v>
       </c>
       <c r="C223" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D223">
         <v>572</v>
       </c>
       <c r="E223" t="s">
+        <v>665</v>
+      </c>
+      <c r="F223" t="s">
         <v>666</v>
-      </c>
-      <c r="F223" t="s">
-        <v>667</v>
       </c>
       <c r="G223" t="s">
         <v>15</v>
@@ -10289,7 +10261,7 @@
         <v>44949</v>
       </c>
       <c r="J223" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
@@ -10300,13 +10272,13 @@
         <v>197</v>
       </c>
       <c r="C224" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D224">
         <v>553</v>
       </c>
       <c r="E224" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F224" t="s">
         <v>82</v>
@@ -10321,7 +10293,7 @@
         <v>44921</v>
       </c>
       <c r="J224" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
@@ -10332,13 +10304,13 @@
         <v>383</v>
       </c>
       <c r="C225" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D225">
         <v>552</v>
       </c>
       <c r="E225" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F225" t="s">
         <v>14</v>
@@ -10353,7 +10325,7 @@
         <v>44921</v>
       </c>
       <c r="J225" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
@@ -10364,7 +10336,7 @@
         <v>35</v>
       </c>
       <c r="C226" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D226">
         <v>548</v>
@@ -10373,7 +10345,7 @@
         <v>193</v>
       </c>
       <c r="F226" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G226" t="s">
         <v>15</v>
@@ -10385,7 +10357,7 @@
         <v>44909</v>
       </c>
       <c r="J226" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
@@ -10396,13 +10368,13 @@
         <v>89</v>
       </c>
       <c r="C227" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D227">
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F227" t="s">
         <v>328</v>
@@ -10417,7 +10389,7 @@
         <v>44909</v>
       </c>
       <c r="J227" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
@@ -10428,13 +10400,13 @@
         <v>178</v>
       </c>
       <c r="C228" t="s">
+        <v>675</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="D228" s="3" t="s">
+      <c r="E228" t="s">
         <v>677</v>
-      </c>
-      <c r="E228" t="s">
-        <v>678</v>
       </c>
       <c r="F228" t="s">
         <v>648</v>
@@ -10449,7 +10421,7 @@
         <v>44907</v>
       </c>
       <c r="J228" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
@@ -10460,10 +10432,10 @@
         <v>30</v>
       </c>
       <c r="C229" t="s">
+        <v>678</v>
+      </c>
+      <c r="D229" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>680</v>
       </c>
       <c r="E229" t="s">
         <v>178</v>
@@ -10481,7 +10453,7 @@
         <v>44902</v>
       </c>
       <c r="J229" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
@@ -10492,13 +10464,13 @@
         <v>383</v>
       </c>
       <c r="C230" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D230">
         <v>545</v>
       </c>
       <c r="E230" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F230" t="s">
         <v>82</v>
@@ -10513,7 +10485,7 @@
         <v>44900</v>
       </c>
       <c r="J230" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
@@ -10524,10 +10496,10 @@
         <v>30</v>
       </c>
       <c r="C231" t="s">
+        <v>682</v>
+      </c>
+      <c r="D231" s="3" t="s">
         <v>683</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>684</v>
       </c>
       <c r="E231" t="s">
         <v>96</v>
@@ -10545,7 +10517,7 @@
         <v>44900</v>
       </c>
       <c r="J231" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
@@ -10556,13 +10528,13 @@
         <v>178</v>
       </c>
       <c r="C232" t="s">
+        <v>684</v>
+      </c>
+      <c r="D232" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="D232" s="3" t="s">
+      <c r="E232" t="s">
         <v>686</v>
-      </c>
-      <c r="E232" t="s">
-        <v>687</v>
       </c>
       <c r="F232" t="s">
         <v>648</v>
@@ -10577,7 +10549,7 @@
         <v>44894</v>
       </c>
       <c r="J232" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
@@ -10588,16 +10560,16 @@
         <v>24</v>
       </c>
       <c r="C233" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D233">
         <v>539</v>
       </c>
       <c r="E233" t="s">
+        <v>688</v>
+      </c>
+      <c r="F233" t="s">
         <v>689</v>
-      </c>
-      <c r="F233" t="s">
-        <v>690</v>
       </c>
       <c r="G233" t="s">
         <v>15</v>
@@ -10609,7 +10581,7 @@
         <v>44874</v>
       </c>
       <c r="J233" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
@@ -10620,13 +10592,13 @@
         <v>35</v>
       </c>
       <c r="C234" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D234">
         <v>538</v>
       </c>
       <c r="E234" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F234" t="s">
         <v>446</v>
@@ -10641,7 +10613,7 @@
         <v>44874</v>
       </c>
       <c r="J234" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
@@ -10652,28 +10624,28 @@
         <v>330</v>
       </c>
       <c r="C235" t="s">
+        <v>692</v>
+      </c>
+      <c r="D235" s="3" t="s">
         <v>693</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>694</v>
       </c>
       <c r="E235" t="s">
         <v>48</v>
       </c>
       <c r="F235" t="s">
+        <v>694</v>
+      </c>
+      <c r="G235" t="s">
+        <v>15</v>
+      </c>
+      <c r="H235" t="s">
         <v>695</v>
-      </c>
-      <c r="G235" t="s">
-        <v>15</v>
-      </c>
-      <c r="H235" t="s">
-        <v>696</v>
       </c>
       <c r="I235" s="2">
         <v>44866</v>
       </c>
       <c r="J235" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
@@ -10684,13 +10656,13 @@
         <v>35</v>
       </c>
       <c r="C236" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D236">
         <v>533</v>
       </c>
       <c r="E236" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F236" t="s">
         <v>61</v>
@@ -10699,45 +10671,45 @@
         <v>15</v>
       </c>
       <c r="H236" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="I236" s="2">
         <v>44851</v>
       </c>
       <c r="J236" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
+        <v>699</v>
+      </c>
+      <c r="B237" t="s">
+        <v>699</v>
+      </c>
+      <c r="C237" t="s">
         <v>700</v>
       </c>
-      <c r="B237" t="s">
-        <v>700</v>
-      </c>
-      <c r="C237" t="s">
+      <c r="D237" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="D237" s="3" t="s">
+      <c r="E237" t="s">
         <v>702</v>
       </c>
-      <c r="E237" t="s">
+      <c r="F237" t="s">
         <v>703</v>
-      </c>
-      <c r="F237" t="s">
-        <v>704</v>
       </c>
       <c r="G237" t="s">
         <v>176</v>
       </c>
       <c r="H237" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="I237" s="2">
         <v>44840</v>
       </c>
       <c r="J237" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
@@ -10748,13 +10720,13 @@
         <v>206</v>
       </c>
       <c r="C238" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D238">
         <v>528</v>
       </c>
       <c r="E238" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F238" t="s">
         <v>82</v>
@@ -10769,7 +10741,7 @@
         <v>44830</v>
       </c>
       <c r="J238" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
@@ -10780,7 +10752,7 @@
         <v>330</v>
       </c>
       <c r="C239" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D239">
         <v>523</v>
@@ -10795,13 +10767,13 @@
         <v>15</v>
       </c>
       <c r="H239" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="I239" s="2">
         <v>44823</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
@@ -10812,16 +10784,16 @@
         <v>358</v>
       </c>
       <c r="C240" t="s">
+        <v>709</v>
+      </c>
+      <c r="D240" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="D240" s="3" t="s">
+      <c r="E240" t="s">
         <v>711</v>
       </c>
-      <c r="E240" t="s">
+      <c r="F240" t="s">
         <v>712</v>
-      </c>
-      <c r="F240" t="s">
-        <v>713</v>
       </c>
       <c r="G240" t="s">
         <v>363</v>
@@ -10833,7 +10805,7 @@
         <v>44774</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
@@ -10844,13 +10816,13 @@
         <v>197</v>
       </c>
       <c r="C241" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D241">
         <v>919</v>
       </c>
       <c r="E241" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F241" t="s">
         <v>82</v>
@@ -10865,7 +10837,7 @@
         <v>44746</v>
       </c>
       <c r="J241" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
@@ -10876,13 +10848,13 @@
         <v>79</v>
       </c>
       <c r="C242" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D242">
         <v>495</v>
       </c>
       <c r="E242" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F242" t="s">
         <v>82</v>
@@ -10897,39 +10869,39 @@
         <v>44720</v>
       </c>
       <c r="J242" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B243" t="s">
         <v>129</v>
       </c>
       <c r="C243" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D243">
         <v>493</v>
       </c>
       <c r="E243" t="s">
+        <v>718</v>
+      </c>
+      <c r="F243" t="s">
         <v>719</v>
       </c>
-      <c r="F243" t="s">
+      <c r="G243" t="s">
+        <v>15</v>
+      </c>
+      <c r="H243" t="s">
         <v>720</v>
-      </c>
-      <c r="G243" t="s">
-        <v>15</v>
-      </c>
-      <c r="H243" t="s">
-        <v>721</v>
       </c>
       <c r="I243" s="2">
         <v>44718</v>
       </c>
       <c r="J243" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
@@ -10940,16 +10912,16 @@
         <v>17</v>
       </c>
       <c r="C244" t="s">
+        <v>721</v>
+      </c>
+      <c r="D244" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="D244" s="3" t="s">
+      <c r="E244" t="s">
         <v>723</v>
       </c>
-      <c r="E244" t="s">
+      <c r="F244" t="s">
         <v>724</v>
-      </c>
-      <c r="F244" t="s">
-        <v>725</v>
       </c>
       <c r="G244" t="s">
         <v>21</v>
@@ -10961,7 +10933,7 @@
         <v>44714</v>
       </c>
       <c r="J244" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
@@ -10972,16 +10944,16 @@
         <v>89</v>
       </c>
       <c r="C245" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D245">
         <v>491</v>
       </c>
       <c r="E245" t="s">
+        <v>726</v>
+      </c>
+      <c r="F245" t="s">
         <v>727</v>
-      </c>
-      <c r="F245" t="s">
-        <v>728</v>
       </c>
       <c r="G245" t="s">
         <v>15</v>
@@ -10993,7 +10965,7 @@
         <v>44713</v>
       </c>
       <c r="J245" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
@@ -11004,13 +10976,13 @@
         <v>89</v>
       </c>
       <c r="C246" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D246">
         <v>489</v>
       </c>
       <c r="E246" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F246" t="s">
         <v>328</v>
@@ -11025,7 +10997,7 @@
         <v>44692</v>
       </c>
       <c r="J246" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
@@ -11036,7 +11008,7 @@
         <v>63</v>
       </c>
       <c r="C247" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D247">
         <v>487</v>
@@ -11057,7 +11029,7 @@
         <v>44690</v>
       </c>
       <c r="J247" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
@@ -11068,13 +11040,13 @@
         <v>53</v>
       </c>
       <c r="C248" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D248">
         <v>483</v>
       </c>
       <c r="E248" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F248" t="s">
         <v>20</v>
@@ -11089,7 +11061,7 @@
         <v>44671</v>
       </c>
       <c r="J248" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
@@ -11100,16 +11072,16 @@
         <v>302</v>
       </c>
       <c r="C249" t="s">
+        <v>733</v>
+      </c>
+      <c r="D249" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="D249" s="3" t="s">
+      <c r="E249" t="s">
         <v>735</v>
       </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>736</v>
-      </c>
-      <c r="F249" t="s">
-        <v>737</v>
       </c>
       <c r="G249" t="s">
         <v>15</v>
@@ -11121,7 +11093,7 @@
         <v>44652</v>
       </c>
       <c r="J249" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
@@ -11132,13 +11104,13 @@
         <v>383</v>
       </c>
       <c r="C250" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D250">
         <v>474</v>
       </c>
       <c r="E250" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F250" t="s">
         <v>82</v>
@@ -11153,7 +11125,7 @@
         <v>44641</v>
       </c>
       <c r="J250" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
@@ -11164,13 +11136,13 @@
         <v>145</v>
       </c>
       <c r="C251" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D251">
         <v>469</v>
       </c>
       <c r="E251" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F251" t="s">
         <v>43</v>
@@ -11185,7 +11157,7 @@
         <v>44630</v>
       </c>
       <c r="J251" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
@@ -11196,7 +11168,7 @@
         <v>89</v>
       </c>
       <c r="C252" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D252">
         <v>451</v>
@@ -11205,7 +11177,7 @@
         <v>88</v>
       </c>
       <c r="F252" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G252" t="s">
         <v>15</v>
@@ -11217,7 +11189,7 @@
         <v>44573</v>
       </c>
       <c r="J252" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
@@ -11228,10 +11200,10 @@
         <v>30</v>
       </c>
       <c r="C253" t="s">
+        <v>743</v>
+      </c>
+      <c r="D253" s="3" t="s">
         <v>744</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>745</v>
       </c>
       <c r="E253" t="s">
         <v>29</v>
@@ -11249,7 +11221,7 @@
         <v>44562</v>
       </c>
       <c r="J253" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
@@ -11260,16 +11232,16 @@
         <v>89</v>
       </c>
       <c r="C254" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D254">
         <v>447</v>
       </c>
       <c r="E254" t="s">
+        <v>746</v>
+      </c>
+      <c r="F254" t="s">
         <v>747</v>
-      </c>
-      <c r="F254" t="s">
-        <v>748</v>
       </c>
       <c r="G254" t="s">
         <v>15</v>
@@ -11281,7 +11253,7 @@
         <v>44550</v>
       </c>
       <c r="J254" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
@@ -11292,16 +11264,16 @@
         <v>131</v>
       </c>
       <c r="C255" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D255">
         <v>441</v>
       </c>
       <c r="E255" t="s">
+        <v>749</v>
+      </c>
+      <c r="F255" t="s">
         <v>750</v>
-      </c>
-      <c r="F255" t="s">
-        <v>751</v>
       </c>
       <c r="G255" t="s">
         <v>15</v>
@@ -11313,7 +11285,7 @@
         <v>44546</v>
       </c>
       <c r="J255" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
@@ -11324,16 +11296,16 @@
         <v>131</v>
       </c>
       <c r="C256" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D256">
         <v>439</v>
       </c>
       <c r="E256" t="s">
+        <v>752</v>
+      </c>
+      <c r="F256" t="s">
         <v>753</v>
-      </c>
-      <c r="F256" t="s">
-        <v>754</v>
       </c>
       <c r="G256" t="s">
         <v>15</v>
@@ -11345,7 +11317,7 @@
         <v>44543</v>
       </c>
       <c r="J256" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
@@ -11356,16 +11328,16 @@
         <v>24</v>
       </c>
       <c r="C257" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D257">
         <v>434</v>
       </c>
       <c r="E257" t="s">
+        <v>755</v>
+      </c>
+      <c r="F257" t="s">
         <v>756</v>
-      </c>
-      <c r="F257" t="s">
-        <v>757</v>
       </c>
       <c r="G257" t="s">
         <v>15</v>
@@ -11377,7 +11349,7 @@
         <v>44531</v>
       </c>
       <c r="J257" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
@@ -11388,13 +11360,13 @@
         <v>35</v>
       </c>
       <c r="C258" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D258">
         <v>433</v>
       </c>
       <c r="E258" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F258" t="s">
         <v>61</v>
@@ -11403,13 +11375,13 @@
         <v>15</v>
       </c>
       <c r="H258" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="I258" s="2">
         <v>44522</v>
       </c>
       <c r="J258" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
@@ -11420,28 +11392,28 @@
         <v>283</v>
       </c>
       <c r="C259" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D259">
         <v>431</v>
       </c>
       <c r="E259" t="s">
+        <v>761</v>
+      </c>
+      <c r="F259" t="s">
         <v>762</v>
       </c>
-      <c r="F259" t="s">
+      <c r="G259" t="s">
+        <v>15</v>
+      </c>
+      <c r="H259" t="s">
         <v>763</v>
-      </c>
-      <c r="G259" t="s">
-        <v>15</v>
-      </c>
-      <c r="H259" t="s">
-        <v>764</v>
       </c>
       <c r="I259" s="2">
         <v>44522</v>
       </c>
       <c r="J259" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
@@ -11452,7 +11424,7 @@
         <v>101</v>
       </c>
       <c r="C260" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D260">
         <v>430</v>
@@ -11473,7 +11445,7 @@
         <v>44501</v>
       </c>
       <c r="J260" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
@@ -11484,13 +11456,13 @@
         <v>17</v>
       </c>
       <c r="C261" t="s">
+        <v>765</v>
+      </c>
+      <c r="D261" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="D261" s="3" t="s">
+      <c r="E261" t="s">
         <v>767</v>
-      </c>
-      <c r="E261" t="s">
-        <v>768</v>
       </c>
       <c r="F261" t="s">
         <v>436</v>
@@ -11505,7 +11477,7 @@
         <v>44494</v>
       </c>
       <c r="J261" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
@@ -11516,13 +11488,13 @@
         <v>35</v>
       </c>
       <c r="C262" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D262">
         <v>418</v>
       </c>
       <c r="E262" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F262" t="s">
         <v>636</v>
@@ -11537,7 +11509,7 @@
         <v>44482</v>
       </c>
       <c r="J262" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
@@ -11548,7 +11520,7 @@
         <v>630</v>
       </c>
       <c r="C263" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D263">
         <v>414</v>
@@ -11557,19 +11529,19 @@
         <v>472</v>
       </c>
       <c r="F263" t="s">
+        <v>771</v>
+      </c>
+      <c r="G263" t="s">
+        <v>15</v>
+      </c>
+      <c r="H263" t="s">
         <v>772</v>
-      </c>
-      <c r="G263" t="s">
-        <v>15</v>
-      </c>
-      <c r="H263" t="s">
-        <v>773</v>
       </c>
       <c r="I263" s="2">
         <v>44470</v>
       </c>
       <c r="J263" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
@@ -11580,13 +11552,13 @@
         <v>53</v>
       </c>
       <c r="C264" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D264">
         <v>401</v>
       </c>
       <c r="E264" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F264" t="s">
         <v>57</v>
@@ -11601,7 +11573,7 @@
         <v>44391</v>
       </c>
       <c r="J264" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
@@ -11612,28 +11584,28 @@
         <v>283</v>
       </c>
       <c r="C265" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D265">
         <v>388</v>
       </c>
       <c r="E265" t="s">
+        <v>776</v>
+      </c>
+      <c r="F265" t="s">
         <v>777</v>
       </c>
-      <c r="F265" t="s">
-        <v>778</v>
-      </c>
       <c r="G265" t="s">
         <v>15</v>
       </c>
       <c r="H265" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="I265" s="2">
         <v>44348</v>
       </c>
       <c r="J265" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
@@ -11644,7 +11616,7 @@
         <v>514</v>
       </c>
       <c r="C266" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D266">
         <v>390</v>
@@ -11653,19 +11625,19 @@
         <v>329</v>
       </c>
       <c r="F266" t="s">
+        <v>779</v>
+      </c>
+      <c r="G266" t="s">
+        <v>15</v>
+      </c>
+      <c r="H266" t="s">
         <v>780</v>
-      </c>
-      <c r="G266" t="s">
-        <v>15</v>
-      </c>
-      <c r="H266" t="s">
-        <v>781</v>
       </c>
       <c r="I266" s="2">
         <v>44342</v>
       </c>
       <c r="J266" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
@@ -11676,13 +11648,13 @@
         <v>206</v>
       </c>
       <c r="C267" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D267">
         <v>841</v>
       </c>
       <c r="E267" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F267" t="s">
         <v>14</v>
@@ -11697,7 +11669,7 @@
         <v>44292</v>
       </c>
       <c r="J267" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
@@ -11708,16 +11680,16 @@
         <v>111</v>
       </c>
       <c r="C268" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D268">
         <v>376</v>
       </c>
       <c r="E268" t="s">
+        <v>784</v>
+      </c>
+      <c r="F268" t="s">
         <v>785</v>
-      </c>
-      <c r="F268" t="s">
-        <v>786</v>
       </c>
       <c r="G268" t="s">
         <v>15</v>
@@ -11729,7 +11701,7 @@
         <v>44259</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
@@ -11740,13 +11712,13 @@
         <v>206</v>
       </c>
       <c r="C269" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D269">
         <v>373</v>
       </c>
       <c r="E269" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F269" t="s">
         <v>82</v>
@@ -11761,7 +11733,7 @@
         <v>44249</v>
       </c>
       <c r="J269" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
@@ -11769,19 +11741,19 @@
         <v>601</v>
       </c>
       <c r="B270" t="s">
+        <v>788</v>
+      </c>
+      <c r="C270" t="s">
         <v>789</v>
-      </c>
-      <c r="C270" t="s">
-        <v>790</v>
       </c>
       <c r="D270">
         <v>370</v>
       </c>
       <c r="E270" t="s">
+        <v>790</v>
+      </c>
+      <c r="F270" t="s">
         <v>791</v>
-      </c>
-      <c r="F270" t="s">
-        <v>792</v>
       </c>
       <c r="G270" t="s">
         <v>15</v>
@@ -11793,39 +11765,39 @@
         <v>44228</v>
       </c>
       <c r="J270" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B271" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C271" t="s">
+        <v>793</v>
+      </c>
+      <c r="D271" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="D271" s="3" t="s">
+      <c r="E271" t="s">
         <v>795</v>
       </c>
-      <c r="E271" t="s">
-        <v>796</v>
-      </c>
       <c r="F271" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G271" t="s">
         <v>176</v>
       </c>
       <c r="H271" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="I271" s="2">
         <v>44197</v>
       </c>
       <c r="J271" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
@@ -11836,13 +11808,13 @@
         <v>145</v>
       </c>
       <c r="C272" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D272">
         <v>356</v>
       </c>
       <c r="E272" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="F272" t="s">
         <v>43</v>
@@ -11857,7 +11829,7 @@
         <v>44097</v>
       </c>
       <c r="J272" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
@@ -11868,16 +11840,16 @@
         <v>89</v>
       </c>
       <c r="C273" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D273">
         <v>349</v>
       </c>
       <c r="E273" t="s">
+        <v>799</v>
+      </c>
+      <c r="F273" t="s">
         <v>800</v>
-      </c>
-      <c r="F273" t="s">
-        <v>801</v>
       </c>
       <c r="G273" t="s">
         <v>15</v>
@@ -11889,7 +11861,7 @@
         <v>43985</v>
       </c>
       <c r="J273" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
@@ -11900,13 +11872,13 @@
         <v>178</v>
       </c>
       <c r="C274" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D274">
         <v>343</v>
       </c>
       <c r="E274" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F274" t="s">
         <v>99</v>
@@ -11921,7 +11893,7 @@
         <v>43888</v>
       </c>
       <c r="J274" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
@@ -11932,16 +11904,16 @@
         <v>137</v>
       </c>
       <c r="C275" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D275">
         <v>329</v>
       </c>
       <c r="E275" t="s">
+        <v>804</v>
+      </c>
+      <c r="F275" t="s">
         <v>805</v>
-      </c>
-      <c r="F275" t="s">
-        <v>806</v>
       </c>
       <c r="G275" t="s">
         <v>15</v>
@@ -11953,7 +11925,7 @@
         <v>43682</v>
       </c>
       <c r="J275" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
@@ -11964,7 +11936,7 @@
         <v>53</v>
       </c>
       <c r="C276" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D276">
         <v>314</v>
@@ -11973,7 +11945,7 @@
         <v>52</v>
       </c>
       <c r="F276" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G276" t="s">
         <v>15</v>
@@ -11985,24 +11957,24 @@
         <v>43605</v>
       </c>
       <c r="J276" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>630</v>
+        <v>283</v>
       </c>
       <c r="B277" t="s">
-        <v>630</v>
+        <v>283</v>
       </c>
       <c r="C277" t="s">
+        <v>808</v>
+      </c>
+      <c r="D277">
+        <v>292</v>
+      </c>
+      <c r="E277" t="s">
         <v>809</v>
-      </c>
-      <c r="D277">
-        <v>627</v>
-      </c>
-      <c r="E277" t="s">
-        <v>343</v>
       </c>
       <c r="F277" t="s">
         <v>810</v>
@@ -12011,126 +11983,126 @@
         <v>15</v>
       </c>
       <c r="H277" t="s">
-        <v>811</v>
+        <v>763</v>
       </c>
       <c r="I277" s="2">
-        <v>43587</v>
+        <v>43556</v>
       </c>
       <c r="J277" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
+        <v>145</v>
+      </c>
+      <c r="B278" t="s">
+        <v>145</v>
+      </c>
+      <c r="C278" t="s">
+        <v>811</v>
+      </c>
+      <c r="D278">
         <v>283</v>
       </c>
-      <c r="B278" t="s">
-        <v>283</v>
-      </c>
-      <c r="C278" t="s">
-        <v>812</v>
-      </c>
-      <c r="D278">
-        <v>292</v>
-      </c>
       <c r="E278" t="s">
-        <v>813</v>
+        <v>607</v>
       </c>
       <c r="F278" t="s">
-        <v>814</v>
+        <v>457</v>
       </c>
       <c r="G278" t="s">
         <v>15</v>
       </c>
       <c r="H278" t="s">
-        <v>764</v>
+        <v>571</v>
       </c>
       <c r="I278" s="2">
-        <v>43556</v>
+        <v>43509</v>
       </c>
       <c r="J278" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>145</v>
+        <v>699</v>
       </c>
       <c r="B279" t="s">
-        <v>145</v>
+        <v>699</v>
       </c>
       <c r="C279" t="s">
+        <v>812</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="E279" t="s">
+        <v>17</v>
+      </c>
+      <c r="F279" t="s">
+        <v>814</v>
+      </c>
+      <c r="G279" t="s">
+        <v>21</v>
+      </c>
+      <c r="H279" t="s">
         <v>815</v>
       </c>
-      <c r="D279">
-        <v>283</v>
-      </c>
-      <c r="E279" t="s">
-        <v>607</v>
-      </c>
-      <c r="F279" t="s">
-        <v>457</v>
-      </c>
-      <c r="G279" t="s">
-        <v>15</v>
-      </c>
-      <c r="H279" t="s">
-        <v>571</v>
-      </c>
       <c r="I279" s="2">
-        <v>43509</v>
+        <v>43500</v>
       </c>
       <c r="J279" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>700</v>
+        <v>329</v>
       </c>
       <c r="B280" t="s">
-        <v>700</v>
+        <v>330</v>
       </c>
       <c r="C280" t="s">
         <v>816</v>
       </c>
-      <c r="D280" s="3" t="s">
+      <c r="D280">
+        <v>274</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+      <c r="F280" t="s">
         <v>817</v>
       </c>
-      <c r="E280" t="s">
-        <v>17</v>
-      </c>
-      <c r="F280" t="s">
+      <c r="G280" t="s">
+        <v>15</v>
+      </c>
+      <c r="H280" t="s">
         <v>818</v>
       </c>
-      <c r="G280" t="s">
-        <v>21</v>
-      </c>
-      <c r="H280" t="s">
-        <v>819</v>
-      </c>
       <c r="I280" s="2">
-        <v>43500</v>
+        <v>43416</v>
       </c>
       <c r="J280" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>329</v>
+        <v>578</v>
       </c>
       <c r="B281" t="s">
-        <v>330</v>
+        <v>35</v>
       </c>
       <c r="C281" t="s">
+        <v>819</v>
+      </c>
+      <c r="D281">
+        <v>272</v>
+      </c>
+      <c r="E281" t="s">
         <v>820</v>
-      </c>
-      <c r="D281">
-        <v>274</v>
-      </c>
-      <c r="E281" t="s">
-        <v>283</v>
       </c>
       <c r="F281" t="s">
         <v>821</v>
@@ -12139,173 +12111,173 @@
         <v>15</v>
       </c>
       <c r="H281" t="s">
-        <v>822</v>
+        <v>698</v>
       </c>
       <c r="I281" s="2">
         <v>43416</v>
       </c>
       <c r="J281" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>578</v>
+        <v>44</v>
       </c>
       <c r="B282" t="s">
         <v>35</v>
       </c>
       <c r="C282" t="s">
+        <v>822</v>
+      </c>
+      <c r="D282">
+        <v>261</v>
+      </c>
+      <c r="E282" t="s">
         <v>823</v>
       </c>
-      <c r="D282">
-        <v>272</v>
-      </c>
-      <c r="E282" t="s">
-        <v>824</v>
-      </c>
       <c r="F282" t="s">
-        <v>825</v>
+        <v>636</v>
       </c>
       <c r="G282" t="s">
         <v>15</v>
       </c>
       <c r="H282" t="s">
-        <v>699</v>
+        <v>47</v>
       </c>
       <c r="I282" s="2">
-        <v>43416</v>
+        <v>43313</v>
       </c>
       <c r="J282" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>44</v>
+        <v>792</v>
       </c>
       <c r="B283" t="s">
-        <v>35</v>
+        <v>824</v>
       </c>
       <c r="C283" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D283">
-        <v>261</v>
+        <v>409</v>
       </c>
       <c r="E283" t="s">
-        <v>827</v>
+        <v>173</v>
       </c>
       <c r="F283" t="s">
-        <v>636</v>
+        <v>413</v>
       </c>
       <c r="G283" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H283" t="s">
-        <v>47</v>
+        <v>177</v>
       </c>
       <c r="I283" s="2">
-        <v>43313</v>
+        <v>43243</v>
       </c>
       <c r="J283" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>793</v>
+        <v>283</v>
       </c>
       <c r="B284" t="s">
+        <v>283</v>
+      </c>
+      <c r="C284" t="s">
+        <v>826</v>
+      </c>
+      <c r="D284">
+        <v>244</v>
+      </c>
+      <c r="E284" t="s">
+        <v>827</v>
+      </c>
+      <c r="F284" t="s">
         <v>828</v>
       </c>
-      <c r="C284" t="s">
+      <c r="G284" t="s">
+        <v>15</v>
+      </c>
+      <c r="H284" t="s">
         <v>829</v>
       </c>
-      <c r="D284">
-        <v>409</v>
-      </c>
-      <c r="E284" t="s">
-        <v>173</v>
-      </c>
-      <c r="F284" t="s">
-        <v>413</v>
-      </c>
-      <c r="G284" t="s">
-        <v>176</v>
-      </c>
-      <c r="H284" t="s">
-        <v>177</v>
-      </c>
       <c r="I284" s="2">
-        <v>43243</v>
+        <v>43160</v>
       </c>
       <c r="J284" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="B285" t="s">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="C285" t="s">
         <v>830</v>
       </c>
       <c r="D285">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E285" t="s">
         <v>831</v>
       </c>
       <c r="F285" t="s">
-        <v>832</v>
+        <v>33</v>
       </c>
       <c r="G285" t="s">
         <v>15</v>
       </c>
       <c r="H285" t="s">
-        <v>833</v>
+        <v>47</v>
       </c>
       <c r="I285" s="2">
-        <v>43160</v>
+        <v>43028</v>
       </c>
       <c r="J285" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="B286" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="C286" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="D286">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="E286" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F286" t="s">
-        <v>33</v>
+        <v>805</v>
       </c>
       <c r="G286" t="s">
         <v>15</v>
       </c>
       <c r="H286" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="I286" s="2">
-        <v>43028</v>
+        <v>42751</v>
       </c>
       <c r="J286" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
@@ -12316,16 +12288,16 @@
         <v>137</v>
       </c>
       <c r="C287" t="s">
+        <v>834</v>
+      </c>
+      <c r="D287">
+        <v>208</v>
+      </c>
+      <c r="E287" t="s">
+        <v>835</v>
+      </c>
+      <c r="F287" t="s">
         <v>836</v>
-      </c>
-      <c r="D287">
-        <v>213</v>
-      </c>
-      <c r="E287" t="s">
-        <v>837</v>
-      </c>
-      <c r="F287" t="s">
-        <v>806</v>
       </c>
       <c r="G287" t="s">
         <v>15</v>
@@ -12334,170 +12306,106 @@
         <v>141</v>
       </c>
       <c r="I287" s="2">
-        <v>42751</v>
+        <v>42614</v>
       </c>
       <c r="J287" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="B288" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="C288" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D288">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="E288" t="s">
-        <v>839</v>
+        <v>209</v>
       </c>
       <c r="F288" t="s">
-        <v>840</v>
+        <v>268</v>
       </c>
       <c r="G288" t="s">
         <v>15</v>
       </c>
       <c r="H288" t="s">
-        <v>141</v>
+        <v>269</v>
       </c>
       <c r="I288" s="2">
-        <v>42614</v>
+        <v>42381</v>
       </c>
       <c r="J288" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>264</v>
+        <v>452</v>
       </c>
       <c r="B289" t="s">
-        <v>53</v>
+        <v>452</v>
       </c>
       <c r="C289" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D289">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E289" t="s">
-        <v>209</v>
+        <v>89</v>
       </c>
       <c r="F289" t="s">
-        <v>268</v>
+        <v>839</v>
       </c>
       <c r="G289" t="s">
         <v>15</v>
       </c>
       <c r="H289" t="s">
-        <v>269</v>
+        <v>840</v>
       </c>
       <c r="I289" s="2">
-        <v>42381</v>
+        <v>42248</v>
       </c>
       <c r="J289" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>452</v>
+        <v>168</v>
       </c>
       <c r="B290" t="s">
-        <v>452</v>
+        <v>168</v>
       </c>
       <c r="C290" t="s">
+        <v>841</v>
+      </c>
+      <c r="D290">
+        <v>131</v>
+      </c>
+      <c r="E290" t="s">
         <v>842</v>
       </c>
-      <c r="D290">
-        <v>169</v>
-      </c>
-      <c r="E290" t="s">
-        <v>89</v>
-      </c>
       <c r="F290" t="s">
-        <v>843</v>
+        <v>185</v>
       </c>
       <c r="G290" t="s">
         <v>15</v>
       </c>
       <c r="H290" t="s">
-        <v>844</v>
+        <v>172</v>
       </c>
       <c r="I290" s="2">
-        <v>42248</v>
+        <v>41255</v>
       </c>
       <c r="J290" s="2" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
-        <v>168</v>
-      </c>
-      <c r="B291" t="s">
-        <v>168</v>
-      </c>
-      <c r="C291" t="s">
-        <v>845</v>
-      </c>
-      <c r="D291">
-        <v>131</v>
-      </c>
-      <c r="E291" t="s">
-        <v>846</v>
-      </c>
-      <c r="F291" t="s">
-        <v>185</v>
-      </c>
-      <c r="G291" t="s">
-        <v>15</v>
-      </c>
-      <c r="H291" t="s">
-        <v>172</v>
-      </c>
-      <c r="I291" s="2">
-        <v>41255</v>
-      </c>
-      <c r="J291" s="2" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>346</v>
-      </c>
-      <c r="B292" t="s">
-        <v>346</v>
-      </c>
-      <c r="C292" t="s">
-        <v>847</v>
-      </c>
-      <c r="D292" s="3" t="s">
-        <v>848</v>
-      </c>
-      <c r="E292" t="s">
-        <v>652</v>
-      </c>
-      <c r="F292" t="s">
-        <v>849</v>
-      </c>
-      <c r="G292" t="s">
-        <v>15</v>
-      </c>
-      <c r="H292" t="s">
-        <v>850</v>
-      </c>
-      <c r="I292" s="2">
-        <v>37163</v>
-      </c>
-      <c r="J292" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
   </sheetData>
@@ -12529,42 +12437,42 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>858</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>859</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -12573,16 +12481,16 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="F2" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="G2" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="H2" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="I2" t="s">
         <v>332</v>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://desenvolvimentocartaodetodo-my.sharepoint.com/personal/peopleanalytics_cartaodetodos_com/Documents/People Analytics/PEPO 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="14_{2E15DFB4-E428-4DE4-88DA-4CA6BE165C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72443148-EC40-4C9A-B642-E69598456F49}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{5297D640-EF3A-4BE8-AE76-8A4BA3E07593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="859">
   <si>
     <t>Gestor Avaliador</t>
   </si>
@@ -2604,13 +2604,13 @@
     <t>REGIANE ANDRADE</t>
   </si>
   <si>
-    <t>regiane.andrade@cartãodetodos.com</t>
-  </si>
-  <si>
-    <t>E-mail gestor validador</t>
-  </si>
-  <si>
     <t>status_resposta</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>Protocolo</t>
   </si>
 </sst>
 </file>
@@ -2784,13 +2784,17 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:J290" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:J290" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:K290" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:K290" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I290">
     <sortCondition descending="1" ref="I1:I290"/>
   </sortState>
-  <tableColumns count="10">
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Gestor Validador"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID"/>
@@ -2800,7 +2804,8 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{924CDE42-02DE-4EFB-A383-D6819D596AFA}" name="E-mail gestor validador"/>
+    <tableColumn id="10" xr3:uid="{924CDE42-02DE-4EFB-A383-D6819D596AFA}" name="Protocolo"/>
+    <tableColumn id="11" xr3:uid="{0F25A13B-D846-4F05-8682-52D4DA6CB76A}" name="Observações"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3113,7 +3118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J290"/>
+  <dimension ref="A1:K290"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.88671875" bestFit="1" customWidth="1"/>
@@ -3126,9 +3131,10 @@
     <col min="8" max="8" width="38.6640625" customWidth="1"/>
     <col min="9" max="9" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="43.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3157,10 +3163,13 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3188,11 +3197,9 @@
       <c r="I2" s="2">
         <v>46053</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3220,11 +3227,9 @@
       <c r="I3" s="2">
         <v>46053</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -3252,11 +3257,9 @@
       <c r="I4" s="2">
         <v>46043</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3284,11 +3287,9 @@
       <c r="I5" s="2">
         <v>46041</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -3316,11 +3317,9 @@
       <c r="I6" s="2">
         <v>46027</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -3348,11 +3347,9 @@
       <c r="I7" s="2">
         <v>46027</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3380,11 +3377,9 @@
       <c r="I8" s="2">
         <v>46006</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -3412,11 +3407,9 @@
       <c r="I9" s="2">
         <v>46006</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -3444,11 +3437,9 @@
       <c r="I10" s="2">
         <v>46006</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -3476,11 +3467,9 @@
       <c r="I11" s="2">
         <v>46006</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -3508,11 +3497,9 @@
       <c r="I12" s="2">
         <v>45992</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -3540,11 +3527,9 @@
       <c r="I13" s="2">
         <v>45992</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -3572,11 +3557,9 @@
       <c r="I14" s="2">
         <v>45992</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -3604,11 +3587,9 @@
       <c r="I15" s="2">
         <v>45992</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -3636,9 +3617,7 @@
       <c r="I16" s="2">
         <v>45978</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -3668,9 +3647,7 @@
       <c r="I17" s="2">
         <v>45978</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -3700,9 +3677,7 @@
       <c r="I18" s="2">
         <v>45978</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -3732,9 +3707,7 @@
       <c r="I19" s="2">
         <v>45978</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -3764,9 +3737,7 @@
       <c r="I20" s="2">
         <v>45978</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -3796,9 +3767,7 @@
       <c r="I21" s="2">
         <v>45978</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -3828,9 +3797,7 @@
       <c r="I22" s="2">
         <v>45978</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -3860,9 +3827,7 @@
       <c r="I23" s="2">
         <v>45978</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -3892,9 +3857,7 @@
       <c r="I24" s="2">
         <v>45978</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -3924,9 +3887,7 @@
       <c r="I25" s="2">
         <v>45978</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -3956,9 +3917,7 @@
       <c r="I26" s="2">
         <v>45966</v>
       </c>
-      <c r="J26" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -3988,9 +3947,7 @@
       <c r="I27" s="2">
         <v>45964</v>
       </c>
-      <c r="J27" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -4020,9 +3977,7 @@
       <c r="I28" s="2">
         <v>45964</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -4052,9 +4007,7 @@
       <c r="I29" s="2">
         <v>45964</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -4084,9 +4037,7 @@
       <c r="I30" s="2">
         <v>45964</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -4116,9 +4067,7 @@
       <c r="I31" s="2">
         <v>45964</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J31" s="2"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -4148,9 +4097,7 @@
       <c r="I32" s="2">
         <v>45964</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -4180,9 +4127,7 @@
       <c r="I33" s="2">
         <v>45950</v>
       </c>
-      <c r="J33" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J33" s="2"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -4212,9 +4157,7 @@
       <c r="I34" s="2">
         <v>45950</v>
       </c>
-      <c r="J34" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -4244,9 +4187,7 @@
       <c r="I35" s="2">
         <v>45936</v>
       </c>
-      <c r="J35" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J35" s="2"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -4276,9 +4217,7 @@
       <c r="I36" s="2">
         <v>45936</v>
       </c>
-      <c r="J36" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J36" s="2"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -4308,9 +4247,7 @@
       <c r="I37" s="2">
         <v>45936</v>
       </c>
-      <c r="J37" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J37" s="2"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -4340,9 +4277,7 @@
       <c r="I38" s="2">
         <v>45936</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J38" s="2"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -4372,9 +4307,7 @@
       <c r="I39" s="2">
         <v>45936</v>
       </c>
-      <c r="J39" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J39" s="2"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -4404,9 +4337,7 @@
       <c r="I40" s="2">
         <v>45915</v>
       </c>
-      <c r="J40" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J40" s="2"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -4436,9 +4367,7 @@
       <c r="I41" s="2">
         <v>45915</v>
       </c>
-      <c r="J41" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J41" s="2"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -4468,9 +4397,7 @@
       <c r="I42" s="2">
         <v>45915</v>
       </c>
-      <c r="J42" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J42" s="2"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
@@ -4500,9 +4427,7 @@
       <c r="I43" s="2">
         <v>45915</v>
       </c>
-      <c r="J43" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J43" s="2"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -4532,9 +4457,7 @@
       <c r="I44" s="2">
         <v>45915</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J44" s="2"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -4564,9 +4487,7 @@
       <c r="I45" s="2">
         <v>45915</v>
       </c>
-      <c r="J45" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J45" s="2"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -4596,9 +4517,7 @@
       <c r="I46" s="2">
         <v>45901</v>
       </c>
-      <c r="J46" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J46" s="2"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -4628,9 +4547,7 @@
       <c r="I47" s="2">
         <v>45901</v>
       </c>
-      <c r="J47" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J47" s="2"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -4660,9 +4577,7 @@
       <c r="I48" s="2">
         <v>45887</v>
       </c>
-      <c r="J48" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J48" s="2"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -4692,9 +4607,7 @@
       <c r="I49" s="2">
         <v>45887</v>
       </c>
-      <c r="J49" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J49" s="2"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -4724,9 +4637,7 @@
       <c r="I50" s="2">
         <v>45887</v>
       </c>
-      <c r="J50" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J50" s="2"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -4756,9 +4667,7 @@
       <c r="I51" s="2">
         <v>45887</v>
       </c>
-      <c r="J51" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J51" s="2"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -4788,9 +4697,7 @@
       <c r="I52" s="2">
         <v>45887</v>
       </c>
-      <c r="J52" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J52" s="2"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -4820,9 +4727,7 @@
       <c r="I53" s="2">
         <v>45873</v>
       </c>
-      <c r="J53" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J53" s="2"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -4852,9 +4757,7 @@
       <c r="I54" s="2">
         <v>45873</v>
       </c>
-      <c r="J54" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J54" s="2"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
@@ -4884,9 +4787,7 @@
       <c r="I55" s="2">
         <v>45873</v>
       </c>
-      <c r="J55" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J55" s="2"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -4916,9 +4817,7 @@
       <c r="I56" s="2">
         <v>45873</v>
       </c>
-      <c r="J56" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J56" s="2"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -4948,9 +4847,7 @@
       <c r="I57" s="2">
         <v>45873</v>
       </c>
-      <c r="J57" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J57" s="2"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -4980,9 +4877,7 @@
       <c r="I58" s="2">
         <v>45873</v>
       </c>
-      <c r="J58" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J58" s="2"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -5012,9 +4907,7 @@
       <c r="I59" s="2">
         <v>45873</v>
       </c>
-      <c r="J59" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J59" s="2"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -5044,9 +4937,7 @@
       <c r="I60" s="2">
         <v>45873</v>
       </c>
-      <c r="J60" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J60" s="2"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -5076,9 +4967,7 @@
       <c r="I61" s="2">
         <v>45873</v>
       </c>
-      <c r="J61" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J61" s="2"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -5108,9 +4997,7 @@
       <c r="I62" s="2">
         <v>45861</v>
       </c>
-      <c r="J62" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J62" s="2"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -5140,9 +5027,7 @@
       <c r="I63" s="2">
         <v>45852</v>
       </c>
-      <c r="J63" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J63" s="2"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -5172,9 +5057,7 @@
       <c r="I64" s="2">
         <v>45852</v>
       </c>
-      <c r="J64" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J64" s="2"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -5204,9 +5087,7 @@
       <c r="I65" s="2">
         <v>45845</v>
       </c>
-      <c r="J65" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J65" s="2"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -5236,9 +5117,7 @@
       <c r="I66" s="2">
         <v>45845</v>
       </c>
-      <c r="J66" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J66" s="2"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -5268,9 +5147,7 @@
       <c r="I67" s="2">
         <v>45839</v>
       </c>
-      <c r="J67" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J67" s="2"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -5300,9 +5177,7 @@
       <c r="I68" s="2">
         <v>45824</v>
       </c>
-      <c r="J68" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J68" s="2"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -5332,9 +5207,7 @@
       <c r="I69" s="2">
         <v>45824</v>
       </c>
-      <c r="J69" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J69" s="2"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -5364,9 +5237,7 @@
       <c r="I70" s="2">
         <v>45824</v>
       </c>
-      <c r="J70" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J70" s="2"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -5396,9 +5267,7 @@
       <c r="I71" s="2">
         <v>45824</v>
       </c>
-      <c r="J71" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J71" s="2"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -5428,9 +5297,7 @@
       <c r="I72" s="2">
         <v>45817</v>
       </c>
-      <c r="J72" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J72" s="2"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -5460,9 +5327,7 @@
       <c r="I73" s="2">
         <v>45810</v>
       </c>
-      <c r="J73" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J73" s="2"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -5492,9 +5357,7 @@
       <c r="I74" s="2">
         <v>45810</v>
       </c>
-      <c r="J74" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J74" s="2"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -5524,9 +5387,7 @@
       <c r="I75" s="2">
         <v>45810</v>
       </c>
-      <c r="J75" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J75" s="2"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -5556,9 +5417,7 @@
       <c r="I76" s="2">
         <v>45810</v>
       </c>
-      <c r="J76" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J76" s="2"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -5588,9 +5447,7 @@
       <c r="I77" s="2">
         <v>45810</v>
       </c>
-      <c r="J77" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J77" s="2"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -5620,9 +5477,7 @@
       <c r="I78" s="2">
         <v>45796</v>
       </c>
-      <c r="J78" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J78" s="2"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
@@ -5652,9 +5507,7 @@
       <c r="I79" s="2">
         <v>45789</v>
       </c>
-      <c r="J79" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J79" s="2"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -5684,9 +5537,7 @@
       <c r="I80" s="2">
         <v>45789</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J80" s="2"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -5716,9 +5567,7 @@
       <c r="I81" s="2">
         <v>45789</v>
       </c>
-      <c r="J81" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J81" s="2"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
@@ -5748,9 +5597,7 @@
       <c r="I82" s="2">
         <v>45789</v>
       </c>
-      <c r="J82" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J82" s="2"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
@@ -5780,9 +5627,7 @@
       <c r="I83" s="2">
         <v>45782</v>
       </c>
-      <c r="J83" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J83" s="2"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -5812,9 +5657,7 @@
       <c r="I84" s="2">
         <v>45782</v>
       </c>
-      <c r="J84" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J84" s="2"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
@@ -5844,9 +5687,7 @@
       <c r="I85" s="2">
         <v>45782</v>
       </c>
-      <c r="J85" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J85" s="2"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -5876,9 +5717,7 @@
       <c r="I86" s="2">
         <v>45782</v>
       </c>
-      <c r="J86" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J86" s="2"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
@@ -5908,9 +5747,7 @@
       <c r="I87" s="2">
         <v>45782</v>
       </c>
-      <c r="J87" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J87" s="2"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -5940,9 +5777,7 @@
       <c r="I88" s="2">
         <v>45761</v>
       </c>
-      <c r="J88" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J88" s="2"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -5972,9 +5807,7 @@
       <c r="I89" s="2">
         <v>45761</v>
       </c>
-      <c r="J89" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J89" s="2"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -6004,9 +5837,7 @@
       <c r="I90" s="2">
         <v>45761</v>
       </c>
-      <c r="J90" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J90" s="2"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
@@ -6036,9 +5867,7 @@
       <c r="I91" s="2">
         <v>45761</v>
       </c>
-      <c r="J91" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J91" s="2"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
@@ -6068,9 +5897,7 @@
       <c r="I92" s="2">
         <v>45761</v>
       </c>
-      <c r="J92" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J92" s="2"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
@@ -6100,9 +5927,7 @@
       <c r="I93" s="2">
         <v>45761</v>
       </c>
-      <c r="J93" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J93" s="2"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
@@ -6132,9 +5957,7 @@
       <c r="I94" s="2">
         <v>45761</v>
       </c>
-      <c r="J94" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J94" s="2"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
@@ -6164,9 +5987,7 @@
       <c r="I95" s="2">
         <v>45761</v>
       </c>
-      <c r="J95" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J95" s="2"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -6196,9 +6017,7 @@
       <c r="I96" s="2">
         <v>45761</v>
       </c>
-      <c r="J96" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J96" s="2"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
@@ -6228,9 +6047,7 @@
       <c r="I97" s="2">
         <v>45761</v>
       </c>
-      <c r="J97" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J97" s="2"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -6260,9 +6077,7 @@
       <c r="I98" s="2">
         <v>45761</v>
       </c>
-      <c r="J98" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J98" s="2"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
@@ -6292,9 +6107,7 @@
       <c r="I99" s="2">
         <v>45758</v>
       </c>
-      <c r="J99" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J99" s="2"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -6324,9 +6137,7 @@
       <c r="I100" s="2">
         <v>45757</v>
       </c>
-      <c r="J100" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J100" s="2"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
@@ -6356,9 +6167,7 @@
       <c r="I101" s="2">
         <v>45754</v>
       </c>
-      <c r="J101" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J101" s="2"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -6388,9 +6197,7 @@
       <c r="I102" s="2">
         <v>45733</v>
       </c>
-      <c r="J102" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J102" s="2"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
@@ -6420,9 +6227,7 @@
       <c r="I103" s="2">
         <v>45722</v>
       </c>
-      <c r="J103" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J103" s="2"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -6452,9 +6257,7 @@
       <c r="I104" s="2">
         <v>45722</v>
       </c>
-      <c r="J104" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J104" s="2"/>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -6484,9 +6287,7 @@
       <c r="I105" s="2">
         <v>45722</v>
       </c>
-      <c r="J105" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J105" s="2"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -6516,9 +6317,7 @@
       <c r="I106" s="2">
         <v>45722</v>
       </c>
-      <c r="J106" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J106" s="2"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
@@ -6548,9 +6347,7 @@
       <c r="I107" s="2">
         <v>45722</v>
       </c>
-      <c r="J107" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J107" s="2"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -6580,9 +6377,7 @@
       <c r="I108" s="2">
         <v>45722</v>
       </c>
-      <c r="J108" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J108" s="2"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -6612,9 +6407,7 @@
       <c r="I109" s="2">
         <v>45722</v>
       </c>
-      <c r="J109" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J109" s="2"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -6644,9 +6437,7 @@
       <c r="I110" s="2">
         <v>45722</v>
       </c>
-      <c r="J110" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J110" s="2"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
@@ -6676,9 +6467,7 @@
       <c r="I111" s="2">
         <v>45721</v>
       </c>
-      <c r="J111" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J111" s="2"/>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -6708,9 +6497,7 @@
       <c r="I112" s="2">
         <v>45705</v>
       </c>
-      <c r="J112" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J112" s="2"/>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -6740,9 +6527,7 @@
       <c r="I113" s="2">
         <v>45705</v>
       </c>
-      <c r="J113" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J113" s="2"/>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
@@ -6772,9 +6557,7 @@
       <c r="I114" s="2">
         <v>45705</v>
       </c>
-      <c r="J114" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J114" s="2"/>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
@@ -6804,9 +6587,7 @@
       <c r="I115" s="2">
         <v>45705</v>
       </c>
-      <c r="J115" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J115" s="2"/>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
@@ -6836,9 +6617,7 @@
       <c r="I116" s="2">
         <v>45705</v>
       </c>
-      <c r="J116" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J116" s="2"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
@@ -6868,9 +6647,7 @@
       <c r="I117" s="2">
         <v>45705</v>
       </c>
-      <c r="J117" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J117" s="2"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
@@ -6900,9 +6677,7 @@
       <c r="I118" s="2">
         <v>45705</v>
       </c>
-      <c r="J118" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J118" s="2"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
@@ -6932,9 +6707,7 @@
       <c r="I119" s="2">
         <v>45705</v>
       </c>
-      <c r="J119" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J119" s="2"/>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
@@ -6964,9 +6737,7 @@
       <c r="I120" s="2">
         <v>45691</v>
       </c>
-      <c r="J120" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J120" s="2"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
@@ -6996,9 +6767,7 @@
       <c r="I121" s="2">
         <v>45691</v>
       </c>
-      <c r="J121" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J121" s="2"/>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
@@ -7028,9 +6797,7 @@
       <c r="I122" s="2">
         <v>45691</v>
       </c>
-      <c r="J122" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J122" s="2"/>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
@@ -7060,9 +6827,7 @@
       <c r="I123" s="2">
         <v>45691</v>
       </c>
-      <c r="J123" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J123" s="2"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
@@ -7092,9 +6857,7 @@
       <c r="I124" s="2">
         <v>45691</v>
       </c>
-      <c r="J124" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J124" s="2"/>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
@@ -7124,9 +6887,7 @@
       <c r="I125" s="2">
         <v>45691</v>
       </c>
-      <c r="J125" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J125" s="2"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
@@ -7156,9 +6917,7 @@
       <c r="I126" s="2">
         <v>45690</v>
       </c>
-      <c r="J126" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J126" s="2"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
@@ -7188,9 +6947,7 @@
       <c r="I127" s="2">
         <v>45684</v>
       </c>
-      <c r="J127" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J127" s="2"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -7220,9 +6977,7 @@
       <c r="I128" s="2">
         <v>45684</v>
       </c>
-      <c r="J128" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J128" s="2"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
@@ -7252,9 +7007,7 @@
       <c r="I129" s="2">
         <v>45680</v>
       </c>
-      <c r="J129" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J129" s="2"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
@@ -7284,9 +7037,7 @@
       <c r="I130" s="2">
         <v>45677</v>
       </c>
-      <c r="J130" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J130" s="2"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
@@ -7316,9 +7067,7 @@
       <c r="I131" s="2">
         <v>45677</v>
       </c>
-      <c r="J131" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J131" s="2"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
@@ -7348,9 +7097,7 @@
       <c r="I132" s="2">
         <v>45663</v>
       </c>
-      <c r="J132" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J132" s="2"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
@@ -7380,9 +7127,7 @@
       <c r="I133" s="2">
         <v>45659</v>
       </c>
-      <c r="J133" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J133" s="2"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
@@ -7412,9 +7157,7 @@
       <c r="I134" s="2">
         <v>45642</v>
       </c>
-      <c r="J134" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J134" s="2"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
@@ -7444,9 +7187,7 @@
       <c r="I135" s="2">
         <v>45628</v>
       </c>
-      <c r="J135" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J135" s="2"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
@@ -7476,9 +7217,7 @@
       <c r="I136" s="2">
         <v>45628</v>
       </c>
-      <c r="J136" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J136" s="2"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
@@ -7508,9 +7247,7 @@
       <c r="I137" s="2">
         <v>45628</v>
       </c>
-      <c r="J137" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J137" s="2"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
@@ -7540,9 +7277,7 @@
       <c r="I138" s="2">
         <v>45628</v>
       </c>
-      <c r="J138" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J138" s="2"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
@@ -7572,9 +7307,7 @@
       <c r="I139" s="2">
         <v>45614</v>
       </c>
-      <c r="J139" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J139" s="2"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
@@ -7604,9 +7337,7 @@
       <c r="I140" s="2">
         <v>45614</v>
       </c>
-      <c r="J140" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J140" s="2"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
@@ -7636,9 +7367,7 @@
       <c r="I141" s="2">
         <v>45600</v>
       </c>
-      <c r="J141" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J141" s="2"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
@@ -7668,9 +7397,7 @@
       <c r="I142" s="2">
         <v>45600</v>
       </c>
-      <c r="J142" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J142" s="2"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
@@ -7700,9 +7427,7 @@
       <c r="I143" s="2">
         <v>45600</v>
       </c>
-      <c r="J143" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J143" s="2"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
@@ -7732,9 +7457,7 @@
       <c r="I144" s="2">
         <v>45600</v>
       </c>
-      <c r="J144" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J144" s="2"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
@@ -7764,9 +7487,7 @@
       <c r="I145" s="2">
         <v>45600</v>
       </c>
-      <c r="J145" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J145" s="2"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
@@ -7796,9 +7517,7 @@
       <c r="I146" s="2">
         <v>45586</v>
       </c>
-      <c r="J146" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J146" s="2"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
@@ -7828,9 +7547,7 @@
       <c r="I147" s="2">
         <v>45580</v>
       </c>
-      <c r="J147" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J147" s="2"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
@@ -7860,9 +7577,7 @@
       <c r="I148" s="2">
         <v>45566</v>
       </c>
-      <c r="J148" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J148" s="2"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
@@ -7892,9 +7607,7 @@
       <c r="I149" s="2">
         <v>45566</v>
       </c>
-      <c r="J149" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J149" s="2"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
@@ -7924,9 +7637,7 @@
       <c r="I150" s="2">
         <v>45566</v>
       </c>
-      <c r="J150" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J150" s="2"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
@@ -7956,9 +7667,7 @@
       <c r="I151" s="2">
         <v>45566</v>
       </c>
-      <c r="J151" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J151" s="2"/>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
@@ -7988,9 +7697,7 @@
       <c r="I152" s="2">
         <v>45564</v>
       </c>
-      <c r="J152" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J152" s="2"/>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
@@ -8020,9 +7727,7 @@
       <c r="I153" s="2">
         <v>45551</v>
       </c>
-      <c r="J153" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J153" s="2"/>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
@@ -8052,9 +7757,7 @@
       <c r="I154" s="2">
         <v>45551</v>
       </c>
-      <c r="J154" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J154" s="2"/>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
@@ -8084,9 +7787,7 @@
       <c r="I155" s="2">
         <v>45545</v>
       </c>
-      <c r="J155" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J155" s="2"/>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
@@ -8116,9 +7817,7 @@
       <c r="I156" s="2">
         <v>45537</v>
       </c>
-      <c r="J156" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J156" s="2"/>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
@@ -8148,9 +7847,7 @@
       <c r="I157" s="2">
         <v>45520</v>
       </c>
-      <c r="J157" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J157" s="2"/>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
@@ -8180,9 +7877,7 @@
       <c r="I158" s="2">
         <v>45520</v>
       </c>
-      <c r="J158" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J158" s="2"/>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
@@ -8212,9 +7907,7 @@
       <c r="I159" s="2">
         <v>45520</v>
       </c>
-      <c r="J159" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J159" s="2"/>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
@@ -8244,9 +7937,7 @@
       <c r="I160" s="2">
         <v>45516</v>
       </c>
-      <c r="J160" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J160" s="2"/>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
@@ -8276,9 +7967,7 @@
       <c r="I161" s="2">
         <v>45505</v>
       </c>
-      <c r="J161" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J161" s="2"/>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
@@ -8308,9 +7997,7 @@
       <c r="I162" s="2">
         <v>45505</v>
       </c>
-      <c r="J162" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J162" s="2"/>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
@@ -8340,9 +8027,7 @@
       <c r="I163" s="2">
         <v>45488</v>
       </c>
-      <c r="J163" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J163" s="2"/>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
@@ -8372,9 +8057,7 @@
       <c r="I164" s="2">
         <v>45481</v>
       </c>
-      <c r="J164" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J164" s="2"/>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
@@ -8404,9 +8087,7 @@
       <c r="I165" s="2">
         <v>45474</v>
       </c>
-      <c r="J165" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J165" s="2"/>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
@@ -8436,9 +8117,7 @@
       <c r="I166" s="2">
         <v>45474</v>
       </c>
-      <c r="J166" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J166" s="2"/>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
@@ -8468,9 +8147,7 @@
       <c r="I167" s="2">
         <v>45460</v>
       </c>
-      <c r="J167" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J167" s="2"/>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
@@ -8500,9 +8177,7 @@
       <c r="I168" s="2">
         <v>45460</v>
       </c>
-      <c r="J168" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J168" s="2"/>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
@@ -8532,9 +8207,7 @@
       <c r="I169" s="2">
         <v>45460</v>
       </c>
-      <c r="J169" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J169" s="2"/>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
@@ -8564,9 +8237,7 @@
       <c r="I170" s="2">
         <v>45453</v>
       </c>
-      <c r="J170" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J170" s="2"/>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
@@ -8596,9 +8267,7 @@
       <c r="I171" s="2">
         <v>45446</v>
       </c>
-      <c r="J171" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J171" s="2"/>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
@@ -8628,9 +8297,7 @@
       <c r="I172" s="2">
         <v>45446</v>
       </c>
-      <c r="J172" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J172" s="2"/>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
@@ -8660,9 +8327,7 @@
       <c r="I173" s="2">
         <v>45446</v>
       </c>
-      <c r="J173" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J173" s="2"/>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
@@ -8692,9 +8357,7 @@
       <c r="I174" s="2">
         <v>45446</v>
       </c>
-      <c r="J174" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J174" s="2"/>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
@@ -8724,9 +8387,7 @@
       <c r="I175" s="2">
         <v>45439</v>
       </c>
-      <c r="J175" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J175" s="2"/>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
@@ -8756,9 +8417,7 @@
       <c r="I176" s="2">
         <v>45414</v>
       </c>
-      <c r="J176" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J176" s="2"/>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
@@ -8788,9 +8447,7 @@
       <c r="I177" s="2">
         <v>45390</v>
       </c>
-      <c r="J177" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J177" s="2"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
@@ -8820,9 +8477,7 @@
       <c r="I178" s="2">
         <v>45386</v>
       </c>
-      <c r="J178" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J178" s="2"/>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
@@ -8852,9 +8507,7 @@
       <c r="I179" s="2">
         <v>45383</v>
       </c>
-      <c r="J179" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J179" s="2"/>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
@@ -8884,9 +8537,7 @@
       <c r="I180" s="2">
         <v>45366</v>
       </c>
-      <c r="J180" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J180" s="2"/>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
@@ -8916,9 +8567,7 @@
       <c r="I181" s="2">
         <v>45357</v>
       </c>
-      <c r="J181" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J181" s="2"/>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
@@ -8948,9 +8597,7 @@
       <c r="I182" s="2">
         <v>45357</v>
       </c>
-      <c r="J182" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J182" s="2"/>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
@@ -8980,9 +8627,7 @@
       <c r="I183" s="2">
         <v>45355</v>
       </c>
-      <c r="J183" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J183" s="2"/>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
@@ -9012,9 +8657,7 @@
       <c r="I184" s="2">
         <v>45337</v>
       </c>
-      <c r="J184" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J184" s="2"/>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
@@ -9044,9 +8687,7 @@
       <c r="I185" s="2">
         <v>45323</v>
       </c>
-      <c r="J185" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J185" s="2"/>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
@@ -9076,9 +8717,7 @@
       <c r="I186" s="2">
         <v>45323</v>
       </c>
-      <c r="J186" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J186" s="2"/>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
@@ -9108,9 +8747,7 @@
       <c r="I187" s="2">
         <v>45313</v>
       </c>
-      <c r="J187" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J187" s="2"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
@@ -9140,9 +8777,7 @@
       <c r="I188" s="2">
         <v>45306</v>
       </c>
-      <c r="J188" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J188" s="2"/>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
@@ -9172,9 +8807,7 @@
       <c r="I189" s="2">
         <v>45306</v>
       </c>
-      <c r="J189" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J189" s="2"/>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
@@ -9204,9 +8837,7 @@
       <c r="I190" s="2">
         <v>45275</v>
       </c>
-      <c r="J190" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J190" s="2"/>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
@@ -9236,9 +8867,7 @@
       <c r="I191" s="2">
         <v>45275</v>
       </c>
-      <c r="J191" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J191" s="2"/>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
@@ -9268,9 +8897,7 @@
       <c r="I192" s="2">
         <v>45275</v>
       </c>
-      <c r="J192" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J192" s="2"/>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
@@ -9300,9 +8927,7 @@
       <c r="I193" s="2">
         <v>45275</v>
       </c>
-      <c r="J193" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J193" s="2"/>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
@@ -9332,9 +8957,7 @@
       <c r="I194" s="2">
         <v>45244</v>
       </c>
-      <c r="J194" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J194" s="2"/>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
@@ -9364,9 +8987,7 @@
       <c r="I195" s="2">
         <v>45233</v>
       </c>
-      <c r="J195" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J195" s="2"/>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
@@ -9396,9 +9017,7 @@
       <c r="I196" s="2">
         <v>45219</v>
       </c>
-      <c r="J196" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J196" s="2"/>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
@@ -9428,9 +9047,7 @@
       <c r="I197" s="2">
         <v>45215</v>
       </c>
-      <c r="J197" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J197" s="2"/>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
@@ -9460,9 +9077,7 @@
       <c r="I198" s="2">
         <v>45201</v>
       </c>
-      <c r="J198" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J198" s="2"/>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
@@ -9492,9 +9107,7 @@
       <c r="I199" s="2">
         <v>45194</v>
       </c>
-      <c r="J199" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J199" s="2"/>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
@@ -9524,9 +9137,7 @@
       <c r="I200" s="2">
         <v>45170</v>
       </c>
-      <c r="J200" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J200" s="2"/>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
@@ -9556,9 +9167,7 @@
       <c r="I201" s="2">
         <v>45170</v>
       </c>
-      <c r="J201" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J201" s="2"/>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
@@ -9588,9 +9197,7 @@
       <c r="I202" s="2">
         <v>45170</v>
       </c>
-      <c r="J202" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J202" s="2"/>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
@@ -9620,9 +9227,7 @@
       <c r="I203" s="2">
         <v>45154</v>
       </c>
-      <c r="J203" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J203" s="2"/>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
@@ -9652,9 +9257,7 @@
       <c r="I204" s="2">
         <v>45154</v>
       </c>
-      <c r="J204" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J204" s="2"/>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
@@ -9684,9 +9287,7 @@
       <c r="I205" s="2">
         <v>45152</v>
       </c>
-      <c r="J205" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J205" s="2"/>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
@@ -9716,9 +9317,7 @@
       <c r="I206" s="2">
         <v>45117</v>
       </c>
-      <c r="J206" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J206" s="2"/>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
@@ -9748,9 +9347,7 @@
       <c r="I207" s="2">
         <v>45110</v>
       </c>
-      <c r="J207" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J207" s="2"/>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
@@ -9780,9 +9377,7 @@
       <c r="I208" s="2">
         <v>45098</v>
       </c>
-      <c r="J208" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J208" s="2"/>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
@@ -9812,9 +9407,7 @@
       <c r="I209" s="2">
         <v>45089</v>
       </c>
-      <c r="J209" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J209" s="2"/>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
@@ -9844,9 +9437,7 @@
       <c r="I210" s="2">
         <v>45082</v>
       </c>
-      <c r="J210" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J210" s="2"/>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
@@ -9876,9 +9467,7 @@
       <c r="I211" s="2">
         <v>45082</v>
       </c>
-      <c r="J211" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J211" s="2"/>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
@@ -9908,9 +9497,7 @@
       <c r="I212" s="2">
         <v>45068</v>
       </c>
-      <c r="J212" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J212" s="2"/>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
@@ -9940,9 +9527,7 @@
       <c r="I213" s="2">
         <v>45063</v>
       </c>
-      <c r="J213" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J213" s="2"/>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
@@ -9972,9 +9557,7 @@
       <c r="I214" s="2">
         <v>45061</v>
       </c>
-      <c r="J214" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J214" s="2"/>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
@@ -10004,9 +9587,7 @@
       <c r="I215" s="2">
         <v>45041</v>
       </c>
-      <c r="J215" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J215" s="2"/>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
@@ -10036,9 +9617,7 @@
       <c r="I216" s="2">
         <v>45041</v>
       </c>
-      <c r="J216" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J216" s="2"/>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
@@ -10068,9 +9647,7 @@
       <c r="I217" s="2">
         <v>45019</v>
       </c>
-      <c r="J217" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J217" s="2"/>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
@@ -10100,9 +9677,7 @@
       <c r="I218" s="2">
         <v>44979</v>
       </c>
-      <c r="J218" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J218" s="2"/>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
@@ -10132,9 +9707,7 @@
       <c r="I219" s="2">
         <v>44958</v>
       </c>
-      <c r="J219" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J219" s="2"/>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
@@ -10164,9 +9737,7 @@
       <c r="I220" s="2">
         <v>44958</v>
       </c>
-      <c r="J220" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J220" s="2"/>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
@@ -10196,9 +9767,7 @@
       <c r="I221" s="2">
         <v>44958</v>
       </c>
-      <c r="J221" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J221" s="2"/>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
@@ -10228,9 +9797,7 @@
       <c r="I222" s="2">
         <v>44951</v>
       </c>
-      <c r="J222" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J222" s="2"/>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
@@ -10260,9 +9827,7 @@
       <c r="I223" s="2">
         <v>44949</v>
       </c>
-      <c r="J223" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J223" s="2"/>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
@@ -10292,9 +9857,7 @@
       <c r="I224" s="2">
         <v>44921</v>
       </c>
-      <c r="J224" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J224" s="2"/>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
@@ -10324,9 +9887,7 @@
       <c r="I225" s="2">
         <v>44921</v>
       </c>
-      <c r="J225" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J225" s="2"/>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
@@ -10356,9 +9917,7 @@
       <c r="I226" s="2">
         <v>44909</v>
       </c>
-      <c r="J226" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J226" s="2"/>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
@@ -10388,9 +9947,7 @@
       <c r="I227" s="2">
         <v>44909</v>
       </c>
-      <c r="J227" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J227" s="2"/>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
@@ -10420,9 +9977,7 @@
       <c r="I228" s="2">
         <v>44907</v>
       </c>
-      <c r="J228" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J228" s="2"/>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
@@ -10452,9 +10007,7 @@
       <c r="I229" s="2">
         <v>44902</v>
       </c>
-      <c r="J229" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J229" s="2"/>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
@@ -10484,9 +10037,7 @@
       <c r="I230" s="2">
         <v>44900</v>
       </c>
-      <c r="J230" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J230" s="2"/>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
@@ -10516,9 +10067,7 @@
       <c r="I231" s="2">
         <v>44900</v>
       </c>
-      <c r="J231" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J231" s="2"/>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
@@ -10548,9 +10097,7 @@
       <c r="I232" s="2">
         <v>44894</v>
       </c>
-      <c r="J232" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J232" s="2"/>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
@@ -10580,9 +10127,7 @@
       <c r="I233" s="2">
         <v>44874</v>
       </c>
-      <c r="J233" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J233" s="2"/>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
@@ -10612,9 +10157,7 @@
       <c r="I234" s="2">
         <v>44874</v>
       </c>
-      <c r="J234" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J234" s="2"/>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
@@ -10644,9 +10187,7 @@
       <c r="I235" s="2">
         <v>44866</v>
       </c>
-      <c r="J235" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J235" s="2"/>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
@@ -10676,9 +10217,7 @@
       <c r="I236" s="2">
         <v>44851</v>
       </c>
-      <c r="J236" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J236" s="2"/>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
@@ -10708,9 +10247,7 @@
       <c r="I237" s="2">
         <v>44840</v>
       </c>
-      <c r="J237" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J237" s="2"/>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
@@ -10740,9 +10277,7 @@
       <c r="I238" s="2">
         <v>44830</v>
       </c>
-      <c r="J238" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J238" s="2"/>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
@@ -10772,9 +10307,7 @@
       <c r="I239" s="2">
         <v>44823</v>
       </c>
-      <c r="J239" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J239" s="2"/>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
@@ -10804,9 +10337,7 @@
       <c r="I240" s="2">
         <v>44774</v>
       </c>
-      <c r="J240" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J240" s="2"/>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
@@ -10836,9 +10367,7 @@
       <c r="I241" s="2">
         <v>44746</v>
       </c>
-      <c r="J241" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J241" s="2"/>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
@@ -10868,9 +10397,7 @@
       <c r="I242" s="2">
         <v>44720</v>
       </c>
-      <c r="J242" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J242" s="2"/>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
@@ -10900,9 +10427,7 @@
       <c r="I243" s="2">
         <v>44718</v>
       </c>
-      <c r="J243" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J243" s="2"/>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
@@ -10932,9 +10457,7 @@
       <c r="I244" s="2">
         <v>44714</v>
       </c>
-      <c r="J244" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J244" s="2"/>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
@@ -10964,9 +10487,7 @@
       <c r="I245" s="2">
         <v>44713</v>
       </c>
-      <c r="J245" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J245" s="2"/>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
@@ -10996,9 +10517,7 @@
       <c r="I246" s="2">
         <v>44692</v>
       </c>
-      <c r="J246" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J246" s="2"/>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
@@ -11028,9 +10547,7 @@
       <c r="I247" s="2">
         <v>44690</v>
       </c>
-      <c r="J247" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J247" s="2"/>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
@@ -11060,9 +10577,7 @@
       <c r="I248" s="2">
         <v>44671</v>
       </c>
-      <c r="J248" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J248" s="2"/>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
@@ -11092,9 +10607,7 @@
       <c r="I249" s="2">
         <v>44652</v>
       </c>
-      <c r="J249" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J249" s="2"/>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
@@ -11124,9 +10637,7 @@
       <c r="I250" s="2">
         <v>44641</v>
       </c>
-      <c r="J250" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J250" s="2"/>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
@@ -11156,9 +10667,7 @@
       <c r="I251" s="2">
         <v>44630</v>
       </c>
-      <c r="J251" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J251" s="2"/>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
@@ -11188,9 +10697,7 @@
       <c r="I252" s="2">
         <v>44573</v>
       </c>
-      <c r="J252" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J252" s="2"/>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
@@ -11220,9 +10727,7 @@
       <c r="I253" s="2">
         <v>44562</v>
       </c>
-      <c r="J253" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J253" s="2"/>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
@@ -11252,9 +10757,7 @@
       <c r="I254" s="2">
         <v>44550</v>
       </c>
-      <c r="J254" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J254" s="2"/>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
@@ -11284,9 +10787,7 @@
       <c r="I255" s="2">
         <v>44546</v>
       </c>
-      <c r="J255" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J255" s="2"/>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
@@ -11316,9 +10817,7 @@
       <c r="I256" s="2">
         <v>44543</v>
       </c>
-      <c r="J256" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J256" s="2"/>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
@@ -11348,9 +10847,7 @@
       <c r="I257" s="2">
         <v>44531</v>
       </c>
-      <c r="J257" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J257" s="2"/>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
@@ -11380,9 +10877,7 @@
       <c r="I258" s="2">
         <v>44522</v>
       </c>
-      <c r="J258" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J258" s="2"/>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
@@ -11412,9 +10907,7 @@
       <c r="I259" s="2">
         <v>44522</v>
       </c>
-      <c r="J259" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J259" s="2"/>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
@@ -11444,9 +10937,7 @@
       <c r="I260" s="2">
         <v>44501</v>
       </c>
-      <c r="J260" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J260" s="2"/>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
@@ -11476,9 +10967,7 @@
       <c r="I261" s="2">
         <v>44494</v>
       </c>
-      <c r="J261" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J261" s="2"/>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
@@ -11508,9 +10997,7 @@
       <c r="I262" s="2">
         <v>44482</v>
       </c>
-      <c r="J262" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J262" s="2"/>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
@@ -11540,9 +11027,7 @@
       <c r="I263" s="2">
         <v>44470</v>
       </c>
-      <c r="J263" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J263" s="2"/>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
@@ -11572,9 +11057,7 @@
       <c r="I264" s="2">
         <v>44391</v>
       </c>
-      <c r="J264" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J264" s="2"/>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
@@ -11604,9 +11087,7 @@
       <c r="I265" s="2">
         <v>44348</v>
       </c>
-      <c r="J265" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J265" s="2"/>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
@@ -11636,9 +11117,7 @@
       <c r="I266" s="2">
         <v>44342</v>
       </c>
-      <c r="J266" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J266" s="2"/>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
@@ -11668,9 +11147,7 @@
       <c r="I267" s="2">
         <v>44292</v>
       </c>
-      <c r="J267" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J267" s="2"/>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
@@ -11700,9 +11177,7 @@
       <c r="I268" s="2">
         <v>44259</v>
       </c>
-      <c r="J268" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J268" s="2"/>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
@@ -11732,9 +11207,7 @@
       <c r="I269" s="2">
         <v>44249</v>
       </c>
-      <c r="J269" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J269" s="2"/>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
@@ -11764,9 +11237,7 @@
       <c r="I270" s="2">
         <v>44228</v>
       </c>
-      <c r="J270" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J270" s="2"/>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
@@ -11796,9 +11267,7 @@
       <c r="I271" s="2">
         <v>44197</v>
       </c>
-      <c r="J271" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J271" s="2"/>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
@@ -11828,9 +11297,7 @@
       <c r="I272" s="2">
         <v>44097</v>
       </c>
-      <c r="J272" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J272" s="2"/>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
@@ -11860,9 +11327,7 @@
       <c r="I273" s="2">
         <v>43985</v>
       </c>
-      <c r="J273" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J273" s="2"/>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
@@ -11892,9 +11357,7 @@
       <c r="I274" s="2">
         <v>43888</v>
       </c>
-      <c r="J274" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J274" s="2"/>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
@@ -11924,9 +11387,7 @@
       <c r="I275" s="2">
         <v>43682</v>
       </c>
-      <c r="J275" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J275" s="2"/>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
@@ -11956,9 +11417,7 @@
       <c r="I276" s="2">
         <v>43605</v>
       </c>
-      <c r="J276" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J276" s="2"/>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
@@ -11988,9 +11447,7 @@
       <c r="I277" s="2">
         <v>43556</v>
       </c>
-      <c r="J277" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J277" s="2"/>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
@@ -12020,9 +11477,7 @@
       <c r="I278" s="2">
         <v>43509</v>
       </c>
-      <c r="J278" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J278" s="2"/>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
@@ -12052,9 +11507,7 @@
       <c r="I279" s="2">
         <v>43500</v>
       </c>
-      <c r="J279" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J279" s="2"/>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
@@ -12084,9 +11537,7 @@
       <c r="I280" s="2">
         <v>43416</v>
       </c>
-      <c r="J280" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J280" s="2"/>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
@@ -12116,9 +11567,7 @@
       <c r="I281" s="2">
         <v>43416</v>
       </c>
-      <c r="J281" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J281" s="2"/>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
@@ -12148,9 +11597,7 @@
       <c r="I282" s="2">
         <v>43313</v>
       </c>
-      <c r="J282" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J282" s="2"/>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
@@ -12180,9 +11627,7 @@
       <c r="I283" s="2">
         <v>43243</v>
       </c>
-      <c r="J283" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J283" s="2"/>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
@@ -12212,9 +11657,7 @@
       <c r="I284" s="2">
         <v>43160</v>
       </c>
-      <c r="J284" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J284" s="2"/>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
@@ -12244,9 +11687,7 @@
       <c r="I285" s="2">
         <v>43028</v>
       </c>
-      <c r="J285" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J285" s="2"/>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
@@ -12276,9 +11717,7 @@
       <c r="I286" s="2">
         <v>42751</v>
       </c>
-      <c r="J286" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J286" s="2"/>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
@@ -12308,9 +11747,7 @@
       <c r="I287" s="2">
         <v>42614</v>
       </c>
-      <c r="J287" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J287" s="2"/>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
@@ -12340,9 +11777,7 @@
       <c r="I288" s="2">
         <v>42381</v>
       </c>
-      <c r="J288" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J288" s="2"/>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
@@ -12372,9 +11807,7 @@
       <c r="I289" s="2">
         <v>42248</v>
       </c>
-      <c r="J289" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J289" s="2"/>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
@@ -12404,9 +11837,7 @@
       <c r="I290" s="2">
         <v>41255</v>
       </c>
-      <c r="J290" s="2" t="s">
-        <v>856</v>
-      </c>
+      <c r="J290" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12467,7 +11898,7 @@
         <v>851</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://desenvolvimentocartaodetodo-my.sharepoint.com/personal/peopleanalytics_cartaodetodos_com/Documents/People Analytics/PEPO 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{5297D640-EF3A-4BE8-AE76-8A4BA3E07593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{4F7E38C3-6FF0-4DC8-A1E1-78678A6B8F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2689,13 +2689,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2705,6 +2708,30 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
@@ -2747,30 +2774,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2789,12 +2792,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:K290" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:K290" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:I290" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:I290" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I290">
     <sortCondition descending="1" ref="I1:I290"/>
   </sortState>
-  <tableColumns count="11">
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Gestor Validador"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID"/>
@@ -2803,18 +2806,16 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{924CDE42-02DE-4EFB-A383-D6819D596AFA}" name="Protocolo"/>
-    <tableColumn id="11" xr3:uid="{0F25A13B-D846-4F05-8682-52D4DA6CB76A}" name="Observações"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:K2" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:K2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:M2" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:M2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{CFF5932B-854B-4B23-A01A-04BA6982E294}" name="Momento do Envio"/>
     <tableColumn id="2" xr3:uid="{9A82702E-3CB5-486A-B49B-3CBF2D1B5744}" name="Nome do Gestor"/>
     <tableColumn id="3" xr3:uid="{15330415-ADF2-4758-8694-FD7A376B81D4}" name="Funcionário Avaliado"/>
@@ -2826,6 +2827,8 @@
     <tableColumn id="9" xr3:uid="{D960B0AB-147E-49C9-81F6-3A62815C92D5}" name="Par 1"/>
     <tableColumn id="10" xr3:uid="{A24B24E4-1150-4A03-93C9-672C68A1D0C8}" name="Par 2"/>
     <tableColumn id="11" xr3:uid="{5AFF58B5-A998-4A5A-9F0A-A92C2CDE82B2}" name="status_resposta"/>
+    <tableColumn id="12" xr3:uid="{93A8C8D4-8B56-4C9E-9D53-37FF16CC480B}" name="Protocolo"/>
+    <tableColumn id="13" xr3:uid="{C8075C3A-27CB-4059-81B8-8246047B429D}" name="Observações"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3118,7 +3121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K290"/>
+  <dimension ref="A1:I290"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.88671875" bestFit="1" customWidth="1"/>
@@ -3130,11 +3133,9 @@
     <col min="7" max="7" width="26.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="38.6640625" customWidth="1"/>
     <col min="9" max="9" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="43.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3162,14 +3163,8 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3197,9 +3192,8 @@
       <c r="I2" s="2">
         <v>46053</v>
       </c>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3227,9 +3221,8 @@
       <c r="I3" s="2">
         <v>46053</v>
       </c>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -3257,9 +3250,8 @@
       <c r="I4" s="2">
         <v>46043</v>
       </c>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3287,9 +3279,8 @@
       <c r="I5" s="2">
         <v>46041</v>
       </c>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -3317,9 +3308,8 @@
       <c r="I6" s="2">
         <v>46027</v>
       </c>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -3347,9 +3337,8 @@
       <c r="I7" s="2">
         <v>46027</v>
       </c>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3377,9 +3366,8 @@
       <c r="I8" s="2">
         <v>46006</v>
       </c>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -3407,9 +3395,8 @@
       <c r="I9" s="2">
         <v>46006</v>
       </c>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -3437,9 +3424,8 @@
       <c r="I10" s="2">
         <v>46006</v>
       </c>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -3467,9 +3453,8 @@
       <c r="I11" s="2">
         <v>46006</v>
       </c>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -3497,9 +3482,8 @@
       <c r="I12" s="2">
         <v>45992</v>
       </c>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -3527,9 +3511,8 @@
       <c r="I13" s="2">
         <v>45992</v>
       </c>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -3557,9 +3540,8 @@
       <c r="I14" s="2">
         <v>45992</v>
       </c>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -3587,9 +3569,8 @@
       <c r="I15" s="2">
         <v>45992</v>
       </c>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -3617,9 +3598,8 @@
       <c r="I16" s="2">
         <v>45978</v>
       </c>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -3647,9 +3627,8 @@
       <c r="I17" s="2">
         <v>45978</v>
       </c>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -3677,9 +3656,8 @@
       <c r="I18" s="2">
         <v>45978</v>
       </c>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -3707,9 +3685,8 @@
       <c r="I19" s="2">
         <v>45978</v>
       </c>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -3737,9 +3714,8 @@
       <c r="I20" s="2">
         <v>45978</v>
       </c>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>101</v>
       </c>
@@ -3767,9 +3743,8 @@
       <c r="I21" s="2">
         <v>45978</v>
       </c>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -3797,9 +3772,8 @@
       <c r="I22" s="2">
         <v>45978</v>
       </c>
-      <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -3827,9 +3801,8 @@
       <c r="I23" s="2">
         <v>45978</v>
       </c>
-      <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -3857,9 +3830,8 @@
       <c r="I24" s="2">
         <v>45978</v>
       </c>
-      <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>111</v>
       </c>
@@ -3887,9 +3859,8 @@
       <c r="I25" s="2">
         <v>45978</v>
       </c>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>96</v>
       </c>
@@ -3917,9 +3888,8 @@
       <c r="I26" s="2">
         <v>45966</v>
       </c>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -3947,9 +3917,8 @@
       <c r="I27" s="2">
         <v>45964</v>
       </c>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -3977,9 +3946,8 @@
       <c r="I28" s="2">
         <v>45964</v>
       </c>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -4007,9 +3975,8 @@
       <c r="I29" s="2">
         <v>45964</v>
       </c>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>129</v>
       </c>
@@ -4037,9 +4004,8 @@
       <c r="I30" s="2">
         <v>45964</v>
       </c>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -4067,9 +4033,8 @@
       <c r="I31" s="2">
         <v>45964</v>
       </c>
-      <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>137</v>
       </c>
@@ -4097,9 +4062,8 @@
       <c r="I32" s="2">
         <v>45964</v>
       </c>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>111</v>
       </c>
@@ -4127,9 +4091,8 @@
       <c r="I33" s="2">
         <v>45950</v>
       </c>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>144</v>
       </c>
@@ -4157,9 +4120,8 @@
       <c r="I34" s="2">
         <v>45950</v>
       </c>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -4187,9 +4149,8 @@
       <c r="I35" s="2">
         <v>45936</v>
       </c>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -4217,9 +4178,8 @@
       <c r="I36" s="2">
         <v>45936</v>
       </c>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>157</v>
       </c>
@@ -4247,9 +4207,8 @@
       <c r="I37" s="2">
         <v>45936</v>
       </c>
-      <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -4277,9 +4236,8 @@
       <c r="I38" s="2">
         <v>45936</v>
       </c>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>168</v>
       </c>
@@ -4307,9 +4265,8 @@
       <c r="I39" s="2">
         <v>45936</v>
       </c>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>173</v>
       </c>
@@ -4337,9 +4294,8 @@
       <c r="I40" s="2">
         <v>45915</v>
       </c>
-      <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>178</v>
       </c>
@@ -4367,9 +4323,8 @@
       <c r="I41" s="2">
         <v>45915</v>
       </c>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>182</v>
       </c>
@@ -4397,9 +4352,8 @@
       <c r="I42" s="2">
         <v>45915</v>
       </c>
-      <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>178</v>
       </c>
@@ -4427,9 +4381,8 @@
       <c r="I43" s="2">
         <v>45915</v>
       </c>
-      <c r="J43" s="2"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>111</v>
       </c>
@@ -4457,9 +4410,8 @@
       <c r="I44" s="2">
         <v>45915</v>
       </c>
-      <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>193</v>
       </c>
@@ -4487,9 +4439,8 @@
       <c r="I45" s="2">
         <v>45915</v>
       </c>
-      <c r="J45" s="2"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -4517,9 +4468,8 @@
       <c r="I46" s="2">
         <v>45901</v>
       </c>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>201</v>
       </c>
@@ -4547,9 +4497,8 @@
       <c r="I47" s="2">
         <v>45901</v>
       </c>
-      <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>206</v>
       </c>
@@ -4577,9 +4526,8 @@
       <c r="I48" s="2">
         <v>45887</v>
       </c>
-      <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>209</v>
       </c>
@@ -4607,9 +4555,8 @@
       <c r="I49" s="2">
         <v>45887</v>
       </c>
-      <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>137</v>
       </c>
@@ -4637,9 +4584,8 @@
       <c r="I50" s="2">
         <v>45887</v>
       </c>
-      <c r="J50" s="2"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>216</v>
       </c>
@@ -4667,9 +4613,8 @@
       <c r="I51" s="2">
         <v>45887</v>
       </c>
-      <c r="J51" s="2"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>221</v>
       </c>
@@ -4697,9 +4642,8 @@
       <c r="I52" s="2">
         <v>45887</v>
       </c>
-      <c r="J52" s="2"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>79</v>
       </c>
@@ -4727,9 +4671,8 @@
       <c r="I53" s="2">
         <v>45873</v>
       </c>
-      <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>201</v>
       </c>
@@ -4757,9 +4700,8 @@
       <c r="I54" s="2">
         <v>45873</v>
       </c>
-      <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>209</v>
       </c>
@@ -4787,9 +4729,8 @@
       <c r="I55" s="2">
         <v>45873</v>
       </c>
-      <c r="J55" s="2"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>35</v>
       </c>
@@ -4817,9 +4758,8 @@
       <c r="I56" s="2">
         <v>45873</v>
       </c>
-      <c r="J56" s="2"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>79</v>
       </c>
@@ -4847,9 +4787,8 @@
       <c r="I57" s="2">
         <v>45873</v>
       </c>
-      <c r="J57" s="2"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -4877,9 +4816,8 @@
       <c r="I58" s="2">
         <v>45873</v>
       </c>
-      <c r="J58" s="2"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>216</v>
       </c>
@@ -4907,9 +4845,8 @@
       <c r="I59" s="2">
         <v>45873</v>
       </c>
-      <c r="J59" s="2"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -4937,9 +4874,8 @@
       <c r="I60" s="2">
         <v>45873</v>
       </c>
-      <c r="J60" s="2"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>88</v>
       </c>
@@ -4967,9 +4903,8 @@
       <c r="I61" s="2">
         <v>45873</v>
       </c>
-      <c r="J61" s="2"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>131</v>
       </c>
@@ -4997,9 +4932,8 @@
       <c r="I62" s="2">
         <v>45861</v>
       </c>
-      <c r="J62" s="2"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -5027,9 +4961,8 @@
       <c r="I63" s="2">
         <v>45852</v>
       </c>
-      <c r="J63" s="2"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>79</v>
       </c>
@@ -5057,9 +4990,8 @@
       <c r="I64" s="2">
         <v>45852</v>
       </c>
-      <c r="J64" s="2"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -5087,9 +5019,8 @@
       <c r="I65" s="2">
         <v>45845</v>
       </c>
-      <c r="J65" s="2"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>62</v>
       </c>
@@ -5117,9 +5048,8 @@
       <c r="I66" s="2">
         <v>45845</v>
       </c>
-      <c r="J66" s="2"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>264</v>
       </c>
@@ -5147,9 +5077,8 @@
       <c r="I67" s="2">
         <v>45839</v>
       </c>
-      <c r="J67" s="2"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>173</v>
       </c>
@@ -5177,9 +5106,8 @@
       <c r="I68" s="2">
         <v>45824</v>
       </c>
-      <c r="J68" s="2"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -5207,9 +5135,8 @@
       <c r="I69" s="2">
         <v>45824</v>
       </c>
-      <c r="J69" s="2"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>63</v>
       </c>
@@ -5237,9 +5164,8 @@
       <c r="I70" s="2">
         <v>45824</v>
       </c>
-      <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>216</v>
       </c>
@@ -5267,9 +5193,8 @@
       <c r="I71" s="2">
         <v>45824</v>
       </c>
-      <c r="J71" s="2"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>279</v>
       </c>
@@ -5297,9 +5222,8 @@
       <c r="I72" s="2">
         <v>45817</v>
       </c>
-      <c r="J72" s="2"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>283</v>
       </c>
@@ -5327,9 +5251,8 @@
       <c r="I73" s="2">
         <v>45810</v>
       </c>
-      <c r="J73" s="2"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>52</v>
       </c>
@@ -5357,9 +5280,8 @@
       <c r="I74" s="2">
         <v>45810</v>
       </c>
-      <c r="J74" s="2"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>23</v>
       </c>
@@ -5387,9 +5309,8 @@
       <c r="I75" s="2">
         <v>45810</v>
       </c>
-      <c r="J75" s="2"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>279</v>
       </c>
@@ -5417,9 +5338,8 @@
       <c r="I76" s="2">
         <v>45810</v>
       </c>
-      <c r="J76" s="2"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>62</v>
       </c>
@@ -5447,9 +5367,8 @@
       <c r="I77" s="2">
         <v>45810</v>
       </c>
-      <c r="J77" s="2"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>63</v>
       </c>
@@ -5477,9 +5396,8 @@
       <c r="I78" s="2">
         <v>45796</v>
       </c>
-      <c r="J78" s="2"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -5507,9 +5425,8 @@
       <c r="I79" s="2">
         <v>45789</v>
       </c>
-      <c r="J79" s="2"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>306</v>
       </c>
@@ -5537,9 +5454,8 @@
       <c r="I80" s="2">
         <v>45789</v>
       </c>
-      <c r="J80" s="2"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>131</v>
       </c>
@@ -5567,9 +5483,8 @@
       <c r="I81" s="2">
         <v>45789</v>
       </c>
-      <c r="J81" s="2"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>283</v>
       </c>
@@ -5597,9 +5512,8 @@
       <c r="I82" s="2">
         <v>45789</v>
       </c>
-      <c r="J82" s="2"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>96</v>
       </c>
@@ -5627,9 +5541,8 @@
       <c r="I83" s="2">
         <v>45782</v>
       </c>
-      <c r="J83" s="2"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>96</v>
       </c>
@@ -5657,9 +5570,8 @@
       <c r="I84" s="2">
         <v>45782</v>
       </c>
-      <c r="J84" s="2"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>74</v>
       </c>
@@ -5687,9 +5599,8 @@
       <c r="I85" s="2">
         <v>45782</v>
       </c>
-      <c r="J85" s="2"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>122</v>
       </c>
@@ -5717,9 +5628,8 @@
       <c r="I86" s="2">
         <v>45782</v>
       </c>
-      <c r="J86" s="2"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -5747,9 +5657,8 @@
       <c r="I87" s="2">
         <v>45782</v>
       </c>
-      <c r="J87" s="2"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>329</v>
       </c>
@@ -5777,9 +5686,8 @@
       <c r="I88" s="2">
         <v>45761</v>
       </c>
-      <c r="J88" s="2"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -5807,9 +5715,8 @@
       <c r="I89" s="2">
         <v>45761</v>
       </c>
-      <c r="J89" s="2"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>206</v>
       </c>
@@ -5837,9 +5744,8 @@
       <c r="I90" s="2">
         <v>45761</v>
       </c>
-      <c r="J90" s="2"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>122</v>
       </c>
@@ -5867,9 +5773,8 @@
       <c r="I91" s="2">
         <v>45761</v>
       </c>
-      <c r="J91" s="2"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>329</v>
       </c>
@@ -5897,9 +5802,8 @@
       <c r="I92" s="2">
         <v>45761</v>
       </c>
-      <c r="J92" s="2"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>343</v>
       </c>
@@ -5927,9 +5831,8 @@
       <c r="I93" s="2">
         <v>45761</v>
       </c>
-      <c r="J93" s="2"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>79</v>
       </c>
@@ -5957,9 +5860,8 @@
       <c r="I94" s="2">
         <v>45761</v>
       </c>
-      <c r="J94" s="2"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>329</v>
       </c>
@@ -5987,9 +5889,8 @@
       <c r="I95" s="2">
         <v>45761</v>
       </c>
-      <c r="J95" s="2"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>329</v>
       </c>
@@ -6017,9 +5918,8 @@
       <c r="I96" s="2">
         <v>45761</v>
       </c>
-      <c r="J96" s="2"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>329</v>
       </c>
@@ -6047,9 +5947,8 @@
       <c r="I97" s="2">
         <v>45761</v>
       </c>
-      <c r="J97" s="2"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>283</v>
       </c>
@@ -6077,9 +5976,8 @@
       <c r="I98" s="2">
         <v>45761</v>
       </c>
-      <c r="J98" s="2"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>358</v>
       </c>
@@ -6107,9 +6005,8 @@
       <c r="I99" s="2">
         <v>45758</v>
       </c>
-      <c r="J99" s="2"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -6137,9 +6034,8 @@
       <c r="I100" s="2">
         <v>45757</v>
       </c>
-      <c r="J100" s="2"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>201</v>
       </c>
@@ -6167,9 +6063,8 @@
       <c r="I101" s="2">
         <v>45754</v>
       </c>
-      <c r="J101" s="2"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>202</v>
       </c>
@@ -6197,9 +6092,8 @@
       <c r="I102" s="2">
         <v>45733</v>
       </c>
-      <c r="J102" s="2"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>96</v>
       </c>
@@ -6227,9 +6121,8 @@
       <c r="I103" s="2">
         <v>45722</v>
       </c>
-      <c r="J103" s="2"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>168</v>
       </c>
@@ -6257,9 +6150,8 @@
       <c r="I104" s="2">
         <v>45722</v>
       </c>
-      <c r="J104" s="2"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>96</v>
       </c>
@@ -6287,9 +6179,8 @@
       <c r="I105" s="2">
         <v>45722</v>
       </c>
-      <c r="J105" s="2"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>79</v>
       </c>
@@ -6317,9 +6208,8 @@
       <c r="I106" s="2">
         <v>45722</v>
       </c>
-      <c r="J106" s="2"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>79</v>
       </c>
@@ -6347,9 +6237,8 @@
       <c r="I107" s="2">
         <v>45722</v>
       </c>
-      <c r="J107" s="2"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>383</v>
       </c>
@@ -6377,9 +6266,8 @@
       <c r="I108" s="2">
         <v>45722</v>
       </c>
-      <c r="J108" s="2"/>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -6407,9 +6295,8 @@
       <c r="I109" s="2">
         <v>45722</v>
       </c>
-      <c r="J109" s="2"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>35</v>
       </c>
@@ -6437,9 +6324,8 @@
       <c r="I110" s="2">
         <v>45722</v>
       </c>
-      <c r="J110" s="2"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>79</v>
       </c>
@@ -6467,9 +6353,8 @@
       <c r="I111" s="2">
         <v>45721</v>
       </c>
-      <c r="J111" s="2"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>96</v>
       </c>
@@ -6497,9 +6382,8 @@
       <c r="I112" s="2">
         <v>45705</v>
       </c>
-      <c r="J112" s="2"/>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>201</v>
       </c>
@@ -6527,9 +6411,8 @@
       <c r="I113" s="2">
         <v>45705</v>
       </c>
-      <c r="J113" s="2"/>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>197</v>
       </c>
@@ -6557,9 +6440,8 @@
       <c r="I114" s="2">
         <v>45705</v>
       </c>
-      <c r="J114" s="2"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>197</v>
       </c>
@@ -6587,9 +6469,8 @@
       <c r="I115" s="2">
         <v>45705</v>
       </c>
-      <c r="J115" s="2"/>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>383</v>
       </c>
@@ -6617,9 +6498,8 @@
       <c r="I116" s="2">
         <v>45705</v>
       </c>
-      <c r="J116" s="2"/>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>197</v>
       </c>
@@ -6647,9 +6527,8 @@
       <c r="I117" s="2">
         <v>45705</v>
       </c>
-      <c r="J117" s="2"/>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>383</v>
       </c>
@@ -6677,9 +6556,8 @@
       <c r="I118" s="2">
         <v>45705</v>
       </c>
-      <c r="J118" s="2"/>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>111</v>
       </c>
@@ -6707,9 +6585,8 @@
       <c r="I119" s="2">
         <v>45705</v>
       </c>
-      <c r="J119" s="2"/>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>173</v>
       </c>
@@ -6737,9 +6614,8 @@
       <c r="I120" s="2">
         <v>45691</v>
       </c>
-      <c r="J120" s="2"/>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>411</v>
       </c>
@@ -6767,9 +6643,8 @@
       <c r="I121" s="2">
         <v>45691</v>
       </c>
-      <c r="J121" s="2"/>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>173</v>
       </c>
@@ -6797,9 +6672,8 @@
       <c r="I122" s="2">
         <v>45691</v>
       </c>
-      <c r="J122" s="2"/>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -6827,9 +6701,8 @@
       <c r="I123" s="2">
         <v>45691</v>
       </c>
-      <c r="J123" s="2"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>173</v>
       </c>
@@ -6857,9 +6730,8 @@
       <c r="I124" s="2">
         <v>45691</v>
       </c>
-      <c r="J124" s="2"/>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>173</v>
       </c>
@@ -6887,9 +6759,8 @@
       <c r="I125" s="2">
         <v>45691</v>
       </c>
-      <c r="J125" s="2"/>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>173</v>
       </c>
@@ -6917,9 +6788,8 @@
       <c r="I126" s="2">
         <v>45690</v>
       </c>
-      <c r="J126" s="2"/>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>283</v>
       </c>
@@ -6947,9 +6817,8 @@
       <c r="I127" s="2">
         <v>45684</v>
       </c>
-      <c r="J127" s="2"/>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>197</v>
       </c>
@@ -6977,9 +6846,8 @@
       <c r="I128" s="2">
         <v>45684</v>
       </c>
-      <c r="J128" s="2"/>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>197</v>
       </c>
@@ -7007,9 +6875,8 @@
       <c r="I129" s="2">
         <v>45680</v>
       </c>
-      <c r="J129" s="2"/>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>209</v>
       </c>
@@ -7037,9 +6904,8 @@
       <c r="I130" s="2">
         <v>45677</v>
       </c>
-      <c r="J130" s="2"/>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>17</v>
       </c>
@@ -7067,9 +6933,8 @@
       <c r="I131" s="2">
         <v>45677</v>
       </c>
-      <c r="J131" s="2"/>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>52</v>
       </c>
@@ -7097,9 +6962,8 @@
       <c r="I132" s="2">
         <v>45663</v>
       </c>
-      <c r="J132" s="2"/>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>343</v>
       </c>
@@ -7127,9 +6991,8 @@
       <c r="I133" s="2">
         <v>45659</v>
       </c>
-      <c r="J133" s="2"/>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>89</v>
       </c>
@@ -7157,9 +7020,8 @@
       <c r="I134" s="2">
         <v>45642</v>
       </c>
-      <c r="J134" s="2"/>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>44</v>
       </c>
@@ -7187,9 +7049,8 @@
       <c r="I135" s="2">
         <v>45628</v>
       </c>
-      <c r="J135" s="2"/>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>96</v>
       </c>
@@ -7217,9 +7078,8 @@
       <c r="I136" s="2">
         <v>45628</v>
       </c>
-      <c r="J136" s="2"/>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>96</v>
       </c>
@@ -7247,9 +7107,8 @@
       <c r="I137" s="2">
         <v>45628</v>
       </c>
-      <c r="J137" s="2"/>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>452</v>
       </c>
@@ -7277,9 +7136,8 @@
       <c r="I138" s="2">
         <v>45628</v>
       </c>
-      <c r="J138" s="2"/>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>182</v>
       </c>
@@ -7307,9 +7165,8 @@
       <c r="I139" s="2">
         <v>45614</v>
       </c>
-      <c r="J139" s="2"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>69</v>
       </c>
@@ -7337,9 +7194,8 @@
       <c r="I140" s="2">
         <v>45614</v>
       </c>
-      <c r="J140" s="2"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>96</v>
       </c>
@@ -7367,9 +7223,8 @@
       <c r="I141" s="2">
         <v>45600</v>
       </c>
-      <c r="J141" s="2"/>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>17</v>
       </c>
@@ -7397,9 +7252,8 @@
       <c r="I142" s="2">
         <v>45600</v>
       </c>
-      <c r="J142" s="2"/>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>306</v>
       </c>
@@ -7427,9 +7281,8 @@
       <c r="I143" s="2">
         <v>45600</v>
       </c>
-      <c r="J143" s="2"/>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>306</v>
       </c>
@@ -7457,9 +7310,8 @@
       <c r="I144" s="2">
         <v>45600</v>
       </c>
-      <c r="J144" s="2"/>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>472</v>
       </c>
@@ -7487,9 +7339,8 @@
       <c r="I145" s="2">
         <v>45600</v>
       </c>
-      <c r="J145" s="2"/>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>283</v>
       </c>
@@ -7517,9 +7368,8 @@
       <c r="I146" s="2">
         <v>45586</v>
       </c>
-      <c r="J146" s="2"/>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>131</v>
       </c>
@@ -7547,9 +7397,8 @@
       <c r="I147" s="2">
         <v>45580</v>
       </c>
-      <c r="J147" s="2"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>23</v>
       </c>
@@ -7577,9 +7426,8 @@
       <c r="I148" s="2">
         <v>45566</v>
       </c>
-      <c r="J148" s="2"/>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>96</v>
       </c>
@@ -7607,9 +7455,8 @@
       <c r="I149" s="2">
         <v>45566</v>
       </c>
-      <c r="J149" s="2"/>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>157</v>
       </c>
@@ -7637,9 +7484,8 @@
       <c r="I150" s="2">
         <v>45566</v>
       </c>
-      <c r="J150" s="2"/>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>96</v>
       </c>
@@ -7667,9 +7513,8 @@
       <c r="I151" s="2">
         <v>45566</v>
       </c>
-      <c r="J151" s="2"/>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>267</v>
       </c>
@@ -7697,9 +7542,8 @@
       <c r="I152" s="2">
         <v>45564</v>
       </c>
-      <c r="J152" s="2"/>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>206</v>
       </c>
@@ -7727,9 +7571,8 @@
       <c r="I153" s="2">
         <v>45551</v>
       </c>
-      <c r="J153" s="2"/>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>279</v>
       </c>
@@ -7757,9 +7600,8 @@
       <c r="I154" s="2">
         <v>45551</v>
       </c>
-      <c r="J154" s="2"/>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>302</v>
       </c>
@@ -7787,9 +7629,8 @@
       <c r="I155" s="2">
         <v>45545</v>
       </c>
-      <c r="J155" s="2"/>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>267</v>
       </c>
@@ -7817,9 +7658,8 @@
       <c r="I156" s="2">
         <v>45537</v>
       </c>
-      <c r="J156" s="2"/>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>44</v>
       </c>
@@ -7847,9 +7687,8 @@
       <c r="I157" s="2">
         <v>45520</v>
       </c>
-      <c r="J157" s="2"/>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>279</v>
       </c>
@@ -7877,9 +7716,8 @@
       <c r="I158" s="2">
         <v>45520</v>
       </c>
-      <c r="J158" s="2"/>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>96</v>
       </c>
@@ -7907,9 +7745,8 @@
       <c r="I159" s="2">
         <v>45520</v>
       </c>
-      <c r="J159" s="2"/>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>514</v>
       </c>
@@ -7937,9 +7774,8 @@
       <c r="I160" s="2">
         <v>45516</v>
       </c>
-      <c r="J160" s="2"/>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>209</v>
       </c>
@@ -7967,9 +7803,8 @@
       <c r="I161" s="2">
         <v>45505</v>
       </c>
-      <c r="J161" s="2"/>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>62</v>
       </c>
@@ -7997,9 +7832,8 @@
       <c r="I162" s="2">
         <v>45505</v>
       </c>
-      <c r="J162" s="2"/>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>173</v>
       </c>
@@ -8027,9 +7861,8 @@
       <c r="I163" s="2">
         <v>45488</v>
       </c>
-      <c r="J163" s="2"/>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>358</v>
       </c>
@@ -8057,9 +7890,8 @@
       <c r="I164" s="2">
         <v>45481</v>
       </c>
-      <c r="J164" s="2"/>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>267</v>
       </c>
@@ -8087,9 +7919,8 @@
       <c r="I165" s="2">
         <v>45474</v>
       </c>
-      <c r="J165" s="2"/>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>530</v>
       </c>
@@ -8117,9 +7948,8 @@
       <c r="I166" s="2">
         <v>45474</v>
       </c>
-      <c r="J166" s="2"/>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>96</v>
       </c>
@@ -8147,9 +7977,8 @@
       <c r="I167" s="2">
         <v>45460</v>
       </c>
-      <c r="J167" s="2"/>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>264</v>
       </c>
@@ -8177,9 +8006,8 @@
       <c r="I168" s="2">
         <v>45460</v>
       </c>
-      <c r="J168" s="2"/>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>206</v>
       </c>
@@ -8207,9 +8035,8 @@
       <c r="I169" s="2">
         <v>45460</v>
       </c>
-      <c r="J169" s="2"/>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>302</v>
       </c>
@@ -8237,9 +8064,8 @@
       <c r="I170" s="2">
         <v>45453</v>
       </c>
-      <c r="J170" s="2"/>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>96</v>
       </c>
@@ -8267,9 +8093,8 @@
       <c r="I171" s="2">
         <v>45446</v>
       </c>
-      <c r="J171" s="2"/>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>69</v>
       </c>
@@ -8297,9 +8122,8 @@
       <c r="I172" s="2">
         <v>45446</v>
       </c>
-      <c r="J172" s="2"/>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>209</v>
       </c>
@@ -8327,9 +8151,8 @@
       <c r="I173" s="2">
         <v>45446</v>
       </c>
-      <c r="J173" s="2"/>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>74</v>
       </c>
@@ -8357,9 +8180,8 @@
       <c r="I174" s="2">
         <v>45446</v>
       </c>
-      <c r="J174" s="2"/>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>69</v>
       </c>
@@ -8387,9 +8209,8 @@
       <c r="I175" s="2">
         <v>45439</v>
       </c>
-      <c r="J175" s="2"/>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -8417,9 +8238,8 @@
       <c r="I176" s="2">
         <v>45414</v>
       </c>
-      <c r="J176" s="2"/>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>149</v>
       </c>
@@ -8447,9 +8267,8 @@
       <c r="I177" s="2">
         <v>45390</v>
       </c>
-      <c r="J177" s="2"/>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>178</v>
       </c>
@@ -8477,9 +8296,8 @@
       <c r="I178" s="2">
         <v>45386</v>
       </c>
-      <c r="J178" s="2"/>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>17</v>
       </c>
@@ -8507,9 +8325,8 @@
       <c r="I179" s="2">
         <v>45383</v>
       </c>
-      <c r="J179" s="2"/>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>178</v>
       </c>
@@ -8537,9 +8354,8 @@
       <c r="I180" s="2">
         <v>45366</v>
       </c>
-      <c r="J180" s="2"/>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>96</v>
       </c>
@@ -8567,9 +8383,8 @@
       <c r="I181" s="2">
         <v>45357</v>
       </c>
-      <c r="J181" s="2"/>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>145</v>
       </c>
@@ -8597,9 +8412,8 @@
       <c r="I182" s="2">
         <v>45357</v>
       </c>
-      <c r="J182" s="2"/>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>182</v>
       </c>
@@ -8627,9 +8441,8 @@
       <c r="I183" s="2">
         <v>45355</v>
       </c>
-      <c r="J183" s="2"/>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>221</v>
       </c>
@@ -8657,9 +8470,8 @@
       <c r="I184" s="2">
         <v>45337</v>
       </c>
-      <c r="J184" s="2"/>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>74</v>
       </c>
@@ -8687,9 +8499,8 @@
       <c r="I185" s="2">
         <v>45323</v>
       </c>
-      <c r="J185" s="2"/>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>44</v>
       </c>
@@ -8717,9 +8528,8 @@
       <c r="I186" s="2">
         <v>45323</v>
       </c>
-      <c r="J186" s="2"/>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>79</v>
       </c>
@@ -8747,9 +8557,8 @@
       <c r="I187" s="2">
         <v>45313</v>
       </c>
-      <c r="J187" s="2"/>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>329</v>
       </c>
@@ -8777,9 +8586,8 @@
       <c r="I188" s="2">
         <v>45306</v>
       </c>
-      <c r="J188" s="2"/>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>149</v>
       </c>
@@ -8807,9 +8615,8 @@
       <c r="I189" s="2">
         <v>45306</v>
       </c>
-      <c r="J189" s="2"/>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>173</v>
       </c>
@@ -8837,9 +8644,8 @@
       <c r="I190" s="2">
         <v>45275</v>
       </c>
-      <c r="J190" s="2"/>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>52</v>
       </c>
@@ -8867,9 +8673,8 @@
       <c r="I191" s="2">
         <v>45275</v>
       </c>
-      <c r="J191" s="2"/>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>122</v>
       </c>
@@ -8897,9 +8702,8 @@
       <c r="I192" s="2">
         <v>45275</v>
       </c>
-      <c r="J192" s="2"/>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>530</v>
       </c>
@@ -8927,9 +8731,8 @@
       <c r="I193" s="2">
         <v>45275</v>
       </c>
-      <c r="J193" s="2"/>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -8957,9 +8760,8 @@
       <c r="I194" s="2">
         <v>45244</v>
       </c>
-      <c r="J194" s="2"/>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>197</v>
       </c>
@@ -8987,9 +8789,8 @@
       <c r="I195" s="2">
         <v>45233</v>
       </c>
-      <c r="J195" s="2"/>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>514</v>
       </c>
@@ -9017,9 +8818,8 @@
       <c r="I196" s="2">
         <v>45219</v>
       </c>
-      <c r="J196" s="2"/>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>173</v>
       </c>
@@ -9047,9 +8847,8 @@
       <c r="I197" s="2">
         <v>45215</v>
       </c>
-      <c r="J197" s="2"/>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>607</v>
       </c>
@@ -9077,9 +8876,8 @@
       <c r="I198" s="2">
         <v>45201</v>
       </c>
-      <c r="J198" s="2"/>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>607</v>
       </c>
@@ -9107,9 +8905,8 @@
       <c r="I199" s="2">
         <v>45194</v>
       </c>
-      <c r="J199" s="2"/>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>178</v>
       </c>
@@ -9137,9 +8934,8 @@
       <c r="I200" s="2">
         <v>45170</v>
       </c>
-      <c r="J200" s="2"/>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>209</v>
       </c>
@@ -9167,9 +8963,8 @@
       <c r="I201" s="2">
         <v>45170</v>
       </c>
-      <c r="J201" s="2"/>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>209</v>
       </c>
@@ -9197,9 +8992,8 @@
       <c r="I202" s="2">
         <v>45170</v>
       </c>
-      <c r="J202" s="2"/>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>96</v>
       </c>
@@ -9227,9 +9021,8 @@
       <c r="I203" s="2">
         <v>45154</v>
       </c>
-      <c r="J203" s="2"/>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>122</v>
       </c>
@@ -9257,9 +9050,8 @@
       <c r="I204" s="2">
         <v>45154</v>
       </c>
-      <c r="J204" s="2"/>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>178</v>
       </c>
@@ -9287,9 +9079,8 @@
       <c r="I205" s="2">
         <v>45152</v>
       </c>
-      <c r="J205" s="2"/>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>221</v>
       </c>
@@ -9317,9 +9108,8 @@
       <c r="I206" s="2">
         <v>45117</v>
       </c>
-      <c r="J206" s="2"/>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>343</v>
       </c>
@@ -9347,9 +9137,8 @@
       <c r="I207" s="2">
         <v>45110</v>
       </c>
-      <c r="J207" s="2"/>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>630</v>
       </c>
@@ -9377,9 +9166,8 @@
       <c r="I208" s="2">
         <v>45098</v>
       </c>
-      <c r="J208" s="2"/>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -9407,9 +9195,8 @@
       <c r="I209" s="2">
         <v>45089</v>
       </c>
-      <c r="J209" s="2"/>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>383</v>
       </c>
@@ -9437,9 +9224,8 @@
       <c r="I210" s="2">
         <v>45082</v>
       </c>
-      <c r="J210" s="2"/>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -9467,9 +9253,8 @@
       <c r="I211" s="2">
         <v>45082</v>
       </c>
-      <c r="J211" s="2"/>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>48</v>
       </c>
@@ -9497,9 +9282,8 @@
       <c r="I212" s="2">
         <v>45068</v>
       </c>
-      <c r="J212" s="2"/>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>157</v>
       </c>
@@ -9527,9 +9311,8 @@
       <c r="I213" s="2">
         <v>45063</v>
       </c>
-      <c r="J213" s="2"/>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>48</v>
       </c>
@@ -9557,9 +9340,8 @@
       <c r="I214" s="2">
         <v>45061</v>
       </c>
-      <c r="J214" s="2"/>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>178</v>
       </c>
@@ -9587,9 +9369,8 @@
       <c r="I215" s="2">
         <v>45041</v>
       </c>
-      <c r="J215" s="2"/>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>131</v>
       </c>
@@ -9617,9 +9398,8 @@
       <c r="I216" s="2">
         <v>45041</v>
       </c>
-      <c r="J216" s="2"/>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>145</v>
       </c>
@@ -9647,9 +9427,8 @@
       <c r="I217" s="2">
         <v>45019</v>
       </c>
-      <c r="J217" s="2"/>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>52</v>
       </c>
@@ -9677,9 +9456,8 @@
       <c r="I218" s="2">
         <v>44979</v>
       </c>
-      <c r="J218" s="2"/>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>283</v>
       </c>
@@ -9707,9 +9485,8 @@
       <c r="I219" s="2">
         <v>44958</v>
       </c>
-      <c r="J219" s="2"/>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>48</v>
       </c>
@@ -9737,9 +9514,8 @@
       <c r="I220" s="2">
         <v>44958</v>
       </c>
-      <c r="J220" s="2"/>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>206</v>
       </c>
@@ -9767,9 +9543,8 @@
       <c r="I221" s="2">
         <v>44958</v>
       </c>
-      <c r="J221" s="2"/>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>35</v>
       </c>
@@ -9797,9 +9572,8 @@
       <c r="I222" s="2">
         <v>44951</v>
       </c>
-      <c r="J222" s="2"/>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>69</v>
       </c>
@@ -9827,9 +9601,8 @@
       <c r="I223" s="2">
         <v>44949</v>
       </c>
-      <c r="J223" s="2"/>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>197</v>
       </c>
@@ -9857,9 +9630,8 @@
       <c r="I224" s="2">
         <v>44921</v>
       </c>
-      <c r="J224" s="2"/>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>383</v>
       </c>
@@ -9887,9 +9659,8 @@
       <c r="I225" s="2">
         <v>44921</v>
       </c>
-      <c r="J225" s="2"/>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>44</v>
       </c>
@@ -9917,9 +9688,8 @@
       <c r="I226" s="2">
         <v>44909</v>
       </c>
-      <c r="J226" s="2"/>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>88</v>
       </c>
@@ -9947,9 +9717,8 @@
       <c r="I227" s="2">
         <v>44909</v>
       </c>
-      <c r="J227" s="2"/>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>178</v>
       </c>
@@ -9977,9 +9746,8 @@
       <c r="I228" s="2">
         <v>44907</v>
       </c>
-      <c r="J228" s="2"/>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>48</v>
       </c>
@@ -10007,9 +9775,8 @@
       <c r="I229" s="2">
         <v>44902</v>
       </c>
-      <c r="J229" s="2"/>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>383</v>
       </c>
@@ -10037,9 +9804,8 @@
       <c r="I230" s="2">
         <v>44900</v>
       </c>
-      <c r="J230" s="2"/>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>48</v>
       </c>
@@ -10067,9 +9833,8 @@
       <c r="I231" s="2">
         <v>44900</v>
       </c>
-      <c r="J231" s="2"/>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>178</v>
       </c>
@@ -10097,9 +9862,8 @@
       <c r="I232" s="2">
         <v>44894</v>
       </c>
-      <c r="J232" s="2"/>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>182</v>
       </c>
@@ -10127,9 +9891,8 @@
       <c r="I233" s="2">
         <v>44874</v>
       </c>
-      <c r="J233" s="2"/>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>44</v>
       </c>
@@ -10157,9 +9920,8 @@
       <c r="I234" s="2">
         <v>44874</v>
       </c>
-      <c r="J234" s="2"/>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>472</v>
       </c>
@@ -10187,9 +9949,8 @@
       <c r="I235" s="2">
         <v>44866</v>
       </c>
-      <c r="J235" s="2"/>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>578</v>
       </c>
@@ -10217,9 +9978,8 @@
       <c r="I236" s="2">
         <v>44851</v>
       </c>
-      <c r="J236" s="2"/>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>699</v>
       </c>
@@ -10247,9 +10007,8 @@
       <c r="I237" s="2">
         <v>44840</v>
       </c>
-      <c r="J237" s="2"/>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>206</v>
       </c>
@@ -10277,9 +10036,8 @@
       <c r="I238" s="2">
         <v>44830</v>
       </c>
-      <c r="J238" s="2"/>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>472</v>
       </c>
@@ -10307,9 +10065,8 @@
       <c r="I239" s="2">
         <v>44823</v>
       </c>
-      <c r="J239" s="2"/>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>358</v>
       </c>
@@ -10337,9 +10094,8 @@
       <c r="I240" s="2">
         <v>44774</v>
       </c>
-      <c r="J240" s="2"/>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>197</v>
       </c>
@@ -10367,9 +10123,8 @@
       <c r="I241" s="2">
         <v>44746</v>
       </c>
-      <c r="J241" s="2"/>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>79</v>
       </c>
@@ -10397,9 +10152,8 @@
       <c r="I242" s="2">
         <v>44720</v>
       </c>
-      <c r="J242" s="2"/>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>688</v>
       </c>
@@ -10427,9 +10181,8 @@
       <c r="I243" s="2">
         <v>44718</v>
       </c>
-      <c r="J243" s="2"/>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>17</v>
       </c>
@@ -10457,9 +10210,8 @@
       <c r="I244" s="2">
         <v>44714</v>
       </c>
-      <c r="J244" s="2"/>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>88</v>
       </c>
@@ -10487,9 +10239,8 @@
       <c r="I245" s="2">
         <v>44713</v>
       </c>
-      <c r="J245" s="2"/>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>88</v>
       </c>
@@ -10517,9 +10268,8 @@
       <c r="I246" s="2">
         <v>44692</v>
       </c>
-      <c r="J246" s="2"/>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>63</v>
       </c>
@@ -10547,9 +10297,8 @@
       <c r="I247" s="2">
         <v>44690</v>
       </c>
-      <c r="J247" s="2"/>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>52</v>
       </c>
@@ -10577,9 +10326,8 @@
       <c r="I248" s="2">
         <v>44671</v>
       </c>
-      <c r="J248" s="2"/>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>302</v>
       </c>
@@ -10607,9 +10355,8 @@
       <c r="I249" s="2">
         <v>44652</v>
       </c>
-      <c r="J249" s="2"/>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>383</v>
       </c>
@@ -10637,9 +10384,8 @@
       <c r="I250" s="2">
         <v>44641</v>
       </c>
-      <c r="J250" s="2"/>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>144</v>
       </c>
@@ -10667,9 +10413,8 @@
       <c r="I251" s="2">
         <v>44630</v>
       </c>
-      <c r="J251" s="2"/>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>89</v>
       </c>
@@ -10697,9 +10442,8 @@
       <c r="I252" s="2">
         <v>44573</v>
       </c>
-      <c r="J252" s="2"/>
-    </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>48</v>
       </c>
@@ -10727,9 +10471,8 @@
       <c r="I253" s="2">
         <v>44562</v>
       </c>
-      <c r="J253" s="2"/>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>88</v>
       </c>
@@ -10757,9 +10500,8 @@
       <c r="I254" s="2">
         <v>44550</v>
       </c>
-      <c r="J254" s="2"/>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>131</v>
       </c>
@@ -10787,9 +10529,8 @@
       <c r="I255" s="2">
         <v>44546</v>
       </c>
-      <c r="J255" s="2"/>
-    </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>131</v>
       </c>
@@ -10817,9 +10558,8 @@
       <c r="I256" s="2">
         <v>44543</v>
       </c>
-      <c r="J256" s="2"/>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>182</v>
       </c>
@@ -10847,9 +10587,8 @@
       <c r="I257" s="2">
         <v>44531</v>
       </c>
-      <c r="J257" s="2"/>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>506</v>
       </c>
@@ -10877,9 +10616,8 @@
       <c r="I258" s="2">
         <v>44522</v>
       </c>
-      <c r="J258" s="2"/>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>283</v>
       </c>
@@ -10907,9 +10645,8 @@
       <c r="I259" s="2">
         <v>44522</v>
       </c>
-      <c r="J259" s="2"/>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>101</v>
       </c>
@@ -10937,9 +10674,8 @@
       <c r="I260" s="2">
         <v>44501</v>
       </c>
-      <c r="J260" s="2"/>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>17</v>
       </c>
@@ -10967,9 +10703,8 @@
       <c r="I261" s="2">
         <v>44494</v>
       </c>
-      <c r="J261" s="2"/>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>44</v>
       </c>
@@ -10997,9 +10732,8 @@
       <c r="I262" s="2">
         <v>44482</v>
       </c>
-      <c r="J262" s="2"/>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>630</v>
       </c>
@@ -11027,9 +10761,8 @@
       <c r="I263" s="2">
         <v>44470</v>
       </c>
-      <c r="J263" s="2"/>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>52</v>
       </c>
@@ -11057,9 +10790,8 @@
       <c r="I264" s="2">
         <v>44391</v>
       </c>
-      <c r="J264" s="2"/>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>283</v>
       </c>
@@ -11087,9 +10819,8 @@
       <c r="I265" s="2">
         <v>44348</v>
       </c>
-      <c r="J265" s="2"/>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>514</v>
       </c>
@@ -11117,9 +10848,8 @@
       <c r="I266" s="2">
         <v>44342</v>
       </c>
-      <c r="J266" s="2"/>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>206</v>
       </c>
@@ -11147,9 +10877,8 @@
       <c r="I267" s="2">
         <v>44292</v>
       </c>
-      <c r="J267" s="2"/>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>111</v>
       </c>
@@ -11177,9 +10906,8 @@
       <c r="I268" s="2">
         <v>44259</v>
       </c>
-      <c r="J268" s="2"/>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>206</v>
       </c>
@@ -11207,9 +10935,8 @@
       <c r="I269" s="2">
         <v>44249</v>
       </c>
-      <c r="J269" s="2"/>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>601</v>
       </c>
@@ -11237,9 +10964,8 @@
       <c r="I270" s="2">
         <v>44228</v>
       </c>
-      <c r="J270" s="2"/>
-    </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>699</v>
       </c>
@@ -11267,9 +10993,8 @@
       <c r="I271" s="2">
         <v>44197</v>
       </c>
-      <c r="J271" s="2"/>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>607</v>
       </c>
@@ -11297,9 +11022,8 @@
       <c r="I272" s="2">
         <v>44097</v>
       </c>
-      <c r="J272" s="2"/>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>88</v>
       </c>
@@ -11327,9 +11051,8 @@
       <c r="I273" s="2">
         <v>43985</v>
       </c>
-      <c r="J273" s="2"/>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>178</v>
       </c>
@@ -11357,9 +11080,8 @@
       <c r="I274" s="2">
         <v>43888</v>
       </c>
-      <c r="J274" s="2"/>
-    </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>137</v>
       </c>
@@ -11387,9 +11109,8 @@
       <c r="I275" s="2">
         <v>43682</v>
       </c>
-      <c r="J275" s="2"/>
-    </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>264</v>
       </c>
@@ -11417,9 +11138,8 @@
       <c r="I276" s="2">
         <v>43605</v>
       </c>
-      <c r="J276" s="2"/>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>283</v>
       </c>
@@ -11447,9 +11167,8 @@
       <c r="I277" s="2">
         <v>43556</v>
       </c>
-      <c r="J277" s="2"/>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>145</v>
       </c>
@@ -11477,9 +11196,8 @@
       <c r="I278" s="2">
         <v>43509</v>
       </c>
-      <c r="J278" s="2"/>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>699</v>
       </c>
@@ -11507,9 +11225,8 @@
       <c r="I279" s="2">
         <v>43500</v>
       </c>
-      <c r="J279" s="2"/>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>329</v>
       </c>
@@ -11537,9 +11254,8 @@
       <c r="I280" s="2">
         <v>43416</v>
       </c>
-      <c r="J280" s="2"/>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>578</v>
       </c>
@@ -11567,9 +11283,8 @@
       <c r="I281" s="2">
         <v>43416</v>
       </c>
-      <c r="J281" s="2"/>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>44</v>
       </c>
@@ -11597,9 +11312,8 @@
       <c r="I282" s="2">
         <v>43313</v>
       </c>
-      <c r="J282" s="2"/>
-    </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>792</v>
       </c>
@@ -11627,9 +11341,8 @@
       <c r="I283" s="2">
         <v>43243</v>
       </c>
-      <c r="J283" s="2"/>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>283</v>
       </c>
@@ -11657,9 +11370,8 @@
       <c r="I284" s="2">
         <v>43160</v>
       </c>
-      <c r="J284" s="2"/>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>178</v>
       </c>
@@ -11687,9 +11399,8 @@
       <c r="I285" s="2">
         <v>43028</v>
       </c>
-      <c r="J285" s="2"/>
-    </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>137</v>
       </c>
@@ -11717,9 +11428,8 @@
       <c r="I286" s="2">
         <v>42751</v>
       </c>
-      <c r="J286" s="2"/>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>137</v>
       </c>
@@ -11747,9 +11457,8 @@
       <c r="I287" s="2">
         <v>42614</v>
       </c>
-      <c r="J287" s="2"/>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>264</v>
       </c>
@@ -11777,9 +11486,8 @@
       <c r="I288" s="2">
         <v>42381</v>
       </c>
-      <c r="J288" s="2"/>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>452</v>
       </c>
@@ -11807,9 +11515,8 @@
       <c r="I289" s="2">
         <v>42248</v>
       </c>
-      <c r="J289" s="2"/>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>168</v>
       </c>
@@ -11837,7 +11544,6 @@
       <c r="I290" s="2">
         <v>41255</v>
       </c>
-      <c r="J290" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11850,7 +11556,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
@@ -11866,7 +11572,7 @@
     <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>848</v>
       </c>
@@ -11900,8 +11606,14 @@
       <c r="K1" s="5" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>852</v>
       </c>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://desenvolvimentocartaodetodo-my.sharepoint.com/personal/peopleanalytics_cartaodetodos_com/Documents/People Analytics/PEPO 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9086DB2E-B452-4B24-AF5E-833C46120ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A277E892-F346-4191-B0DC-6BA0404A53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4270,8 +4270,8 @@
   <cols>
     <col min="1" max="1" width="49.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.5546875" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="3" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12" style="3" customWidth="1"/>
     <col min="5" max="5" width="47.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="60.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.5546875" bestFit="1" customWidth="1"/>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://desenvolvimentocartaodetodo-my.sharepoint.com/personal/peopleanalytics_cartaodetodos_com/Documents/People Analytics/PEPO 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A277E892-F346-4191-B0DC-6BA0404A53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C6EB9C5-0873-410A-A5D0-CE4D04CC26F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2478,10 +2478,10 @@
     <t xml:space="preserve">RESPOSTA PENDENTE: </t>
   </si>
   <si>
-    <t>FUNCIONARIO</t>
-  </si>
-  <si>
-    <t>VANUZA DOS SANTOS PRESTES(gestor 1 :1)</t>
+    <t>VANUZA DOS SANTOS PRESTES(gestor 11)</t>
+  </si>
+  <si>
+    <t>Nome</t>
   </si>
 </sst>
 </file>
@@ -2523,20 +2523,24 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFEF8B02"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3762,10 +3766,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46105.306089351849" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
   <cacheSource type="worksheet">
@@ -3868,7 +3868,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A2:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -3940,7 +3940,7 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Gestor Validador"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Matrícula"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="FUNCIONARIO"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento"/>
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>4</v>
@@ -9272,7 +9272,7 @@
         <v>72</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C173" t="s">
         <v>542</v>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05A97192-B170-4662-B0D9-B8B2C6292DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDA9E4D0-19C1-4FEE-BAA3-2BBB1CDDE6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="11" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2412,292 +2412,292 @@
     <t>Responderam</t>
   </si>
   <si>
+    <t>Total Gestores</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESPOSTA PENDENTE: </t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>ALTAIR DE JESUS VILAR GUIMARAES</t>
+  </si>
+  <si>
+    <t>13205</t>
+  </si>
+  <si>
+    <t>SANDRO YUKIO YAMANO</t>
+  </si>
+  <si>
+    <t>ASSESSOR DA PRESIDENCIA</t>
+  </si>
+  <si>
+    <t>25 - PRESIDENCIA - ALTAIR</t>
+  </si>
+  <si>
+    <t>13213</t>
+  </si>
+  <si>
+    <t>UARLAS BONFIM</t>
+  </si>
+  <si>
+    <t>365535</t>
+  </si>
+  <si>
+    <t>M01</t>
+  </si>
+  <si>
+    <t>COORDENADORA ADMINISTRATIVA FINANCEIRA (M.I)</t>
+  </si>
+  <si>
+    <t>25 - MARA - COORDENADOR</t>
+  </si>
+  <si>
+    <t>13203</t>
+  </si>
+  <si>
+    <t>SAMARA DOS REIS FERREIRA</t>
+  </si>
+  <si>
+    <t>SECRETÁRIA EXECUTIVA</t>
+  </si>
+  <si>
+    <t>13709</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>AQUILES VILAR MOTA GUIMARAES</t>
+  </si>
+  <si>
+    <t>VICE PRESIDENTE GLOBAL</t>
+  </si>
+  <si>
+    <t>15019</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>ICARO VILAR MOTA GUIMARAES</t>
+  </si>
+  <si>
+    <t>15018</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>TALES VILAR MOTA GUIMARAES</t>
+  </si>
+  <si>
+    <t>Planeta de TODOS</t>
+  </si>
+  <si>
+    <t>1093178</t>
+  </si>
+  <si>
+    <t>CFO CHIEF FINANCIAL OFFICER</t>
+  </si>
+  <si>
+    <t>25 - FINANCAS - DIRETORIA</t>
+  </si>
+  <si>
+    <t>176654</t>
+  </si>
+  <si>
+    <t>CHIEF TECHNICAL OFFICER</t>
+  </si>
+  <si>
+    <t>25 - TI - DIRETORIA</t>
+  </si>
+  <si>
+    <t>13200</t>
+  </si>
+  <si>
+    <t>CPCO  CHIEF PEOPLE AND CULTURE OFFICER</t>
+  </si>
+  <si>
+    <t>25 - P&amp;C - DIRETORIA</t>
+  </si>
+  <si>
+    <t>94726</t>
+  </si>
+  <si>
+    <t>IC02</t>
+  </si>
+  <si>
+    <t>DIRETOR</t>
+  </si>
+  <si>
+    <t>25 - INCUBADORA - DIRETORIA</t>
+  </si>
+  <si>
+    <t>1286039</t>
+  </si>
+  <si>
+    <t>PJ15</t>
+  </si>
+  <si>
+    <t>FERNANDO BAUMANN MARCOMINI</t>
+  </si>
+  <si>
+    <t>25 - EXPANSÃO INTERNACIONAL</t>
+  </si>
+  <si>
+    <t>70234</t>
+  </si>
+  <si>
+    <t>PJ14</t>
+  </si>
+  <si>
+    <t>SEVERINO SERAFIM RODRIGUES</t>
+  </si>
+  <si>
+    <t>70337</t>
+  </si>
+  <si>
+    <t>IN1</t>
+  </si>
+  <si>
+    <t>GERENTE DE INCORPORAÇÕES</t>
+  </si>
+  <si>
+    <t>25 - INCORPORA - GERENCIA</t>
+  </si>
+  <si>
+    <t>15020</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>PRESIDENTE</t>
+  </si>
+  <si>
+    <t>25 - PRESIDENCIA</t>
+  </si>
+  <si>
+    <t>236295</t>
+  </si>
+  <si>
+    <t>MARIA APARECIDA FERRAZ</t>
+  </si>
+  <si>
+    <t>AUXILIAR DE SERVICOS GERAIS</t>
+  </si>
+  <si>
+    <t>25 - ADM GERAL</t>
+  </si>
+  <si>
+    <t>236385</t>
+  </si>
+  <si>
+    <t>MARIA DO CARMO SILVA</t>
+  </si>
+  <si>
+    <t>2461252</t>
+  </si>
+  <si>
+    <t>ISADORA MARIA DIAS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>RECEPCIONISTA</t>
+  </si>
+  <si>
+    <t>2563257</t>
+  </si>
+  <si>
+    <t>RAIANE JAMILLY ALVES SIMPLICIO</t>
+  </si>
+  <si>
+    <t>236292</t>
+  </si>
+  <si>
+    <t>MARCOS VINICIUS DA SILVA</t>
+  </si>
+  <si>
+    <t>SERVICOS DE MANUTENCAO E EDIFICACOES</t>
+  </si>
+  <si>
+    <t>1772334</t>
+  </si>
+  <si>
+    <t>CHIEF CUSTOMER EXPERIENCE OFFICER - CCXO</t>
+  </si>
+  <si>
+    <t>25 - CRM - DIRETORIA</t>
+  </si>
+  <si>
+    <t>121485</t>
+  </si>
+  <si>
+    <t>CHIEF OPERATING OFFICER COO</t>
+  </si>
+  <si>
+    <t>25 - OPERACOES - DIRETORIA</t>
+  </si>
+  <si>
+    <t>1299967</t>
+  </si>
+  <si>
+    <t>DIRETOR EXECUTIVO PLANETA DE TODOS</t>
+  </si>
+  <si>
+    <t>13154</t>
+  </si>
+  <si>
+    <t>PJ16</t>
+  </si>
+  <si>
+    <t>DIRETOR REGIONAL</t>
+  </si>
+  <si>
+    <t>REGIONAL EQUATORIAL - DIRETORIA</t>
+  </si>
+  <si>
+    <t>70319</t>
+  </si>
+  <si>
+    <t>PJ17</t>
+  </si>
+  <si>
+    <t>REGIONAL CENTRO SUL - DIRETORIA</t>
+  </si>
+  <si>
+    <t>70338</t>
+  </si>
+  <si>
+    <t>PJ23</t>
+  </si>
+  <si>
+    <t>REGIONAL COSTA LESTE - DIRETORIA</t>
+  </si>
+  <si>
+    <t>70320</t>
+  </si>
+  <si>
+    <t>PJ24</t>
+  </si>
+  <si>
+    <t>REGIONAL SÃO PAULO - MINAS - DIRETORIA</t>
+  </si>
+  <si>
+    <t>70327</t>
+  </si>
+  <si>
+    <t>PJ26</t>
+  </si>
+  <si>
+    <t>REGIONAL INTERIOR - DIRETORIA</t>
+  </si>
+  <si>
     <t>(vazio)</t>
-  </si>
-  <si>
-    <t>Total Gestores</t>
-  </si>
-  <si>
-    <t>Total Geral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESPOSTA PENDENTE: </t>
-  </si>
-  <si>
-    <t>Nome</t>
-  </si>
-  <si>
-    <t>ALTAIR DE JESUS VILAR GUIMARAES</t>
-  </si>
-  <si>
-    <t>13205</t>
-  </si>
-  <si>
-    <t>SANDRO YUKIO YAMANO</t>
-  </si>
-  <si>
-    <t>ASSESSOR DA PRESIDENCIA</t>
-  </si>
-  <si>
-    <t>25 - PRESIDENCIA - ALTAIR</t>
-  </si>
-  <si>
-    <t>13213</t>
-  </si>
-  <si>
-    <t>UARLAS BONFIM</t>
-  </si>
-  <si>
-    <t>365535</t>
-  </si>
-  <si>
-    <t>M01</t>
-  </si>
-  <si>
-    <t>COORDENADORA ADMINISTRATIVA FINANCEIRA (M.I)</t>
-  </si>
-  <si>
-    <t>25 - MARA - COORDENADOR</t>
-  </si>
-  <si>
-    <t>13203</t>
-  </si>
-  <si>
-    <t>SAMARA DOS REIS FERREIRA</t>
-  </si>
-  <si>
-    <t>SECRETÁRIA EXECUTIVA</t>
-  </si>
-  <si>
-    <t>13709</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>AQUILES VILAR MOTA GUIMARAES</t>
-  </si>
-  <si>
-    <t>VICE PRESIDENTE GLOBAL</t>
-  </si>
-  <si>
-    <t>15019</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>ICARO VILAR MOTA GUIMARAES</t>
-  </si>
-  <si>
-    <t>15018</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>TALES VILAR MOTA GUIMARAES</t>
-  </si>
-  <si>
-    <t>Planeta de TODOS</t>
-  </si>
-  <si>
-    <t>1093178</t>
-  </si>
-  <si>
-    <t>CFO CHIEF FINANCIAL OFFICER</t>
-  </si>
-  <si>
-    <t>25 - FINANCAS - DIRETORIA</t>
-  </si>
-  <si>
-    <t>176654</t>
-  </si>
-  <si>
-    <t>CHIEF TECHNICAL OFFICER</t>
-  </si>
-  <si>
-    <t>25 - TI - DIRETORIA</t>
-  </si>
-  <si>
-    <t>13200</t>
-  </si>
-  <si>
-    <t>CPCO  CHIEF PEOPLE AND CULTURE OFFICER</t>
-  </si>
-  <si>
-    <t>25 - P&amp;C - DIRETORIA</t>
-  </si>
-  <si>
-    <t>94726</t>
-  </si>
-  <si>
-    <t>IC02</t>
-  </si>
-  <si>
-    <t>DIRETOR</t>
-  </si>
-  <si>
-    <t>25 - INCUBADORA - DIRETORIA</t>
-  </si>
-  <si>
-    <t>1286039</t>
-  </si>
-  <si>
-    <t>PJ15</t>
-  </si>
-  <si>
-    <t>FERNANDO BAUMANN MARCOMINI</t>
-  </si>
-  <si>
-    <t>25 - EXPANSÃO INTERNACIONAL</t>
-  </si>
-  <si>
-    <t>70234</t>
-  </si>
-  <si>
-    <t>PJ14</t>
-  </si>
-  <si>
-    <t>SEVERINO SERAFIM RODRIGUES</t>
-  </si>
-  <si>
-    <t>70337</t>
-  </si>
-  <si>
-    <t>IN1</t>
-  </si>
-  <si>
-    <t>GERENTE DE INCORPORAÇÕES</t>
-  </si>
-  <si>
-    <t>25 - INCORPORA - GERENCIA</t>
-  </si>
-  <si>
-    <t>15020</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>PRESIDENTE</t>
-  </si>
-  <si>
-    <t>25 - PRESIDENCIA</t>
-  </si>
-  <si>
-    <t>236295</t>
-  </si>
-  <si>
-    <t>MARIA APARECIDA FERRAZ</t>
-  </si>
-  <si>
-    <t>AUXILIAR DE SERVICOS GERAIS</t>
-  </si>
-  <si>
-    <t>25 - ADM GERAL</t>
-  </si>
-  <si>
-    <t>236385</t>
-  </si>
-  <si>
-    <t>MARIA DO CARMO SILVA</t>
-  </si>
-  <si>
-    <t>2461252</t>
-  </si>
-  <si>
-    <t>ISADORA MARIA DIAS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>RECEPCIONISTA</t>
-  </si>
-  <si>
-    <t>2563257</t>
-  </si>
-  <si>
-    <t>RAIANE JAMILLY ALVES SIMPLICIO</t>
-  </si>
-  <si>
-    <t>236292</t>
-  </si>
-  <si>
-    <t>MARCOS VINICIUS DA SILVA</t>
-  </si>
-  <si>
-    <t>SERVICOS DE MANUTENCAO E EDIFICACOES</t>
-  </si>
-  <si>
-    <t>1772334</t>
-  </si>
-  <si>
-    <t>CHIEF CUSTOMER EXPERIENCE OFFICER - CCXO</t>
-  </si>
-  <si>
-    <t>25 - CRM - DIRETORIA</t>
-  </si>
-  <si>
-    <t>121485</t>
-  </si>
-  <si>
-    <t>CHIEF OPERATING OFFICER COO</t>
-  </si>
-  <si>
-    <t>25 - OPERACOES - DIRETORIA</t>
-  </si>
-  <si>
-    <t>1299967</t>
-  </si>
-  <si>
-    <t>DIRETOR EXECUTIVO PLANETA DE TODOS</t>
-  </si>
-  <si>
-    <t>13154</t>
-  </si>
-  <si>
-    <t>PJ16</t>
-  </si>
-  <si>
-    <t>DIRETOR REGIONAL</t>
-  </si>
-  <si>
-    <t>REGIONAL EQUATORIAL - DIRETORIA</t>
-  </si>
-  <si>
-    <t>70319</t>
-  </si>
-  <si>
-    <t>PJ17</t>
-  </si>
-  <si>
-    <t>REGIONAL CENTRO SUL - DIRETORIA</t>
-  </si>
-  <si>
-    <t>70338</t>
-  </si>
-  <si>
-    <t>PJ23</t>
-  </si>
-  <si>
-    <t>REGIONAL COSTA LESTE - DIRETORIA</t>
-  </si>
-  <si>
-    <t>70320</t>
-  </si>
-  <si>
-    <t>PJ24</t>
-  </si>
-  <si>
-    <t>REGIONAL SÃO PAULO - MINAS - DIRETORIA</t>
-  </si>
-  <si>
-    <t>70327</t>
-  </si>
-  <si>
-    <t>PJ26</t>
-  </si>
-  <si>
-    <t>REGIONAL INTERIOR - DIRETORIA</t>
   </si>
 </sst>
 </file>
@@ -2707,7 +2707,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2764,6 +2764,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -2818,7 +2823,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2838,6 +2843,9 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2845,87 +2853,6 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="19">
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -3042,6 +2969,87 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3323,7 +3331,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>64</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -4079,7 +4087,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Regiane Aparecida De Souza Andrade" refreshedDate="46106.651637847222" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Regiane Aparecida De Souza Andrade" refreshedDate="46106.735348148148" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
   <cacheSource type="worksheet">
     <worksheetSource name="TabelaRespostas"/>
   </cacheSource>
@@ -4088,8 +4096,9 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Nome do Gestor" numFmtId="0">
-      <sharedItems containsNonDate="0" containsBlank="1" count="10">
+      <sharedItems containsNonDate="0" containsBlank="1" count="11">
         <m/>
+        <s v="AMANDA MIRANDA DE CARVALHO" u="1"/>
         <s v="VANUZA DOS SANTOS PRESTES" u="1"/>
         <s v="ANDRE NADDEO" u="1"/>
         <s v="THIAGO DA SILVA CHISNANDES" u="1"/>
@@ -4180,22 +4189,23 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A2:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="11">
+      <items count="12">
+        <item m="1" x="4"/>
+        <item m="1" x="2"/>
+        <item m="1" x="5"/>
+        <item m="1" x="6"/>
         <item m="1" x="3"/>
-        <item m="1" x="1"/>
-        <item m="1" x="4"/>
-        <item m="1" x="5"/>
-        <item m="1" x="2"/>
-        <item m="1" x="6"/>
         <item m="1" x="7"/>
         <item m="1" x="8"/>
         <item m="1" x="9"/>
+        <item m="1" x="10"/>
         <item x="0"/>
+        <item m="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4242,25 +4252,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:I291" totalsRowShown="0" headerRowDxfId="18" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:I291" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A1:I291" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Gestor Validador" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Matrícula" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Gestor Validador" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Matrícula" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q2" insertRow="1" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q2" insertRow="1" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="A1:Q2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{CFF5932B-854B-4B23-A01A-04BA6982E294}" name="Momento do Envio"/>
@@ -4268,16 +4278,16 @@
     <tableColumn id="3" xr3:uid="{15330415-ADF2-4758-8694-FD7A376B81D4}" name="Funcionário Avaliado"/>
     <tableColumn id="4" xr3:uid="{594E5835-552B-4D6E-A822-81B896CFAF13}" name="ID"/>
     <tableColumn id="5" xr3:uid="{7F5AB4D9-45E8-46BC-B411-788B139EE062}" name="Gestor Correto?"/>
-    <tableColumn id="14" xr3:uid="{6B9D9653-6673-4CC6-90AD-CF40C644B8FE}" name="Novo Gestor" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{6B9D9653-6673-4CC6-90AD-CF40C644B8FE}" name="Novo Gestor" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{C5062DFD-1E5B-4585-8B3D-D5D926B5E2B4}" name="Cargo Correto?"/>
-    <tableColumn id="15" xr3:uid="{707FD308-5DC8-456C-87E0-1C1C71076AD0}" name="Novo Cargo" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{707FD308-5DC8-456C-87E0-1C1C71076AD0}" name="Novo Cargo" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{23F4A278-6130-4156-B2C6-092BB614E4A9}" name="Unidade Correta?"/>
-    <tableColumn id="16" xr3:uid="{B1691D3F-F123-42C6-A2B6-E169F7E0C857}" name="Nova Unidade" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{B1691D3F-F123-42C6-A2B6-E169F7E0C857}" name="Nova Unidade" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{2FF534DC-1CF1-4C48-B7C4-CAF3960253B8}" name="Departamento Correto?"/>
-    <tableColumn id="17" xr3:uid="{A89472CB-3BFB-45F5-AB02-1F4A971F64C0}" name="Novo Depto" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{A89472CB-3BFB-45F5-AB02-1F4A971F64C0}" name="Novo Depto" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{D960B0AB-147E-49C9-81F6-3A62815C92D5}" name="Par 1"/>
     <tableColumn id="10" xr3:uid="{A24B24E4-1150-4A03-93C9-672C68A1D0C8}" name="Par 2"/>
-    <tableColumn id="11" xr3:uid="{5AFF58B5-A998-4A5A-9F0A-A92C2CDE82B2}" name="status_resposta" dataDxfId="10">
+    <tableColumn id="11" xr3:uid="{5AFF58B5-A998-4A5A-9F0A-A92C2CDE82B2}" name="status_resposta" dataDxfId="0">
       <calculatedColumnFormula>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{532FFC7B-A440-4E0F-AF70-FBD92751D24E}" name="Protocolo"/>
@@ -4602,7 +4612,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -4967,28 +4977,28 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>787</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>787</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>788</v>
       </c>
       <c r="D14" s="11">
         <v>139</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>788</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>789</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="11" t="s">
         <v>790</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>791</v>
       </c>
       <c r="I14" s="12">
         <v>41582</v>
@@ -4996,28 +5006,28 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D15" s="11">
         <v>101</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F15" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>790</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>791</v>
       </c>
       <c r="I15" s="12">
         <v>39203</v>
@@ -5025,28 +5035,28 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>793</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>794</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>795</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>138</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>142</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="I16" s="12">
         <v>44636</v>
@@ -5054,28 +5064,28 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D17" s="11">
         <v>207</v>
       </c>
       <c r="E17" s="11" t="s">
+        <v>798</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>799</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>800</v>
-      </c>
       <c r="G17" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="I17" s="12">
         <v>42522</v>
@@ -5083,28 +5093,28 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>800</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>801</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="E18" s="11" t="s">
         <v>802</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="F18" s="11" t="s">
         <v>803</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>804</v>
-      </c>
       <c r="G18" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="I18" s="12">
         <v>36527</v>
@@ -5112,28 +5122,28 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>804</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>805</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="E19" s="11" t="s">
         <v>806</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>807</v>
-      </c>
       <c r="F19" s="11" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="I19" s="12">
         <v>37163</v>
@@ -5141,28 +5151,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>807</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>808</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="E20" s="11" t="s">
         <v>809</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>810</v>
-      </c>
       <c r="F20" s="11" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="I20" s="12">
         <v>43823</v>
@@ -5565,7 +5575,7 @@
         <v>726</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>555</v>
@@ -5924,13 +5934,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D47" s="11">
         <v>617</v>
@@ -5939,13 +5949,13 @@
         <v>410</v>
       </c>
       <c r="F47" s="11" t="s">
+        <v>812</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="11" t="s">
         <v>813</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>814</v>
       </c>
       <c r="I47" s="12">
         <v>45098</v>
@@ -5953,13 +5963,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D48" s="11">
         <v>414</v>
@@ -5968,13 +5978,13 @@
         <v>430</v>
       </c>
       <c r="F48" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H48" s="11" t="s">
         <v>816</v>
-      </c>
-      <c r="G48" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>817</v>
       </c>
       <c r="I48" s="12">
         <v>44470</v>
@@ -5982,13 +5992,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D49" s="11">
         <v>627</v>
@@ -5997,13 +6007,13 @@
         <v>312</v>
       </c>
       <c r="F49" s="11" t="s">
+        <v>818</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>819</v>
-      </c>
-      <c r="G49" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>820</v>
       </c>
       <c r="I49" s="12">
         <v>43587</v>
@@ -6011,28 +6021,28 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>820</v>
+      </c>
+      <c r="D50" s="13" t="s">
         <v>821</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>822</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>319</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G50" s="11" t="s">
         <v>324</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I50" s="12">
         <v>44322</v>
@@ -8070,28 +8080,28 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C121" s="11" t="s">
+        <v>824</v>
+      </c>
+      <c r="D121" s="13" t="s">
         <v>825</v>
       </c>
-      <c r="D121" s="13" t="s">
+      <c r="E121" s="11" t="s">
         <v>826</v>
       </c>
-      <c r="E121" s="11" t="s">
-        <v>827</v>
-      </c>
       <c r="F121" s="11" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G121" s="11" t="s">
         <v>163</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I121" s="12">
         <v>44840</v>
@@ -8099,28 +8109,28 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C122" s="11" t="s">
+        <v>828</v>
+      </c>
+      <c r="D122" s="13" t="s">
         <v>829</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="E122" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="E122" s="11" t="s">
-        <v>831</v>
-      </c>
       <c r="F122" s="11" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G122" s="11" t="s">
         <v>163</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I122" s="12">
         <v>44197</v>
@@ -8128,28 +8138,28 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C123" s="11" t="s">
+        <v>831</v>
+      </c>
+      <c r="D123" s="13" t="s">
         <v>832</v>
-      </c>
-      <c r="D123" s="13" t="s">
-        <v>833</v>
       </c>
       <c r="E123" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G123" s="11" t="s">
         <v>18</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I123" s="12">
         <v>43500</v>
@@ -9723,28 +9733,28 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
-        <v>313</v>
+        <v>786</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>313</v>
       </c>
       <c r="C178" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="D178" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="D178" s="13" t="s">
+      <c r="E178" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="F178" s="11" t="s">
         <v>837</v>
       </c>
-      <c r="E178" s="11" t="s">
-        <v>787</v>
-      </c>
-      <c r="F178" s="11" t="s">
+      <c r="G178" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H178" s="11" t="s">
         <v>838</v>
-      </c>
-      <c r="G178" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H178" s="11" t="s">
-        <v>839</v>
       </c>
       <c r="I178" s="12">
         <v>37163</v>
@@ -11057,28 +11067,28 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B224" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D224" s="11">
         <v>213</v>
       </c>
       <c r="E224" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="F224" s="11" t="s">
         <v>841</v>
       </c>
-      <c r="F224" s="11" t="s">
+      <c r="G224" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H224" s="11" t="s">
         <v>842</v>
-      </c>
-      <c r="G224" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H224" s="11" t="s">
-        <v>843</v>
       </c>
       <c r="I224" s="12">
         <v>42751</v>
@@ -11086,28 +11096,28 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B225" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C225" s="11" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D225" s="11">
         <v>329</v>
       </c>
       <c r="E225" s="11" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F225" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="G225" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H225" s="11" t="s">
         <v>842</v>
-      </c>
-      <c r="G225" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H225" s="11" t="s">
-        <v>843</v>
       </c>
       <c r="I225" s="12">
         <v>43682</v>
@@ -11115,28 +11125,28 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D226" s="11">
         <v>908</v>
       </c>
       <c r="E226" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="F226" s="11" t="s">
         <v>847</v>
       </c>
-      <c r="F226" s="11" t="s">
-        <v>848</v>
-      </c>
       <c r="G226" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H226" s="11" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I226" s="12">
         <v>45887</v>
@@ -11144,28 +11154,28 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B227" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C227" s="11" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D227" s="11">
         <v>937</v>
       </c>
       <c r="E227" s="11" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G227" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H227" s="11" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I227" s="12">
         <v>45964</v>
@@ -11173,28 +11183,28 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B228" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C228" s="11" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D228" s="11">
         <v>208</v>
       </c>
       <c r="E228" s="11" t="s">
+        <v>851</v>
+      </c>
+      <c r="F228" s="11" t="s">
         <v>852</v>
       </c>
-      <c r="F228" s="11" t="s">
-        <v>853</v>
-      </c>
       <c r="G228" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H228" s="11" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I228" s="12">
         <v>42614</v>
@@ -11579,13 +11589,13 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B242" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C242" s="11" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D242" s="11">
         <v>740</v>
@@ -11594,13 +11604,13 @@
         <v>60</v>
       </c>
       <c r="F242" s="11" t="s">
+        <v>854</v>
+      </c>
+      <c r="G242" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H242" s="11" t="s">
         <v>855</v>
-      </c>
-      <c r="G242" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H242" s="11" t="s">
-        <v>856</v>
       </c>
       <c r="I242" s="12">
         <v>45516</v>
@@ -11608,13 +11618,13 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C243" s="11" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D243" s="11">
         <v>390</v>
@@ -11623,13 +11633,13 @@
         <v>304</v>
       </c>
       <c r="F243" s="11" t="s">
+        <v>857</v>
+      </c>
+      <c r="G243" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H243" s="11" t="s">
         <v>858</v>
-      </c>
-      <c r="G243" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H243" s="11" t="s">
-        <v>859</v>
       </c>
       <c r="I243" s="12">
         <v>44342</v>
@@ -11637,13 +11647,13 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B244" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C244" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D244" s="11">
         <v>645</v>
@@ -11652,10 +11662,10 @@
         <v>554</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H244" s="11" t="s">
         <v>555</v>
@@ -11666,28 +11676,28 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C245" s="11" t="s">
+        <v>861</v>
+      </c>
+      <c r="D245" s="13" t="s">
         <v>862</v>
-      </c>
-      <c r="D245" s="13" t="s">
-        <v>863</v>
       </c>
       <c r="E245" s="11" t="s">
         <v>748</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G245" s="11" t="s">
         <v>163</v>
       </c>
       <c r="H245" s="11" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="I245" s="12">
         <v>44197</v>
@@ -11695,28 +11705,28 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B246" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C246" s="11" t="s">
+        <v>865</v>
+      </c>
+      <c r="D246" s="13" t="s">
         <v>866</v>
-      </c>
-      <c r="D246" s="13" t="s">
-        <v>867</v>
       </c>
       <c r="E246" s="11" t="s">
         <v>372</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G246" s="11" t="s">
         <v>163</v>
       </c>
       <c r="H246" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="I246" s="12">
         <v>44197</v>
@@ -11724,28 +11734,28 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B247" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C247" s="11" t="s">
+        <v>868</v>
+      </c>
+      <c r="D247" s="13" t="s">
         <v>869</v>
-      </c>
-      <c r="D247" s="13" t="s">
-        <v>870</v>
       </c>
       <c r="E247" s="11" t="s">
         <v>95</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G247" s="11" t="s">
         <v>163</v>
       </c>
       <c r="H247" s="11" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="I247" s="12">
         <v>44197</v>
@@ -11753,28 +11763,28 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C248" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="D248" s="13" t="s">
         <v>872</v>
-      </c>
-      <c r="D248" s="13" t="s">
-        <v>873</v>
       </c>
       <c r="E248" s="11" t="s">
         <v>8</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G248" s="11" t="s">
         <v>163</v>
       </c>
       <c r="H248" s="11" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="I248" s="12">
         <v>44246</v>
@@ -11782,28 +11792,28 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C249" s="11" t="s">
+        <v>874</v>
+      </c>
+      <c r="D249" s="13" t="s">
         <v>875</v>
-      </c>
-      <c r="D249" s="13" t="s">
-        <v>876</v>
       </c>
       <c r="E249" s="11" t="s">
         <v>184</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G249" s="11" t="s">
         <v>163</v>
       </c>
       <c r="H249" s="11" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="I249" s="12">
         <v>44197</v>
@@ -13039,7 +13049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
@@ -13120,13 +13130,13 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="F2" s="15"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="H2" s="15"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="J2" s="15"/>
       <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+      <c r="L2" s="15"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
@@ -13141,9 +13151,6 @@
     <row r="8" spans="1:17" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -13172,7 +13179,7 @@
       </c>
       <c r="D1">
         <f>D3-D2</f>
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -13193,19 +13200,19 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>877</v>
+      </c>
+      <c r="C3" t="s">
         <v>782</v>
-      </c>
-      <c r="C3" t="s">
-        <v>783</v>
       </c>
       <c r="D3">
         <f>COUNTA(_xlfn.UNIQUE(Base_Dados!A:A))-1</f>
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
   </sheetData>
@@ -13226,12 +13233,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="str" cm="1">
-        <f t="array" ref="A2:A65">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A502, (Base_Dados!A2:A502&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A502)=0), "✅ Todos responderam!")))</f>
+        <f t="array" ref="A2:A64">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A502, (Base_Dados!A2:A502&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A502)=0), "✅ Todos responderam!")))</f>
         <v>ALEX ALVARES PIMENTEL MACIEL</v>
       </c>
     </row>
@@ -13437,118 +13444,116 @@
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="str">
-        <v>NÃO ATRIBUIDO</v>
+        <v>NUBIA AQUINO DA SILVA</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="str">
-        <v>NUBIA AQUINO DA SILVA</v>
+        <v>PAULA ROBERTA GOMES LISBOA</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="str">
-        <v>PAULA ROBERTA GOMES LISBOA</v>
+        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="str">
-        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
+        <v>RAPHAEL AZEVEDO</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="str">
-        <v>RAPHAEL AZEVEDO</v>
+        <v>RENNAN LUCIO DE MOURA</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="str">
-        <v>RENNAN LUCIO DE MOURA</v>
+        <v>RENNAN VILAR GUIMARAES CASTRO ANTUNES</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="str">
-        <v>RENNAN VILAR GUIMARAES CASTRO ANTUNES</v>
+        <v>RICARDO ESTEVAO DE ALMEIDA</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="str">
-        <v>RICARDO ESTEVAO DE ALMEIDA</v>
+        <v>RODNEY DUARTE DOS SANTOS</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="str">
-        <v>RODNEY DUARTE DOS SANTOS</v>
+        <v>RODRIGO ASSUMPÇÃO</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="str">
-        <v>RODRIGO ASSUMPÇÃO</v>
+        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="str">
-        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
+        <v>SAMUEL NUNES RIOS SILVA</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="str">
-        <v>SAMUEL NUNES RIOS SILVA</v>
+        <v>SANDRO YUKIO YAMANO</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="str">
-        <v>SANDRO YUKIO YAMANO</v>
+        <v>SLAYNE FERNANDA NERES GOMES BRUM ARAUJO</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="str">
-        <v>SLAYNE FERNANDA NERES GOMES BRUM ARAUJO</v>
+        <v>STAEL MARLEI DE SOUZA E SILVA</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="str">
-        <v>STAEL MARLEI DE SOUZA E SILVA</v>
+        <v>TALES VILAR MOTA GUIMARAES</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="str">
-        <v>TALES VILAR MOTA GUIMARAES</v>
+        <v>THIAGO DA SILVA CHISNANDES</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="str">
-        <v>THIAGO DA SILVA CHISNANDES</v>
+        <v>TIAGO DANIEL DE SOUZA</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="str">
-        <v>TIAGO DANIEL DE SOUZA</v>
+        <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="str">
-        <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
+        <v>VANUZA DOS SANTOS PRESTES</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="str">
-        <v>VANUZA DOS SANTOS PRESTES</v>
+        <v>VICTOR JOSE ALVES FERNANDES</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="str">
-        <v>VICTOR JOSE ALVES FERNANDES</v>
+        <v>WANDERSON LAGE</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="str">
-        <v>WANDERSON LAGE</v>
+        <v>WELLYNGTON ALVES BORGES</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="9" t="str">
-        <v>WELLYNGTON ALVES BORGES</v>
-      </c>
+      <c r="A65" s="9"/>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDA9E4D0-19C1-4FEE-BAA3-2BBB1CDDE6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B9E6143-4F50-451C-A286-683C9128646F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2113" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2113" uniqueCount="879">
   <si>
     <t>Gestor Avaliador</t>
   </si>
@@ -2698,6 +2698,9 @@
   </si>
   <si>
     <t>(vazio)</t>
+  </si>
+  <si>
+    <t>_</t>
   </si>
 </sst>
 </file>
@@ -3331,7 +3334,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>63</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -4189,7 +4192,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A2:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -9733,7 +9736,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
-        <v>786</v>
+        <v>878</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>313</v>
@@ -13179,7 +13182,7 @@
       </c>
       <c r="D1">
         <f>D3-D2</f>
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -13207,7 +13210,7 @@
       </c>
       <c r="D3">
         <f>COUNTA(_xlfn.UNIQUE(Base_Dados!A:A))-1</f>
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -13238,322 +13241,324 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="str" cm="1">
-        <f t="array" ref="A2:A64">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A502, (Base_Dados!A2:A502&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A502)=0), "✅ Todos responderam!")))</f>
-        <v>ALEX ALVARES PIMENTEL MACIEL</v>
+        <f t="array" ref="A2:A65">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A502, (Base_Dados!A2:A502&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A502)=0), "✅ Todos responderam!")))</f>
+        <v>_</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="str">
-        <v>ALINE DE GOES CAMARGO</v>
+        <v>ALEX ALVARES PIMENTEL MACIEL</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="str">
-        <v>ALTAIR DE JESUS VILAR GUIMARAES</v>
+        <v>ALINE DE GOES CAMARGO</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="str">
-        <v>AMANDA MIRANDA DE CARVALHO</v>
+        <v>ALTAIR DE JESUS VILAR GUIMARAES</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="str">
-        <v>AMANDA STEFANI SOUSA DE ALMEIDA SANTOS</v>
+        <v>AMANDA MIRANDA DE CARVALHO</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="str">
-        <v>ANDRE NADDEO</v>
+        <v>AMANDA STEFANI SOUSA DE ALMEIDA SANTOS</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="str">
-        <v>ANDRESSA RODRIGUES MORATO MAIA</v>
+        <v>ANDRE NADDEO</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="str">
-        <v>ANEDINA IZABEL DUARTE SOUZA</v>
+        <v>ANDRESSA RODRIGUES MORATO MAIA</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="str">
-        <v>AQUILES VILAR MOTA GUIMARAES</v>
+        <v>ANEDINA IZABEL DUARTE SOUZA</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="str">
-        <v>BRAULIO PIOVEZANA RINCO</v>
+        <v>AQUILES VILAR MOTA GUIMARAES</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="str">
-        <v>BRUNNA KAROLINE QUEIROZ RODRIGUES</v>
+        <v>BRAULIO PIOVEZANA RINCO</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="str">
-        <v>BRUNO CASTRO METZKER</v>
+        <v>BRUNNA KAROLINE QUEIROZ RODRIGUES</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="str">
-        <v>BRUNO NUNES DE SOUZA SANTOS</v>
+        <v>BRUNO CASTRO METZKER</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="str">
-        <v>CAMILA DA SILVA ANDRADE</v>
+        <v>BRUNO NUNES DE SOUZA SANTOS</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="str">
-        <v>CARINE REIS DOS SANTOS</v>
+        <v>CAMILA DA SILVA ANDRADE</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="str">
-        <v>CAROLINE PAIXÃO VIEIRA DE SENA</v>
+        <v>CARINE REIS DOS SANTOS</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="str">
-        <v>CATERINE NUNES BARBOSA</v>
+        <v>CAROLINE PAIXÃO VIEIRA DE SENA</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="str">
-        <v>DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH</v>
+        <v>CATERINE NUNES BARBOSA</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="str">
-        <v>DENIS GABRIEL ABREU DE MELO</v>
+        <v>DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="str">
-        <v>DIEGO PIRES</v>
+        <v>DENIS GABRIEL ABREU DE MELO</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="str">
-        <v>ELIANE PEREIRA DA SILVA HIDALGO</v>
+        <v>DIEGO PIRES</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="str">
-        <v>ELISANGELA PEDRO RODRIGUES OLIVEIRA</v>
+        <v>ELIANE PEREIRA DA SILVA HIDALGO</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="str">
-        <v>ELISON GLAUBER DE CASTRO</v>
+        <v>ELISANGELA PEDRO RODRIGUES OLIVEIRA</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="str">
-        <v>FERNANDA DE SOUZA SILVEIRA</v>
+        <v>ELISON GLAUBER DE CASTRO</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="str">
-        <v>FLAVIO HENRIQUE ALMEIDA FERREIRA DE MELO</v>
+        <v>FERNANDA DE SOUZA SILVEIRA</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="str">
-        <v>GIOVANNA DE ARAUJO GIACON</v>
+        <v>FLAVIO HENRIQUE ALMEIDA FERREIRA DE MELO</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="str">
-        <v>GUSTAVO ARANDA DAMBROSKI</v>
+        <v>GIOVANNA DE ARAUJO GIACON</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="str">
-        <v>HAYNA CARDOSO PINTO</v>
+        <v>GUSTAVO ARANDA DAMBROSKI</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="str">
-        <v>ICARO VILAR MOTA GUIMARAES</v>
+        <v>HAYNA CARDOSO PINTO</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="str">
-        <v>JEZI FERNANDO OLIVEIRA</v>
+        <v>ICARO VILAR MOTA GUIMARAES</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="str">
-        <v>KETTULY FERNANDA ALVES DE AMORIM SANTIAGO</v>
+        <v>JEZI FERNANDO OLIVEIRA</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="str">
-        <v>LEON DOS REIS CALIXTO</v>
+        <v>KETTULY FERNANDA ALVES DE AMORIM SANTIAGO</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="str">
-        <v>LORRAYNE CRISTINE THEZA DO CARMO</v>
+        <v>LEON DOS REIS CALIXTO</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="str">
-        <v>LUCAS BICALHO DE FREITAS</v>
+        <v>LORRAYNE CRISTINE THEZA DO CARMO</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="str">
-        <v>LUCAS BUETTO DE ANGELIS</v>
+        <v>LUCAS BICALHO DE FREITAS</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="str">
-        <v>LUIS FERNANDO KALIL ROSENBURG DE CASTRO</v>
+        <v>LUCAS BUETTO DE ANGELIS</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="str">
-        <v>LUÍS HENRIQUE SOARES DUTRA DE ANDRADE</v>
+        <v>LUIS FERNANDO KALIL ROSENBURG DE CASTRO</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="str">
-        <v>MAIARA SCHWENGBER CORREA</v>
+        <v>LUÍS HENRIQUE SOARES DUTRA DE ANDRADE</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="str">
-        <v>MARCELA REGGIANI MORAES</v>
+        <v>MAIARA SCHWENGBER CORREA</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="str">
-        <v>MARIANA DE ALBUQUERQUE LOPES</v>
+        <v>MARCELA REGGIANI MORAES</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="str">
-        <v>MATHEUS ARTHUR FACHIN</v>
+        <v>MARIANA DE ALBUQUERQUE LOPES</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="str">
-        <v>NUBIA AQUINO DA SILVA</v>
+        <v>MATHEUS ARTHUR FACHIN</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="str">
-        <v>PAULA ROBERTA GOMES LISBOA</v>
+        <v>NUBIA AQUINO DA SILVA</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="str">
-        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
+        <v>PAULA ROBERTA GOMES LISBOA</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="str">
-        <v>RAPHAEL AZEVEDO</v>
+        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="str">
-        <v>RENNAN LUCIO DE MOURA</v>
+        <v>RAPHAEL AZEVEDO</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="str">
-        <v>RENNAN VILAR GUIMARAES CASTRO ANTUNES</v>
+        <v>RENNAN LUCIO DE MOURA</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="str">
-        <v>RICARDO ESTEVAO DE ALMEIDA</v>
+        <v>RENNAN VILAR GUIMARAES CASTRO ANTUNES</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="str">
-        <v>RODNEY DUARTE DOS SANTOS</v>
+        <v>RICARDO ESTEVAO DE ALMEIDA</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="str">
-        <v>RODRIGO ASSUMPÇÃO</v>
+        <v>RODNEY DUARTE DOS SANTOS</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="str">
-        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
+        <v>RODRIGO ASSUMPÇÃO</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="str">
-        <v>SAMUEL NUNES RIOS SILVA</v>
+        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="str">
-        <v>SANDRO YUKIO YAMANO</v>
+        <v>SAMUEL NUNES RIOS SILVA</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="str">
-        <v>SLAYNE FERNANDA NERES GOMES BRUM ARAUJO</v>
+        <v>SANDRO YUKIO YAMANO</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="str">
-        <v>STAEL MARLEI DE SOUZA E SILVA</v>
+        <v>SLAYNE FERNANDA NERES GOMES BRUM ARAUJO</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="str">
-        <v>TALES VILAR MOTA GUIMARAES</v>
+        <v>STAEL MARLEI DE SOUZA E SILVA</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="str">
-        <v>THIAGO DA SILVA CHISNANDES</v>
+        <v>TALES VILAR MOTA GUIMARAES</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="str">
-        <v>TIAGO DANIEL DE SOUZA</v>
+        <v>THIAGO DA SILVA CHISNANDES</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="str">
-        <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
+        <v>TIAGO DANIEL DE SOUZA</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="str">
-        <v>VANUZA DOS SANTOS PRESTES</v>
+        <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="str">
-        <v>VICTOR JOSE ALVES FERNANDES</v>
+        <v>VANUZA DOS SANTOS PRESTES</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="str">
-        <v>WANDERSON LAGE</v>
+        <v>VICTOR JOSE ALVES FERNANDES</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="str">
+        <v>WANDERSON LAGE</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9" t="str">
         <v>WELLYNGTON ALVES BORGES</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="9"/>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B9E6143-4F50-451C-A286-683C9128646F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5336863B-B17F-42B2-8BB2-A843FD527B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -4078,6 +4078,13 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -11998,10 +12005,10 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="11" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="C256" s="11" t="s">
         <v>529</v>
@@ -13521,59 +13528,59 @@
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="9" t="str">
+      <c r="A58" s="10" t="str">
         <v>TALES VILAR MOTA GUIMARAES</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="str">
+      <c r="A59" s="10" t="str">
         <v>THIAGO DA SILVA CHISNANDES</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="9" t="str">
+      <c r="A60" s="10" t="str">
         <v>TIAGO DANIEL DE SOUZA</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="9" t="str">
+      <c r="A61" s="10" t="str">
         <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9" t="str">
+      <c r="A62" s="10" t="str">
         <v>VANUZA DOS SANTOS PRESTES</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="9" t="str">
+      <c r="A63" s="10" t="str">
         <v>VICTOR JOSE ALVES FERNANDES</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="9" t="str">
+      <c r="A64" s="10" t="str">
         <v>WANDERSON LAGE</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="9" t="str">
+      <c r="A65" s="10" t="str">
         <v>WELLYNGTON ALVES BORGES</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="9"/>
+      <c r="A66" s="10"/>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="9"/>
+      <c r="A67" s="10"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="9"/>
+      <c r="A68" s="10"/>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="9"/>
+      <c r="A69" s="10"/>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="9"/>
+      <c r="A70" s="10"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5336863B-B17F-42B2-8BB2-A843FD527B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{003E4C3E-6198-4E30-9727-FC0BCEB486D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="705" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -4078,13 +4078,6 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -12005,7 +11998,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="11" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="B256" s="11" t="s">
         <v>189</v>
@@ -13528,59 +13521,59 @@
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="10" t="str">
+      <c r="A58" s="9" t="str">
         <v>TALES VILAR MOTA GUIMARAES</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="10" t="str">
+      <c r="A59" s="9" t="str">
         <v>THIAGO DA SILVA CHISNANDES</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="10" t="str">
+      <c r="A60" s="9" t="str">
         <v>TIAGO DANIEL DE SOUZA</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="10" t="str">
+      <c r="A61" s="9" t="str">
         <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="10" t="str">
+      <c r="A62" s="9" t="str">
         <v>VANUZA DOS SANTOS PRESTES</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="10" t="str">
+      <c r="A63" s="9" t="str">
         <v>VICTOR JOSE ALVES FERNANDES</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="10" t="str">
+      <c r="A64" s="9" t="str">
         <v>WANDERSON LAGE</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="10" t="str">
+      <c r="A65" s="9" t="str">
         <v>WELLYNGTON ALVES BORGES</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="10"/>
+      <c r="A66" s="9"/>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="10"/>
+      <c r="A67" s="9"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="10"/>
+      <c r="A68" s="9"/>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="10"/>
+      <c r="A69" s="9"/>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="10"/>
+      <c r="A70" s="9"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D25665C6-5EC0-4CFE-8EA2-DDC599A3B82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A7D4A8F-52B7-4BA2-992B-E5B305E8A525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="863">
   <si>
     <t>Gestor Avaliador</t>
   </si>
@@ -1611,9 +1611,6 @@
     <t>458230</t>
   </si>
   <si>
-    <t>JULIO CESAR BARBOSA BENEDITO DA COSTA</t>
-  </si>
-  <si>
     <t>ASSISTENTE DE EVENTOS</t>
   </si>
   <si>
@@ -2650,6 +2647,12 @@
   </si>
   <si>
     <t xml:space="preserve">RESPOSTA PENDENTE: </t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>FINANCAS</t>
   </si>
 </sst>
 </file>
@@ -8428,7 +8431,7 @@
         <v>35</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>187</v>
+        <v>426</v>
       </c>
       <c r="I131" s="9">
         <v>44573</v>
@@ -8486,7 +8489,7 @@
         <v>35</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>259</v>
+        <v>426</v>
       </c>
       <c r="I133" s="9">
         <v>45964</v>
@@ -9393,7 +9396,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B165" s="8" t="s">
         <v>395</v>
@@ -9405,16 +9408,16 @@
         <v>493</v>
       </c>
       <c r="E165" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="F165" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="F165" s="8" t="s">
+      <c r="G165" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H165" s="8" t="s">
         <v>516</v>
-      </c>
-      <c r="G165" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H165" s="8" t="s">
-        <v>517</v>
       </c>
       <c r="I165" s="9">
         <v>44718</v>
@@ -9422,22 +9425,22 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="C166" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="B166" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="C166" s="8" t="s">
+      <c r="D166" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="D166" s="10" t="s">
+      <c r="E166" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="E166" s="8" t="s">
+      <c r="F166" s="8" t="s">
         <v>521</v>
-      </c>
-      <c r="F166" s="8" t="s">
-        <v>522</v>
       </c>
       <c r="G166" s="8" t="s">
         <v>35</v>
@@ -9451,22 +9454,22 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C167" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="D167" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="D167" s="10" t="s">
+      <c r="E167" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="E167" s="8" t="s">
-        <v>525</v>
-      </c>
       <c r="F167" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G167" s="8" t="s">
         <v>35</v>
@@ -9480,22 +9483,22 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C168" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="D168" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="D168" s="10" t="s">
+      <c r="E168" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="E168" s="8" t="s">
-        <v>528</v>
-      </c>
       <c r="F168" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>35</v>
@@ -9509,19 +9512,19 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C169" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="D169" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="D169" s="10" t="s">
+      <c r="E169" s="8" t="s">
         <v>530</v>
-      </c>
-      <c r="E169" s="8" t="s">
-        <v>531</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>301</v>
@@ -9538,19 +9541,19 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D170" s="8">
         <v>924</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>301</v>
@@ -9567,19 +9570,19 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C171" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="D171" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="D171" s="10" t="s">
+      <c r="E171" s="8" t="s">
         <v>535</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>536</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>301</v>
@@ -9596,19 +9599,19 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B172" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C172" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D172">
         <v>690</v>
       </c>
       <c r="E172" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F172" t="s">
         <v>305</v>
@@ -9625,19 +9628,19 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D173" s="8">
         <v>343</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>305</v>
@@ -9654,19 +9657,19 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D174" s="8">
         <v>236</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>312</v>
@@ -9683,19 +9686,19 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C175" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="D175" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="D175" s="10" t="s">
+      <c r="E175" s="8" t="s">
         <v>544</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>545</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>312</v>
@@ -9712,19 +9715,19 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D176" s="8">
         <v>922</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>467</v>
@@ -9741,28 +9744,28 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="B177" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="B177" s="8" t="s">
+      <c r="C177" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="C177" s="8" t="s">
+      <c r="D177" s="10" t="s">
         <v>550</v>
-      </c>
-      <c r="D177" s="10" t="s">
-        <v>551</v>
       </c>
       <c r="E177" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F177" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H177" s="8" t="s">
         <v>552</v>
-      </c>
-      <c r="G177" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H177" s="8" t="s">
-        <v>553</v>
       </c>
       <c r="I177" s="9">
         <v>37163</v>
@@ -9776,13 +9779,13 @@
         <v>326</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D178" s="8">
         <v>634</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>228</v>
@@ -9805,13 +9808,13 @@
         <v>326</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D179" s="8">
         <v>356</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>175</v>
@@ -9834,13 +9837,13 @@
         <v>326</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D180" s="8">
         <v>637</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>235</v>
@@ -9863,22 +9866,22 @@
         <v>166</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D181" s="8">
         <v>434</v>
       </c>
       <c r="E181" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="F181" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="F181" s="8" t="s">
+      <c r="G181" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H181" s="8" t="s">
         <v>562</v>
-      </c>
-      <c r="G181" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H181" s="8" t="s">
-        <v>563</v>
       </c>
       <c r="I181" s="9">
         <v>44531</v>
@@ -9892,13 +9895,13 @@
         <v>166</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D182" s="8">
         <v>927</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>228</v>
@@ -9907,7 +9910,7 @@
         <v>35</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I182" s="9">
         <v>45915</v>
@@ -9921,22 +9924,22 @@
         <v>166</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D183" s="8">
         <v>539</v>
       </c>
       <c r="E183" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="F183" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="F183" s="8" t="s">
-        <v>568</v>
-      </c>
       <c r="G183" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I183" s="9">
         <v>44874</v>
@@ -9950,7 +9953,7 @@
         <v>166</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D184" s="8">
         <v>684</v>
@@ -9979,7 +9982,7 @@
         <v>166</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D185" s="8">
         <v>788</v>
@@ -10002,19 +10005,19 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="C186" s="8" t="s">
         <v>571</v>
-      </c>
-      <c r="B186" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="C186" s="8" t="s">
-        <v>572</v>
       </c>
       <c r="D186" s="8">
         <v>943</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>12</v>
@@ -10031,13 +10034,13 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="8" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D187" s="8">
         <v>430</v>
@@ -10060,19 +10063,19 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="C188" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="B188" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="C188" s="8" t="s">
+      <c r="D188" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="D188" s="10" t="s">
+      <c r="E188" s="8" t="s">
         <v>577</v>
-      </c>
-      <c r="E188" s="8" t="s">
-        <v>578</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>12</v>
@@ -10089,13 +10092,13 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="8" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D189" s="8">
         <v>610</v>
@@ -10124,16 +10127,16 @@
         <v>30</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D190" s="8">
         <v>809</v>
       </c>
       <c r="E190" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="F190" s="8" t="s">
         <v>581</v>
-      </c>
-      <c r="F190" s="8" t="s">
-        <v>582</v>
       </c>
       <c r="G190" s="8" t="s">
         <v>35</v>
@@ -10153,16 +10156,16 @@
         <v>30</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D191" s="8">
         <v>741</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F191" s="8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G191" s="8" t="s">
         <v>35</v>
@@ -10182,16 +10185,16 @@
         <v>30</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D192" s="8">
         <v>902</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F192" s="8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G192" s="8" t="s">
         <v>35</v>
@@ -10211,16 +10214,16 @@
         <v>30</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D193" s="8">
         <v>913</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G193" s="8" t="s">
         <v>35</v>
@@ -10240,16 +10243,16 @@
         <v>30</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D194" s="8">
         <v>712</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G194" s="8" t="s">
         <v>35</v>
@@ -10269,16 +10272,16 @@
         <v>30</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D195" s="8">
         <v>630</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>35</v>
@@ -10298,16 +10301,16 @@
         <v>30</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D196" s="8">
         <v>632</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>35</v>
@@ -10327,7 +10330,7 @@
         <v>284</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D197" s="8">
         <v>802</v>
@@ -10336,13 +10339,13 @@
         <v>326</v>
       </c>
       <c r="F197" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H197" s="8" t="s">
         <v>596</v>
-      </c>
-      <c r="G197" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H197" s="8" t="s">
-        <v>597</v>
       </c>
       <c r="I197" s="9">
         <v>45659</v>
@@ -10356,7 +10359,7 @@
         <v>148</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D198" s="8">
         <v>795</v>
@@ -10365,13 +10368,13 @@
         <v>395</v>
       </c>
       <c r="F198" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H198" s="8" t="s">
         <v>599</v>
-      </c>
-      <c r="G198" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H198" s="8" t="s">
-        <v>600</v>
       </c>
       <c r="I198" s="9">
         <v>45628</v>
@@ -10385,7 +10388,7 @@
         <v>148</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D199" s="8">
         <v>169</v>
@@ -10394,13 +10397,13 @@
         <v>183</v>
       </c>
       <c r="F199" s="8" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G199" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="I199" s="9">
         <v>42248</v>
@@ -10408,28 +10411,28 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D200" s="8">
         <v>860</v>
       </c>
       <c r="E200" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="F200" s="8" t="s">
         <v>605</v>
       </c>
-      <c r="F200" s="8" t="s">
+      <c r="G200" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H200" s="8" t="s">
         <v>606</v>
-      </c>
-      <c r="G200" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H200" s="8" t="s">
-        <v>607</v>
       </c>
       <c r="I200" s="9">
         <v>45754</v>
@@ -10437,28 +10440,28 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D201" s="8">
         <v>826</v>
       </c>
       <c r="E201" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="F201" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="F201" s="8" t="s">
-        <v>610</v>
-      </c>
       <c r="G201" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I201" s="9">
         <v>45705</v>
@@ -10466,28 +10469,28 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D202" s="8">
         <v>905</v>
       </c>
       <c r="E202" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="F202" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="F202" s="8" t="s">
-        <v>613</v>
-      </c>
       <c r="G202" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I202" s="9">
         <v>45873</v>
@@ -10495,19 +10498,19 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D203" s="8">
         <v>915</v>
       </c>
       <c r="E203" s="8" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>467</v>
@@ -10516,7 +10519,7 @@
         <v>35</v>
       </c>
       <c r="H203" s="8" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I203" s="9">
         <v>45901</v>
@@ -10524,19 +10527,19 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="C204" s="8" t="s">
         <v>616</v>
-      </c>
-      <c r="B204" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="C204" s="8" t="s">
-        <v>617</v>
       </c>
       <c r="D204" s="8">
         <v>553</v>
       </c>
       <c r="E204" s="8" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>12</v>
@@ -10545,7 +10548,7 @@
         <v>13</v>
       </c>
       <c r="H204" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I204" s="9">
         <v>44921</v>
@@ -10553,19 +10556,19 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D205" s="8">
         <v>917</v>
       </c>
       <c r="E205" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>12</v>
@@ -10574,7 +10577,7 @@
         <v>13</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I205" s="9">
         <v>45901</v>
@@ -10582,19 +10585,19 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D206" s="8">
         <v>810</v>
       </c>
       <c r="E206" s="8" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>12</v>
@@ -10603,7 +10606,7 @@
         <v>13</v>
       </c>
       <c r="H206" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I206" s="9">
         <v>45680</v>
@@ -10611,19 +10614,19 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D207" s="8">
         <v>838</v>
       </c>
       <c r="E207" s="8" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>12</v>
@@ -10632,7 +10635,7 @@
         <v>13</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I207" s="9">
         <v>45705</v>
@@ -10640,19 +10643,19 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D208" s="8">
         <v>919</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>12</v>
@@ -10661,7 +10664,7 @@
         <v>13</v>
       </c>
       <c r="H208" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I208" s="9">
         <v>44746</v>
@@ -10669,19 +10672,19 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D209" s="8">
         <v>843</v>
       </c>
       <c r="E209" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>12</v>
@@ -10690,7 +10693,7 @@
         <v>13</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I209" s="9">
         <v>45705</v>
@@ -10698,19 +10701,19 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D210" s="8">
         <v>817</v>
       </c>
       <c r="E210" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>12</v>
@@ -10719,7 +10722,7 @@
         <v>13</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I210" s="9">
         <v>45684</v>
@@ -10727,19 +10730,19 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D211" s="8">
         <v>833</v>
       </c>
       <c r="E211" s="8" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>12</v>
@@ -10748,7 +10751,7 @@
         <v>13</v>
       </c>
       <c r="H211" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I211" s="9">
         <v>45705</v>
@@ -10756,19 +10759,19 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D212" s="8">
         <v>647</v>
       </c>
       <c r="E212" s="8" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>12</v>
@@ -10777,7 +10780,7 @@
         <v>13</v>
       </c>
       <c r="H212" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I212" s="9">
         <v>45233</v>
@@ -10791,16 +10794,16 @@
         <v>298</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D213" s="8">
         <v>674</v>
       </c>
       <c r="E213" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="F213" s="8" t="s">
         <v>637</v>
-      </c>
-      <c r="F213" s="8" t="s">
-        <v>638</v>
       </c>
       <c r="G213" s="8" t="s">
         <v>35</v>
@@ -10820,16 +10823,16 @@
         <v>298</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D214" s="8">
         <v>957</v>
       </c>
       <c r="E214" s="8" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F214" s="8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G214" s="8" t="s">
         <v>35</v>
@@ -10849,16 +10852,16 @@
         <v>298</v>
       </c>
       <c r="C215" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="D215" s="10" t="s">
         <v>641</v>
       </c>
-      <c r="D215" s="10" t="s">
+      <c r="E215" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="E215" s="8" t="s">
-        <v>643</v>
-      </c>
       <c r="F215" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G215" s="8" t="s">
         <v>35</v>
@@ -10878,7 +10881,7 @@
         <v>298</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D216" s="8">
         <v>606</v>
@@ -10907,7 +10910,7 @@
         <v>298</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D217" s="8">
         <v>604</v>
@@ -10936,10 +10939,10 @@
         <v>298</v>
       </c>
       <c r="C218" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="D218" s="10" t="s">
         <v>646</v>
-      </c>
-      <c r="D218" s="10" t="s">
-        <v>647</v>
       </c>
       <c r="E218" s="8" t="s">
         <v>455</v>
@@ -10965,13 +10968,13 @@
         <v>298</v>
       </c>
       <c r="C219" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="D219" s="10" t="s">
         <v>648</v>
       </c>
-      <c r="D219" s="10" t="s">
-        <v>649</v>
-      </c>
       <c r="E219" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>473</v>
@@ -10988,19 +10991,19 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B220" s="8" t="s">
         <v>291</v>
       </c>
       <c r="C220" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D220" s="8">
         <v>533</v>
       </c>
       <c r="E220" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>369</v>
@@ -11017,28 +11020,28 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B221" s="8" t="s">
         <v>291</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D221" s="8">
         <v>272</v>
       </c>
       <c r="E221" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="F221" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="F221" s="8" t="s">
+      <c r="G221" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H221" s="8" t="s">
         <v>655</v>
-      </c>
-      <c r="G221" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H221" s="8" t="s">
-        <v>656</v>
       </c>
       <c r="I221" s="9">
         <v>43416</v>
@@ -11052,22 +11055,22 @@
         <v>50</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D222" s="8">
         <v>213</v>
       </c>
       <c r="E222" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="F222" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="F222" s="8" t="s">
+      <c r="G222" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H222" s="8" t="s">
         <v>659</v>
-      </c>
-      <c r="G222" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H222" s="8" t="s">
-        <v>660</v>
       </c>
       <c r="I222" s="9">
         <v>42751</v>
@@ -11081,22 +11084,22 @@
         <v>50</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D223" s="8">
         <v>329</v>
       </c>
       <c r="E223" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F223" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H223" s="8" t="s">
         <v>659</v>
-      </c>
-      <c r="G223" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H223" s="8" t="s">
-        <v>660</v>
       </c>
       <c r="I223" s="9">
         <v>43682</v>
@@ -11110,22 +11113,22 @@
         <v>50</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D224" s="8">
         <v>908</v>
       </c>
       <c r="E224" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="F224" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="F224" s="8" t="s">
-        <v>665</v>
-      </c>
       <c r="G224" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="I224" s="9">
         <v>45887</v>
@@ -11139,22 +11142,22 @@
         <v>50</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D225" s="8">
         <v>937</v>
       </c>
       <c r="E225" s="8" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="I225" s="9">
         <v>45964</v>
@@ -11168,22 +11171,22 @@
         <v>50</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D226" s="8">
         <v>208</v>
       </c>
       <c r="E226" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="F226" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="F226" s="8" t="s">
-        <v>670</v>
-      </c>
       <c r="G226" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="I226" s="9">
         <v>42614</v>
@@ -11197,16 +11200,16 @@
         <v>30</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D227" s="8">
         <v>765</v>
       </c>
       <c r="E227" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="F227" s="8" t="s">
         <v>672</v>
-      </c>
-      <c r="F227" s="8" t="s">
-        <v>673</v>
       </c>
       <c r="G227" s="8" t="s">
         <v>35</v>
@@ -11226,16 +11229,16 @@
         <v>30</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D228" s="8">
         <v>754</v>
       </c>
       <c r="E228" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="F228" s="8" t="s">
         <v>675</v>
-      </c>
-      <c r="F228" s="8" t="s">
-        <v>676</v>
       </c>
       <c r="G228" s="8" t="s">
         <v>35</v>
@@ -11255,16 +11258,16 @@
         <v>30</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D229" s="8">
         <v>883</v>
       </c>
       <c r="E229" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="F229" s="8" t="s">
         <v>678</v>
-      </c>
-      <c r="F229" s="8" t="s">
-        <v>679</v>
       </c>
       <c r="G229" s="8" t="s">
         <v>35</v>
@@ -11284,22 +11287,22 @@
         <v>391</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D230" s="10">
         <v>0</v>
       </c>
       <c r="E230" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="F230" s="8" t="s">
         <v>681</v>
-      </c>
-      <c r="F230" s="8" t="s">
-        <v>682</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I230" s="9">
         <v>45964</v>
@@ -11313,22 +11316,22 @@
         <v>391</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D231" s="10">
         <v>0</v>
       </c>
       <c r="E231" s="8" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F231" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I231" s="9">
         <v>45757</v>
@@ -11342,22 +11345,22 @@
         <v>391</v>
       </c>
       <c r="C232" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="D232" s="10" t="s">
         <v>686</v>
       </c>
-      <c r="D232" s="10" t="s">
+      <c r="E232" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="E232" s="8" t="s">
-        <v>688</v>
-      </c>
       <c r="F232" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G232" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H232" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I232" s="9">
         <v>45244</v>
@@ -11371,22 +11374,22 @@
         <v>391</v>
       </c>
       <c r="C233" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="D233" s="10" t="s">
         <v>689</v>
       </c>
-      <c r="D233" s="10" t="s">
+      <c r="E233" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="E233" s="8" t="s">
+      <c r="F233" s="8" t="s">
         <v>691</v>
-      </c>
-      <c r="F233" s="8" t="s">
-        <v>692</v>
       </c>
       <c r="G233" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H233" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I233" s="9">
         <v>45677</v>
@@ -11400,22 +11403,22 @@
         <v>391</v>
       </c>
       <c r="C234" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="D234" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="D234" s="10" t="s">
+      <c r="E234" s="8" t="s">
         <v>694</v>
       </c>
-      <c r="E234" s="8" t="s">
-        <v>695</v>
-      </c>
       <c r="F234" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I234" s="9">
         <v>44494</v>
@@ -11429,13 +11432,13 @@
         <v>391</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D235" s="10">
         <v>0</v>
       </c>
       <c r="E235" s="8" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>254</v>
@@ -11444,7 +11447,7 @@
         <v>393</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I235" s="9">
         <v>46043</v>
@@ -11458,22 +11461,22 @@
         <v>391</v>
       </c>
       <c r="C236" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="D236" s="10" t="s">
         <v>698</v>
       </c>
-      <c r="D236" s="10" t="s">
+      <c r="E236" s="8" t="s">
         <v>699</v>
       </c>
-      <c r="E236" s="8" t="s">
+      <c r="F236" s="8" t="s">
         <v>700</v>
-      </c>
-      <c r="F236" s="8" t="s">
-        <v>701</v>
       </c>
       <c r="G236" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H236" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I236" s="9">
         <v>44714</v>
@@ -11487,22 +11490,22 @@
         <v>391</v>
       </c>
       <c r="C237" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="D237" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="D237" s="10" t="s">
+      <c r="E237" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="E237" s="8" t="s">
+      <c r="F237" s="8" t="s">
         <v>704</v>
-      </c>
-      <c r="F237" s="8" t="s">
-        <v>705</v>
       </c>
       <c r="G237" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I237" s="9">
         <v>45600</v>
@@ -11516,22 +11519,22 @@
         <v>391</v>
       </c>
       <c r="C238" s="8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D238" s="10">
         <v>0</v>
       </c>
       <c r="E238" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="F238" s="8" t="s">
         <v>707</v>
-      </c>
-      <c r="F238" s="8" t="s">
-        <v>708</v>
       </c>
       <c r="G238" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H238" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I238" s="9">
         <v>45824</v>
@@ -11545,22 +11548,22 @@
         <v>391</v>
       </c>
       <c r="C239" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="D239" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="D239" s="10" t="s">
+      <c r="E239" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="E239" s="8" t="s">
-        <v>711</v>
-      </c>
       <c r="F239" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H239" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I239" s="9">
         <v>45383</v>
@@ -11574,7 +11577,7 @@
         <v>70</v>
       </c>
       <c r="C240" s="8" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D240" s="8">
         <v>740</v>
@@ -11583,13 +11586,13 @@
         <v>112</v>
       </c>
       <c r="F240" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H240" s="8" t="s">
         <v>713</v>
-      </c>
-      <c r="G240" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H240" s="8" t="s">
-        <v>714</v>
       </c>
       <c r="I240" s="9">
         <v>45516</v>
@@ -11603,7 +11606,7 @@
         <v>70</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D241" s="8">
         <v>390</v>
@@ -11612,13 +11615,13 @@
         <v>415</v>
       </c>
       <c r="F241" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="G241" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H241" s="8" t="s">
         <v>716</v>
-      </c>
-      <c r="G241" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H241" s="8" t="s">
-        <v>717</v>
       </c>
       <c r="I241" s="9">
         <v>44342</v>
@@ -11632,7 +11635,7 @@
         <v>70</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D242" s="8">
         <v>645</v>
@@ -11641,7 +11644,7 @@
         <v>104</v>
       </c>
       <c r="F242" s="8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G242" s="8" t="s">
         <v>109</v>
@@ -11661,22 +11664,22 @@
         <v>70</v>
       </c>
       <c r="C243" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="D243" s="10" t="s">
         <v>720</v>
-      </c>
-      <c r="D243" s="10" t="s">
-        <v>721</v>
       </c>
       <c r="E243" s="8" t="s">
         <v>209</v>
       </c>
       <c r="F243" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H243" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="I243" s="9">
         <v>44197</v>
@@ -11690,22 +11693,22 @@
         <v>48</v>
       </c>
       <c r="C244" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D244" s="10" t="s">
         <v>724</v>
-      </c>
-      <c r="D244" s="10" t="s">
-        <v>725</v>
       </c>
       <c r="E244" s="8" t="s">
         <v>315</v>
       </c>
       <c r="F244" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H244" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="I244" s="9">
         <v>44197</v>
@@ -11719,22 +11722,22 @@
         <v>48</v>
       </c>
       <c r="C245" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="D245" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="D245" s="10" t="s">
-        <v>728</v>
-      </c>
       <c r="E245" s="8" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F245" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G245" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I245" s="9">
         <v>44197</v>
@@ -11748,22 +11751,22 @@
         <v>48</v>
       </c>
       <c r="C246" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="D246" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="D246" s="10" t="s">
-        <v>731</v>
-      </c>
       <c r="E246" s="8" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F246" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G246" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H246" s="8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I246" s="9">
         <v>44246</v>
@@ -11777,22 +11780,22 @@
         <v>48</v>
       </c>
       <c r="C247" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="D247" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="D247" s="10" t="s">
-        <v>734</v>
-      </c>
       <c r="E247" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F247" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H247" s="8" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I247" s="9">
         <v>44197</v>
@@ -11806,22 +11809,22 @@
         <v>183</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D248" s="8">
         <v>879</v>
       </c>
       <c r="E248" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="F248" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="F248" s="8" t="s">
-        <v>738</v>
-      </c>
       <c r="G248" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H248" s="8" t="s">
-        <v>426</v>
+        <v>862</v>
       </c>
       <c r="I248" s="9">
         <v>45789</v>
@@ -11835,22 +11838,22 @@
         <v>183</v>
       </c>
       <c r="C249" s="8" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D249" s="8">
         <v>783</v>
       </c>
       <c r="E249" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F249" s="8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G249" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H249" s="8" t="s">
-        <v>426</v>
+        <v>862</v>
       </c>
       <c r="I249" s="9">
         <v>45600</v>
@@ -11864,22 +11867,22 @@
         <v>183</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D250" s="8">
         <v>784</v>
       </c>
       <c r="E250" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="F250" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="F250" s="8" t="s">
-        <v>743</v>
-      </c>
       <c r="G250" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H250" s="8" t="s">
-        <v>426</v>
+        <v>862</v>
       </c>
       <c r="I250" s="9">
         <v>45600</v>
@@ -11887,28 +11890,28 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="C251" s="8" t="s">
         <v>744</v>
-      </c>
-      <c r="B251" s="8" t="s">
-        <v>744</v>
-      </c>
-      <c r="C251" s="8" t="s">
-        <v>745</v>
       </c>
       <c r="D251" s="8">
         <v>871</v>
       </c>
       <c r="E251" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="F251" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="F251" s="8" t="s">
+      <c r="G251" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H251" s="8" t="s">
         <v>747</v>
-      </c>
-      <c r="G251" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H251" s="8" t="s">
-        <v>748</v>
       </c>
       <c r="I251" s="9">
         <v>45782</v>
@@ -11916,28 +11919,28 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C252" s="8" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D252" s="8">
         <v>899</v>
       </c>
       <c r="E252" s="8" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F252" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H252" s="8" t="s">
         <v>747</v>
-      </c>
-      <c r="G252" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H252" s="8" t="s">
-        <v>748</v>
       </c>
       <c r="I252" s="9">
         <v>45873</v>
@@ -11945,28 +11948,28 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D253" s="8">
         <v>936</v>
       </c>
       <c r="E253" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="F253" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="F253" s="8" t="s">
-        <v>753</v>
-      </c>
       <c r="G253" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H253" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I253" s="9">
         <v>45964</v>
@@ -11974,28 +11977,28 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B254" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C254" s="8" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D254" s="8">
         <v>672</v>
       </c>
       <c r="E254" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="F254" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="F254" s="8" t="s">
-        <v>756</v>
-      </c>
       <c r="G254" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H254" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I254" s="9">
         <v>45323</v>
@@ -12003,28 +12006,28 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B255" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C255" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D255" s="8">
         <v>706</v>
       </c>
       <c r="E255" s="8" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F255" s="8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G255" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H255" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I255" s="9">
         <v>45446</v>
@@ -12038,16 +12041,16 @@
         <v>112</v>
       </c>
       <c r="C256" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="D256" s="10" t="s">
         <v>759</v>
-      </c>
-      <c r="D256" s="10" t="s">
-        <v>760</v>
       </c>
       <c r="E256" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G256" s="8" t="s">
         <v>35</v>
@@ -12067,7 +12070,7 @@
         <v>112</v>
       </c>
       <c r="C257" s="8" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D257" s="8">
         <v>487</v>
@@ -12076,7 +12079,7 @@
         <v>111</v>
       </c>
       <c r="F257" s="8" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G257" s="8" t="s">
         <v>35</v>
@@ -12096,16 +12099,16 @@
         <v>112</v>
       </c>
       <c r="C258" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="D258" s="10" t="s">
         <v>763</v>
-      </c>
-      <c r="D258" s="10" t="s">
-        <v>764</v>
       </c>
       <c r="E258" s="8" t="s">
         <v>215</v>
       </c>
       <c r="F258" s="8" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G258" s="8" t="s">
         <v>35</v>
@@ -12125,7 +12128,7 @@
         <v>112</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D259" s="8">
         <v>891</v>
@@ -12134,7 +12137,7 @@
         <v>332</v>
       </c>
       <c r="F259" s="8" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G259" s="8" t="s">
         <v>35</v>
@@ -12154,13 +12157,13 @@
         <v>295</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D260" s="8">
         <v>856</v>
       </c>
       <c r="E260" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>473</v>
@@ -12169,7 +12172,7 @@
         <v>35</v>
       </c>
       <c r="H260" s="8" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I260" s="9">
         <v>45733</v>
@@ -12183,16 +12186,16 @@
         <v>291</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D261" s="8">
         <v>794</v>
       </c>
       <c r="E261" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="F261" s="8" t="s">
         <v>768</v>
-      </c>
-      <c r="F261" s="8" t="s">
-        <v>769</v>
       </c>
       <c r="G261" s="8" t="s">
         <v>35</v>
@@ -12212,16 +12215,16 @@
         <v>291</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D262" s="8">
         <v>538</v>
       </c>
       <c r="E262" s="8" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F262" s="8" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G262" s="8" t="s">
         <v>35</v>
@@ -12241,13 +12244,13 @@
         <v>291</v>
       </c>
       <c r="C263" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D263" s="8">
         <v>950</v>
       </c>
       <c r="E263" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>369</v>
@@ -12270,7 +12273,7 @@
         <v>291</v>
       </c>
       <c r="C264" s="8" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D264" s="8">
         <v>548</v>
@@ -12279,7 +12282,7 @@
         <v>366</v>
       </c>
       <c r="F264" s="8" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G264" s="8" t="s">
         <v>35</v>
@@ -12299,13 +12302,13 @@
         <v>291</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D265" s="8">
         <v>261</v>
       </c>
       <c r="E265" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>344</v>
@@ -12328,13 +12331,13 @@
         <v>291</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D266" s="8">
         <v>418</v>
       </c>
       <c r="E266" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>344</v>
@@ -12357,7 +12360,7 @@
         <v>291</v>
       </c>
       <c r="C267" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D267" s="8">
         <v>749</v>
@@ -12366,7 +12369,7 @@
         <v>371</v>
       </c>
       <c r="F267" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G267" s="8" t="s">
         <v>35</v>
@@ -12386,16 +12389,16 @@
         <v>291</v>
       </c>
       <c r="C268" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D268" s="8">
         <v>673</v>
       </c>
       <c r="E268" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F268" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G268" s="8" t="s">
         <v>35</v>
@@ -12415,13 +12418,13 @@
         <v>291</v>
       </c>
       <c r="C269" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D269" s="8">
         <v>954</v>
       </c>
       <c r="E269" s="8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>481</v>
@@ -12444,22 +12447,22 @@
         <v>161</v>
       </c>
       <c r="C270" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="D270" s="10" t="s">
         <v>786</v>
       </c>
-      <c r="D270" s="10" t="s">
+      <c r="E270" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="E270" s="8" t="s">
+      <c r="F270" s="8" t="s">
         <v>788</v>
-      </c>
-      <c r="F270" s="8" t="s">
-        <v>789</v>
       </c>
       <c r="G270" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H270" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="I270" s="9">
         <v>44774</v>
@@ -12473,22 +12476,22 @@
         <v>161</v>
       </c>
       <c r="C271" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="D271" s="10" t="s">
         <v>791</v>
       </c>
-      <c r="D271" s="10" t="s">
+      <c r="E271" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="E271" s="8" t="s">
+      <c r="F271" s="8" t="s">
         <v>793</v>
-      </c>
-      <c r="F271" s="8" t="s">
-        <v>794</v>
       </c>
       <c r="G271" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H271" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="I271" s="9">
         <v>45758</v>
@@ -12502,22 +12505,22 @@
         <v>161</v>
       </c>
       <c r="C272" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="D272" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="D272" s="10" t="s">
+      <c r="E272" s="8" t="s">
         <v>796</v>
       </c>
-      <c r="E272" s="8" t="s">
+      <c r="F272" s="8" t="s">
         <v>797</v>
-      </c>
-      <c r="F272" s="8" t="s">
-        <v>798</v>
       </c>
       <c r="G272" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H272" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="I272" s="9">
         <v>45481</v>
@@ -12525,19 +12528,19 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D273" s="8">
         <v>770</v>
       </c>
       <c r="E273" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>305</v>
@@ -12554,19 +12557,19 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D274" s="8">
         <v>786</v>
       </c>
       <c r="E274" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>305</v>
@@ -12583,19 +12586,19 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D275" s="8">
         <v>720</v>
       </c>
       <c r="E275" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>305</v>
@@ -12612,19 +12615,19 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D276" s="8">
         <v>940</v>
       </c>
       <c r="E276" s="8" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>305</v>
@@ -12641,19 +12644,19 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C277" s="8" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D277" s="8">
         <v>687</v>
       </c>
       <c r="E277" s="8" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>312</v>
@@ -12670,19 +12673,19 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D278" s="8">
         <v>623</v>
       </c>
       <c r="E278" s="8" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>312</v>
@@ -12699,19 +12702,19 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D279" s="8">
         <v>792</v>
       </c>
       <c r="E279" s="8" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>312</v>
@@ -12728,19 +12731,19 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B280" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D280" s="8">
         <v>771</v>
       </c>
       <c r="E280" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>312</v>
@@ -12757,19 +12760,19 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B281" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D281" s="8">
         <v>711</v>
       </c>
       <c r="E281" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>463</v>
@@ -12786,19 +12789,19 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D282" s="8">
         <v>874</v>
       </c>
       <c r="E282" s="8" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>463</v>
@@ -12815,19 +12818,19 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D283" s="8">
         <v>875</v>
       </c>
       <c r="E283" s="8" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>463</v>
@@ -12844,19 +12847,19 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D284" s="8">
         <v>852</v>
       </c>
       <c r="E284" s="8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>463</v>
@@ -12873,19 +12876,19 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D285" s="8">
         <v>790</v>
       </c>
       <c r="E285" s="8" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>463</v>
@@ -12902,19 +12905,19 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D286" s="8">
         <v>847</v>
       </c>
       <c r="E286" s="8" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>463</v>
@@ -12931,19 +12934,19 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D287" s="8">
         <v>939</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>463</v>
@@ -12960,19 +12963,19 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D288" s="8">
         <v>753</v>
       </c>
       <c r="E288" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>463</v>
@@ -12989,19 +12992,19 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D289" s="8">
         <v>828</v>
       </c>
       <c r="E289" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>467</v>
@@ -13055,312 +13058,312 @@
   <sheetData>
     <row r="1" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>833</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>834</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>835</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>836</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>837</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>839</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>841</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>844</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>847</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>424</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O2" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="Q2" s="12"/>
     </row>
     <row r="3" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>424</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H3" s="13"/>
       <c r="I3" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J3" s="13"/>
       <c r="K3" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L3" s="13"/>
       <c r="M3" s="12" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O3" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="Q3" s="12"/>
     </row>
     <row r="4" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>424</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="O4" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="Q4" s="12"/>
     </row>
     <row r="5" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>502</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="12" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="O5" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="Q5" s="12"/>
     </row>
     <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>502</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="O6" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="Q6" s="12"/>
     </row>
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>502</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L7" s="13"/>
       <c r="M7" s="12" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="O7" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="Q7" s="12"/>
     </row>
     <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>255</v>
@@ -13370,19 +13373,19 @@
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="12" t="s">
@@ -13396,13 +13399,13 @@
         <v>SIM</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="Q8" s="12"/>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>255</v>
@@ -13412,19 +13415,19 @@
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="12" t="s">
@@ -13438,13 +13441,13 @@
         <v>SIM</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="Q9" s="12"/>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>255</v>
@@ -13454,19 +13457,19 @@
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="12" t="s">
@@ -13480,13 +13483,13 @@
         <v>SIM</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="Q10" s="12"/>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>255</v>
@@ -13496,19 +13499,19 @@
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="12" t="s">
@@ -13522,13 +13525,13 @@
         <v>SIM</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="Q11" s="12"/>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>255</v>
@@ -13538,19 +13541,19 @@
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="12" t="s">
@@ -13564,7 +13567,7 @@
         <v>SIM</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="Q12" s="12"/>
     </row>
@@ -13592,10 +13595,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C1" t="s">
         <v>856</v>
-      </c>
-      <c r="C1" t="s">
-        <v>857</v>
       </c>
       <c r="D1">
         <f>D3-D2</f>
@@ -13604,14 +13607,14 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B2">
         <f>COUNTA(A:A)-2</f>
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D2">
         <f>B2</f>
@@ -13623,7 +13626,7 @@
         <v>424</v>
       </c>
       <c r="C3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D3">
         <f>COUNTA(_xlfn.UNIQUE(Base_Dados!A:A))-1</f>
@@ -13637,7 +13640,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
   </sheetData>
@@ -13661,7 +13664,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -14225,15 +14228,15 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A7D4A8F-52B7-4BA2-992B-E5B305E8A525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C77AE3A-83A8-4BAF-B252-71F3B21F5E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2649,10 +2649,10 @@
     <t xml:space="preserve">RESPOSTA PENDENTE: </t>
   </si>
   <si>
-    <t>Q</t>
-  </si>
-  <si>
     <t>FINANCAS</t>
+  </si>
+  <si>
+    <t>JULIO CESAR BARBOSA BENEDITO COSTA</t>
   </si>
 </sst>
 </file>
@@ -9408,7 +9408,7 @@
         <v>493</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>515</v>
@@ -11824,7 +11824,7 @@
         <v>35</v>
       </c>
       <c r="H248" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="I248" s="9">
         <v>45789</v>
@@ -11853,7 +11853,7 @@
         <v>35</v>
       </c>
       <c r="H249" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="I249" s="9">
         <v>45600</v>
@@ -11882,7 +11882,7 @@
         <v>35</v>
       </c>
       <c r="H250" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="I250" s="9">
         <v>45600</v>

--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C77AE3A-83A8-4BAF-B252-71F3B21F5E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED29D2DF-F294-45AB-9FAA-9A7A283D672C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="73" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="882">
   <si>
     <t>Gestor Avaliador</t>
   </si>
@@ -2388,9 +2388,6 @@
     <t>802145</t>
   </si>
   <si>
-    <t>DESENVOLVEDOR UI UX SR</t>
-  </si>
-  <si>
     <t>13168</t>
   </si>
   <si>
@@ -2649,10 +2646,71 @@
     <t xml:space="preserve">RESPOSTA PENDENTE: </t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>FINANCAS</t>
   </si>
   <si>
+    <t>31/03/2026 11:01</t>
+  </si>
+  <si>
+    <t>PEPO-202603311101</t>
+  </si>
+  <si>
+    <t>31/03/2026 12:14</t>
+  </si>
+  <si>
+    <t>PEPO-202603311214</t>
+  </si>
+  <si>
+    <t>A colaboradora Slayne Araujo está em licença maternidade.
+Com as alterações de estrutura em Operações, o Luis Kalil passou a ser o líder direto da colaboradora Carine Santos, porém a avaliação se refere ao período em que ela estava sob minha gestão, por isso preenchi o formulário.</t>
+  </si>
+  <si>
+    <t>31/03/2026 12:26</t>
+  </si>
+  <si>
+    <t>PEPO-202603311226</t>
+  </si>
+  <si>
+    <t>O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon.</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>31/03/2026 12:31</t>
+  </si>
+  <si>
+    <t>PEPO-202603311231</t>
+  </si>
+  <si>
+    <t>31/03/2026 12:50</t>
+  </si>
+  <si>
+    <t>PEPO-202603311250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanderson Lage não irá participar do ciclo, pode retira-lo </t>
+  </si>
+  <si>
+    <t>31/03/2026 14:08</t>
+  </si>
+  <si>
+    <t>PEPO-202603311408</t>
+  </si>
+  <si>
+    <t>31/03/2026 14:40</t>
+  </si>
+  <si>
+    <t>PEPO-202603311440</t>
+  </si>
+  <si>
     <t>JULIO CESAR BARBOSA BENEDITO COSTA</t>
+  </si>
+  <si>
+    <t>PEPO-202604011025</t>
   </si>
 </sst>
 </file>
@@ -2766,7 +2824,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2785,6 +2843,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3273,10 +3337,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>58</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4024,30 +4088,41 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46112.186870486112" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Regiane Aparecida De Souza Andrade" refreshedDate="46113.453509259256" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="46" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
   <cacheSource type="worksheet">
     <worksheetSource name="TabelaRespostas"/>
   </cacheSource>
   <cacheFields count="17">
     <cacheField name="Momento do Envio" numFmtId="0">
-      <sharedItems/>
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-04T10:25:00" maxDate="2026-01-04T10:25:00"/>
     </cacheField>
     <cacheField name="Nome do Gestor" numFmtId="0">
-      <sharedItems containsBlank="1" count="13">
+      <sharedItems containsBlank="1" count="20">
         <s v="THIAGO DA SILVA CHISNANDES"/>
         <s v="NUBIA AQUINO DA SILVA"/>
+        <s v="CAROLINE PAIXÃO VIEIRA DE SENA"/>
+        <s v="RENNAN LUCIO DE MOURA"/>
+        <s v="ALINE DE GOES CAMARGO"/>
+        <s v="VICTOR JOSE ALVES FERNANDES"/>
+        <s v="LORRAYNE CRISTINE THEZA DO CARMO"/>
+        <s v="AQUILES VILAR MOTA GUIMARAES"/>
+        <s v="JEZI FERNANDO OLIVEIRA"/>
+        <s v="MARCELA REGGIANI MORAES"/>
+        <s v="MARIANA DE ALBUQUERQUE LOPES"/>
         <m u="1"/>
         <s v="VANUZA DOS SANTOS PRESTES" u="1"/>
         <s v="CAMILA DA SILVA ANDRADE" u="1"/>
         <s v="ANDRE NADDEO" u="1"/>
         <s v="AMANDA MIRANDA DE CARVALHO" u="1"/>
         <s v="ELISON GLAUBER DE CASTRO" u="1"/>
-        <s v="ALINE DE GOES CAMARGO" u="1"/>
         <s v="DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH" u="1"/>
         <s v="DIEGO PIRES" u="1"/>
         <s v="ELIANE PEREIRA DA SILVA HIDALGO" u="1"/>
-        <s v="LORRAYNE CRISTINE THEZA DO CARMO" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Funcionário Avaliado" numFmtId="0">
@@ -4060,13 +4135,13 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Novo Gestor" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Cargo Correto?" numFmtId="0">
       <sharedItems/>
     </cacheField>
     <cacheField name="Novo Cargo" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Unidade Correta?" numFmtId="0">
       <sharedItems/>
@@ -4093,7 +4168,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Observações" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsBlank="1" longText="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -4105,7 +4180,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="6">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="46">
   <r>
     <s v="30/03/2026 17:50"/>
     <x v="0"/>
@@ -4220,29 +4295,796 @@
     <s v="PEPO-202603310754"/>
     <m/>
   </r>
+  <r>
+    <s v="31/03/2026 08:23"/>
+    <x v="2"/>
+    <s v="RODRIGO FERREIRA DA SILVA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="JENNEFER HONORIO SOUZA"/>
+    <s v="VICTORIA CAROLINNE SOLANO NOVAIS"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603310823"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 08:23"/>
+    <x v="2"/>
+    <s v="VICTORIA CAROLINNE SOLANO NOVAIS"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="STEPHANY MAGALHAES DIAS"/>
+    <s v="JENNEFER HONORIO SOUZA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603310823"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 08:23"/>
+    <x v="2"/>
+    <s v="JENNEFER HONORIO SOUZA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RODRIGO FERREIRA DA SILVA"/>
+    <s v="VITORIA BARBOSA SENRA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603310823"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 08:23"/>
+    <x v="2"/>
+    <s v="STEPHANY MAGALHAES DIAS"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="VITORIA BARBOSA SENRA"/>
+    <s v="VICTORIA CAROLINNE SOLANO NOVAIS"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603310823"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 08:23"/>
+    <x v="2"/>
+    <s v="VITORIA BARBOSA SENRA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="STEPHANY MAGALHAES DIAS"/>
+    <s v="VICTORIA CAROLINNE SOLANO NOVAIS"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603310823"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 11:01"/>
+    <x v="3"/>
+    <s v="ARTHUR RODRIGUES MENEZES"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="CAUA MARQUES GOMES DA SILVA FARIA"/>
+    <s v="CHRISTIAN NEVES TORRES"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311101"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 11:01"/>
+    <x v="3"/>
+    <s v="CAUA MARQUES GOMES DA SILVA FARIA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ARTHUR RODRIGUES MENEZES"/>
+    <s v="DAMARIS MARTINHO SOARES SOUZA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311101"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 11:01"/>
+    <x v="3"/>
+    <s v="CHRISTIAN NEVES TORRES"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="DAMARIS MARTINHO SOARES SOUZA"/>
+    <s v="ERICK GONCALVES OLIVEIRA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311101"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 11:01"/>
+    <x v="3"/>
+    <s v="DAMARIS MARTINHO SOARES SOUZA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="CAUA MARQUES GOMES DA SILVA FARIA"/>
+    <s v="CHRISTIAN NEVES TORRES"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311101"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 11:01"/>
+    <x v="3"/>
+    <s v="ERICK GONCALVES OLIVEIRA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ARTHUR RODRIGUES MENEZES"/>
+    <s v="MATHEUS FERNANDO OLIVEIRA ROCHA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311101"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 11:01"/>
+    <x v="3"/>
+    <s v="MATHEUS FERNANDO OLIVEIRA ROCHA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="SERGIO TEIXEIRA DA COSTA FILHO"/>
+    <s v="ERICK GONCALVES OLIVEIRA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311101"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 11:01"/>
+    <x v="3"/>
+    <s v="SERGIO TEIXEIRA DA COSTA FILHO"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="CHRISTIAN NEVES TORRES"/>
+    <s v="DAMARIS MARTINHO SOARES SOUZA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311101"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:14"/>
+    <x v="4"/>
+    <s v="ELIANE PEREIRA DA SILVA HIDALGO"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RENNAN LUCIO DE MOURA"/>
+    <s v="CATERINE NUNES BARBOSA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311214"/>
+    <s v="A colaboradora Slayne Araujo está em licença maternidade._x000a_Com as alterações de estrutura em Operações, o Luis Kalil passou a ser o líder direto da colaboradora Carine Santos, porém a avaliação se refere ao período em que ela estava sob minha gestão, por isso preenchi o formulário."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:14"/>
+    <x v="4"/>
+    <s v="RENNAN LUCIO DE MOURA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ELIANE PEREIRA DA SILVA HIDALGO"/>
+    <s v="CARINE REIS DOS SANTOS"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311214"/>
+    <s v="A colaboradora Slayne Araujo está em licença maternidade._x000a_Com as alterações de estrutura em Operações, o Luis Kalil passou a ser o líder direto da colaboradora Carine Santos, porém a avaliação se refere ao período em que ela estava sob minha gestão, por isso preenchi o formulário."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:14"/>
+    <x v="4"/>
+    <s v="CARINE REIS DOS SANTOS"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RENNAN LUCIO DE MOURA"/>
+    <s v="ELIANE PEREIRA DA SILVA HIDALGO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311214"/>
+    <s v="A colaboradora Slayne Araujo está em licença maternidade._x000a_Com as alterações de estrutura em Operações, o Luis Kalil passou a ser o líder direto da colaboradora Carine Santos, porém a avaliação se refere ao período em que ela estava sob minha gestão, por isso preenchi o formulário."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:14"/>
+    <x v="4"/>
+    <s v="SLAYNE FERNANDA NERES GOMES BRUM ARAUJO"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RENNAN LUCIO DE MOURA"/>
+    <s v="CARINE REIS DOS SANTOS"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311214"/>
+    <s v="A colaboradora Slayne Araujo está em licença maternidade._x000a_Com as alterações de estrutura em Operações, o Luis Kalil passou a ser o líder direto da colaboradora Carine Santos, porém a avaliação se refere ao período em que ela estava sob minha gestão, por isso preenchi o formulário."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="PEDRO HENRIQUE COSTA OLIVEIRA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RAYLAN NUNES BARBOSA"/>
+    <s v="VICTOR ARAUJO PORTO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="VITOR ZARETZKI DE SOUZA"/>
+    <m/>
+    <s v="Não"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="THAIS HERINGER DA SILVA"/>
+    <s v="EMANUELLY ASSUERIA BEZERRA MARTINS"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="CASSIO LUIZ RODRIGUES DA SILVA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="SERGIO TEIXEIRA DA COSTA FILHO"/>
+    <s v="DAMARIS MARTINHO SOARES SOUZA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="NATALIA DE ABREU PIRES"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="GUILHERME GOMES DA SILVA"/>
+    <s v="RAYLAN NUNES BARBOSA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="LEANDRO CORREA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RAYLAN NUNES BARBOSA"/>
+    <s v="GIOVANNA DE ARAUJO GIACON"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="GIOVANNA DE ARAUJO GIACON"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Não"/>
+    <s v="PRODUCT OPS JR"/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RAYLAN NUNES BARBOSA"/>
+    <s v="CAROLINE ANDRADE SANTOS BACELAR"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="GUILHERME GOMES DA SILVA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="NATALIA DE ABREU PIRES"/>
+    <s v="VICTOR ARAUJO PORTO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="RAYLAN NUNES BARBOSA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="VICTOR ARAUJO PORTO"/>
+    <s v="NATALIA DE ABREU PIRES"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="GUSTAVO ARANDA DAMBROSKI"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="SAMUEL NUNES RIOS SILVA"/>
+    <s v="GIOVANNA DE ARAUJO GIACON"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="SAMUEL NUNES RIOS SILVA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="GUSTAVO ARANDA DAMBROSKI"/>
+    <s v="GIOVANNA DE ARAUJO GIACON"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:26"/>
+    <x v="5"/>
+    <s v="MARIANA RIBEIRO DA SILVA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="NATALIA DE ABREU PIRES"/>
+    <s v="GUILHERME GOMES DA SILVA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311226"/>
+    <s v="O cargo atual da Giovanna Giacon é Product Ops Jr, e ela exerce a função de PO do App do Vendedor. O gestor do Vitor de Souza é a Giovanna Giacon."/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:31"/>
+    <x v="6"/>
+    <s v="BRUNNA KAROLINE QUEIROZ RODRIGUES"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Não"/>
+    <m/>
+    <s v="THIAGO DA SILVA CHISNANDES"/>
+    <s v="CAROLINE PAIXÃO VIEIRA DE SENA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311231"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:31"/>
+    <x v="6"/>
+    <s v="THIAGO DA SILVA CHISNANDES"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="BRUNNA KAROLINE QUEIROZ RODRIGUES"/>
+    <s v="CAROLINE PAIXÃO VIEIRA DE SENA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311231"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:31"/>
+    <x v="6"/>
+    <s v="CAROLINE PAIXÃO VIEIRA DE SENA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Não"/>
+    <m/>
+    <s v="BRUNNA KAROLINE QUEIROZ RODRIGUES"/>
+    <s v="THIAGO DA SILVA CHISNANDES"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311231"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:50"/>
+    <x v="7"/>
+    <s v="RICARDO ESTEVAO DE ALMEIDA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RENNAN VILAR GUIMARAES CASTRO ANTUNES"/>
+    <s v="LEON DOS REIS CALIXTO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311250"/>
+    <s v="Wanderson Lage não irá participar do ciclo, pode retira-lo "/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:50"/>
+    <x v="7"/>
+    <s v="DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH"/>
+    <m/>
+    <s v="Não"/>
+    <s v="TALES VILAR MOTA GUIMARAES"/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ULISSES LEANDRO CARVALHO FERREIRA"/>
+    <s v="LEON DOS REIS CALIXTO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311250"/>
+    <s v="Wanderson Lage não irá participar do ciclo, pode retira-lo "/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:50"/>
+    <x v="7"/>
+    <s v="RENNAN VILAR GUIMARAES CASTRO ANTUNES"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RICARDO ESTEVAO DE ALMEIDA"/>
+    <s v="DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311250"/>
+    <s v="Wanderson Lage não irá participar do ciclo, pode retira-lo "/>
+  </r>
+  <r>
+    <s v="31/03/2026 12:50"/>
+    <x v="7"/>
+    <s v="WANDERSON LAGE"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="RENNAN VILAR GUIMARAES CASTRO ANTUNES"/>
+    <s v="RICARDO ESTEVAO DE ALMEIDA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311250"/>
+    <s v="Wanderson Lage não irá participar do ciclo, pode retira-lo "/>
+  </r>
+  <r>
+    <s v="31/03/2026 14:08"/>
+    <x v="8"/>
+    <s v="KETTULY FERNANDA ALVES DE AMORIM SANTIAGO"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="CAROLINE PAIXÃO VIEIRA DE SENA"/>
+    <s v="THIAGO DA SILVA CHISNANDES"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311408"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 14:40"/>
+    <x v="9"/>
+    <s v="GABRIELA ARBELLI COLAQUISES ZAGO"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ANA BEATRIZ DA SILVA COSTA"/>
+    <s v="MARIA LUIZA FERREIRA PINTO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311440"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 14:40"/>
+    <x v="9"/>
+    <s v="ANA BEATRIZ DA SILVA COSTA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="GABRIELA ARBELLI COLAQUISES ZAGO"/>
+    <s v="KATHARYNE CRISTINA LOPES DA SILVA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311440"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 14:40"/>
+    <x v="9"/>
+    <s v="MARIA LUIZA FERREIRA PINTO"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ANA BEATRIZ DA SILVA COSTA"/>
+    <s v="KATHARYNE CRISTINA LOPES DA SILVA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311440"/>
+    <m/>
+  </r>
+  <r>
+    <s v="31/03/2026 14:40"/>
+    <x v="9"/>
+    <s v="KATHARYNE CRISTINA LOPES DA SILVA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="GABRIELA ARBELLI COLAQUISES ZAGO"/>
+    <s v="MARIA LUIZA FERREIRA PINTO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202603311440"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-01-04T10:25:00"/>
+    <x v="10"/>
+    <s v="JULIO CESAR BARBOSA BENEDITO COSTA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="MARIA LUIZA SOUZA FILGUEIRAS"/>
+    <s v="RAISSA MENDES LOPES"/>
+    <s v="SIM"/>
+    <s v="PEPO-202604011025"/>
+    <m/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A2:A5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="73" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A2:A14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="14">
+      <items count="21">
         <item x="0"/>
-        <item m="1" x="3"/>
-        <item m="1" x="7"/>
-        <item m="1" x="8"/>
-        <item m="1" x="5"/>
-        <item m="1" x="9"/>
-        <item m="1" x="10"/>
+        <item m="1" x="12"/>
+        <item m="1" x="16"/>
+        <item x="4"/>
+        <item m="1" x="14"/>
+        <item m="1" x="17"/>
+        <item m="1" x="18"/>
+        <item m="1" x="19"/>
+        <item x="6"/>
         <item m="1" x="11"/>
-        <item m="1" x="12"/>
-        <item m="1" x="2"/>
-        <item m="1" x="6"/>
-        <item m="1" x="4"/>
+        <item m="1" x="15"/>
+        <item m="1" x="13"/>
         <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4265,12 +5107,39 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="12">
     <i>
       <x/>
     </i>
     <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
       <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
     </i>
     <i t="grand">
       <x/>
@@ -4310,8 +5179,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q12" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A1:Q12" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q47" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A1:Q47" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{CFF5932B-854B-4B23-A01A-04BA6982E294}" name="Momento do Envio"/>
     <tableColumn id="2" xr3:uid="{9A82702E-3CB5-486A-B49B-3CBF2D1B5744}" name="Nome do Gestor"/>
@@ -5133,7 +6002,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>48</v>
@@ -7975,7 +8844,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="B116" s="8" t="s">
         <v>366</v>
@@ -9408,7 +10277,7 @@
         <v>493</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>515</v>
@@ -12282,7 +13151,7 @@
         <v>366</v>
       </c>
       <c r="F264" s="8" t="s">
-        <v>774</v>
+        <v>344</v>
       </c>
       <c r="G264" s="8" t="s">
         <v>35</v>
@@ -12302,13 +13171,13 @@
         <v>291</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D265" s="8">
         <v>261</v>
       </c>
       <c r="E265" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>344</v>
@@ -12331,13 +13200,13 @@
         <v>291</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D266" s="8">
         <v>418</v>
       </c>
       <c r="E266" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>344</v>
@@ -12360,7 +13229,7 @@
         <v>291</v>
       </c>
       <c r="C267" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D267" s="8">
         <v>749</v>
@@ -12369,7 +13238,7 @@
         <v>371</v>
       </c>
       <c r="F267" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G267" s="8" t="s">
         <v>35</v>
@@ -12389,7 +13258,7 @@
         <v>291</v>
       </c>
       <c r="C268" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D268" s="8">
         <v>673</v>
@@ -12398,7 +13267,7 @@
         <v>649</v>
       </c>
       <c r="F268" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G268" s="8" t="s">
         <v>35</v>
@@ -12418,13 +13287,13 @@
         <v>291</v>
       </c>
       <c r="C269" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D269" s="8">
         <v>954</v>
       </c>
       <c r="E269" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>481</v>
@@ -12447,22 +13316,22 @@
         <v>161</v>
       </c>
       <c r="C270" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="D270" s="10" t="s">
         <v>785</v>
       </c>
-      <c r="D270" s="10" t="s">
+      <c r="E270" s="8" t="s">
         <v>786</v>
       </c>
-      <c r="E270" s="8" t="s">
+      <c r="F270" s="8" t="s">
         <v>787</v>
-      </c>
-      <c r="F270" s="8" t="s">
-        <v>788</v>
       </c>
       <c r="G270" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H270" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I270" s="9">
         <v>44774</v>
@@ -12476,22 +13345,22 @@
         <v>161</v>
       </c>
       <c r="C271" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="D271" s="10" t="s">
         <v>790</v>
       </c>
-      <c r="D271" s="10" t="s">
+      <c r="E271" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="E271" s="8" t="s">
+      <c r="F271" s="8" t="s">
         <v>792</v>
-      </c>
-      <c r="F271" s="8" t="s">
-        <v>793</v>
       </c>
       <c r="G271" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H271" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I271" s="9">
         <v>45758</v>
@@ -12505,22 +13374,22 @@
         <v>161</v>
       </c>
       <c r="C272" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="D272" s="10" t="s">
         <v>794</v>
       </c>
-      <c r="D272" s="10" t="s">
+      <c r="E272" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="E272" s="8" t="s">
+      <c r="F272" s="8" t="s">
         <v>796</v>
-      </c>
-      <c r="F272" s="8" t="s">
-        <v>797</v>
       </c>
       <c r="G272" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H272" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I272" s="9">
         <v>45481</v>
@@ -12534,13 +13403,13 @@
         <v>642</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D273" s="8">
         <v>770</v>
       </c>
       <c r="E273" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>305</v>
@@ -12563,13 +13432,13 @@
         <v>642</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D274" s="8">
         <v>786</v>
       </c>
       <c r="E274" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>305</v>
@@ -12592,13 +13461,13 @@
         <v>642</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D275" s="8">
         <v>720</v>
       </c>
       <c r="E275" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>305</v>
@@ -12621,13 +13490,13 @@
         <v>642</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D276" s="8">
         <v>940</v>
       </c>
       <c r="E276" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>305</v>
@@ -12650,13 +13519,13 @@
         <v>642</v>
       </c>
       <c r="C277" s="8" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D277" s="8">
         <v>687</v>
       </c>
       <c r="E277" s="8" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>312</v>
@@ -12679,13 +13548,13 @@
         <v>642</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D278" s="8">
         <v>623</v>
       </c>
       <c r="E278" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>312</v>
@@ -12708,13 +13577,13 @@
         <v>642</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D279" s="8">
         <v>792</v>
       </c>
       <c r="E279" s="8" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>312</v>
@@ -12737,13 +13606,13 @@
         <v>642</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D280" s="8">
         <v>771</v>
       </c>
       <c r="E280" s="8" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>312</v>
@@ -12766,13 +13635,13 @@
         <v>642</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D281" s="8">
         <v>711</v>
       </c>
       <c r="E281" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>463</v>
@@ -12795,13 +13664,13 @@
         <v>642</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D282" s="8">
         <v>874</v>
       </c>
       <c r="E282" s="8" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>463</v>
@@ -12824,13 +13693,13 @@
         <v>642</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D283" s="8">
         <v>875</v>
       </c>
       <c r="E283" s="8" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>463</v>
@@ -12853,13 +13722,13 @@
         <v>642</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D284" s="8">
         <v>852</v>
       </c>
       <c r="E284" s="8" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>463</v>
@@ -12882,13 +13751,13 @@
         <v>642</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D285" s="8">
         <v>790</v>
       </c>
       <c r="E285" s="8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>463</v>
@@ -12911,13 +13780,13 @@
         <v>642</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D286" s="8">
         <v>847</v>
       </c>
       <c r="E286" s="8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>463</v>
@@ -12940,13 +13809,13 @@
         <v>642</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D287" s="8">
         <v>939</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>463</v>
@@ -12969,13 +13838,13 @@
         <v>642</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D288" s="8">
         <v>753</v>
       </c>
       <c r="E288" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>463</v>
@@ -12998,13 +13867,13 @@
         <v>642</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D289" s="8">
         <v>828</v>
       </c>
       <c r="E289" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>467</v>
@@ -13034,84 +13903,84 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.6640625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="129.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>833</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>834</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>836</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>837</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>839</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>841</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>844</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>846</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>424</v>
@@ -13121,19 +13990,19 @@
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="12" t="s">
@@ -13147,13 +14016,13 @@
         <v>SIM</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="Q2" s="12"/>
     </row>
     <row r="3" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>424</v>
@@ -13163,19 +14032,19 @@
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H3" s="13"/>
       <c r="I3" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J3" s="13"/>
       <c r="K3" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L3" s="13"/>
       <c r="M3" s="12" t="s">
@@ -13189,13 +14058,13 @@
         <v>SIM</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="Q3" s="12"/>
     </row>
     <row r="4" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>424</v>
@@ -13205,19 +14074,19 @@
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="12" t="s">
@@ -13231,13 +14100,13 @@
         <v>SIM</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="Q4" s="12"/>
     </row>
     <row r="5" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>502</v>
@@ -13247,19 +14116,19 @@
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="12" t="s">
@@ -13273,13 +14142,13 @@
         <v>SIM</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="Q5" s="12"/>
     </row>
     <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>502</v>
@@ -13289,19 +14158,19 @@
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="12" t="s">
@@ -13315,13 +14184,13 @@
         <v>SIM</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="Q6" s="12"/>
     </row>
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>502</v>
@@ -13331,19 +14200,19 @@
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L7" s="13"/>
       <c r="M7" s="12" t="s">
@@ -13357,13 +14226,13 @@
         <v>SIM</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="Q7" s="12"/>
     </row>
     <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>255</v>
@@ -13373,19 +14242,19 @@
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="12" t="s">
@@ -13399,13 +14268,13 @@
         <v>SIM</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="Q8" s="12"/>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>255</v>
@@ -13415,19 +14284,19 @@
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="12" t="s">
@@ -13441,13 +14310,13 @@
         <v>SIM</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="Q9" s="12"/>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>255</v>
@@ -13457,19 +14326,19 @@
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="12" t="s">
@@ -13483,13 +14352,13 @@
         <v>SIM</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="Q10" s="12"/>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>255</v>
@@ -13499,19 +14368,19 @@
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="12" t="s">
@@ -13525,13 +14394,13 @@
         <v>SIM</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="Q11" s="12"/>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>255</v>
@@ -13541,19 +14410,19 @@
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="12" t="s">
@@ -13567,9 +14436,1521 @@
         <v>SIM</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="Q12" s="12"/>
+    </row>
+    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F13" s="13"/>
+      <c r="G13" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L13" s="13"/>
+      <c r="M13" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="O13" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q13" s="12"/>
+    </row>
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F14" s="13"/>
+      <c r="G14" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="O14" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q14" s="12"/>
+    </row>
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H15" s="13"/>
+      <c r="I15" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="O15" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q15" s="12"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H16" s="13"/>
+      <c r="I16" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="K16" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="O16" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q16" s="12"/>
+    </row>
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="O17" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q17" s="12"/>
+    </row>
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L18" s="13"/>
+      <c r="M18" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="O18" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q18" s="12"/>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F19" s="13"/>
+      <c r="G19" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H19" s="13"/>
+      <c r="I19" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L19" s="13"/>
+      <c r="M19" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="O19" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q19" s="12"/>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F20" s="13"/>
+      <c r="G20" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H20" s="13"/>
+      <c r="I20" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L20" s="13"/>
+      <c r="M20" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="O20" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q20" s="14" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="G21" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H21" s="13"/>
+      <c r="I21" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L21" s="13"/>
+      <c r="M21" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="O21" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q21" s="14" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H22" s="13"/>
+      <c r="I22" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L22" s="13"/>
+      <c r="M22" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="O22" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P22" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q22" s="14" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F23" s="13"/>
+      <c r="G23" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H23" s="13"/>
+      <c r="I23" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L23" s="13"/>
+      <c r="M23" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="O23" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P23" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q23" s="14" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H24" s="13"/>
+      <c r="I24" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L24" s="13"/>
+      <c r="M24" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="O24" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q24" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L25" s="13"/>
+      <c r="M25" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="O25" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q25" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>767</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H26" s="13"/>
+      <c r="I26" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L26" s="13"/>
+      <c r="M26" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="O26" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q26" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>770</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F27" s="13"/>
+      <c r="G27" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H27" s="13"/>
+      <c r="I27" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L27" s="13"/>
+      <c r="M27" s="12" t="s">
+        <v>775</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="O27" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q27" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>772</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F28" s="13"/>
+      <c r="G28" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H28" s="13"/>
+      <c r="I28" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L28" s="13"/>
+      <c r="M28" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="O28" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q28" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L29" s="13"/>
+      <c r="M29" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="O29" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q29" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>775</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H30" s="13"/>
+      <c r="I30" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J30" s="13"/>
+      <c r="K30" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L30" s="13"/>
+      <c r="M30" s="12" t="s">
+        <v>770</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="O30" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P30" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q30" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H31" s="13"/>
+      <c r="I31" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J31" s="13"/>
+      <c r="K31" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L31" s="13"/>
+      <c r="M31" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>770</v>
+      </c>
+      <c r="O31" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q31" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F32" s="13"/>
+      <c r="G32" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H32" s="13"/>
+      <c r="I32" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J32" s="13"/>
+      <c r="K32" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L32" s="13"/>
+      <c r="M32" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="O32" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P32" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q32" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H33" s="13"/>
+      <c r="I33" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J33" s="13"/>
+      <c r="K33" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L33" s="13"/>
+      <c r="M33" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="O33" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P33" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q33" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>783</v>
+      </c>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F34" s="13"/>
+      <c r="G34" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H34" s="13"/>
+      <c r="I34" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J34" s="13"/>
+      <c r="K34" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L34" s="13"/>
+      <c r="M34" s="12" t="s">
+        <v>770</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>775</v>
+      </c>
+      <c r="O34" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P34" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q34" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F35" s="13"/>
+      <c r="G35" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H35" s="13"/>
+      <c r="I35" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="L35" s="13"/>
+      <c r="M35" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="O35" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P35" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="Q35" s="14"/>
+    </row>
+    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F36" s="13"/>
+      <c r="G36" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H36" s="13"/>
+      <c r="I36" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L36" s="13"/>
+      <c r="M36" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="O36" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P36" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="Q36" s="14"/>
+    </row>
+    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F37" s="13"/>
+      <c r="G37" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H37" s="13"/>
+      <c r="I37" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J37" s="13"/>
+      <c r="K37" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="L37" s="13"/>
+      <c r="M37" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="O37" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P37" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="Q37" s="14"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F38" s="13"/>
+      <c r="G38" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H38" s="13"/>
+      <c r="I38" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J38" s="13"/>
+      <c r="K38" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L38" s="13"/>
+      <c r="M38" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="O38" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P38" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q38" s="14" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H39" s="13"/>
+      <c r="I39" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="K39" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L39" s="13"/>
+      <c r="M39" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="O39" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P39" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q39" s="14" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F40" s="13"/>
+      <c r="G40" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H40" s="13"/>
+      <c r="I40" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J40" s="13"/>
+      <c r="K40" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L40" s="13"/>
+      <c r="M40" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="O40" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P40" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q40" s="14" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F41" s="13"/>
+      <c r="G41" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H41" s="13"/>
+      <c r="I41" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J41" s="13"/>
+      <c r="K41" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L41" s="13"/>
+      <c r="M41" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="O41" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P41" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q41" s="14" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
+        <v>876</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F42" s="13"/>
+      <c r="G42" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J42" s="13"/>
+      <c r="K42" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L42" s="13"/>
+      <c r="M42" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="O42" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P42" s="12" t="s">
+        <v>877</v>
+      </c>
+      <c r="Q42" s="14"/>
+    </row>
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F43" s="13"/>
+      <c r="G43" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H43" s="13"/>
+      <c r="I43" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J43" s="13"/>
+      <c r="K43" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L43" s="13"/>
+      <c r="M43" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="O43" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q43" s="14"/>
+    </row>
+    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F44" s="13"/>
+      <c r="G44" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H44" s="13"/>
+      <c r="I44" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J44" s="13"/>
+      <c r="K44" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L44" s="13"/>
+      <c r="M44" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="O44" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P44" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q44" s="14"/>
+    </row>
+    <row r="45" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F45" s="13"/>
+      <c r="G45" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H45" s="13"/>
+      <c r="I45" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J45" s="13"/>
+      <c r="K45" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L45" s="13"/>
+      <c r="M45" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="O45" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P45" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q45" s="14"/>
+    </row>
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F46" s="13"/>
+      <c r="G46" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H46" s="13"/>
+      <c r="I46" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J46" s="13"/>
+      <c r="K46" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L46" s="13"/>
+      <c r="M46" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="O46" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P46" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q46" s="14"/>
+    </row>
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="15">
+        <v>46026.434027777781</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>880</v>
+      </c>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F47" s="13"/>
+      <c r="G47" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H47" s="13"/>
+      <c r="I47" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J47" s="13"/>
+      <c r="K47" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L47" s="13"/>
+      <c r="M47" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="O47" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P47" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="Q47" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13584,7 +15965,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D594CA1-84CE-4635-82A0-1A17CF6D309A}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
@@ -13595,30 +15976,30 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
+        <v>854</v>
+      </c>
+      <c r="C1" t="s">
         <v>855</v>
-      </c>
-      <c r="C1" t="s">
-        <v>856</v>
       </c>
       <c r="D1">
         <f>D3-D2</f>
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B2">
         <f>COUNTA(A:A)-2</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D2">
         <f>B2</f>
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -13626,21 +16007,66 @@
         <v>424</v>
       </c>
       <c r="C3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D3">
         <f>COUNTA(_xlfn.UNIQUE(Base_Dados!A:A))-1</f>
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>502</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>859</v>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -13664,12 +16090,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="str" cm="1">
-        <f t="array" ref="A2:A57">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A500, (Base_Dados!A2:A500&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A500)=0), "✅ Todos responderam!")))</f>
+        <f t="array" ref="A2:A50">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A500, (Base_Dados!A2:A500&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A500)=0), "✅ Todos responderam!")))</f>
         <v>_</v>
       </c>
     </row>
@@ -13680,273 +16106,259 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="str">
-        <v>ALINE DE GOES CAMARGO</v>
+        <v>ALTAIR DE JESUS VILAR GUIMARAES</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="str">
-        <v>ALTAIR DE JESUS VILAR GUIMARAES</v>
+        <v>AMANDA MIRANDA DE CARVALHO</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="str">
-        <v>AMANDA MIRANDA DE CARVALHO</v>
+        <v>AMANDA STEFANI SOUSA DE ALMEIDA SANTOS</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="str">
-        <v>AMANDA STEFANI SOUSA DE ALMEIDA SANTOS</v>
+        <v>ANDRE NADDEO</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="str">
-        <v>ANDRE NADDEO</v>
+        <v>ANDRESSA RODRIGUES MORATO MAIA</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="str">
-        <v>ANDRESSA RODRIGUES MORATO MAIA</v>
+        <v>ANEDINA IZABEL DUARTE SOUZA</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="str">
-        <v>ANEDINA IZABEL DUARTE SOUZA</v>
+        <v>BRAULIO PIOVEZANA RINCO</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="str">
-        <v>AQUILES VILAR MOTA GUIMARAES</v>
+        <v>BRUNNA KAROLINE QUEIROZ RODRIGUES</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="str">
-        <v>BRAULIO PIOVEZANA RINCO</v>
+        <v>BRUNO CASTRO METZKER</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="str">
-        <v>BRUNNA KAROLINE QUEIROZ RODRIGUES</v>
+        <v>BRUNO NUNES DE SOUZA SANTOS</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="str">
-        <v>BRUNO CASTRO METZKER</v>
+        <v>CAMILA DA SILVA ANDRADE</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="str">
-        <v>BRUNO NUNES DE SOUZA SANTOS</v>
+        <v>CARINE REIS DOS SANTOS</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="str">
-        <v>CAMILA DA SILVA ANDRADE</v>
+        <v>CATERINE NUNES BARBOSA</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="str">
-        <v>CARINE REIS DOS SANTOS</v>
+        <v>DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="str">
-        <v>CATERINE NUNES BARBOSA</v>
+        <v>DENIS GABRIEL ABREU DE MELO</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="str">
-        <v>DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH</v>
+        <v>DIEGO PIRES</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="str">
-        <v>DENIS GABRIEL ABREU DE MELO</v>
+        <v>ELIANE PEREIRA DA SILVA HIDALGO</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="str">
-        <v>DIEGO PIRES</v>
+        <v>ELISANGELA PEDRO RODRIGUES OLIVEIRA</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="str">
-        <v>ELIANE PEREIRA DA SILVA HIDALGO</v>
+        <v>ELISON GLAUBER DE CASTRO</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="str">
-        <v>ELISANGELA PEDRO RODRIGUES OLIVEIRA</v>
+        <v>FLAVIO HENRIQUE ALMEIDA FERREIRA DE MELO</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="str">
-        <v>ELISON GLAUBER DE CASTRO</v>
+        <v>GIOVANNA DE ARAUJO GIACON</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="str">
-        <v>FLAVIO HENRIQUE ALMEIDA FERREIRA DE MELO</v>
+        <v>GUSTAVO ARANDA DAMBROSKI</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="str">
-        <v>GUSTAVO ARANDA DAMBROSKI</v>
+        <v>HAYNA CARDOSO PINTO</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="str">
-        <v>HAYNA CARDOSO PINTO</v>
+        <v>KETTULY FERNANDA ALVES DE AMORIM SANTIAGO</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="str">
-        <v>JEZI FERNANDO OLIVEIRA</v>
+        <v>LEON DOS REIS CALIXTO</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="str">
-        <v>KETTULY FERNANDA ALVES DE AMORIM SANTIAGO</v>
+        <v>LUCAS BICALHO DE FREITAS</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="str">
-        <v>LEON DOS REIS CALIXTO</v>
+        <v>LUCAS BUETTO DE ANGELIS</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="str">
-        <v>LORRAYNE CRISTINE THEZA DO CARMO</v>
+        <v>LUIS FERNANDO KALIL ROSENBURG DE CASTRO</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="str">
-        <v>LUCAS BICALHO DE FREITAS</v>
+        <v>LUÍS HENRIQUE SOARES DUTRA DE ANDRADE</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="str">
-        <v>LUCAS BUETTO DE ANGELIS</v>
+        <v>MAIARA SCHWENGBER CORREA</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="str">
-        <v>LUIS FERNANDO KALIL ROSENBURG DE CASTRO</v>
+        <v>MATHEUS ARTHUR FACHIN</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="str">
-        <v>LUÍS HENRIQUE SOARES DUTRA DE ANDRADE</v>
+        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="str">
-        <v>MAIARA SCHWENGBER CORREA</v>
+        <v>RAPHAEL AZEVEDO</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="str">
-        <v>MARCELA REGGIANI MORAES</v>
+        <v>RENNAN VILAR GUIMARAES CASTRO ANTUNES</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="str">
-        <v>MARIANA DE ALBUQUERQUE LOPES</v>
+        <v>RICARDO ESTEVAO DE ALMEIDA</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="str">
-        <v>MATHEUS ARTHUR FACHIN</v>
+        <v>RODNEY DUARTE DOS SANTOS</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="str">
-        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
+        <v>RODRIGO ASSUMPÇÃO</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="str">
-        <v>RAPHAEL AZEVEDO</v>
+        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="str">
-        <v>RENNAN LUCIO DE MOURA</v>
+        <v>SAMUEL NUNES RIOS SILVA</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="str">
-        <v>RENNAN VILAR GUIMARAES CASTRO ANTUNES</v>
+        <v>SANDRO YUKIO YAMANO</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="str">
-        <v>RICARDO ESTEVAO DE ALMEIDA</v>
+        <v>STAEL MARLEI DE SOUZA E SILVA</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="str">
-        <v>RODNEY DUARTE DOS SANTOS</v>
+        <v>TALES VILAR MOTA GUIMARAES</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="str">
-        <v>RODRIGO ASSUMPÇÃO</v>
+        <v>TIAGO DANIEL DE SOUZA</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="str">
-        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
+        <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="str">
-        <v>SAMUEL NUNES RIOS SILVA</v>
+        <v>VANUZA DOS SANTOS PRESTES</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="str">
-        <v>SANDRO YUKIO YAMANO</v>
+        <v>WANDERSON LAGE</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="str">
-        <v>STAEL MARLEI DE SOUZA E SILVA</v>
+        <v>WELLYNGTON ALVES BORGES</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="str">
-        <v>TALES VILAR MOTA GUIMARAES</v>
-      </c>
+      <c r="A51" s="7"/>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="str">
-        <v>TIAGO DANIEL DE SOUZA</v>
-      </c>
+      <c r="A52" s="7"/>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="str">
-        <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
-      </c>
+      <c r="A53" s="7"/>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="str">
-        <v>VANUZA DOS SANTOS PRESTES</v>
-      </c>
+      <c r="A54" s="7"/>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="str">
-        <v>VICTOR JOSE ALVES FERNANDES</v>
-      </c>
+      <c r="A55" s="7"/>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="str">
-        <v>WANDERSON LAGE</v>
-      </c>
+      <c r="A56" s="7"/>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="str">
-        <v>WELLYNGTON ALVES BORGES</v>
-      </c>
+      <c r="A57" s="7"/>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
@@ -14009,6 +16421,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A6981D71312D3B4BBFEE96F8801BDB9F" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9b11b7dbc0483446f454d619f6ade395">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d25a7fee-0375-4291-87e9-efb469dc66be" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0135f8e613f542a9121ee4594cb88a49" ns3:_="">
     <xsd:import namespace="d25a7fee-0375-4291-87e9-efb469dc66be"/>
@@ -14190,24 +16619,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B313A1-8C2D-4B88-BC5D-62A0C8810371}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14223,28 +16659,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29926"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://desenvolvimentocartaodetodo-my.sharepoint.com/personal/regianeandrade_cartaodetodos_com/Documents/PEPO_2026/VALIDAÇÃO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED29D2DF-F294-45AB-9FAA-9A7A283D672C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACDDEE0A-E6DE-407A-B3FA-1B82AE8A40CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="73" r:id="rId5"/>
+    <pivotCache cacheId="2796" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="883">
   <si>
     <t>Gestor Avaliador</t>
   </si>
@@ -258,6 +258,9 @@
     <t>SECRETÁRIA EXECUTIVA</t>
   </si>
   <si>
+    <t>TALES VILAR MOTA GUIMARAES</t>
+  </si>
+  <si>
     <t>13709</t>
   </si>
   <si>
@@ -276,9 +279,6 @@
     <t>S04</t>
   </si>
   <si>
-    <t>TALES VILAR MOTA GUIMARAES</t>
-  </si>
-  <si>
     <t>AMANDA MIRANDA DE CARVALHO</t>
   </si>
   <si>
@@ -1335,6 +1335,9 @@
     <t>COORDENADOR CONTÁBIL</t>
   </si>
   <si>
+    <t>FINANCAS - FP&amp;A</t>
+  </si>
+  <si>
     <t>2075471</t>
   </si>
   <si>
@@ -1344,9 +1347,6 @@
     <t>COORDENADOR DE PLANEJAMENTO FINANCEIRO E ORÇAMENTARIO</t>
   </si>
   <si>
-    <t>FINANCAS - FP&amp;A</t>
-  </si>
-  <si>
     <t>2563064</t>
   </si>
   <si>
@@ -1608,9 +1608,15 @@
     <t>KATHARYNE CRISTINA LOPES DA SILVA</t>
   </si>
   <si>
+    <t>MARIANA DE ALBUQUERQUE LOPES</t>
+  </si>
+  <si>
     <t>458230</t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>ASSISTENTE DE EVENTOS</t>
   </si>
   <si>
@@ -1764,9 +1770,6 @@
     <t>734857</t>
   </si>
   <si>
-    <t>MARIANA DE ALBUQUERQUE LOPES</t>
-  </si>
-  <si>
     <t>COORDENADOR ADMINISTRATIVO</t>
   </si>
   <si>
@@ -2280,6 +2283,9 @@
     <t>ANALISTA DE FP&amp;A PL</t>
   </si>
   <si>
+    <t>FINANCAS</t>
+  </si>
+  <si>
     <t>2011504</t>
   </si>
   <si>
@@ -2626,30 +2632,6 @@
   </si>
   <si>
     <t>PEPO-202603310823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total de Gestores </t>
-  </si>
-  <si>
-    <t>Falta Responder</t>
-  </si>
-  <si>
-    <t>Responderam</t>
-  </si>
-  <si>
-    <t>Total Gestores</t>
-  </si>
-  <si>
-    <t>Total Geral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESPOSTA PENDENTE: </t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>FINANCAS</t>
   </si>
   <si>
     <t>31/03/2026 11:01</t>
@@ -2711,6 +2693,27 @@
   </si>
   <si>
     <t>PEPO-202604011025</t>
+  </si>
+  <si>
+    <t>PEPO-202604011112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total de Gestores </t>
+  </si>
+  <si>
+    <t>Falta Responder</t>
+  </si>
+  <si>
+    <t>Responderam</t>
+  </si>
+  <si>
+    <t>Total Gestores</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESPOSTA PENDENTE: </t>
   </si>
 </sst>
 </file>
@@ -2720,7 +2723,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2935,16 +2938,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -3337,10 +3340,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4088,21 +4091,17 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Regiane Aparecida De Souza Andrade" refreshedDate="46113.453509259256" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="46" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46113.580760416669" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="47" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
   <cacheSource type="worksheet">
     <worksheetSource name="TabelaRespostas"/>
   </cacheSource>
   <cacheFields count="17">
     <cacheField name="Momento do Envio" numFmtId="0">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-04T10:25:00" maxDate="2026-01-04T10:25:00"/>
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-04T10:25:00" maxDate="2026-01-04T11:12:00"/>
     </cacheField>
     <cacheField name="Nome do Gestor" numFmtId="0">
-      <sharedItems containsBlank="1" count="20">
+      <sharedItems containsBlank="1" count="21">
         <s v="THIAGO DA SILVA CHISNANDES"/>
         <s v="NUBIA AQUINO DA SILVA"/>
         <s v="CAROLINE PAIXÃO VIEIRA DE SENA"/>
@@ -4114,6 +4113,7 @@
         <s v="JEZI FERNANDO OLIVEIRA"/>
         <s v="MARCELA REGGIANI MORAES"/>
         <s v="MARIANA DE ALBUQUERQUE LOPES"/>
+        <s v="GIOVANNA DE ARAUJO GIACON"/>
         <m u="1"/>
         <s v="VANUZA DOS SANTOS PRESTES" u="1"/>
         <s v="CAMILA DA SILVA ANDRADE" u="1"/>
@@ -4180,7 +4180,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="46">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="47">
   <r>
     <s v="30/03/2026 17:50"/>
     <x v="0"/>
@@ -5055,28 +5055,47 @@
     <s v="PEPO-202604011025"/>
     <m/>
   </r>
+  <r>
+    <d v="2026-01-04T11:12:00"/>
+    <x v="11"/>
+    <s v="VITOR ZARETZKI DE SOUZA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="TIAGO PEREIRA DO NASCIMENTO"/>
+    <s v="VINICIUS NASCIMENTO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202604011112"/>
+    <m/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="73" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A2:A14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="2796" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A2:A15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="21">
+      <items count="22">
         <item x="0"/>
+        <item m="1" x="13"/>
+        <item m="1" x="17"/>
+        <item x="4"/>
+        <item m="1" x="15"/>
+        <item m="1" x="18"/>
+        <item m="1" x="19"/>
+        <item m="1" x="20"/>
+        <item x="6"/>
         <item m="1" x="12"/>
         <item m="1" x="16"/>
-        <item x="4"/>
         <item m="1" x="14"/>
-        <item m="1" x="17"/>
-        <item m="1" x="18"/>
-        <item m="1" x="19"/>
-        <item x="6"/>
-        <item m="1" x="11"/>
-        <item m="1" x="15"/>
-        <item m="1" x="13"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
@@ -5085,6 +5104,7 @@
         <item x="8"/>
         <item x="9"/>
         <item x="10"/>
+        <item x="11"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -5107,7 +5127,7 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="12">
+  <rowItems count="13">
     <i>
       <x/>
     </i>
@@ -5140,6 +5160,9 @@
     </i>
     <i>
       <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
     </i>
     <i t="grand">
       <x/>
@@ -5179,7 +5202,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q47" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q47" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="5" tableBorderDxfId="6">
   <autoFilter ref="A1:Q47" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{CFF5932B-854B-4B23-A01A-04BA6982E294}" name="Momento do Envio"/>
@@ -5494,20 +5517,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I289"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="49.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="4" width="12" style="2" customWidth="1"/>
-    <col min="5" max="5" width="47.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="60.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5536,7 +5559,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -5565,7 +5588,7 @@
         <v>45551</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
@@ -5594,7 +5617,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" s="8" t="s">
         <v>9</v>
       </c>
@@ -5623,7 +5646,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
@@ -5652,7 +5675,7 @@
         <v>44249</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" s="8" t="s">
         <v>9</v>
       </c>
@@ -5681,7 +5704,7 @@
         <v>44830</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
@@ -5710,7 +5733,7 @@
         <v>44958</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
@@ -5739,7 +5762,7 @@
         <v>45460</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" s="8" t="s">
         <v>9</v>
       </c>
@@ -5768,7 +5791,7 @@
         <v>44292</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="8" t="s">
         <v>29</v>
       </c>
@@ -5797,7 +5820,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
         <v>29</v>
       </c>
@@ -5826,7 +5849,7 @@
         <v>42381</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" s="8" t="s">
         <v>29</v>
       </c>
@@ -5855,7 +5878,7 @@
         <v>43605</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" s="8" t="s">
         <v>29</v>
       </c>
@@ -5884,7 +5907,7 @@
         <v>45460</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" s="8" t="s">
         <v>48</v>
       </c>
@@ -5913,7 +5936,7 @@
         <v>41582</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" s="8" t="s">
         <v>48</v>
       </c>
@@ -5942,7 +5965,7 @@
         <v>39203</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" s="8" t="s">
         <v>48</v>
       </c>
@@ -5971,7 +5994,7 @@
         <v>44636</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
@@ -6000,24 +6023,24 @@
         <v>42522</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>35</v>
@@ -6029,7 +6052,7 @@
         <v>36527</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -6037,16 +6060,16 @@
         <v>48</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>35</v>
@@ -6058,7 +6081,7 @@
         <v>43823</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" s="8" t="s">
         <v>71</v>
       </c>
@@ -6087,7 +6110,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21" s="8" t="s">
         <v>71</v>
       </c>
@@ -6116,7 +6139,7 @@
         <v>45337</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22" s="8" t="s">
         <v>71</v>
       </c>
@@ -6145,7 +6168,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" s="8" t="s">
         <v>82</v>
       </c>
@@ -6174,7 +6197,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" s="8" t="s">
         <v>82</v>
       </c>
@@ -6203,7 +6226,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25" s="8" t="s">
         <v>82</v>
       </c>
@@ -6232,7 +6255,7 @@
         <v>44720</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" s="8" t="s">
         <v>82</v>
       </c>
@@ -6261,7 +6284,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" s="8" t="s">
         <v>82</v>
       </c>
@@ -6290,7 +6313,7 @@
         <v>45852</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" s="8" t="s">
         <v>82</v>
       </c>
@@ -6319,7 +6342,7 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" s="8" t="s">
         <v>82</v>
       </c>
@@ -6348,7 +6371,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="8" t="s">
         <v>82</v>
       </c>
@@ -6377,7 +6400,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="A31" s="8" t="s">
         <v>82</v>
       </c>
@@ -6406,7 +6429,7 @@
         <v>45313</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="A32" s="8" t="s">
         <v>82</v>
       </c>
@@ -6435,7 +6458,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9">
       <c r="A33" s="8" t="s">
         <v>104</v>
       </c>
@@ -6464,7 +6487,7 @@
         <v>44228</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9">
       <c r="A34" s="8" t="s">
         <v>111</v>
       </c>
@@ -6493,7 +6516,7 @@
         <v>45414</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9">
       <c r="A35" s="8" t="s">
         <v>111</v>
       </c>
@@ -6522,7 +6545,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9">
       <c r="A36" s="8" t="s">
         <v>111</v>
       </c>
@@ -6551,7 +6574,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9">
       <c r="A37" s="8" t="s">
         <v>111</v>
       </c>
@@ -6580,7 +6603,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9">
       <c r="A38" s="8" t="s">
         <v>111</v>
       </c>
@@ -6609,7 +6632,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9">
       <c r="A39" s="8" t="s">
         <v>111</v>
       </c>
@@ -6638,7 +6661,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9">
       <c r="A40" s="8" t="s">
         <v>111</v>
       </c>
@@ -6667,7 +6690,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9">
       <c r="A41" s="8" t="s">
         <v>111</v>
       </c>
@@ -6696,7 +6719,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9">
       <c r="A42" s="8" t="s">
         <v>111</v>
       </c>
@@ -6725,7 +6748,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9">
       <c r="A43" s="8" t="s">
         <v>57</v>
       </c>
@@ -6754,7 +6777,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9">
       <c r="A44" s="8" t="s">
         <v>57</v>
       </c>
@@ -6783,7 +6806,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9">
       <c r="A45" s="8" t="s">
         <v>57</v>
       </c>
@@ -6812,12 +6835,12 @@
         <v>45306</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9">
       <c r="A46" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>147</v>
@@ -6841,12 +6864,12 @@
         <v>45098</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9">
       <c r="A47" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>151</v>
@@ -6870,12 +6893,12 @@
         <v>44470</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9">
       <c r="A48" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>155</v>
@@ -6899,9 +6922,9 @@
         <v>43587</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9">
       <c r="A49" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>48</v>
@@ -6928,7 +6951,7 @@
         <v>44322</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9">
       <c r="A50" s="8" t="s">
         <v>165</v>
       </c>
@@ -6957,7 +6980,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9">
       <c r="A51" s="8" t="s">
         <v>165</v>
       </c>
@@ -6986,7 +7009,7 @@
         <v>45439</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9">
       <c r="A52" s="8" t="s">
         <v>165</v>
       </c>
@@ -7015,7 +7038,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9">
       <c r="A53" s="8" t="s">
         <v>165</v>
       </c>
@@ -7044,7 +7067,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9">
       <c r="A54" s="8" t="s">
         <v>165</v>
       </c>
@@ -7073,7 +7096,7 @@
         <v>44949</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9">
       <c r="A55" s="8" t="s">
         <v>182</v>
       </c>
@@ -7102,7 +7125,7 @@
         <v>44692</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9">
       <c r="A56" s="8" t="s">
         <v>182</v>
       </c>
@@ -7131,7 +7154,7 @@
         <v>44909</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9">
       <c r="A57" s="8" t="s">
         <v>182</v>
       </c>
@@ -7160,7 +7183,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9">
       <c r="A58" s="8" t="s">
         <v>182</v>
       </c>
@@ -7189,7 +7212,7 @@
         <v>44550</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9">
       <c r="A59" s="8" t="s">
         <v>182</v>
       </c>
@@ -7218,7 +7241,7 @@
         <v>44713</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9">
       <c r="A60" s="8" t="s">
         <v>182</v>
       </c>
@@ -7247,7 +7270,7 @@
         <v>43985</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9">
       <c r="A61" s="8" t="s">
         <v>182</v>
       </c>
@@ -7276,7 +7299,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9">
       <c r="A62" s="8" t="s">
         <v>182</v>
       </c>
@@ -7305,7 +7328,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9">
       <c r="A63" s="8" t="s">
         <v>182</v>
       </c>
@@ -7334,7 +7357,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9">
       <c r="A64" s="8" t="s">
         <v>209</v>
       </c>
@@ -7363,7 +7386,7 @@
         <v>43243</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9">
       <c r="A65" s="8" t="s">
         <v>215</v>
       </c>
@@ -7392,7 +7415,7 @@
         <v>45545</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9">
       <c r="A66" s="8" t="s">
         <v>215</v>
       </c>
@@ -7421,7 +7444,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9">
       <c r="A67" s="8" t="s">
         <v>215</v>
       </c>
@@ -7450,7 +7473,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9">
       <c r="A68" s="8" t="s">
         <v>225</v>
       </c>
@@ -7479,7 +7502,7 @@
         <v>41255</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9">
       <c r="A69" s="8" t="s">
         <v>225</v>
       </c>
@@ -7508,7 +7531,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9">
       <c r="A70" s="8" t="s">
         <v>225</v>
       </c>
@@ -7537,7 +7560,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9">
       <c r="A71" s="8" t="s">
         <v>41</v>
       </c>
@@ -7566,7 +7589,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9">
       <c r="A72" s="8" t="s">
         <v>41</v>
       </c>
@@ -7595,7 +7618,7 @@
         <v>44979</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9">
       <c r="A73" s="8" t="s">
         <v>41</v>
       </c>
@@ -7624,7 +7647,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9">
       <c r="A74" s="8" t="s">
         <v>41</v>
       </c>
@@ -7653,7 +7676,7 @@
         <v>44391</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9">
       <c r="A75" s="8" t="s">
         <v>41</v>
       </c>
@@ -7682,7 +7705,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76" s="8" t="s">
         <v>41</v>
       </c>
@@ -7711,7 +7734,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9">
       <c r="A77" s="8" t="s">
         <v>41</v>
       </c>
@@ -7740,7 +7763,7 @@
         <v>44671</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9">
       <c r="A78" s="8" t="s">
         <v>255</v>
       </c>
@@ -7769,7 +7792,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9">
       <c r="A79" s="8" t="s">
         <v>255</v>
       </c>
@@ -7798,7 +7821,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9">
       <c r="A80" s="8" t="s">
         <v>255</v>
       </c>
@@ -7827,7 +7850,7 @@
         <v>44259</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9">
       <c r="A81" s="8" t="s">
         <v>255</v>
       </c>
@@ -7856,7 +7879,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9">
       <c r="A82" s="8" t="s">
         <v>255</v>
       </c>
@@ -7885,7 +7908,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9">
       <c r="A83" s="8" t="s">
         <v>270</v>
       </c>
@@ -7914,7 +7937,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9">
       <c r="A84" s="8" t="s">
         <v>270</v>
       </c>
@@ -7943,7 +7966,7 @@
         <v>45063</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9">
       <c r="A85" s="8" t="s">
         <v>270</v>
       </c>
@@ -7972,7 +7995,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9">
       <c r="A86" s="8" t="s">
         <v>270</v>
       </c>
@@ -8001,7 +8024,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9">
       <c r="A87" s="8" t="s">
         <v>152</v>
       </c>
@@ -8030,7 +8053,7 @@
         <v>44866</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9">
       <c r="A88" s="8" t="s">
         <v>152</v>
       </c>
@@ -8059,7 +8082,7 @@
         <v>44823</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9">
       <c r="A89" s="8" t="s">
         <v>152</v>
       </c>
@@ -8088,7 +8111,7 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9">
       <c r="A90" s="8" t="s">
         <v>297</v>
       </c>
@@ -8117,7 +8140,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9">
       <c r="A91" s="8" t="s">
         <v>297</v>
       </c>
@@ -8146,7 +8169,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9">
       <c r="A92" s="8" t="s">
         <v>297</v>
       </c>
@@ -8175,7 +8198,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9">
       <c r="A93" s="8" t="s">
         <v>297</v>
       </c>
@@ -8204,7 +8227,7 @@
         <v>45154</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9">
       <c r="A94" s="8" t="s">
         <v>297</v>
       </c>
@@ -8233,7 +8256,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9">
       <c r="A95" s="8" t="s">
         <v>297</v>
       </c>
@@ -8262,7 +8285,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9">
       <c r="A96" s="8" t="s">
         <v>315</v>
       </c>
@@ -8291,7 +8314,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9">
       <c r="A97" s="8" t="s">
         <v>33</v>
       </c>
@@ -8320,7 +8343,7 @@
         <v>45537</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9">
       <c r="A98" s="8" t="s">
         <v>33</v>
       </c>
@@ -8349,7 +8372,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9">
       <c r="A99" s="8" t="s">
         <v>33</v>
       </c>
@@ -8378,7 +8401,7 @@
         <v>45564</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9">
       <c r="A100" s="8" t="s">
         <v>325</v>
       </c>
@@ -8407,7 +8430,7 @@
         <v>44630</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9">
       <c r="A101" s="8" t="s">
         <v>325</v>
       </c>
@@ -8436,7 +8459,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9">
       <c r="A102" s="8" t="s">
         <v>332</v>
       </c>
@@ -8465,7 +8488,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9">
       <c r="A103" s="8" t="s">
         <v>332</v>
       </c>
@@ -8494,7 +8517,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9">
       <c r="A104" s="8" t="s">
         <v>332</v>
       </c>
@@ -8523,7 +8546,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9">
       <c r="A105" s="8" t="s">
         <v>341</v>
       </c>
@@ -8552,7 +8575,7 @@
         <v>45089</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9">
       <c r="A106" s="8" t="s">
         <v>212</v>
       </c>
@@ -8581,7 +8604,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9">
       <c r="A107" s="8" t="s">
         <v>212</v>
       </c>
@@ -8610,7 +8633,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9">
       <c r="A108" s="8" t="s">
         <v>212</v>
       </c>
@@ -8639,7 +8662,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9">
       <c r="A109" s="8" t="s">
         <v>212</v>
       </c>
@@ -8668,7 +8691,7 @@
         <v>45690</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9">
       <c r="A110" s="8" t="s">
         <v>212</v>
       </c>
@@ -8697,7 +8720,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9">
       <c r="A111" s="8" t="s">
         <v>212</v>
       </c>
@@ -8726,7 +8749,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9">
       <c r="A112" s="8" t="s">
         <v>212</v>
       </c>
@@ -8755,7 +8778,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9">
       <c r="A113" s="8" t="s">
         <v>212</v>
       </c>
@@ -8784,7 +8807,7 @@
         <v>45215</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9">
       <c r="A114" s="8" t="s">
         <v>212</v>
       </c>
@@ -8813,7 +8836,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9">
       <c r="A115" s="8" t="s">
         <v>212</v>
       </c>
@@ -8842,7 +8865,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9">
       <c r="A116" s="8" t="s">
         <v>366</v>
       </c>
@@ -8871,7 +8894,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9">
       <c r="A117" s="8" t="s">
         <v>371</v>
       </c>
@@ -8900,7 +8923,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9">
       <c r="A118" s="8" t="s">
         <v>375</v>
       </c>
@@ -8929,7 +8952,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9">
       <c r="A119" s="8" t="s">
         <v>375</v>
       </c>
@@ -8958,9 +8981,9 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9">
       <c r="A120" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B120" s="8" t="s">
         <v>381</v>
@@ -8987,9 +9010,9 @@
         <v>44840</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9">
       <c r="A121" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B121" s="8" t="s">
         <v>381</v>
@@ -9016,9 +9039,9 @@
         <v>44197</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9">
       <c r="A122" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B122" s="8" t="s">
         <v>381</v>
@@ -9045,7 +9068,7 @@
         <v>43500</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9">
       <c r="A123" s="8" t="s">
         <v>395</v>
       </c>
@@ -9074,7 +9097,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9">
       <c r="A124" s="8" t="s">
         <v>397</v>
       </c>
@@ -9103,7 +9126,7 @@
         <v>44543</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9">
       <c r="A125" s="8" t="s">
         <v>397</v>
       </c>
@@ -9132,7 +9155,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9">
       <c r="A126" s="8" t="s">
         <v>397</v>
       </c>
@@ -9161,7 +9184,7 @@
         <v>45041</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9">
       <c r="A127" s="8" t="s">
         <v>397</v>
       </c>
@@ -9190,7 +9213,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9">
       <c r="A128" s="8" t="s">
         <v>397</v>
       </c>
@@ -9219,7 +9242,7 @@
         <v>45580</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9">
       <c r="A129" s="8" t="s">
         <v>415</v>
       </c>
@@ -9248,7 +9271,7 @@
         <v>43416</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9">
       <c r="A130" s="8" t="s">
         <v>415</v>
       </c>
@@ -9277,7 +9300,7 @@
         <v>45306</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9">
       <c r="A131" s="8" t="s">
         <v>183</v>
       </c>
@@ -9300,13 +9323,13 @@
         <v>35</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="I131" s="9">
         <v>44573</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9">
       <c r="A132" s="8" t="s">
         <v>183</v>
       </c>
@@ -9314,28 +9337,28 @@
         <v>183</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D132" s="8">
         <v>800</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G132" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="I132" s="9">
         <v>45642</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9">
       <c r="A133" s="8" t="s">
         <v>183</v>
       </c>
@@ -9358,13 +9381,13 @@
         <v>35</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="I133" s="9">
         <v>45964</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9">
       <c r="A134" s="8" t="s">
         <v>417</v>
       </c>
@@ -9393,7 +9416,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9">
       <c r="A135" s="8" t="s">
         <v>417</v>
       </c>
@@ -9422,7 +9445,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9">
       <c r="A136" s="8" t="s">
         <v>417</v>
       </c>
@@ -9451,7 +9474,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9">
       <c r="A137" s="8" t="s">
         <v>417</v>
       </c>
@@ -9480,7 +9503,7 @@
         <v>44958</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9">
       <c r="A138" s="8" t="s">
         <v>417</v>
       </c>
@@ -9509,7 +9532,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9">
       <c r="A139" s="8" t="s">
         <v>417</v>
       </c>
@@ -9538,7 +9561,7 @@
         <v>43556</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9">
       <c r="A140" s="8" t="s">
         <v>417</v>
       </c>
@@ -9567,7 +9590,7 @@
         <v>44348</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9">
       <c r="A141" s="8" t="s">
         <v>417</v>
       </c>
@@ -9596,7 +9619,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9">
       <c r="A142" s="8" t="s">
         <v>417</v>
       </c>
@@ -9625,7 +9648,7 @@
         <v>43160</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9">
       <c r="A143" s="8" t="s">
         <v>455</v>
       </c>
@@ -9654,7 +9677,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9">
       <c r="A144" s="8" t="s">
         <v>455</v>
       </c>
@@ -9683,7 +9706,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9">
       <c r="A145" s="8" t="s">
         <v>291</v>
       </c>
@@ -9712,7 +9735,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9">
       <c r="A146" s="8" t="s">
         <v>291</v>
       </c>
@@ -9741,7 +9764,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9">
       <c r="A147" s="8" t="s">
         <v>291</v>
       </c>
@@ -9770,7 +9793,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9">
       <c r="A148" s="8" t="s">
         <v>291</v>
       </c>
@@ -9799,7 +9822,7 @@
         <v>44951</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9">
       <c r="A149" s="8" t="s">
         <v>291</v>
       </c>
@@ -9828,7 +9851,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9">
       <c r="A150" s="8" t="s">
         <v>291</v>
       </c>
@@ -9857,7 +9880,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9">
       <c r="A151" s="8" t="s">
         <v>482</v>
       </c>
@@ -9886,7 +9909,7 @@
         <v>45082</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9">
       <c r="A152" s="8" t="s">
         <v>482</v>
       </c>
@@ -9915,7 +9938,7 @@
         <v>44641</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9">
       <c r="A153" s="8" t="s">
         <v>482</v>
       </c>
@@ -9944,7 +9967,7 @@
         <v>44900</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9">
       <c r="A154" s="8" t="s">
         <v>482</v>
       </c>
@@ -9973,7 +9996,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9">
       <c r="A155" s="8" t="s">
         <v>482</v>
       </c>
@@ -10002,7 +10025,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9">
       <c r="A156" s="8" t="s">
         <v>482</v>
       </c>
@@ -10031,7 +10054,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9">
       <c r="A157" s="8" t="s">
         <v>482</v>
       </c>
@@ -10060,7 +10083,7 @@
         <v>44921</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9">
       <c r="A158" s="8" t="s">
         <v>326</v>
       </c>
@@ -10089,7 +10112,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9">
       <c r="A159" s="8" t="s">
         <v>326</v>
       </c>
@@ -10118,7 +10141,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9">
       <c r="A160" s="8" t="s">
         <v>326</v>
       </c>
@@ -10147,7 +10170,7 @@
         <v>43509</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9">
       <c r="A161" s="8" t="s">
         <v>504</v>
       </c>
@@ -10176,7 +10199,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9">
       <c r="A162" s="8" t="s">
         <v>504</v>
       </c>
@@ -10205,7 +10228,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9">
       <c r="A163" s="8" t="s">
         <v>504</v>
       </c>
@@ -10234,7 +10257,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9">
       <c r="A164" s="8" t="s">
         <v>504</v>
       </c>
@@ -10263,53 +10286,53 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9">
       <c r="A165" s="8" t="s">
-        <v>566</v>
+        <v>514</v>
       </c>
       <c r="B165" s="8" t="s">
         <v>395</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D165" s="8">
         <v>493</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>860</v>
+        <v>516</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G165" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H165" s="8" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I165" s="9">
         <v>44718</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9">
       <c r="A166" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G166" s="8" t="s">
         <v>35</v>
@@ -10321,24 +10344,24 @@
         <v>45041</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9">
       <c r="A167" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D167" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="F167" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="F167" s="8" t="s">
-        <v>521</v>
       </c>
       <c r="G167" s="8" t="s">
         <v>35</v>
@@ -10350,24 +10373,24 @@
         <v>44907</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9">
       <c r="A168" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E168" s="8" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>35</v>
@@ -10379,21 +10402,21 @@
         <v>44894</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9">
       <c r="A169" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>301</v>
@@ -10408,21 +10431,21 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9">
       <c r="A170" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D170" s="8">
         <v>924</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>301</v>
@@ -10437,21 +10460,21 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9">
       <c r="A171" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>301</v>
@@ -10466,21 +10489,21 @@
         <v>45152</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B172" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C172" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D172">
         <v>690</v>
       </c>
       <c r="E172" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F172" t="s">
         <v>305</v>
@@ -10495,21 +10518,21 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9">
       <c r="A173" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D173" s="8">
         <v>343</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>305</v>
@@ -10524,21 +10547,21 @@
         <v>43888</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9">
       <c r="A174" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D174" s="8">
         <v>236</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>312</v>
@@ -10553,21 +10576,21 @@
         <v>43028</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9">
       <c r="A175" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>312</v>
@@ -10582,21 +10605,21 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9">
       <c r="A176" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D176" s="8">
         <v>922</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>467</v>
@@ -10611,36 +10634,36 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9">
       <c r="A177" s="8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E177" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F177" s="8" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H177" s="8" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I177" s="9">
         <v>37163</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9">
       <c r="A178" s="8" t="s">
         <v>502</v>
       </c>
@@ -10648,13 +10671,13 @@
         <v>326</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D178" s="8">
         <v>634</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>228</v>
@@ -10669,7 +10692,7 @@
         <v>45194</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9">
       <c r="A179" s="8" t="s">
         <v>502</v>
       </c>
@@ -10677,13 +10700,13 @@
         <v>326</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D179" s="8">
         <v>356</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>175</v>
@@ -10698,7 +10721,7 @@
         <v>44097</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9">
       <c r="A180" s="8" t="s">
         <v>502</v>
       </c>
@@ -10706,13 +10729,13 @@
         <v>326</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D180" s="8">
         <v>637</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>235</v>
@@ -10727,7 +10750,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9">
       <c r="A181" s="8" t="s">
         <v>326</v>
       </c>
@@ -10735,28 +10758,28 @@
         <v>166</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D181" s="8">
         <v>434</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F181" s="8" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G181" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I181" s="9">
         <v>44531</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9">
       <c r="A182" s="8" t="s">
         <v>326</v>
       </c>
@@ -10764,13 +10787,13 @@
         <v>166</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D182" s="8">
         <v>927</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>228</v>
@@ -10779,13 +10802,13 @@
         <v>35</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I182" s="9">
         <v>45915</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9">
       <c r="A183" s="8" t="s">
         <v>326</v>
       </c>
@@ -10793,28 +10816,28 @@
         <v>166</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D183" s="8">
         <v>539</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>566</v>
+        <v>514</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G183" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I183" s="9">
         <v>44874</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9">
       <c r="A184" s="8" t="s">
         <v>326</v>
       </c>
@@ -10822,7 +10845,7 @@
         <v>166</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D184" s="8">
         <v>684</v>
@@ -10843,7 +10866,7 @@
         <v>45355</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9">
       <c r="A185" s="8" t="s">
         <v>326</v>
       </c>
@@ -10851,7 +10874,7 @@
         <v>166</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D185" s="8">
         <v>788</v>
@@ -10872,21 +10895,21 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9">
       <c r="A186" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D186" s="8">
         <v>943</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>12</v>
@@ -10901,15 +10924,15 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9">
       <c r="A187" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D187" s="8">
         <v>430</v>
@@ -10930,21 +10953,21 @@
         <v>44501</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9">
       <c r="A188" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>12</v>
@@ -10959,15 +10982,15 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9">
       <c r="A189" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D189" s="8">
         <v>610</v>
@@ -10988,7 +11011,7 @@
         <v>45082</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9">
       <c r="A190" s="8" t="s">
         <v>38</v>
       </c>
@@ -10996,16 +11019,16 @@
         <v>30</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D190" s="8">
         <v>809</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G190" s="8" t="s">
         <v>35</v>
@@ -11017,7 +11040,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9">
       <c r="A191" s="8" t="s">
         <v>38</v>
       </c>
@@ -11025,16 +11048,16 @@
         <v>30</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D191" s="8">
         <v>741</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F191" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G191" s="8" t="s">
         <v>35</v>
@@ -11046,7 +11069,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9">
       <c r="A192" s="8" t="s">
         <v>38</v>
       </c>
@@ -11054,16 +11077,16 @@
         <v>30</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D192" s="8">
         <v>902</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F192" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G192" s="8" t="s">
         <v>35</v>
@@ -11075,7 +11098,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9">
       <c r="A193" s="8" t="s">
         <v>38</v>
       </c>
@@ -11083,16 +11106,16 @@
         <v>30</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D193" s="8">
         <v>913</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G193" s="8" t="s">
         <v>35</v>
@@ -11104,7 +11127,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9">
       <c r="A194" s="8" t="s">
         <v>38</v>
       </c>
@@ -11112,16 +11135,16 @@
         <v>30</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D194" s="8">
         <v>712</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G194" s="8" t="s">
         <v>35</v>
@@ -11133,7 +11156,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9">
       <c r="A195" s="8" t="s">
         <v>38</v>
       </c>
@@ -11141,16 +11164,16 @@
         <v>30</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D195" s="8">
         <v>630</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>35</v>
@@ -11162,7 +11185,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9">
       <c r="A196" s="8" t="s">
         <v>38</v>
       </c>
@@ -11170,16 +11193,16 @@
         <v>30</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D196" s="8">
         <v>632</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>35</v>
@@ -11191,7 +11214,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9">
       <c r="A197" s="8" t="s">
         <v>156</v>
       </c>
@@ -11199,7 +11222,7 @@
         <v>284</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D197" s="8">
         <v>802</v>
@@ -11208,19 +11231,19 @@
         <v>326</v>
       </c>
       <c r="F197" s="8" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G197" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H197" s="8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I197" s="9">
         <v>45659</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9">
       <c r="A198" s="8" t="s">
         <v>148</v>
       </c>
@@ -11228,7 +11251,7 @@
         <v>148</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D198" s="8">
         <v>795</v>
@@ -11237,19 +11260,19 @@
         <v>395</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G198" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I198" s="9">
         <v>45628</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9">
       <c r="A199" s="8" t="s">
         <v>148</v>
       </c>
@@ -11257,7 +11280,7 @@
         <v>148</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D199" s="8">
         <v>169</v>
@@ -11266,120 +11289,120 @@
         <v>183</v>
       </c>
       <c r="F199" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G199" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I199" s="9">
         <v>42248</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9">
       <c r="A200" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D200" s="8">
         <v>860</v>
       </c>
       <c r="E200" s="8" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G200" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I200" s="9">
         <v>45754</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9">
       <c r="A201" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D201" s="8">
         <v>826</v>
       </c>
       <c r="E201" s="8" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F201" s="8" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G201" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I201" s="9">
         <v>45705</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9">
       <c r="A202" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D202" s="8">
         <v>905</v>
       </c>
       <c r="E202" s="8" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F202" s="8" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I202" s="9">
         <v>45873</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9">
       <c r="A203" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D203" s="8">
         <v>915</v>
       </c>
       <c r="E203" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>467</v>
@@ -11388,27 +11411,27 @@
         <v>35</v>
       </c>
       <c r="H203" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I203" s="9">
         <v>45901</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9">
       <c r="A204" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D204" s="8">
         <v>553</v>
       </c>
       <c r="E204" s="8" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>12</v>
@@ -11417,27 +11440,27 @@
         <v>13</v>
       </c>
       <c r="H204" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I204" s="9">
         <v>44921</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9">
       <c r="A205" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D205" s="8">
         <v>917</v>
       </c>
       <c r="E205" s="8" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>12</v>
@@ -11446,27 +11469,27 @@
         <v>13</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I205" s="9">
         <v>45901</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9">
       <c r="A206" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D206" s="8">
         <v>810</v>
       </c>
       <c r="E206" s="8" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>12</v>
@@ -11475,27 +11498,27 @@
         <v>13</v>
       </c>
       <c r="H206" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I206" s="9">
         <v>45680</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9">
       <c r="A207" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D207" s="8">
         <v>838</v>
       </c>
       <c r="E207" s="8" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>12</v>
@@ -11504,27 +11527,27 @@
         <v>13</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I207" s="9">
         <v>45705</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9">
       <c r="A208" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D208" s="8">
         <v>919</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>12</v>
@@ -11533,27 +11556,27 @@
         <v>13</v>
       </c>
       <c r="H208" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I208" s="9">
         <v>44746</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9">
       <c r="A209" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D209" s="8">
         <v>843</v>
       </c>
       <c r="E209" s="8" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>12</v>
@@ -11562,27 +11585,27 @@
         <v>13</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I209" s="9">
         <v>45705</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9">
       <c r="A210" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D210" s="8">
         <v>817</v>
       </c>
       <c r="E210" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>12</v>
@@ -11591,27 +11614,27 @@
         <v>13</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I210" s="9">
         <v>45684</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9">
       <c r="A211" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D211" s="8">
         <v>833</v>
       </c>
       <c r="E211" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>12</v>
@@ -11620,27 +11643,27 @@
         <v>13</v>
       </c>
       <c r="H211" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I211" s="9">
         <v>45705</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9">
       <c r="A212" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D212" s="8">
         <v>647</v>
       </c>
       <c r="E212" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>12</v>
@@ -11649,13 +11672,13 @@
         <v>13</v>
       </c>
       <c r="H212" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I212" s="9">
         <v>45233</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9">
       <c r="A213" s="8" t="s">
         <v>287</v>
       </c>
@@ -11663,16 +11686,16 @@
         <v>298</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D213" s="8">
         <v>674</v>
       </c>
       <c r="E213" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F213" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G213" s="8" t="s">
         <v>35</v>
@@ -11684,7 +11707,7 @@
         <v>44958</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9">
       <c r="A214" s="8" t="s">
         <v>287</v>
       </c>
@@ -11692,16 +11715,16 @@
         <v>298</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D214" s="8">
         <v>957</v>
       </c>
       <c r="E214" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F214" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G214" s="8" t="s">
         <v>35</v>
@@ -11713,7 +11736,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9">
       <c r="A215" s="8" t="s">
         <v>287</v>
       </c>
@@ -11721,16 +11744,16 @@
         <v>298</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D215" s="10" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E215" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F215" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G215" s="8" t="s">
         <v>35</v>
@@ -11742,7 +11765,7 @@
         <v>44900</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9">
       <c r="A216" s="8" t="s">
         <v>287</v>
       </c>
@@ -11750,7 +11773,7 @@
         <v>298</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D216" s="8">
         <v>606</v>
@@ -11771,7 +11794,7 @@
         <v>45068</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9">
       <c r="A217" s="8" t="s">
         <v>287</v>
       </c>
@@ -11779,7 +11802,7 @@
         <v>298</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D217" s="8">
         <v>604</v>
@@ -11800,7 +11823,7 @@
         <v>45061</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9">
       <c r="A218" s="8" t="s">
         <v>287</v>
       </c>
@@ -11808,10 +11831,10 @@
         <v>298</v>
       </c>
       <c r="C218" s="8" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D218" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E218" s="8" t="s">
         <v>455</v>
@@ -11829,7 +11852,7 @@
         <v>44562</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9">
       <c r="A219" s="8" t="s">
         <v>287</v>
       </c>
@@ -11837,13 +11860,13 @@
         <v>298</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D219" s="10" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E219" s="8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>473</v>
@@ -11858,21 +11881,21 @@
         <v>44902</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9">
       <c r="A220" s="8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B220" s="8" t="s">
         <v>291</v>
       </c>
       <c r="C220" s="8" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D220" s="8">
         <v>533</v>
       </c>
       <c r="E220" s="8" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>369</v>
@@ -11887,36 +11910,36 @@
         <v>44851</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9">
       <c r="A221" s="8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B221" s="8" t="s">
         <v>291</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D221" s="8">
         <v>272</v>
       </c>
       <c r="E221" s="8" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F221" s="8" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G221" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H221" s="8" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I221" s="9">
         <v>43416</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9">
       <c r="A222" s="8" t="s">
         <v>50</v>
       </c>
@@ -11924,28 +11947,28 @@
         <v>50</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D222" s="8">
         <v>213</v>
       </c>
       <c r="E222" s="8" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F222" s="8" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H222" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I222" s="9">
         <v>42751</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9">
       <c r="A223" s="8" t="s">
         <v>50</v>
       </c>
@@ -11953,28 +11976,28 @@
         <v>50</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D223" s="8">
         <v>329</v>
       </c>
       <c r="E223" s="8" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F223" s="8" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H223" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I223" s="9">
         <v>43682</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9">
       <c r="A224" s="8" t="s">
         <v>50</v>
       </c>
@@ -11982,28 +12005,28 @@
         <v>50</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D224" s="8">
         <v>908</v>
       </c>
       <c r="E224" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F224" s="8" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I224" s="9">
         <v>45887</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9">
       <c r="A225" s="8" t="s">
         <v>50</v>
       </c>
@@ -12011,28 +12034,28 @@
         <v>50</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D225" s="8">
         <v>937</v>
       </c>
       <c r="E225" s="8" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I225" s="9">
         <v>45964</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9">
       <c r="A226" s="8" t="s">
         <v>50</v>
       </c>
@@ -12040,28 +12063,28 @@
         <v>50</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D226" s="8">
         <v>208</v>
       </c>
       <c r="E226" s="8" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F226" s="8" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="G226" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I226" s="9">
         <v>42614</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9">
       <c r="A227" s="8" t="s">
         <v>33</v>
       </c>
@@ -12069,16 +12092,16 @@
         <v>30</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D227" s="8">
         <v>765</v>
       </c>
       <c r="E227" s="8" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F227" s="8" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G227" s="8" t="s">
         <v>35</v>
@@ -12090,7 +12113,7 @@
         <v>45551</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9">
       <c r="A228" s="8" t="s">
         <v>33</v>
       </c>
@@ -12098,16 +12121,16 @@
         <v>30</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D228" s="8">
         <v>754</v>
       </c>
       <c r="E228" s="8" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F228" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G228" s="8" t="s">
         <v>35</v>
@@ -12119,7 +12142,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9">
       <c r="A229" s="8" t="s">
         <v>33</v>
       </c>
@@ -12127,16 +12150,16 @@
         <v>30</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D229" s="8">
         <v>883</v>
       </c>
       <c r="E229" s="8" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F229" s="8" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G229" s="8" t="s">
         <v>35</v>
@@ -12148,7 +12171,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9">
       <c r="A230" s="8" t="s">
         <v>391</v>
       </c>
@@ -12156,28 +12179,28 @@
         <v>391</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D230" s="10">
         <v>0</v>
       </c>
       <c r="E230" s="8" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F230" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I230" s="9">
         <v>45964</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9">
       <c r="A231" s="8" t="s">
         <v>391</v>
       </c>
@@ -12185,28 +12208,28 @@
         <v>391</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D231" s="10">
         <v>0</v>
       </c>
       <c r="E231" s="8" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F231" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I231" s="9">
         <v>45757</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9">
       <c r="A232" s="8" t="s">
         <v>391</v>
       </c>
@@ -12214,28 +12237,28 @@
         <v>391</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D232" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E232" s="8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F232" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G232" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H232" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I232" s="9">
         <v>45244</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9">
       <c r="A233" s="8" t="s">
         <v>391</v>
       </c>
@@ -12243,28 +12266,28 @@
         <v>391</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D233" s="10" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E233" s="8" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F233" s="8" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G233" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H233" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I233" s="9">
         <v>45677</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9">
       <c r="A234" s="8" t="s">
         <v>391</v>
       </c>
@@ -12272,28 +12295,28 @@
         <v>391</v>
       </c>
       <c r="C234" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="D234" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="E234" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="F234" s="8" t="s">
         <v>692</v>
-      </c>
-      <c r="D234" s="10" t="s">
-        <v>693</v>
-      </c>
-      <c r="E234" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="F234" s="8" t="s">
-        <v>691</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I234" s="9">
         <v>44494</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9">
       <c r="A235" s="8" t="s">
         <v>391</v>
       </c>
@@ -12301,13 +12324,13 @@
         <v>391</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D235" s="10">
         <v>0</v>
       </c>
       <c r="E235" s="8" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>254</v>
@@ -12316,13 +12339,13 @@
         <v>393</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I235" s="9">
         <v>46043</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9">
       <c r="A236" s="8" t="s">
         <v>391</v>
       </c>
@@ -12330,28 +12353,28 @@
         <v>391</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D236" s="10" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E236" s="8" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F236" s="8" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G236" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H236" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I236" s="9">
         <v>44714</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9">
       <c r="A237" s="8" t="s">
         <v>391</v>
       </c>
@@ -12359,28 +12382,28 @@
         <v>391</v>
       </c>
       <c r="C237" s="8" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D237" s="10" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E237" s="8" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F237" s="8" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G237" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I237" s="9">
         <v>45600</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9">
       <c r="A238" s="8" t="s">
         <v>391</v>
       </c>
@@ -12388,28 +12411,28 @@
         <v>391</v>
       </c>
       <c r="C238" s="8" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D238" s="10">
         <v>0</v>
       </c>
       <c r="E238" s="8" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F238" s="8" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G238" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H238" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I238" s="9">
         <v>45824</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9">
       <c r="A239" s="8" t="s">
         <v>391</v>
       </c>
@@ -12417,36 +12440,36 @@
         <v>391</v>
       </c>
       <c r="C239" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="D239" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="E239" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="F239" s="8" t="s">
         <v>708</v>
-      </c>
-      <c r="D239" s="10" t="s">
-        <v>709</v>
-      </c>
-      <c r="E239" s="8" t="s">
-        <v>710</v>
-      </c>
-      <c r="F239" s="8" t="s">
-        <v>707</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H239" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I239" s="9">
         <v>45383</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9">
       <c r="A240" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C240" s="8" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D240" s="8">
         <v>740</v>
@@ -12455,27 +12478,27 @@
         <v>112</v>
       </c>
       <c r="F240" s="8" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G240" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H240" s="8" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I240" s="9">
         <v>45516</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9">
       <c r="A241" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D241" s="8">
         <v>390</v>
@@ -12484,27 +12507,27 @@
         <v>415</v>
       </c>
       <c r="F241" s="8" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H241" s="8" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I241" s="9">
         <v>44342</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9">
       <c r="A242" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D242" s="8">
         <v>645</v>
@@ -12513,7 +12536,7 @@
         <v>104</v>
       </c>
       <c r="F242" s="8" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G242" s="8" t="s">
         <v>109</v>
@@ -12525,384 +12548,384 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9">
       <c r="A243" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C243" s="8" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D243" s="10" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E243" s="8" t="s">
         <v>209</v>
       </c>
       <c r="F243" s="8" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H243" s="8" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I243" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9">
       <c r="A244" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B244" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C244" s="8" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D244" s="10" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E244" s="8" t="s">
         <v>315</v>
       </c>
       <c r="F244" s="8" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H244" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I244" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9">
       <c r="A245" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B245" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D245" s="10" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E245" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F245" s="8" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G245" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I245" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9">
       <c r="A246" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B246" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C246" s="8" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D246" s="10" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E246" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F246" s="8" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G246" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H246" s="8" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I246" s="9">
         <v>44246</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9">
       <c r="A247" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B247" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C247" s="8" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D247" s="10" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E247" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F247" s="8" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H247" s="8" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I247" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9">
       <c r="A248" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B248" s="8" t="s">
         <v>183</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D248" s="8">
         <v>879</v>
       </c>
       <c r="E248" s="8" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F248" s="8" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G248" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H248" s="8" t="s">
-        <v>861</v>
+        <v>739</v>
       </c>
       <c r="I248" s="9">
         <v>45789</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9">
       <c r="A249" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B249" s="8" t="s">
         <v>183</v>
       </c>
       <c r="C249" s="8" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D249" s="8">
         <v>783</v>
       </c>
       <c r="E249" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="F249" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H249" s="8" t="s">
         <v>739</v>
-      </c>
-      <c r="F249" s="8" t="s">
-        <v>737</v>
-      </c>
-      <c r="G249" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H249" s="8" t="s">
-        <v>861</v>
       </c>
       <c r="I249" s="9">
         <v>45600</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9">
       <c r="A250" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B250" s="8" t="s">
         <v>183</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D250" s="8">
         <v>784</v>
       </c>
       <c r="E250" s="8" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F250" s="8" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G250" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H250" s="8" t="s">
-        <v>861</v>
+        <v>739</v>
       </c>
       <c r="I250" s="9">
         <v>45600</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9">
       <c r="A251" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B251" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D251" s="8">
         <v>871</v>
       </c>
       <c r="E251" s="8" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="F251" s="8" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="G251" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H251" s="8" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="I251" s="9">
         <v>45782</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9">
       <c r="A252" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C252" s="8" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D252" s="8">
         <v>899</v>
       </c>
       <c r="E252" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="F252" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H252" s="8" t="s">
         <v>749</v>
-      </c>
-      <c r="F252" s="8" t="s">
-        <v>746</v>
-      </c>
-      <c r="G252" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H252" s="8" t="s">
-        <v>747</v>
       </c>
       <c r="I252" s="9">
         <v>45873</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9">
       <c r="A253" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D253" s="8">
         <v>936</v>
       </c>
       <c r="E253" s="8" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F253" s="8" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G253" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H253" s="8" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="I253" s="9">
         <v>45964</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9">
       <c r="A254" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B254" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C254" s="8" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D254" s="8">
         <v>672</v>
       </c>
       <c r="E254" s="8" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="F254" s="8" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="G254" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H254" s="8" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="I254" s="9">
         <v>45323</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9">
       <c r="A255" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B255" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C255" s="8" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D255" s="8">
         <v>706</v>
       </c>
       <c r="E255" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="F255" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="F255" s="8" t="s">
-        <v>755</v>
-      </c>
       <c r="G255" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H255" s="8" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="I255" s="9">
         <v>45446</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9">
       <c r="A256" s="8" t="s">
         <v>112</v>
       </c>
@@ -12910,16 +12933,16 @@
         <v>112</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D256" s="10" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E256" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G256" s="8" t="s">
         <v>35</v>
@@ -12931,7 +12954,7 @@
         <v>45845</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9">
       <c r="A257" s="8" t="s">
         <v>112</v>
       </c>
@@ -12939,7 +12962,7 @@
         <v>112</v>
       </c>
       <c r="C257" s="8" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D257" s="8">
         <v>487</v>
@@ -12948,7 +12971,7 @@
         <v>111</v>
       </c>
       <c r="F257" s="8" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G257" s="8" t="s">
         <v>35</v>
@@ -12960,7 +12983,7 @@
         <v>44690</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9">
       <c r="A258" s="8" t="s">
         <v>112</v>
       </c>
@@ -12968,16 +12991,16 @@
         <v>112</v>
       </c>
       <c r="C258" s="8" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D258" s="10" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E258" s="8" t="s">
         <v>215</v>
       </c>
       <c r="F258" s="8" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G258" s="8" t="s">
         <v>35</v>
@@ -12989,7 +13012,7 @@
         <v>45796</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9">
       <c r="A259" s="8" t="s">
         <v>112</v>
       </c>
@@ -12997,7 +13020,7 @@
         <v>112</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D259" s="8">
         <v>891</v>
@@ -13006,7 +13029,7 @@
         <v>332</v>
       </c>
       <c r="F259" s="8" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G259" s="8" t="s">
         <v>35</v>
@@ -13018,7 +13041,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9">
       <c r="A260" s="8" t="s">
         <v>295</v>
       </c>
@@ -13026,13 +13049,13 @@
         <v>295</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D260" s="8">
         <v>856</v>
       </c>
       <c r="E260" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>473</v>
@@ -13041,13 +13064,13 @@
         <v>35</v>
       </c>
       <c r="H260" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I260" s="9">
         <v>45733</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9">
       <c r="A261" s="8" t="s">
         <v>341</v>
       </c>
@@ -13055,16 +13078,16 @@
         <v>291</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D261" s="8">
         <v>794</v>
       </c>
       <c r="E261" s="8" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F261" s="8" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G261" s="8" t="s">
         <v>35</v>
@@ -13076,7 +13099,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9">
       <c r="A262" s="8" t="s">
         <v>341</v>
       </c>
@@ -13084,16 +13107,16 @@
         <v>291</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D262" s="8">
         <v>538</v>
       </c>
       <c r="E262" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="F262" s="8" t="s">
         <v>770</v>
-      </c>
-      <c r="F262" s="8" t="s">
-        <v>768</v>
       </c>
       <c r="G262" s="8" t="s">
         <v>35</v>
@@ -13105,7 +13128,7 @@
         <v>44874</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9">
       <c r="A263" s="8" t="s">
         <v>341</v>
       </c>
@@ -13113,13 +13136,13 @@
         <v>291</v>
       </c>
       <c r="C263" s="8" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D263" s="8">
         <v>950</v>
       </c>
       <c r="E263" s="8" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>369</v>
@@ -13134,7 +13157,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9">
       <c r="A264" s="8" t="s">
         <v>341</v>
       </c>
@@ -13142,7 +13165,7 @@
         <v>291</v>
       </c>
       <c r="C264" s="8" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D264" s="8">
         <v>548</v>
@@ -13163,7 +13186,7 @@
         <v>44909</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9">
       <c r="A265" s="8" t="s">
         <v>341</v>
       </c>
@@ -13171,13 +13194,13 @@
         <v>291</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D265" s="8">
         <v>261</v>
       </c>
       <c r="E265" s="8" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>344</v>
@@ -13192,7 +13215,7 @@
         <v>43313</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9">
       <c r="A266" s="8" t="s">
         <v>341</v>
       </c>
@@ -13200,13 +13223,13 @@
         <v>291</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D266" s="8">
         <v>418</v>
       </c>
       <c r="E266" s="8" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>344</v>
@@ -13221,7 +13244,7 @@
         <v>44482</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9">
       <c r="A267" s="8" t="s">
         <v>341</v>
       </c>
@@ -13229,7 +13252,7 @@
         <v>291</v>
       </c>
       <c r="C267" s="8" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D267" s="8">
         <v>749</v>
@@ -13238,7 +13261,7 @@
         <v>371</v>
       </c>
       <c r="F267" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G267" s="8" t="s">
         <v>35</v>
@@ -13250,7 +13273,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9">
       <c r="A268" s="8" t="s">
         <v>341</v>
       </c>
@@ -13258,16 +13281,16 @@
         <v>291</v>
       </c>
       <c r="C268" s="8" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D268" s="8">
         <v>673</v>
       </c>
       <c r="E268" s="8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F268" s="8" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="G268" s="8" t="s">
         <v>35</v>
@@ -13279,7 +13302,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9">
       <c r="A269" s="8" t="s">
         <v>341</v>
       </c>
@@ -13287,13 +13310,13 @@
         <v>291</v>
       </c>
       <c r="C269" s="8" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D269" s="8">
         <v>954</v>
       </c>
       <c r="E269" s="8" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>481</v>
@@ -13308,7 +13331,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9">
       <c r="A270" s="8" t="s">
         <v>161</v>
       </c>
@@ -13316,28 +13339,28 @@
         <v>161</v>
       </c>
       <c r="C270" s="8" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D270" s="10" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E270" s="8" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="F270" s="8" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="G270" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H270" s="8" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="I270" s="9">
         <v>44774</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9">
       <c r="A271" s="8" t="s">
         <v>161</v>
       </c>
@@ -13345,28 +13368,28 @@
         <v>161</v>
       </c>
       <c r="C271" s="8" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D271" s="10" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E271" s="8" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F271" s="8" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="G271" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H271" s="8" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="I271" s="9">
         <v>45758</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9">
       <c r="A272" s="8" t="s">
         <v>161</v>
       </c>
@@ -13374,42 +13397,42 @@
         <v>161</v>
       </c>
       <c r="C272" s="8" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D272" s="10" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="E272" s="8" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F272" s="8" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="G272" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H272" s="8" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="I272" s="9">
         <v>45481</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9">
       <c r="A273" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D273" s="8">
         <v>770</v>
       </c>
       <c r="E273" s="8" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>305</v>
@@ -13424,21 +13447,21 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9">
       <c r="A274" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D274" s="8">
         <v>786</v>
       </c>
       <c r="E274" s="8" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>305</v>
@@ -13453,21 +13476,21 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9">
       <c r="A275" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D275" s="8">
         <v>720</v>
       </c>
       <c r="E275" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>305</v>
@@ -13482,21 +13505,21 @@
         <v>45460</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9">
       <c r="A276" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D276" s="8">
         <v>940</v>
       </c>
       <c r="E276" s="8" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>305</v>
@@ -13511,21 +13534,21 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9">
       <c r="A277" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C277" s="8" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D277" s="8">
         <v>687</v>
       </c>
       <c r="E277" s="8" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>312</v>
@@ -13540,21 +13563,21 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9">
       <c r="A278" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D278" s="8">
         <v>623</v>
       </c>
       <c r="E278" s="8" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>312</v>
@@ -13569,21 +13592,21 @@
         <v>45154</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9">
       <c r="A279" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D279" s="8">
         <v>792</v>
       </c>
       <c r="E279" s="8" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>312</v>
@@ -13598,21 +13621,21 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9">
       <c r="A280" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B280" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D280" s="8">
         <v>771</v>
       </c>
       <c r="E280" s="8" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>312</v>
@@ -13627,21 +13650,21 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9">
       <c r="A281" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B281" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D281" s="8">
         <v>711</v>
       </c>
       <c r="E281" s="8" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>463</v>
@@ -13656,21 +13679,21 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9">
       <c r="A282" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D282" s="8">
         <v>874</v>
       </c>
       <c r="E282" s="8" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>463</v>
@@ -13685,21 +13708,21 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9">
       <c r="A283" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D283" s="8">
         <v>875</v>
       </c>
       <c r="E283" s="8" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>463</v>
@@ -13714,21 +13737,21 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9">
       <c r="A284" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D284" s="8">
         <v>852</v>
       </c>
       <c r="E284" s="8" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>463</v>
@@ -13743,21 +13766,21 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9">
       <c r="A285" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D285" s="8">
         <v>790</v>
       </c>
       <c r="E285" s="8" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>463</v>
@@ -13772,21 +13795,21 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9">
       <c r="A286" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="D286" s="8">
         <v>847</v>
       </c>
       <c r="E286" s="8" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>463</v>
@@ -13801,21 +13824,21 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9">
       <c r="A287" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D287" s="8">
         <v>939</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>463</v>
@@ -13830,21 +13853,21 @@
         <v>45966</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9">
       <c r="A288" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D288" s="8">
         <v>753</v>
       </c>
       <c r="E288" s="8" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>463</v>
@@ -13859,21 +13882,21 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9">
       <c r="A289" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D289" s="8">
         <v>828</v>
       </c>
       <c r="E289" s="8" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>467</v>
@@ -13904,335 +13927,335 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="47.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="129.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="129.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="14.45">
       <c r="A1" s="4" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="14.45">
       <c r="A2" s="12" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="N2" s="12" t="s">
         <v>741</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>739</v>
       </c>
       <c r="O2" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q2" s="12"/>
+    </row>
+    <row r="3" spans="1:17" ht="14.45">
+      <c r="A3" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="Q2" s="12"/>
-    </row>
-    <row r="3" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>847</v>
-      </c>
       <c r="B3" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H3" s="13"/>
       <c r="I3" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J3" s="13"/>
       <c r="K3" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L3" s="13"/>
       <c r="M3" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="O3" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q3" s="12"/>
+    </row>
+    <row r="4" spans="1:17" ht="14.45">
+      <c r="A4" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="Q3" s="12"/>
-    </row>
-    <row r="4" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>847</v>
-      </c>
       <c r="B4" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="12" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O4" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="Q4" s="12"/>
     </row>
-    <row r="5" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="14.45">
       <c r="A5" s="12" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>502</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="12" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O5" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="Q5" s="12"/>
     </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="15" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>502</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="12" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O6" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="Q6" s="12"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="15" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>502</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L7" s="13"/>
       <c r="M7" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="N7" s="12" t="s">
         <v>556</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>554</v>
       </c>
       <c r="O7" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="Q7" s="12"/>
     </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="15" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>255</v>
@@ -14242,19 +14265,19 @@
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="12" t="s">
@@ -14268,13 +14291,13 @@
         <v>SIM</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="Q8" s="12"/>
     </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>255</v>
@@ -14284,19 +14307,19 @@
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="12" t="s">
@@ -14310,13 +14333,13 @@
         <v>SIM</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="Q9" s="12"/>
     </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="15" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>255</v>
@@ -14326,19 +14349,19 @@
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="12" t="s">
@@ -14352,13 +14375,13 @@
         <v>SIM</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="Q10" s="12"/>
     </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>255</v>
@@ -14368,19 +14391,19 @@
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="12" t="s">
@@ -14394,13 +14417,13 @@
         <v>SIM</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="Q11" s="12"/>
     </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="15" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>255</v>
@@ -14410,19 +14433,19 @@
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="12" t="s">
@@ -14436,307 +14459,307 @@
         <v>SIM</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="Q12" s="12"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="15" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J13" s="13"/>
       <c r="K13" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O13" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="Q13" s="12"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="15" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O14" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="Q14" s="12"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="15" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O15" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="Q15" s="12"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O16" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="Q16" s="12"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="15" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O17" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="Q17" s="12"/>
     </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="15" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O18" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="Q18" s="12"/>
     </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="15" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L19" s="13"/>
       <c r="M19" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O19" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="Q19" s="12"/>
     </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="15" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>29</v>
@@ -14746,19 +14769,19 @@
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J20" s="13"/>
       <c r="K20" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L20" s="13"/>
       <c r="M20" s="12" t="s">
@@ -14772,15 +14795,15 @@
         <v>SIM</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>29</v>
@@ -14790,19 +14813,19 @@
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L21" s="13"/>
       <c r="M21" s="12" t="s">
@@ -14816,15 +14839,15 @@
         <v>SIM</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>29</v>
@@ -14834,19 +14857,19 @@
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L22" s="13"/>
       <c r="M22" s="12" t="s">
@@ -14860,15 +14883,15 @@
         <v>SIM</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>29</v>
@@ -14878,19 +14901,19 @@
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F23" s="13"/>
       <c r="G23" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L23" s="13"/>
       <c r="M23" s="12" t="s">
@@ -14904,15 +14927,15 @@
         <v>SIM</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1">
       <c r="A24" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>341</v>
@@ -14922,377 +14945,377 @@
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L24" s="13"/>
       <c r="M24" s="12" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O24" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q24" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1">
       <c r="A25" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>341</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>368</v>
+        <v>769</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L25" s="13"/>
       <c r="M25" s="12" t="s">
-        <v>651</v>
+        <v>594</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>373</v>
+        <v>588</v>
       </c>
       <c r="O25" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1">
       <c r="A26" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>341</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F26" s="13"/>
       <c r="G26" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H26" s="13"/>
       <c r="I26" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L26" s="13"/>
       <c r="M26" s="12" t="s">
-        <v>593</v>
+        <v>777</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>587</v>
+        <v>779</v>
       </c>
       <c r="O26" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" customHeight="1">
       <c r="A27" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>341</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F27" s="13"/>
       <c r="G27" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H27" s="13"/>
       <c r="I27" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L27" s="13"/>
       <c r="M27" s="12" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>777</v>
+        <v>366</v>
       </c>
       <c r="O27" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1">
       <c r="A28" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>341</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>772</v>
+        <v>366</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F28" s="13"/>
       <c r="G28" s="12" t="s">
-        <v>848</v>
-      </c>
-      <c r="H28" s="13"/>
+        <v>864</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>344</v>
+      </c>
       <c r="I28" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J28" s="13"/>
       <c r="K28" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L28" s="13"/>
       <c r="M28" s="12" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>366</v>
+        <v>562</v>
       </c>
       <c r="O28" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1">
       <c r="A29" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>341</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>366</v>
+        <v>777</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="12" t="s">
-        <v>870</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>344</v>
-      </c>
+        <v>850</v>
+      </c>
+      <c r="H29" s="13"/>
       <c r="I29" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J29" s="13"/>
       <c r="K29" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L29" s="13"/>
       <c r="M29" s="12" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>560</v>
+        <v>654</v>
       </c>
       <c r="O29" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1">
       <c r="A30" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>341</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J30" s="13"/>
       <c r="K30" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L30" s="13"/>
       <c r="M30" s="12" t="s">
-        <v>770</v>
+        <v>654</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>653</v>
+        <v>772</v>
       </c>
       <c r="O30" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1">
       <c r="A31" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>341</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>777</v>
+        <v>371</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F31" s="13"/>
       <c r="G31" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L31" s="13"/>
       <c r="M31" s="12" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>770</v>
+        <v>366</v>
       </c>
       <c r="O31" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1">
       <c r="A32" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>341</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>371</v>
+        <v>650</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F32" s="13"/>
       <c r="G32" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J32" s="13"/>
       <c r="K32" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L32" s="13"/>
       <c r="M32" s="12" t="s">
-        <v>649</v>
+        <v>371</v>
       </c>
       <c r="N32" s="12" t="s">
         <v>366</v>
@@ -15302,129 +15325,127 @@
         <v>SIM</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1">
       <c r="A33" s="12" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>341</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>649</v>
+        <v>785</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F33" s="13"/>
       <c r="G33" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J33" s="13"/>
       <c r="K33" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L33" s="13"/>
       <c r="M33" s="12" t="s">
-        <v>371</v>
+        <v>772</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>366</v>
+        <v>777</v>
       </c>
       <c r="O33" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1">
       <c r="A34" s="12" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>341</v>
+        <v>183</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>783</v>
+        <v>182</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="12" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="L34" s="13"/>
       <c r="M34" s="12" t="s">
-        <v>770</v>
+        <v>425</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>775</v>
+        <v>255</v>
       </c>
       <c r="O34" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P34" s="12" t="s">
-        <v>868</v>
-      </c>
-      <c r="Q34" s="14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>866</v>
+      </c>
+      <c r="Q34" s="14"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1">
       <c r="A35" s="12" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>183</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>182</v>
+        <v>425</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F35" s="13"/>
       <c r="G35" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H35" s="13"/>
       <c r="I35" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="12" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="L35" s="13"/>
       <c r="M35" s="12" t="s">
-        <v>424</v>
+        <v>182</v>
       </c>
       <c r="N35" s="12" t="s">
         <v>255</v>
@@ -15434,123 +15455,127 @@
         <v>SIM</v>
       </c>
       <c r="P35" s="12" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="Q35" s="14"/>
     </row>
-    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="15" customHeight="1">
       <c r="A36" s="12" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>183</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>424</v>
+        <v>255</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="12" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="L36" s="13"/>
       <c r="M36" s="12" t="s">
         <v>182</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
       <c r="O36" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P36" s="12" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="Q36" s="14"/>
     </row>
-    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="15" customHeight="1">
       <c r="A37" s="12" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>255</v>
+        <v>148</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H37" s="13"/>
       <c r="I37" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J37" s="13"/>
       <c r="K37" s="12" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="L37" s="13"/>
       <c r="M37" s="12" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="O37" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P37" s="12" t="s">
-        <v>872</v>
-      </c>
-      <c r="Q37" s="14"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+      <c r="Q37" s="14" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1">
       <c r="A38" s="12" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12" t="s">
-        <v>848</v>
-      </c>
-      <c r="F38" s="13"/>
+        <v>864</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>64</v>
+      </c>
       <c r="G38" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J38" s="13"/>
       <c r="K38" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L38" s="13"/>
       <c r="M38" s="12" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="N38" s="12" t="s">
         <v>415</v>
@@ -15560,259 +15585,255 @@
         <v>SIM</v>
       </c>
       <c r="P38" s="12" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1">
       <c r="A39" s="12" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12" t="s">
-        <v>870</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>70</v>
-      </c>
+        <v>850</v>
+      </c>
+      <c r="F39" s="13"/>
       <c r="G39" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L39" s="13"/>
       <c r="M39" s="12" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>415</v>
+        <v>152</v>
       </c>
       <c r="O39" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1">
       <c r="A40" s="12" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F40" s="13"/>
       <c r="G40" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H40" s="13"/>
       <c r="I40" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L40" s="13"/>
       <c r="M40" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="N40" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="N40" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="O40" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1">
       <c r="A41" s="12" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>66</v>
+        <v>395</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>161</v>
+        <v>397</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F41" s="13"/>
       <c r="G41" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L41" s="13"/>
       <c r="M41" s="12" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>148</v>
+        <v>425</v>
       </c>
       <c r="O41" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P41" s="12" t="s">
-        <v>874</v>
-      </c>
-      <c r="Q41" s="14" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>871</v>
+      </c>
+      <c r="Q41" s="14"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" customHeight="1">
       <c r="A42" s="12" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>395</v>
+        <v>504</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>397</v>
+        <v>506</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F42" s="13"/>
       <c r="G42" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H42" s="13"/>
       <c r="I42" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L42" s="13"/>
       <c r="M42" s="12" t="s">
-        <v>255</v>
+        <v>509</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>424</v>
+        <v>511</v>
       </c>
       <c r="O42" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="Q42" s="14"/>
     </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" ht="15" customHeight="1">
       <c r="A43" s="12" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>504</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F43" s="13"/>
       <c r="G43" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H43" s="13"/>
       <c r="I43" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J43" s="13"/>
       <c r="K43" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L43" s="13"/>
       <c r="M43" s="12" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O43" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P43" s="12" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="Q43" s="14"/>
     </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="15" customHeight="1">
       <c r="A44" s="12" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>504</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F44" s="13"/>
       <c r="G44" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H44" s="13"/>
       <c r="I44" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J44" s="13"/>
       <c r="K44" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L44" s="13"/>
       <c r="M44" s="12" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="N44" s="12" t="s">
         <v>513</v>
@@ -15822,133 +15843,133 @@
         <v>SIM</v>
       </c>
       <c r="P44" s="12" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="Q44" s="14"/>
     </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" ht="15" customHeight="1">
       <c r="A45" s="12" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>504</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F45" s="13"/>
       <c r="G45" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H45" s="13"/>
       <c r="I45" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J45" s="13"/>
       <c r="K45" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L45" s="13"/>
       <c r="M45" s="12" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="N45" s="12" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="O45" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P45" s="12" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="Q45" s="14"/>
     </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="12" t="s">
-        <v>878</v>
+    <row r="46" spans="1:17" ht="15" customHeight="1">
+      <c r="A46" s="15">
+        <v>46026.434027777781</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>513</v>
+        <v>874</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F46" s="13"/>
       <c r="G46" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H46" s="13"/>
       <c r="I46" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J46" s="13"/>
       <c r="K46" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L46" s="13"/>
       <c r="M46" s="12" t="s">
-        <v>506</v>
+        <v>180</v>
       </c>
       <c r="N46" s="12" t="s">
-        <v>511</v>
+        <v>413</v>
       </c>
       <c r="O46" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P46" s="12" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="Q46" s="14"/>
     </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" ht="15" customHeight="1">
       <c r="A47" s="15">
-        <v>46026.434027777781</v>
+        <v>46026.466666666667</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>566</v>
+        <v>366</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>880</v>
+        <v>368</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F47" s="13"/>
       <c r="G47" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="12" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="L47" s="13"/>
       <c r="M47" s="12" t="s">
-        <v>180</v>
+        <v>377</v>
       </c>
       <c r="N47" s="12" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="O47" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
       <c r="P47" s="12" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="Q47" s="14"/>
     </row>
@@ -15965,108 +15986,113 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D594CA1-84CE-4635-82A0-1A17CF6D309A}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="3.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="B1" t="s">
-        <v>854</v>
+        <v>877</v>
       </c>
       <c r="C1" t="s">
-        <v>855</v>
+        <v>878</v>
       </c>
       <c r="D1">
         <f>D3-D2</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B2">
         <f>COUNTA(A:A)-2</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>856</v>
+        <v>879</v>
       </c>
       <c r="D2">
         <f>B2</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C3" t="s">
-        <v>857</v>
+        <v>880</v>
       </c>
       <c r="D3">
         <f>COUNTA(_xlfn.UNIQUE(Base_Dados!A:A))-1</f>
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>858</v>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>881</v>
       </c>
     </row>
   </sheetData>
@@ -16080,335 +16106,333 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5220A42A-3042-4B66-B73A-8D92322E745E}">
   <dimension ref="A1:A74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="49.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" customWidth="1"/>
+    <col min="1" max="1" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" s="6" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="7" t="str" cm="1">
-        <f t="array" ref="A2:A50">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A500, (Base_Dados!A2:A500&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A500)=0), "✅ Todos responderam!")))</f>
+        <f t="array" ref="A2:A49">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A500, (Base_Dados!A2:A500&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A500)=0), "✅ Todos responderam!")))</f>
         <v>_</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" s="7" t="str">
         <v>ALEX ALVARES PIMENTEL MACIEL</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" s="7" t="str">
         <v>ALTAIR DE JESUS VILAR GUIMARAES</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" s="7" t="str">
         <v>AMANDA MIRANDA DE CARVALHO</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1">
       <c r="A6" s="7" t="str">
         <v>AMANDA STEFANI SOUSA DE ALMEIDA SANTOS</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1">
       <c r="A7" s="7" t="str">
         <v>ANDRE NADDEO</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1">
       <c r="A8" s="7" t="str">
         <v>ANDRESSA RODRIGUES MORATO MAIA</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1">
       <c r="A9" s="7" t="str">
         <v>ANEDINA IZABEL DUARTE SOUZA</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1">
       <c r="A10" s="7" t="str">
         <v>BRAULIO PIOVEZANA RINCO</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1">
       <c r="A11" s="7" t="str">
         <v>BRUNNA KAROLINE QUEIROZ RODRIGUES</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1">
       <c r="A12" s="7" t="str">
         <v>BRUNO CASTRO METZKER</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1">
       <c r="A13" s="7" t="str">
         <v>BRUNO NUNES DE SOUZA SANTOS</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1">
       <c r="A14" s="7" t="str">
         <v>CAMILA DA SILVA ANDRADE</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1">
       <c r="A15" s="7" t="str">
         <v>CARINE REIS DOS SANTOS</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1">
       <c r="A16" s="7" t="str">
         <v>CATERINE NUNES BARBOSA</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1">
       <c r="A17" s="7" t="str">
         <v>DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1">
       <c r="A18" s="7" t="str">
         <v>DENIS GABRIEL ABREU DE MELO</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1">
       <c r="A19" s="7" t="str">
         <v>DIEGO PIRES</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1">
       <c r="A20" s="7" t="str">
         <v>ELIANE PEREIRA DA SILVA HIDALGO</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1">
       <c r="A21" s="7" t="str">
         <v>ELISANGELA PEDRO RODRIGUES OLIVEIRA</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1">
       <c r="A22" s="7" t="str">
         <v>ELISON GLAUBER DE CASTRO</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1">
       <c r="A23" s="7" t="str">
         <v>FLAVIO HENRIQUE ALMEIDA FERREIRA DE MELO</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1">
       <c r="A24" s="7" t="str">
-        <v>GIOVANNA DE ARAUJO GIACON</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+        <v>GUSTAVO ARANDA DAMBROSKI</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" s="7" t="str">
-        <v>GUSTAVO ARANDA DAMBROSKI</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+        <v>HAYNA CARDOSO PINTO</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
       <c r="A26" s="7" t="str">
-        <v>HAYNA CARDOSO PINTO</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+        <v>KETTULY FERNANDA ALVES DE AMORIM SANTIAGO</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
       <c r="A27" s="7" t="str">
-        <v>KETTULY FERNANDA ALVES DE AMORIM SANTIAGO</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+        <v>LEON DOS REIS CALIXTO</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
       <c r="A28" s="7" t="str">
-        <v>LEON DOS REIS CALIXTO</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+        <v>LUCAS BICALHO DE FREITAS</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" s="7" t="str">
-        <v>LUCAS BICALHO DE FREITAS</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+        <v>LUCAS BUETTO DE ANGELIS</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
       <c r="A30" s="7" t="str">
-        <v>LUCAS BUETTO DE ANGELIS</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+        <v>LUIS FERNANDO KALIL ROSENBURG DE CASTRO</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
       <c r="A31" s="7" t="str">
-        <v>LUIS FERNANDO KALIL ROSENBURG DE CASTRO</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+        <v>LUÍS HENRIQUE SOARES DUTRA DE ANDRADE</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
       <c r="A32" s="7" t="str">
-        <v>LUÍS HENRIQUE SOARES DUTRA DE ANDRADE</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+        <v>MAIARA SCHWENGBER CORREA</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
       <c r="A33" s="7" t="str">
-        <v>MAIARA SCHWENGBER CORREA</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+        <v>MATHEUS ARTHUR FACHIN</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" s="7" t="str">
-        <v>MATHEUS ARTHUR FACHIN</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
       <c r="A35" s="7" t="str">
-        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+        <v>RAPHAEL AZEVEDO</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" s="7" t="str">
-        <v>RAPHAEL AZEVEDO</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+        <v>RENNAN VILAR GUIMARAES CASTRO ANTUNES</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
       <c r="A37" s="7" t="str">
-        <v>RENNAN VILAR GUIMARAES CASTRO ANTUNES</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+        <v>RICARDO ESTEVAO DE ALMEIDA</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" s="7" t="str">
-        <v>RICARDO ESTEVAO DE ALMEIDA</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+        <v>RODNEY DUARTE DOS SANTOS</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
       <c r="A39" s="7" t="str">
-        <v>RODNEY DUARTE DOS SANTOS</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+        <v>RODRIGO ASSUMPÇÃO</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
       <c r="A40" s="7" t="str">
-        <v>RODRIGO ASSUMPÇÃO</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
       <c r="A41" s="7" t="str">
-        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+        <v>SAMUEL NUNES RIOS SILVA</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
       <c r="A42" s="7" t="str">
-        <v>SAMUEL NUNES RIOS SILVA</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+        <v>SANDRO YUKIO YAMANO</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
       <c r="A43" s="7" t="str">
-        <v>SANDRO YUKIO YAMANO</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+        <v>STAEL MARLEI DE SOUZA E SILVA</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
       <c r="A44" s="7" t="str">
-        <v>STAEL MARLEI DE SOUZA E SILVA</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+        <v>TALES VILAR MOTA GUIMARAES</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
       <c r="A45" s="7" t="str">
-        <v>TALES VILAR MOTA GUIMARAES</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+        <v>TIAGO DANIEL DE SOUZA</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
       <c r="A46" s="7" t="str">
-        <v>TIAGO DANIEL DE SOUZA</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+        <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
       <c r="A47" s="7" t="str">
-        <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+        <v>VANUZA DOS SANTOS PRESTES</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
       <c r="A48" s="7" t="str">
-        <v>VANUZA DOS SANTOS PRESTES</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+        <v>WANDERSON LAGE</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
       <c r="A49" s="7" t="str">
-        <v>WANDERSON LAGE</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="str">
         <v>WELLYNGTON ALVES BORGES</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1">
+      <c r="A50" s="7"/>
+    </row>
+    <row r="51" spans="1:1">
       <c r="A51" s="7"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1">
       <c r="A52" s="7"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1">
       <c r="A53" s="7"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1">
       <c r="A54" s="7"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:1">
       <c r="A55" s="7"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1">
       <c r="A56" s="7"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1">
       <c r="A57" s="7"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1">
       <c r="A58" s="7"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1">
       <c r="A59" s="7"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:1">
       <c r="A60" s="7"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:1">
       <c r="A61" s="7"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1">
       <c r="A62" s="7"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1">
       <c r="A63" s="7"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1">
       <c r="A64" s="7"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1">
       <c r="A65" s="7"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1">
       <c r="A66" s="7"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1">
       <c r="A67" s="7"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1">
       <c r="A68" s="7"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1">
       <c r="A69" s="7"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1">
       <c r="A70" s="7"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1">
       <c r="A71" s="7"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1">
       <c r="A72" s="7"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1">
       <c r="A73" s="7"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1">
       <c r="A74" s="7"/>
     </row>
   </sheetData>
@@ -16430,14 +16454,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A6981D71312D3B4BBFEE96F8801BDB9F" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9b11b7dbc0483446f454d619f6ade395">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d25a7fee-0375-4291-87e9-efb469dc66be" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0135f8e613f542a9121ee4594cb88a49" ns3:_="">
     <xsd:import namespace="d25a7fee-0375-4291-87e9-efb469dc66be"/>
@@ -16619,44 +16635,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B313A1-8C2D-4B88-BC5D-62A0C8810371}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B313A1-8C2D-4B88-BC5D-62A0C8810371}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}"/>
 </file>
--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://desenvolvimentocartaodetodo-my.sharepoint.com/personal/regianeandrade_cartaodetodos_com/Documents/PEPO_2026/VALIDAÇÃO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="397" documentId="14_{C56899F8-BB0D-45DD-965A-7C7088EBB26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66BCF354-39E9-4DBD-8DC4-47E2D400D7F0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{312AF1FE-8452-4657-8771-3F7B6AC8E817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2938,7 +2938,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2965,24 +2965,8 @@
     <xf numFmtId="22" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="22" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2991,6 +2975,109 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="19">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -3107,109 +3194,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7929,7 +7913,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A2:A40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -8133,31 +8117,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:I288" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:I288" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="VICTOR JOSE ALVES FERNANDES"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:I288" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I288" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Gestor Validador" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Matrícula" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Gestor Validador" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Matrícula" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q190" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q190" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
   <autoFilter ref="A1:Q190" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{CFF5932B-854B-4B23-A01A-04BA6982E294}" name="Momento do Envio"/>
@@ -8165,16 +8143,16 @@
     <tableColumn id="3" xr3:uid="{15330415-ADF2-4758-8694-FD7A376B81D4}" name="Funcionário Avaliado"/>
     <tableColumn id="4" xr3:uid="{594E5835-552B-4D6E-A822-81B896CFAF13}" name="ID"/>
     <tableColumn id="5" xr3:uid="{7F5AB4D9-45E8-46BC-B411-788B139EE062}" name="Gestor Correto?"/>
-    <tableColumn id="14" xr3:uid="{6B9D9653-6673-4CC6-90AD-CF40C644B8FE}" name="Novo Gestor" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{6B9D9653-6673-4CC6-90AD-CF40C644B8FE}" name="Novo Gestor" dataDxfId="15"/>
     <tableColumn id="6" xr3:uid="{C5062DFD-1E5B-4585-8B3D-D5D926B5E2B4}" name="Cargo Correto?"/>
-    <tableColumn id="15" xr3:uid="{707FD308-5DC8-456C-87E0-1C1C71076AD0}" name="Novo Cargo" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{707FD308-5DC8-456C-87E0-1C1C71076AD0}" name="Novo Cargo" dataDxfId="14"/>
     <tableColumn id="7" xr3:uid="{23F4A278-6130-4156-B2C6-092BB614E4A9}" name="Unidade Correta?"/>
-    <tableColumn id="16" xr3:uid="{B1691D3F-F123-42C6-A2B6-E169F7E0C857}" name="Nova Unidade" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{B1691D3F-F123-42C6-A2B6-E169F7E0C857}" name="Nova Unidade" dataDxfId="13"/>
     <tableColumn id="8" xr3:uid="{2FF534DC-1CF1-4C48-B7C4-CAF3960253B8}" name="Departamento Correto?"/>
-    <tableColumn id="17" xr3:uid="{A89472CB-3BFB-45F5-AB02-1F4A971F64C0}" name="Novo Depto" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{A89472CB-3BFB-45F5-AB02-1F4A971F64C0}" name="Novo Depto" dataDxfId="12"/>
     <tableColumn id="9" xr3:uid="{D960B0AB-147E-49C9-81F6-3A62815C92D5}" name="Par 1"/>
     <tableColumn id="10" xr3:uid="{A24B24E4-1150-4A03-93C9-672C68A1D0C8}" name="Par 2"/>
-    <tableColumn id="11" xr3:uid="{5AFF58B5-A998-4A5A-9F0A-A92C2CDE82B2}" name="status_resposta" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{5AFF58B5-A998-4A5A-9F0A-A92C2CDE82B2}" name="status_resposta" dataDxfId="11">
       <calculatedColumnFormula>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{532FFC7B-A440-4E0F-AF70-FBD92751D24E}" name="Protocolo"/>
@@ -8514,7 +8492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -8543,7 +8521,7 @@
         <v>45551</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
@@ -8572,7 +8550,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>9</v>
       </c>
@@ -8601,7 +8579,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
@@ -8630,7 +8608,7 @@
         <v>44249</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>9</v>
       </c>
@@ -8659,7 +8637,7 @@
         <v>44830</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
@@ -8688,7 +8666,7 @@
         <v>44958</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
@@ -8717,7 +8695,7 @@
         <v>45460</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>9</v>
       </c>
@@ -8746,7 +8724,7 @@
         <v>44292</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>29</v>
       </c>
@@ -8775,7 +8753,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>29</v>
       </c>
@@ -8804,7 +8782,7 @@
         <v>42381</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>29</v>
       </c>
@@ -8833,7 +8811,7 @@
         <v>43605</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>29</v>
       </c>
@@ -8862,7 +8840,7 @@
         <v>45460</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>48</v>
       </c>
@@ -8891,7 +8869,7 @@
         <v>41582</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>48</v>
       </c>
@@ -8920,7 +8898,7 @@
         <v>39203</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>48</v>
       </c>
@@ -8949,7 +8927,7 @@
         <v>44636</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
@@ -8978,7 +8956,7 @@
         <v>42522</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>64</v>
       </c>
@@ -9007,7 +8985,7 @@
         <v>36527</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -9036,7 +9014,7 @@
         <v>43823</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>71</v>
       </c>
@@ -9065,7 +9043,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>71</v>
       </c>
@@ -9094,7 +9072,7 @@
         <v>45337</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>71</v>
       </c>
@@ -9123,7 +9101,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>82</v>
       </c>
@@ -9152,7 +9130,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>82</v>
       </c>
@@ -9181,7 +9159,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>82</v>
       </c>
@@ -9210,7 +9188,7 @@
         <v>44720</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>82</v>
       </c>
@@ -9239,7 +9217,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>82</v>
       </c>
@@ -9268,7 +9246,7 @@
         <v>45852</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>82</v>
       </c>
@@ -9297,7 +9275,7 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>82</v>
       </c>
@@ -9326,7 +9304,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>82</v>
       </c>
@@ -9355,7 +9333,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>82</v>
       </c>
@@ -9384,7 +9362,7 @@
         <v>45313</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>82</v>
       </c>
@@ -9413,7 +9391,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>104</v>
       </c>
@@ -9442,7 +9420,7 @@
         <v>44228</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>111</v>
       </c>
@@ -9471,7 +9449,7 @@
         <v>45414</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>111</v>
       </c>
@@ -9500,7 +9478,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>111</v>
       </c>
@@ -9529,7 +9507,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>111</v>
       </c>
@@ -9558,7 +9536,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>111</v>
       </c>
@@ -9587,7 +9565,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>111</v>
       </c>
@@ -9616,7 +9594,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>111</v>
       </c>
@@ -9645,7 +9623,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>111</v>
       </c>
@@ -9674,7 +9652,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>111</v>
       </c>
@@ -9703,7 +9681,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>57</v>
       </c>
@@ -9732,7 +9710,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>57</v>
       </c>
@@ -9761,7 +9739,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>57</v>
       </c>
@@ -9790,7 +9768,7 @@
         <v>45306</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>67</v>
       </c>
@@ -9819,7 +9797,7 @@
         <v>45098</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>64</v>
       </c>
@@ -9848,7 +9826,7 @@
         <v>44470</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>67</v>
       </c>
@@ -9877,7 +9855,7 @@
         <v>43587</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>67</v>
       </c>
@@ -9906,7 +9884,7 @@
         <v>44322</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>165</v>
       </c>
@@ -9935,7 +9913,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>165</v>
       </c>
@@ -9964,7 +9942,7 @@
         <v>45439</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>165</v>
       </c>
@@ -9993,7 +9971,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>165</v>
       </c>
@@ -10022,7 +10000,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>165</v>
       </c>
@@ -10051,7 +10029,7 @@
         <v>44949</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>182</v>
       </c>
@@ -10080,7 +10058,7 @@
         <v>44692</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>182</v>
       </c>
@@ -10109,7 +10087,7 @@
         <v>44909</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>182</v>
       </c>
@@ -10138,7 +10116,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>182</v>
       </c>
@@ -10167,7 +10145,7 @@
         <v>44550</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>182</v>
       </c>
@@ -10196,7 +10174,7 @@
         <v>44713</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>182</v>
       </c>
@@ -10225,7 +10203,7 @@
         <v>43985</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>182</v>
       </c>
@@ -10254,7 +10232,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
         <v>182</v>
       </c>
@@ -10283,7 +10261,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
         <v>182</v>
       </c>
@@ -10312,7 +10290,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>209</v>
       </c>
@@ -10341,7 +10319,7 @@
         <v>43243</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>215</v>
       </c>
@@ -10370,7 +10348,7 @@
         <v>45545</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>215</v>
       </c>
@@ -10399,7 +10377,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>215</v>
       </c>
@@ -10428,7 +10406,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>225</v>
       </c>
@@ -10457,7 +10435,7 @@
         <v>41255</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>225</v>
       </c>
@@ -10486,7 +10464,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>225</v>
       </c>
@@ -10515,7 +10493,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>41</v>
       </c>
@@ -10544,7 +10522,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>41</v>
       </c>
@@ -10573,7 +10551,7 @@
         <v>44979</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>41</v>
       </c>
@@ -10602,7 +10580,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>41</v>
       </c>
@@ -10631,7 +10609,7 @@
         <v>44391</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>41</v>
       </c>
@@ -10660,7 +10638,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>41</v>
       </c>
@@ -10689,7 +10667,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>41</v>
       </c>
@@ -10718,7 +10696,7 @@
         <v>44671</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
         <v>255</v>
       </c>
@@ -10747,7 +10725,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>255</v>
       </c>
@@ -10776,7 +10754,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
         <v>255</v>
       </c>
@@ -10805,7 +10783,7 @@
         <v>44259</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>255</v>
       </c>
@@ -10834,7 +10812,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>255</v>
       </c>
@@ -10863,7 +10841,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>270</v>
       </c>
@@ -10892,7 +10870,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>270</v>
       </c>
@@ -10921,7 +10899,7 @@
         <v>45063</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>270</v>
       </c>
@@ -10950,7 +10928,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>270</v>
       </c>
@@ -10979,7 +10957,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>152</v>
       </c>
@@ -11008,7 +10986,7 @@
         <v>44866</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>152</v>
       </c>
@@ -11037,7 +11015,7 @@
         <v>44823</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>152</v>
       </c>
@@ -11066,7 +11044,7 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>297</v>
       </c>
@@ -11095,7 +11073,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
         <v>297</v>
       </c>
@@ -11124,7 +11102,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="8" t="s">
         <v>297</v>
       </c>
@@ -11153,7 +11131,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="8" t="s">
         <v>297</v>
       </c>
@@ -11182,7 +11160,7 @@
         <v>45154</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="8" t="s">
         <v>297</v>
       </c>
@@ -11211,7 +11189,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>297</v>
       </c>
@@ -11240,7 +11218,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="8" t="s">
         <v>315</v>
       </c>
@@ -11269,7 +11247,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
         <v>33</v>
       </c>
@@ -11298,7 +11276,7 @@
         <v>45537</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
         <v>33</v>
       </c>
@@ -11327,7 +11305,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="8" t="s">
         <v>33</v>
       </c>
@@ -11356,7 +11334,7 @@
         <v>45564</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
         <v>325</v>
       </c>
@@ -11385,7 +11363,7 @@
         <v>44630</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="8" t="s">
         <v>325</v>
       </c>
@@ -11414,7 +11392,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
         <v>332</v>
       </c>
@@ -11443,7 +11421,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>332</v>
       </c>
@@ -11472,7 +11450,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>332</v>
       </c>
@@ -11501,7 +11479,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>341</v>
       </c>
@@ -11530,7 +11508,7 @@
         <v>45089</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>212</v>
       </c>
@@ -11559,7 +11537,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>212</v>
       </c>
@@ -11588,7 +11566,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>212</v>
       </c>
@@ -11617,7 +11595,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>212</v>
       </c>
@@ -11646,7 +11624,7 @@
         <v>45690</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>212</v>
       </c>
@@ -11675,7 +11653,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>212</v>
       </c>
@@ -11704,7 +11682,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>212</v>
       </c>
@@ -11733,7 +11711,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>212</v>
       </c>
@@ -11762,7 +11740,7 @@
         <v>45215</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>212</v>
       </c>
@@ -11791,7 +11769,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>212</v>
       </c>
@@ -11820,7 +11798,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>366</v>
       </c>
@@ -11849,7 +11827,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>371</v>
       </c>
@@ -11878,7 +11856,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>375</v>
       </c>
@@ -11907,7 +11885,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>375</v>
       </c>
@@ -11936,7 +11914,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>64</v>
       </c>
@@ -11965,7 +11943,7 @@
         <v>44840</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>64</v>
       </c>
@@ -11994,7 +11972,7 @@
         <v>44197</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>64</v>
       </c>
@@ -12023,7 +12001,7 @@
         <v>43500</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>395</v>
       </c>
@@ -12052,7 +12030,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>397</v>
       </c>
@@ -12081,7 +12059,7 @@
         <v>44543</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>397</v>
       </c>
@@ -12110,7 +12088,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>397</v>
       </c>
@@ -12139,7 +12117,7 @@
         <v>45041</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>397</v>
       </c>
@@ -12168,7 +12146,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>397</v>
       </c>
@@ -12197,7 +12175,7 @@
         <v>45580</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>415</v>
       </c>
@@ -12226,7 +12204,7 @@
         <v>43416</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>415</v>
       </c>
@@ -12255,7 +12233,7 @@
         <v>45306</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>183</v>
       </c>
@@ -12284,7 +12262,7 @@
         <v>44573</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>183</v>
       </c>
@@ -12313,7 +12291,7 @@
         <v>45642</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>183</v>
       </c>
@@ -12342,7 +12320,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>417</v>
       </c>
@@ -12371,7 +12349,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>417</v>
       </c>
@@ -12400,7 +12378,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>417</v>
       </c>
@@ -12429,7 +12407,7 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>417</v>
       </c>
@@ -12458,7 +12436,7 @@
         <v>44958</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>417</v>
       </c>
@@ -12487,7 +12465,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>417</v>
       </c>
@@ -12516,7 +12494,7 @@
         <v>43556</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>417</v>
       </c>
@@ -12545,7 +12523,7 @@
         <v>44348</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>417</v>
       </c>
@@ -12574,7 +12552,7 @@
         <v>44522</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>417</v>
       </c>
@@ -12603,7 +12581,7 @@
         <v>43160</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
         <v>455</v>
       </c>
@@ -12632,7 +12610,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="8" t="s">
         <v>455</v>
       </c>
@@ -12661,7 +12639,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>287</v>
       </c>
@@ -12690,7 +12668,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>287</v>
       </c>
@@ -12719,7 +12697,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
         <v>287</v>
       </c>
@@ -12732,7 +12710,7 @@
       <c r="D147" s="10">
         <v>0</v>
       </c>
-      <c r="E147" s="16" t="s">
+      <c r="E147" t="s">
         <v>470</v>
       </c>
       <c r="F147" s="8" t="s">
@@ -12761,7 +12739,7 @@
       <c r="D148" s="8">
         <v>575</v>
       </c>
-      <c r="E148" s="16" t="s">
+      <c r="E148" t="s">
         <v>341</v>
       </c>
       <c r="F148" s="8" t="s">
@@ -12777,7 +12755,7 @@
         <v>44951</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="8" t="s">
         <v>291</v>
       </c>
@@ -12790,7 +12768,7 @@
       <c r="D149" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="E149" s="16" t="s">
+      <c r="E149" t="s">
         <v>476</v>
       </c>
       <c r="F149" s="8" t="s">
@@ -12806,7 +12784,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="8" t="s">
         <v>287</v>
       </c>
@@ -12819,7 +12797,7 @@
       <c r="D150" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="E150" s="16" t="s">
+      <c r="E150" t="s">
         <v>480</v>
       </c>
       <c r="F150" s="8" t="s">
@@ -12835,7 +12813,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="8" t="s">
         <v>482</v>
       </c>
@@ -12864,7 +12842,7 @@
         <v>45082</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
         <v>482</v>
       </c>
@@ -12893,7 +12871,7 @@
         <v>44641</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="8" t="s">
         <v>482</v>
       </c>
@@ -12922,7 +12900,7 @@
         <v>44900</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>482</v>
       </c>
@@ -12951,7 +12929,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="8" t="s">
         <v>482</v>
       </c>
@@ -12980,7 +12958,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="8" t="s">
         <v>482</v>
       </c>
@@ -13009,7 +12987,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
         <v>482</v>
       </c>
@@ -13038,7 +13016,7 @@
         <v>44921</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>326</v>
       </c>
@@ -13067,7 +13045,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="8" t="s">
         <v>326</v>
       </c>
@@ -13096,7 +13074,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>326</v>
       </c>
@@ -13125,7 +13103,7 @@
         <v>43509</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>504</v>
       </c>
@@ -13154,7 +13132,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>504</v>
       </c>
@@ -13183,7 +13161,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>504</v>
       </c>
@@ -13212,7 +13190,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>504</v>
       </c>
@@ -13241,7 +13219,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>514</v>
       </c>
@@ -13270,7 +13248,7 @@
         <v>44718</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>519</v>
       </c>
@@ -13299,7 +13277,7 @@
         <v>45041</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>519</v>
       </c>
@@ -13328,7 +13306,7 @@
         <v>44907</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>519</v>
       </c>
@@ -13357,7 +13335,7 @@
         <v>44894</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>519</v>
       </c>
@@ -13386,7 +13364,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>519</v>
       </c>
@@ -13415,7 +13393,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>519</v>
       </c>
@@ -13444,7 +13422,7 @@
         <v>45152</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>519</v>
       </c>
@@ -13473,7 +13451,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>519</v>
       </c>
@@ -13502,7 +13480,7 @@
         <v>43888</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>519</v>
       </c>
@@ -13531,7 +13509,7 @@
         <v>43028</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>519</v>
       </c>
@@ -13560,7 +13538,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>519</v>
       </c>
@@ -13589,7 +13567,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>549</v>
       </c>
@@ -13618,7 +13596,7 @@
         <v>37163</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>502</v>
       </c>
@@ -13647,7 +13625,7 @@
         <v>45194</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>502</v>
       </c>
@@ -13676,7 +13654,7 @@
         <v>44097</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="8" t="s">
         <v>502</v>
       </c>
@@ -13705,7 +13683,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="8" t="s">
         <v>326</v>
       </c>
@@ -13734,7 +13712,7 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="8" t="s">
         <v>326</v>
       </c>
@@ -13763,7 +13741,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="8" t="s">
         <v>326</v>
       </c>
@@ -13792,7 +13770,7 @@
         <v>44874</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="8" t="s">
         <v>326</v>
       </c>
@@ -13821,7 +13799,7 @@
         <v>45355</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="8" t="s">
         <v>326</v>
       </c>
@@ -13850,9 +13828,9 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="8" t="s">
-        <v>571</v>
+        <v>9</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>571</v>
@@ -13879,7 +13857,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="8" t="s">
         <v>571</v>
       </c>
@@ -13908,7 +13886,7 @@
         <v>44501</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="8" t="s">
         <v>575</v>
       </c>
@@ -13937,7 +13915,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="8" t="s">
         <v>575</v>
       </c>
@@ -13966,7 +13944,7 @@
         <v>45082</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="8" t="s">
         <v>38</v>
       </c>
@@ -13995,7 +13973,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="8" t="s">
         <v>38</v>
       </c>
@@ -14024,7 +14002,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="8" t="s">
         <v>38</v>
       </c>
@@ -14053,7 +14031,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="8" t="s">
         <v>38</v>
       </c>
@@ -14082,7 +14060,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="8" t="s">
         <v>38</v>
       </c>
@@ -14111,7 +14089,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="8" t="s">
         <v>38</v>
       </c>
@@ -14140,7 +14118,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="8" t="s">
         <v>38</v>
       </c>
@@ -14169,7 +14147,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="8" t="s">
         <v>156</v>
       </c>
@@ -14198,7 +14176,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="8" t="s">
         <v>148</v>
       </c>
@@ -14227,7 +14205,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="8" t="s">
         <v>148</v>
       </c>
@@ -14256,7 +14234,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="8" t="s">
         <v>603</v>
       </c>
@@ -14285,7 +14263,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="8" t="s">
         <v>603</v>
       </c>
@@ -14314,7 +14292,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="8" t="s">
         <v>603</v>
       </c>
@@ -14343,7 +14321,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="8" t="s">
         <v>603</v>
       </c>
@@ -14372,7 +14350,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="8" t="s">
         <v>616</v>
       </c>
@@ -14401,7 +14379,7 @@
         <v>44921</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="8" t="s">
         <v>616</v>
       </c>
@@ -14430,7 +14408,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="8" t="s">
         <v>616</v>
       </c>
@@ -14459,7 +14437,7 @@
         <v>45680</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="8" t="s">
         <v>616</v>
       </c>
@@ -14488,7 +14466,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="8" t="s">
         <v>616</v>
       </c>
@@ -14517,7 +14495,7 @@
         <v>44746</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="8" t="s">
         <v>616</v>
       </c>
@@ -14546,7 +14524,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="8" t="s">
         <v>616</v>
       </c>
@@ -14575,7 +14553,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="8" t="s">
         <v>616</v>
       </c>
@@ -14604,7 +14582,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="8" t="s">
         <v>616</v>
       </c>
@@ -14633,7 +14611,7 @@
         <v>45233</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="8" t="s">
         <v>287</v>
       </c>
@@ -14662,7 +14640,7 @@
         <v>44958</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="8" t="s">
         <v>287</v>
       </c>
@@ -14691,7 +14669,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="8" t="s">
         <v>287</v>
       </c>
@@ -14720,7 +14698,7 @@
         <v>44900</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="8" t="s">
         <v>287</v>
       </c>
@@ -14749,7 +14727,7 @@
         <v>45068</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="8" t="s">
         <v>287</v>
       </c>
@@ -14778,7 +14756,7 @@
         <v>45061</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="8" t="s">
         <v>287</v>
       </c>
@@ -14807,7 +14785,7 @@
         <v>44562</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="8" t="s">
         <v>287</v>
       </c>
@@ -14836,7 +14814,7 @@
         <v>44902</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="8" t="s">
         <v>650</v>
       </c>
@@ -14865,7 +14843,7 @@
         <v>44851</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="8" t="s">
         <v>650</v>
       </c>
@@ -14894,7 +14872,7 @@
         <v>43416</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="8" t="s">
         <v>50</v>
       </c>
@@ -14923,7 +14901,7 @@
         <v>42751</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="8" t="s">
         <v>50</v>
       </c>
@@ -14952,7 +14930,7 @@
         <v>43682</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="8" t="s">
         <v>50</v>
       </c>
@@ -14981,7 +14959,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="8" t="s">
         <v>50</v>
       </c>
@@ -15010,7 +14988,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="8" t="s">
         <v>50</v>
       </c>
@@ -15039,7 +15017,7 @@
         <v>42614</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="8" t="s">
         <v>33</v>
       </c>
@@ -15068,7 +15046,7 @@
         <v>45551</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="8" t="s">
         <v>33</v>
       </c>
@@ -15097,7 +15075,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="8" t="s">
         <v>33</v>
       </c>
@@ -15126,7 +15104,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="8" t="s">
         <v>391</v>
       </c>
@@ -15155,7 +15133,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="8" t="s">
         <v>391</v>
       </c>
@@ -15184,7 +15162,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="8" t="s">
         <v>391</v>
       </c>
@@ -15213,7 +15191,7 @@
         <v>45244</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="8" t="s">
         <v>391</v>
       </c>
@@ -15242,7 +15220,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="8" t="s">
         <v>391</v>
       </c>
@@ -15271,7 +15249,7 @@
         <v>44494</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="8" t="s">
         <v>391</v>
       </c>
@@ -15300,7 +15278,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="8" t="s">
         <v>391</v>
       </c>
@@ -15329,7 +15307,7 @@
         <v>44714</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="8" t="s">
         <v>391</v>
       </c>
@@ -15358,7 +15336,7 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="8" t="s">
         <v>391</v>
       </c>
@@ -15387,7 +15365,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="8" t="s">
         <v>391</v>
       </c>
@@ -15416,7 +15394,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="8" t="s">
         <v>64</v>
       </c>
@@ -15445,7 +15423,7 @@
         <v>45516</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="8" t="s">
         <v>64</v>
       </c>
@@ -15474,7 +15452,7 @@
         <v>44342</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="8" t="s">
         <v>64</v>
       </c>
@@ -15503,7 +15481,7 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="8" t="s">
         <v>64</v>
       </c>
@@ -15532,7 +15510,7 @@
         <v>44197</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="8" t="s">
         <v>64</v>
       </c>
@@ -15561,7 +15539,7 @@
         <v>44197</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="8" t="s">
         <v>64</v>
       </c>
@@ -15590,7 +15568,7 @@
         <v>44197</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="8" t="s">
         <v>64</v>
       </c>
@@ -15619,7 +15597,7 @@
         <v>44246</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="8" t="s">
         <v>64</v>
       </c>
@@ -15648,7 +15626,7 @@
         <v>44197</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="8" t="s">
         <v>425</v>
       </c>
@@ -15677,7 +15655,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="8" t="s">
         <v>425</v>
       </c>
@@ -15706,7 +15684,7 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="8" t="s">
         <v>425</v>
       </c>
@@ -15735,7 +15713,7 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="8" t="s">
         <v>745</v>
       </c>
@@ -15764,7 +15742,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="8" t="s">
         <v>745</v>
       </c>
@@ -15793,7 +15771,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="8" t="s">
         <v>745</v>
       </c>
@@ -15822,7 +15800,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="8" t="s">
         <v>745</v>
       </c>
@@ -15851,7 +15829,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="8" t="s">
         <v>745</v>
       </c>
@@ -15880,7 +15858,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="8" t="s">
         <v>112</v>
       </c>
@@ -15909,7 +15887,7 @@
         <v>45845</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="8" t="s">
         <v>112</v>
       </c>
@@ -15938,7 +15916,7 @@
         <v>44690</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="8" t="s">
         <v>112</v>
       </c>
@@ -15967,7 +15945,7 @@
         <v>45796</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="8" t="s">
         <v>112</v>
       </c>
@@ -15996,7 +15974,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="8" t="s">
         <v>295</v>
       </c>
@@ -16025,7 +16003,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="8" t="s">
         <v>341</v>
       </c>
@@ -16054,7 +16032,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="8" t="s">
         <v>341</v>
       </c>
@@ -16083,7 +16061,7 @@
         <v>44874</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="8" t="s">
         <v>341</v>
       </c>
@@ -16112,7 +16090,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="8" t="s">
         <v>341</v>
       </c>
@@ -16141,7 +16119,7 @@
         <v>44909</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="8" t="s">
         <v>341</v>
       </c>
@@ -16170,7 +16148,7 @@
         <v>43313</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="8" t="s">
         <v>341</v>
       </c>
@@ -16199,7 +16177,7 @@
         <v>44482</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="8" t="s">
         <v>341</v>
       </c>
@@ -16228,7 +16206,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="8" t="s">
         <v>341</v>
       </c>
@@ -16257,7 +16235,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="8" t="s">
         <v>341</v>
       </c>
@@ -16286,7 +16264,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="8" t="s">
         <v>161</v>
       </c>
@@ -16315,7 +16293,7 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="8" t="s">
         <v>161</v>
       </c>
@@ -16344,7 +16322,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="8" t="s">
         <v>161</v>
       </c>
@@ -16373,7 +16351,7 @@
         <v>45481</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="8" t="s">
         <v>643</v>
       </c>
@@ -16402,7 +16380,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="8" t="s">
         <v>643</v>
       </c>
@@ -16431,7 +16409,7 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="8" t="s">
         <v>643</v>
       </c>
@@ -16460,7 +16438,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="8" t="s">
         <v>643</v>
       </c>
@@ -16489,7 +16467,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="8" t="s">
         <v>643</v>
       </c>
@@ -16518,7 +16496,7 @@
         <v>45154</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="8" t="s">
         <v>643</v>
       </c>
@@ -16547,7 +16525,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="8" t="s">
         <v>287</v>
       </c>
@@ -16576,7 +16554,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="8" t="s">
         <v>643</v>
       </c>
@@ -16605,7 +16583,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="8" t="s">
         <v>643</v>
       </c>
@@ -16634,7 +16612,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="8" t="s">
         <v>643</v>
       </c>
@@ -16663,7 +16641,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="8" t="s">
         <v>643</v>
       </c>
@@ -16692,7 +16670,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="8" t="s">
         <v>643</v>
       </c>
@@ -16721,7 +16699,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="8" t="s">
         <v>643</v>
       </c>
@@ -16750,7 +16728,7 @@
         <v>45722</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="8" t="s">
         <v>643</v>
       </c>
@@ -16779,7 +16757,7 @@
         <v>45966</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="8" t="s">
         <v>287</v>
       </c>
@@ -16808,7 +16786,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="8" t="s">
         <v>287</v>
       </c>
@@ -24890,88 +24868,88 @@
       <c r="Q188" s="14"/>
     </row>
     <row r="189" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="18">
+      <c r="A189" s="15">
         <v>46269.723611111112</v>
       </c>
-      <c r="B189" s="17" t="s">
+      <c r="B189" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="C189" s="19" t="s">
+      <c r="C189" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="D189" s="19"/>
-      <c r="E189" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="F189" s="20"/>
-      <c r="G189" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="H189" s="20"/>
-      <c r="I189" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="J189" s="20"/>
-      <c r="K189" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="L189" s="20"/>
-      <c r="M189" s="19" t="s">
+      <c r="D189" s="12"/>
+      <c r="E189" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F189" s="13"/>
+      <c r="G189" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H189" s="13"/>
+      <c r="I189" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J189" s="13"/>
+      <c r="K189" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L189" s="13"/>
+      <c r="M189" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="N189" s="19" t="s">
+      <c r="N189" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="O189" s="21" t="str">
+      <c r="O189" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
-      <c r="P189" s="19" t="s">
+      <c r="P189" s="12" t="s">
         <v>902</v>
       </c>
-      <c r="Q189" s="22"/>
+      <c r="Q189" s="14"/>
     </row>
     <row r="190" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="18">
+      <c r="A190" s="15">
         <v>46269.73541666667</v>
       </c>
-      <c r="B190" s="19" t="s">
+      <c r="B190" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="C190" s="19" t="s">
+      <c r="C190" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="D190" s="19"/>
-      <c r="E190" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="F190" s="20"/>
-      <c r="G190" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="H190" s="20"/>
-      <c r="I190" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="J190" s="20"/>
-      <c r="K190" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="L190" s="20"/>
-      <c r="M190" s="19" t="s">
+      <c r="D190" s="12"/>
+      <c r="E190" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F190" s="13"/>
+      <c r="G190" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H190" s="13"/>
+      <c r="I190" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J190" s="13"/>
+      <c r="K190" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L190" s="13"/>
+      <c r="M190" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="N190" s="19" t="s">
+      <c r="N190" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="O190" s="21" t="str">
+      <c r="O190" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
         <v>SIM</v>
       </c>
-      <c r="P190" s="19" t="s">
+      <c r="P190" s="12" t="s">
         <v>903</v>
       </c>
-      <c r="Q190" s="22"/>
+      <c r="Q190" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25520,12 +25498,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25711,17 +25688,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25745,17 +25731,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{312AF1FE-8452-4657-8771-3F7B6AC8E817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5871D348-DB91-4DE8-A6B2-3E5148046436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="4" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2976,109 +2976,6 @@
   </cellStyles>
   <dxfs count="19">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -3194,6 +3091,109 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4205,8 +4205,12 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Regiane Aparecida De Souza Andrade" refreshedDate="46122.364577430555" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="189" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Regiane Aparecida De Souza Andrade" refreshedDate="46122.380610763888" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="189" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
   <cacheSource type="worksheet">
     <worksheetSource name="TabelaRespostas"/>
   </cacheSource>
@@ -7913,7 +7917,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A2:A40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -8117,25 +8121,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:I288" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaFuncionarios" displayName="TabelaFuncionarios" ref="A1:I288" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A1:I288" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Gestor Validador" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Matrícula" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gestor Avaliador" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Gestor Validador" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Matrícula" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cargo" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unidade" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Departamento" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Data de admissão" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q190" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q190" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="A1:Q190" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{CFF5932B-854B-4B23-A01A-04BA6982E294}" name="Momento do Envio"/>
@@ -8143,16 +8147,16 @@
     <tableColumn id="3" xr3:uid="{15330415-ADF2-4758-8694-FD7A376B81D4}" name="Funcionário Avaliado"/>
     <tableColumn id="4" xr3:uid="{594E5835-552B-4D6E-A822-81B896CFAF13}" name="ID"/>
     <tableColumn id="5" xr3:uid="{7F5AB4D9-45E8-46BC-B411-788B139EE062}" name="Gestor Correto?"/>
-    <tableColumn id="14" xr3:uid="{6B9D9653-6673-4CC6-90AD-CF40C644B8FE}" name="Novo Gestor" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{6B9D9653-6673-4CC6-90AD-CF40C644B8FE}" name="Novo Gestor" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{C5062DFD-1E5B-4585-8B3D-D5D926B5E2B4}" name="Cargo Correto?"/>
-    <tableColumn id="15" xr3:uid="{707FD308-5DC8-456C-87E0-1C1C71076AD0}" name="Novo Cargo" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{707FD308-5DC8-456C-87E0-1C1C71076AD0}" name="Novo Cargo" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{23F4A278-6130-4156-B2C6-092BB614E4A9}" name="Unidade Correta?"/>
-    <tableColumn id="16" xr3:uid="{B1691D3F-F123-42C6-A2B6-E169F7E0C857}" name="Nova Unidade" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{B1691D3F-F123-42C6-A2B6-E169F7E0C857}" name="Nova Unidade" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{2FF534DC-1CF1-4C48-B7C4-CAF3960253B8}" name="Departamento Correto?"/>
-    <tableColumn id="17" xr3:uid="{A89472CB-3BFB-45F5-AB02-1F4A971F64C0}" name="Novo Depto" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{A89472CB-3BFB-45F5-AB02-1F4A971F64C0}" name="Novo Depto" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{D960B0AB-147E-49C9-81F6-3A62815C92D5}" name="Par 1"/>
     <tableColumn id="10" xr3:uid="{A24B24E4-1150-4A03-93C9-672C68A1D0C8}" name="Par 2"/>
-    <tableColumn id="11" xr3:uid="{5AFF58B5-A998-4A5A-9F0A-A92C2CDE82B2}" name="status_resposta" dataDxfId="11">
+    <tableColumn id="11" xr3:uid="{5AFF58B5-A998-4A5A-9F0A-A92C2CDE82B2}" name="status_resposta" dataDxfId="0">
       <calculatedColumnFormula>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{532FFC7B-A440-4E0F-AF70-FBD92751D24E}" name="Protocolo"/>
@@ -12989,7 +12993,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
-        <v>482</v>
+        <v>616</v>
       </c>
       <c r="B157" s="8" t="s">
         <v>482</v>
@@ -25498,11 +25502,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25688,26 +25693,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25731,9 +25727,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5871D348-DB91-4DE8-A6B2-3E5148046436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BAF106F-0498-442E-81A8-1E0639995411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4210,7 +4210,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Regiane Aparecida De Souza Andrade" refreshedDate="46122.380610763888" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="189" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Regiane Aparecida De Souza Andrade" refreshedDate="46122.364577430555" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="189" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
   <cacheSource type="worksheet">
     <worksheetSource name="TabelaRespostas"/>
   </cacheSource>
@@ -7917,7 +7917,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A2:A40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -13008,7 +13008,7 @@
         <v>497</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>12</v>
+        <v>213</v>
       </c>
       <c r="G157" s="8" t="s">
         <v>13</v>
@@ -25511,6 +25511,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A6981D71312D3B4BBFEE96F8801BDB9F" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9b11b7dbc0483446f454d619f6ade395">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d25a7fee-0375-4291-87e9-efb469dc66be" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0135f8e613f542a9121ee4594cb88a49" ns3:_="">
     <xsd:import namespace="d25a7fee-0375-4291-87e9-efb469dc66be"/>
@@ -25692,14 +25700,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
   <ds:schemaRefs>
@@ -25709,6 +25709,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B313A1-8C2D-4B88-BC5D-62A0C8810371}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25724,20 +25740,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/base_pepo.xlsx
+++ b/base_pepo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Regiane\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BAF106F-0498-442E-81A8-1E0639995411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF18DBE3-F476-48AE-922F-F4AC0BCCADA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3926" uniqueCount="910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3991" uniqueCount="912">
   <si>
     <t>Gestor Avaliador</t>
   </si>
@@ -1554,6 +1554,9 @@
     <t>THIAGO BATISTA ROSELLI</t>
   </si>
   <si>
+    <t>RODRIGO ASSUMPÇÃO</t>
+  </si>
+  <si>
     <t>809709</t>
   </si>
   <si>
@@ -1912,9 +1915,6 @@
   </si>
   <si>
     <t>JOÃO MARIO DE OLIVEIRA FREITAS</t>
-  </si>
-  <si>
-    <t>RODRIGO ASSUMPÇÃO</t>
   </si>
   <si>
     <t>809712</t>
@@ -2796,6 +2796,12 @@
   </si>
   <si>
     <t>PEPO-202604091739</t>
+  </si>
+  <si>
+    <t>PEPO-202604100915</t>
+  </si>
+  <si>
+    <t>PEPO-202604100945</t>
   </si>
   <si>
     <t xml:space="preserve">Total de Gestores </t>
@@ -3454,10 +3460,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>24</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>37</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4210,16 +4216,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Regiane Aparecida De Souza Andrade" refreshedDate="46122.364577430555" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="189" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46122.239837962959" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="196" xr:uid="{19354E3C-2ADC-4D7D-9C41-36AB88EBB2BC}">
   <cacheSource type="worksheet">
     <worksheetSource name="TabelaRespostas"/>
   </cacheSource>
   <cacheFields count="17">
     <cacheField name="Momento do Envio" numFmtId="0">
-      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-04T10:25:00" maxDate="2026-09-04T17:39:00"/>
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-04T10:25:00" maxDate="2026-10-04T09:45:00"/>
     </cacheField>
     <cacheField name="Nome do Gestor" numFmtId="0">
-      <sharedItems containsBlank="1" count="44">
+      <sharedItems containsBlank="1" count="45">
         <s v="THIAGO DA SILVA CHISNANDES"/>
         <s v="NUBIA AQUINO DA SILVA"/>
         <s v="CAROLINE PAIXÃO VIEIRA DE SENA"/>
@@ -4257,9 +4263,10 @@
         <s v="RODNEY DUARTE DOS SANTOS"/>
         <s v="ANDRE NADDEO"/>
         <s v="LUIS FERNANDO KALIL ROSENBURG DE CASTRO"/>
+        <s v="CAMILA DA SILVA ANDRADE"/>
+        <s v="ULISSES LEANDRO CARVALHO FERREIRA"/>
         <m u="1"/>
         <s v="VANUZA DOS SANTOS PRESTES" u="1"/>
-        <s v="CAMILA DA SILVA ANDRADE" u="1"/>
         <s v="AMANDA MIRANDA DE CARVALHO" u="1"/>
         <s v="DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH" u="1"/>
         <s v="DIEGO PIRES" u="1"/>
@@ -4321,7 +4328,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="189">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="196">
   <r>
     <s v="30/03/2026 17:50"/>
     <x v="0"/>
@@ -7913,28 +7920,161 @@
     <s v="PEPO-202604091739"/>
     <m/>
   </r>
+  <r>
+    <d v="2026-10-04T09:15:00"/>
+    <x v="37"/>
+    <s v="ALINE BASSO DE AZEVEDO"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="MICHELE CRISTINA DE SOUZA OLIVEIRA"/>
+    <s v="WYNDERSON FERREIRA DIAS"/>
+    <s v="SIM"/>
+    <s v="PEPO-202604100915"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-10-04T09:15:00"/>
+    <x v="37"/>
+    <s v="MICHELE CRISTINA DE SOUZA OLIVEIRA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="CAROLINE ANDRADE SANTOS BACELAR"/>
+    <s v="ALINE BASSO DE AZEVEDO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202604100915"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-10-04T09:15:00"/>
+    <x v="37"/>
+    <s v="WYNDERSON FERREIRA DIAS"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ALINE BASSO DE AZEVEDO"/>
+    <s v="MICHELE CRISTINA DE SOUZA OLIVEIRA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202604100915"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-10-04T09:45:00"/>
+    <x v="38"/>
+    <s v="AMANDA MIRANDA DE CARVALHO"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ANDRESSA RODRIGUES MORATO MAIA"/>
+    <s v="ELISON GLAUBER DE CASTRO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202604100945"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-10-04T09:45:00"/>
+    <x v="38"/>
+    <s v="ANDRESSA RODRIGUES MORATO MAIA"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ELISON GLAUBER DE CASTRO"/>
+    <s v="AMANDA MIRANDA DE CARVALHO"/>
+    <s v="SIM"/>
+    <s v="PEPO-202604100945"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-10-04T09:45:00"/>
+    <x v="38"/>
+    <s v="BRUNO NUNES DE SOUZA SANTOS"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="ELISON GLAUBER DE CASTRO"/>
+    <s v="ANDRESSA RODRIGUES MORATO MAIA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202604100945"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-10-04T09:45:00"/>
+    <x v="38"/>
+    <s v="ELISON GLAUBER DE CASTRO"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="Sim"/>
+    <m/>
+    <s v="AMANDA MIRANDA DE CARVALHO"/>
+    <s v="ANDRESSA RODRIGUES MORATO MAIA"/>
+    <s v="SIM"/>
+    <s v="PEPO-202604100945"/>
+    <m/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{569D775F-3AA3-49B7-B8C3-37BF025E281D}" name="TabelaDinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A2:A40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A2:A42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="45">
+      <items count="46">
         <item x="0"/>
-        <item m="1" x="38"/>
+        <item m="1" x="40"/>
         <item x="28"/>
         <item x="4"/>
         <item x="35"/>
-        <item m="1" x="41"/>
         <item m="1" x="42"/>
         <item m="1" x="43"/>
+        <item m="1" x="44"/>
         <item x="6"/>
-        <item m="1" x="37"/>
-        <item m="1" x="40"/>
         <item m="1" x="39"/>
+        <item m="1" x="41"/>
+        <item x="37"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
@@ -7967,6 +8107,7 @@
         <item x="33"/>
         <item x="34"/>
         <item x="36"/>
+        <item x="38"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -7989,7 +8130,7 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="38">
+  <rowItems count="40">
     <i>
       <x/>
     </i>
@@ -8004,6 +8145,9 @@
     </i>
     <i>
       <x v="8"/>
+    </i>
+    <i>
+      <x v="11"/>
     </i>
     <i>
       <x v="12"/>
@@ -8101,6 +8245,9 @@
     <i>
       <x v="43"/>
     </i>
+    <i>
+      <x v="44"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -8139,8 +8286,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q190" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A1:Q190" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}" name="TabelaRespostas" displayName="TabelaRespostas" ref="A1:Q197" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A1:Q197" xr:uid="{A5682380-8C80-41AF-B908-EF95603075AF}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{CFF5932B-854B-4B23-A01A-04BA6982E294}" name="Momento do Envio"/>
     <tableColumn id="2" xr3:uid="{9A82702E-3CB5-486A-B49B-3CBF2D1B5744}" name="Nome do Gestor"/>
@@ -8962,7 +9109,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>48</v>
@@ -12993,19 +13140,19 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B157" s="8" t="s">
         <v>482</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D157" s="8">
         <v>552</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>213</v>
@@ -13028,7 +13175,7 @@
         <v>326</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D158" s="8">
         <v>686</v>
@@ -13037,7 +13184,7 @@
         <v>225</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G158" s="8" t="s">
         <v>35</v>
@@ -13057,7 +13204,7 @@
         <v>326</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D159" s="8">
         <v>596</v>
@@ -13066,7 +13213,7 @@
         <v>325</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>35</v>
@@ -13086,22 +13233,22 @@
         <v>326</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D160" s="8">
         <v>283</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G160" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I160" s="9">
         <v>43509</v>
@@ -13109,19 +13256,19 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B161" s="8" t="s">
         <v>166</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D161" s="8">
         <v>956</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>175</v>
@@ -13130,7 +13277,7 @@
         <v>35</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I161" s="9">
         <v>46006</v>
@@ -13138,19 +13285,19 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B162" s="8" t="s">
         <v>166</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D162" s="8">
         <v>773</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>232</v>
@@ -13159,7 +13306,7 @@
         <v>35</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I162" s="9">
         <v>45566</v>
@@ -13167,19 +13314,19 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B163" s="8" t="s">
         <v>166</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D163" s="10">
         <v>0</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>232</v>
@@ -13188,7 +13335,7 @@
         <v>35</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I163" s="9">
         <v>46041</v>
@@ -13196,19 +13343,19 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B164" s="8" t="s">
         <v>166</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D164" s="8">
         <v>885</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>235</v>
@@ -13217,7 +13364,7 @@
         <v>35</v>
       </c>
       <c r="H164" s="8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I164" s="9">
         <v>45810</v>
@@ -13225,28 +13372,28 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B165" s="8" t="s">
         <v>395</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D165" s="8">
         <v>493</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G165" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H165" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I165" s="9">
         <v>44718</v>
@@ -13254,22 +13401,22 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G166" s="8" t="s">
         <v>35</v>
@@ -13283,22 +13430,22 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C167" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="D167" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="F167" s="8" t="s">
         <v>524</v>
-      </c>
-      <c r="D167" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="F167" s="8" t="s">
-        <v>523</v>
       </c>
       <c r="G167" s="8" t="s">
         <v>35</v>
@@ -13312,22 +13459,22 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E168" s="8" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>35</v>
@@ -13341,19 +13488,19 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>301</v>
@@ -13370,19 +13517,19 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D170" s="8">
         <v>924</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>301</v>
@@ -13399,19 +13546,19 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>301</v>
@@ -13428,19 +13575,19 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B172" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C172" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D172">
         <v>690</v>
       </c>
       <c r="E172" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F172" t="s">
         <v>305</v>
@@ -13457,19 +13604,19 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D173" s="8">
         <v>343</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>305</v>
@@ -13486,19 +13633,19 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D174" s="8">
         <v>236</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>312</v>
@@ -13515,19 +13662,19 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>312</v>
@@ -13544,19 +13691,19 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D176" s="8">
         <v>922</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>467</v>
@@ -13573,28 +13720,28 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E177" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F177" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H177" s="8" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I177" s="9">
         <v>37163</v>
@@ -13602,19 +13749,19 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B178" s="8" t="s">
         <v>326</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D178" s="8">
         <v>634</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>228</v>
@@ -13623,7 +13770,7 @@
         <v>35</v>
       </c>
       <c r="H178" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I178" s="9">
         <v>45194</v>
@@ -13631,19 +13778,19 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B179" s="8" t="s">
         <v>326</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D179" s="8">
         <v>356</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>175</v>
@@ -13652,7 +13799,7 @@
         <v>35</v>
       </c>
       <c r="H179" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I179" s="9">
         <v>44097</v>
@@ -13660,19 +13807,19 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B180" s="8" t="s">
         <v>326</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D180" s="8">
         <v>637</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>235</v>
@@ -13681,7 +13828,7 @@
         <v>35</v>
       </c>
       <c r="H180" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I180" s="9">
         <v>45201</v>
@@ -13695,22 +13842,22 @@
         <v>166</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D181" s="8">
         <v>434</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F181" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G181" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I181" s="9">
         <v>44531</v>
@@ -13724,13 +13871,13 @@
         <v>166</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D182" s="8">
         <v>927</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>228</v>
@@ -13739,7 +13886,7 @@
         <v>35</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I182" s="9">
         <v>45915</v>
@@ -13753,22 +13900,22 @@
         <v>166</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D183" s="8">
         <v>539</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G183" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I183" s="9">
         <v>44874</v>
@@ -13782,7 +13929,7 @@
         <v>166</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D184" s="8">
         <v>684</v>
@@ -13791,7 +13938,7 @@
         <v>165</v>
       </c>
       <c r="F184" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G184" s="8" t="s">
         <v>35</v>
@@ -13811,22 +13958,22 @@
         <v>166</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D185" s="8">
         <v>788</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F185" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G185" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H185" s="8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I185" s="9">
         <v>45614</v>
@@ -13837,16 +13984,16 @@
         <v>9</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D186" s="8">
         <v>943</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>12</v>
@@ -13863,13 +14010,13 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D187" s="8">
         <v>430</v>
@@ -13892,19 +14039,19 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>12</v>
@@ -13921,13 +14068,13 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D189" s="8">
         <v>610</v>
@@ -13956,16 +14103,16 @@
         <v>30</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D190" s="8">
         <v>809</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G190" s="8" t="s">
         <v>35</v>
@@ -13985,16 +14132,16 @@
         <v>30</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D191" s="8">
         <v>741</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F191" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G191" s="8" t="s">
         <v>35</v>
@@ -14014,16 +14161,16 @@
         <v>30</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D192" s="8">
         <v>902</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F192" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G192" s="8" t="s">
         <v>35</v>
@@ -14043,16 +14190,16 @@
         <v>30</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D193" s="8">
         <v>913</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G193" s="8" t="s">
         <v>35</v>
@@ -14072,16 +14219,16 @@
         <v>30</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D194" s="8">
         <v>712</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G194" s="8" t="s">
         <v>35</v>
@@ -14101,16 +14248,16 @@
         <v>30</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D195" s="8">
         <v>630</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>35</v>
@@ -14130,16 +14277,16 @@
         <v>30</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D196" s="8">
         <v>632</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>35</v>
@@ -14159,7 +14306,7 @@
         <v>284</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D197" s="8">
         <v>802</v>
@@ -14168,13 +14315,13 @@
         <v>326</v>
       </c>
       <c r="F197" s="8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G197" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H197" s="8" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I197" s="9">
         <v>45659</v>
@@ -14188,7 +14335,7 @@
         <v>148</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D198" s="8">
         <v>795</v>
@@ -14197,13 +14344,13 @@
         <v>395</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G198" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I198" s="9">
         <v>45628</v>
@@ -14217,7 +14364,7 @@
         <v>148</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D199" s="8">
         <v>169</v>
@@ -14226,13 +14373,13 @@
         <v>183</v>
       </c>
       <c r="F199" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G199" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I199" s="9">
         <v>42248</v>
@@ -14240,28 +14387,28 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D200" s="8">
         <v>860</v>
       </c>
       <c r="E200" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G200" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I200" s="9">
         <v>45754</v>
@@ -14269,28 +14416,28 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D201" s="8">
         <v>826</v>
       </c>
       <c r="E201" s="8" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F201" s="8" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G201" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I201" s="9">
         <v>45705</v>
@@ -14298,28 +14445,28 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D202" s="8">
         <v>905</v>
       </c>
       <c r="E202" s="8" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F202" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I202" s="9">
         <v>45873</v>
@@ -14327,19 +14474,19 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D203" s="8">
         <v>915</v>
       </c>
       <c r="E203" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>467</v>
@@ -14348,7 +14495,7 @@
         <v>35</v>
       </c>
       <c r="H203" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I203" s="9">
         <v>45901</v>
@@ -14356,10 +14503,10 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="C204" s="8" t="s">
         <v>617</v>
@@ -14385,10 +14532,10 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="C205" s="8" t="s">
         <v>620</v>
@@ -14414,10 +14561,10 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="C206" s="8" t="s">
         <v>622</v>
@@ -14443,10 +14590,10 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="C207" s="8" t="s">
         <v>624</v>
@@ -14472,10 +14619,10 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="C208" s="8" t="s">
         <v>626</v>
@@ -14501,10 +14648,10 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="C209" s="8" t="s">
         <v>628</v>
@@ -14530,10 +14677,10 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="C210" s="8" t="s">
         <v>630</v>
@@ -14559,10 +14706,10 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="C211" s="8" t="s">
         <v>632</v>
@@ -14588,10 +14735,10 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="C212" s="8" t="s">
         <v>634</v>
@@ -14690,7 +14837,7 @@
         <v>643</v>
       </c>
       <c r="F215" s="8" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G215" s="8" t="s">
         <v>35</v>
@@ -14803,7 +14950,7 @@
         <v>649</v>
       </c>
       <c r="E219" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>473</v>
@@ -15557,7 +15704,7 @@
         <v>728</v>
       </c>
       <c r="E245" s="8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>722</v>
@@ -15586,7 +15733,7 @@
         <v>731</v>
       </c>
       <c r="E246" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>722</v>
@@ -15615,7 +15762,7 @@
         <v>734</v>
       </c>
       <c r="E247" s="8" t="s">
-        <v>616</v>
+        <v>496</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>722</v>
@@ -15992,7 +16139,7 @@
         <v>856</v>
       </c>
       <c r="E260" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>473</v>
@@ -16001,7 +16148,7 @@
         <v>35</v>
       </c>
       <c r="H260" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I260" s="9">
         <v>45733</v>
@@ -16834,7 +16981,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q190"/>
+  <dimension ref="A1:Q197"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
@@ -17040,10 +17187,10 @@
         <v>850</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12" t="s">
@@ -17063,10 +17210,10 @@
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O5" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17082,10 +17229,10 @@
         <v>850</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
@@ -17105,10 +17252,10 @@
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O6" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17124,10 +17271,10 @@
         <v>850</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
@@ -17147,10 +17294,10 @@
       </c>
       <c r="L7" s="13"/>
       <c r="M7" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O7" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17379,7 +17526,7 @@
         <v>38</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12" t="s">
@@ -17399,10 +17546,10 @@
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O13" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17421,7 +17568,7 @@
         <v>38</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12" t="s">
@@ -17441,10 +17588,10 @@
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O14" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17463,7 +17610,7 @@
         <v>38</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12" t="s">
@@ -17483,10 +17630,10 @@
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="12" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O15" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17505,7 +17652,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12" t="s">
@@ -17525,10 +17672,10 @@
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O16" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17547,7 +17694,7 @@
         <v>38</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12" t="s">
@@ -17567,10 +17714,10 @@
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O17" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17589,7 +17736,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12" t="s">
@@ -17609,10 +17756,10 @@
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O18" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17631,7 +17778,7 @@
         <v>38</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12" t="s">
@@ -17651,10 +17798,10 @@
       </c>
       <c r="L19" s="13"/>
       <c r="M19" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O19" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -17913,10 +18060,10 @@
       </c>
       <c r="L25" s="13"/>
       <c r="M25" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O25" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -18050,7 +18197,7 @@
         <v>779</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O28" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -18634,10 +18781,10 @@
         <v>870</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="12" t="s">
@@ -18657,10 +18804,10 @@
       </c>
       <c r="L42" s="13"/>
       <c r="M42" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O42" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -18676,10 +18823,10 @@
         <v>870</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12" t="s">
@@ -18699,10 +18846,10 @@
       </c>
       <c r="L43" s="13"/>
       <c r="M43" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O43" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -18718,10 +18865,10 @@
         <v>870</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12" t="s">
@@ -18741,10 +18888,10 @@
       </c>
       <c r="L44" s="13"/>
       <c r="M44" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O44" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -18760,10 +18907,10 @@
         <v>870</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12" t="s">
@@ -18783,10 +18930,10 @@
       </c>
       <c r="L45" s="13"/>
       <c r="M45" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N45" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O45" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -18802,7 +18949,7 @@
         <v>46026.434027777781</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>872</v>
@@ -20253,7 +20400,7 @@
       </c>
       <c r="L80" s="13"/>
       <c r="M80" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N80" s="12" t="s">
         <v>325</v>
@@ -20297,7 +20444,7 @@
       </c>
       <c r="L81" s="13"/>
       <c r="M81" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N81" s="12" t="s">
         <v>225</v>
@@ -20321,7 +20468,7 @@
         <v>326</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D82" s="12"/>
       <c r="E82" s="12" t="s">
@@ -20365,7 +20512,7 @@
         <v>326</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D83" s="12"/>
       <c r="E83" s="12" t="s">
@@ -20385,7 +20532,7 @@
       </c>
       <c r="L83" s="13"/>
       <c r="M83" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N83" s="12" t="s">
         <v>225</v>
@@ -20409,7 +20556,7 @@
         <v>326</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D84" s="12"/>
       <c r="E84" s="12" t="s">
@@ -20429,7 +20576,7 @@
       </c>
       <c r="L84" s="13"/>
       <c r="M84" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N84" s="12" t="s">
         <v>231</v>
@@ -20453,7 +20600,7 @@
         <v>326</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D85" s="12"/>
       <c r="E85" s="12" t="s">
@@ -20473,7 +20620,7 @@
       </c>
       <c r="L85" s="13"/>
       <c r="M85" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N85" s="12" t="s">
         <v>325</v>
@@ -20541,7 +20688,7 @@
         <v>326</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="12" t="s">
@@ -20561,10 +20708,10 @@
       </c>
       <c r="L87" s="13"/>
       <c r="M87" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N87" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O87" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -22460,7 +22607,7 @@
         <v>331</v>
       </c>
       <c r="N132" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O132" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -22502,7 +22649,7 @@
         <v>328</v>
       </c>
       <c r="N133" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O133" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -22844,7 +22991,7 @@
         <v>457</v>
       </c>
       <c r="N141" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O141" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23490,10 +23637,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D157" s="12"/>
       <c r="E157" s="12" t="s">
@@ -23513,10 +23660,10 @@
       </c>
       <c r="L157" s="13"/>
       <c r="M157" s="12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N157" s="12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O157" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23532,10 +23679,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D158" s="12"/>
       <c r="E158" s="12" t="s">
@@ -23555,10 +23702,10 @@
       </c>
       <c r="L158" s="13"/>
       <c r="M158" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N158" s="12" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O158" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23574,10 +23721,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D159" s="12"/>
       <c r="E159" s="12" t="s">
@@ -23597,10 +23744,10 @@
       </c>
       <c r="L159" s="13"/>
       <c r="M159" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N159" s="12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O159" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23616,10 +23763,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D160" s="12"/>
       <c r="E160" s="12" t="s">
@@ -23639,10 +23786,10 @@
       </c>
       <c r="L160" s="13"/>
       <c r="M160" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N160" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O160" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23658,10 +23805,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D161" s="12"/>
       <c r="E161" s="12" t="s">
@@ -23681,10 +23828,10 @@
       </c>
       <c r="L161" s="13"/>
       <c r="M161" s="12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N161" s="12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O161" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23700,10 +23847,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D162" s="12"/>
       <c r="E162" s="12" t="s">
@@ -23723,10 +23870,10 @@
       </c>
       <c r="L162" s="13"/>
       <c r="M162" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N162" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O162" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23742,10 +23889,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D163" s="12"/>
       <c r="E163" s="12" t="s">
@@ -23765,10 +23912,10 @@
       </c>
       <c r="L163" s="13"/>
       <c r="M163" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N163" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O163" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23784,10 +23931,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D164" s="12"/>
       <c r="E164" s="12" t="s">
@@ -23807,10 +23954,10 @@
       </c>
       <c r="L164" s="13"/>
       <c r="M164" s="12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N164" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O164" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23826,10 +23973,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D165" s="12"/>
       <c r="E165" s="12" t="s">
@@ -23849,10 +23996,10 @@
       </c>
       <c r="L165" s="13"/>
       <c r="M165" s="12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N165" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O165" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23868,10 +24015,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D166" s="12"/>
       <c r="E166" s="12" t="s">
@@ -23891,10 +24038,10 @@
       </c>
       <c r="L166" s="13"/>
       <c r="M166" s="12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N166" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O166" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -23910,10 +24057,10 @@
         <v>46269.442361111112</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D167" s="12"/>
       <c r="E167" s="12" t="s">
@@ -23933,10 +24080,10 @@
       </c>
       <c r="L167" s="13"/>
       <c r="M167" s="12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N167" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O167" s="12" t="str">
         <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
@@ -24006,7 +24153,7 @@
         <v>862</v>
       </c>
       <c r="F169" s="13" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G169" s="12" t="s">
         <v>848</v>
@@ -24406,7 +24553,7 @@
         <v>862</v>
       </c>
       <c r="F178" s="13" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G178" s="12" t="s">
         <v>848</v>
@@ -24452,7 +24599,7 @@
         <v>862</v>
       </c>
       <c r="F179" s="13" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>848</v>
@@ -24666,10 +24813,10 @@
         <v>46269.723611111112</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D184" s="12"/>
       <c r="E184" s="12" t="s">
@@ -24689,7 +24836,7 @@
       </c>
       <c r="L184" s="13"/>
       <c r="M184" s="12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N184" s="12" t="s">
         <v>753</v>
@@ -24708,10 +24855,10 @@
         <v>46269.723611111112</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D185" s="12"/>
       <c r="E185" s="12" t="s">
@@ -24731,7 +24878,7 @@
       </c>
       <c r="L185" s="13"/>
       <c r="M185" s="12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N185" s="12" t="s">
         <v>756</v>
@@ -24750,10 +24897,10 @@
         <v>46269.723611111112</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D186" s="12"/>
       <c r="E186" s="12" t="s">
@@ -24773,7 +24920,7 @@
       </c>
       <c r="L186" s="13"/>
       <c r="M186" s="12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N186" s="12" t="s">
         <v>747</v>
@@ -24792,10 +24939,10 @@
         <v>46269.723611111112</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D187" s="12"/>
       <c r="E187" s="12" t="s">
@@ -24815,7 +24962,7 @@
       </c>
       <c r="L187" s="13"/>
       <c r="M187" s="12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N187" s="12" t="s">
         <v>751</v>
@@ -24954,6 +25101,300 @@
         <v>903</v>
       </c>
       <c r="Q190" s="14"/>
+    </row>
+    <row r="191" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="15">
+        <v>46299.385416666664</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D191" s="12"/>
+      <c r="E191" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F191" s="13"/>
+      <c r="G191" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H191" s="13"/>
+      <c r="I191" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J191" s="13"/>
+      <c r="K191" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L191" s="13"/>
+      <c r="M191" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="N191" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="O191" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P191" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="Q191" s="14"/>
+    </row>
+    <row r="192" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="15">
+        <v>46299.385416666664</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D192" s="12"/>
+      <c r="E192" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F192" s="13"/>
+      <c r="G192" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H192" s="13"/>
+      <c r="I192" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J192" s="13"/>
+      <c r="K192" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L192" s="13"/>
+      <c r="M192" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="N192" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="O192" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P192" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="Q192" s="14"/>
+    </row>
+    <row r="193" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="15">
+        <v>46299.385416666664</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D193" s="12"/>
+      <c r="E193" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F193" s="13"/>
+      <c r="G193" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H193" s="13"/>
+      <c r="I193" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J193" s="13"/>
+      <c r="K193" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L193" s="13"/>
+      <c r="M193" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="N193" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="O193" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P193" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="Q193" s="14"/>
+    </row>
+    <row r="194" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="15">
+        <v>46299.40625</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D194" s="12"/>
+      <c r="E194" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F194" s="13"/>
+      <c r="G194" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H194" s="13"/>
+      <c r="I194" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J194" s="13"/>
+      <c r="K194" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L194" s="13"/>
+      <c r="M194" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="N194" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="O194" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P194" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="Q194" s="14"/>
+    </row>
+    <row r="195" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="15">
+        <v>46299.40625</v>
+      </c>
+      <c r="B195" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D195" s="12"/>
+      <c r="E195" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F195" s="13"/>
+      <c r="G195" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H195" s="13"/>
+      <c r="I195" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J195" s="13"/>
+      <c r="K195" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L195" s="13"/>
+      <c r="M195" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="N195" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O195" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P195" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="Q195" s="14"/>
+    </row>
+    <row r="196" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="15">
+        <v>46299.40625</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D196" s="12"/>
+      <c r="E196" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F196" s="13"/>
+      <c r="G196" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H196" s="13"/>
+      <c r="I196" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J196" s="13"/>
+      <c r="K196" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L196" s="13"/>
+      <c r="M196" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="N196" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="O196" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P196" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="Q196" s="14"/>
+    </row>
+    <row r="197" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="15">
+        <v>46299.40625</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="D197" s="12"/>
+      <c r="E197" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="F197" s="13"/>
+      <c r="G197" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="H197" s="13"/>
+      <c r="I197" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="J197" s="13"/>
+      <c r="K197" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="L197" s="13"/>
+      <c r="M197" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="N197" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="O197" s="12" t="str">
+        <f>IF(TabelaRespostas[[#This Row],[Momento do Envio]]&gt;=1,"SIM","NÃO")</f>
+        <v>SIM</v>
+      </c>
+      <c r="P197" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="Q197" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24968,7 +25409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D594CA1-84CE-4635-82A0-1A17CF6D309A}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
@@ -24979,14 +25420,14 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C1" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D1">
         <f>D3-D2</f>
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -24995,14 +25436,14 @@
       </c>
       <c r="B2">
         <f>COUNTA(A:A)-2</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D2">
         <f>B2</f>
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -25010,7 +25451,7 @@
         <v>425</v>
       </c>
       <c r="C3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D3">
         <f>COUNTA(_xlfn.UNIQUE(Base_Dados!A:A))-1</f>
@@ -25039,167 +25480,177 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>502</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>341</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>395</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>504</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>366</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>270</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>417</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>326</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>650</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>371</v>
+        <v>650</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>156</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>745</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>325</v>
+        <v>745</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>209</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>375</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>455</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>397</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>519</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>643</v>
+        <v>520</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>603</v>
+        <v>643</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>291</v>
+        <v>604</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>908</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>910</v>
       </c>
     </row>
   </sheetData>
@@ -25223,12 +25674,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="str" cm="1">
-        <f t="array" ref="A2:A24">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A499, (Base_Dados!A2:A499&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A499)=0), "✅ Todos responderam!")))</f>
+        <f t="array" ref="A2:A22">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Base_Dados!A2:A499, (Base_Dados!A2:A499&lt;&gt;"") * (COUNTIF(Respostas!B:B, Base_Dados!A2:A499)=0), "✅ Todos responderam!")))</f>
         <v>_</v>
       </c>
     </row>
@@ -25254,93 +25705,89 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="str">
-        <v>CAMILA DA SILVA ANDRADE</v>
+        <v>CARINE REIS DOS SANTOS</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="str">
-        <v>CARINE REIS DOS SANTOS</v>
+        <v>DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="str">
-        <v>DANILO ALEXANDRE MONTEIRO DE CASTRO SABBAGH</v>
+        <v>DIEGO PIRES</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="str">
-        <v>DIEGO PIRES</v>
+        <v>ELIANE PEREIRA DA SILVA HIDALGO</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="str">
-        <v>ELIANE PEREIRA DA SILVA HIDALGO</v>
+        <v>FLAVIO HENRIQUE ALMEIDA FERREIRA DE MELO</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="str">
-        <v>FLAVIO HENRIQUE ALMEIDA FERREIRA DE MELO</v>
+        <v>LEON DOS REIS CALIXTO</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="str">
-        <v>LEON DOS REIS CALIXTO</v>
+        <v>LUÍS HENRIQUE SOARES DUTRA DE ANDRADE</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="str">
-        <v>LUÍS HENRIQUE SOARES DUTRA DE ANDRADE</v>
+        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="str">
-        <v>RAMON BARCELOS VILAR GUIMARÃES</v>
+        <v>RAPHAEL AZEVEDO</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="str">
-        <v>RAPHAEL AZEVEDO</v>
+        <v>RODRIGO ASSUMPÇÃO</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="str">
-        <v>RODRIGO ASSUMPÇÃO</v>
+        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="str">
-        <v>RONALDO BRUNO DE SOUZA SANTOS</v>
+        <v>SANDRO YUKIO YAMANO</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="str">
-        <v>SANDRO YUKIO YAMANO</v>
+        <v>STAEL MARLEI DE SOUZA E SILVA</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="str">
-        <v>STAEL MARLEI DE SOUZA E SILVA</v>
+        <v>TALES VILAR MOTA GUIMARAES</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="str">
-        <v>TALES VILAR MOTA GUIMARAES</v>
+        <v>VANUZA DOS SANTOS PRESTES</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="str">
-        <v>ULISSES LEANDRO CARVALHO FERREIRA</v>
+        <v>WANDERSON LAGE</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="str">
-        <v>VANUZA DOS SANTOS PRESTES</v>
-      </c>
+      <c r="A23" s="7"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="str">
-        <v>WANDERSON LAGE</v>
-      </c>
+      <c r="A24" s="7"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
@@ -25502,20 +25949,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d25a7fee-0375-4291-87e9-efb469dc66be" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25701,25 +26148,25 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92384E18-AB68-4DBB-8E5A-132AAEABE0F7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2B36854-38B6-44D7-BC7F-399EDA229B13}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d25a7fee-0375-4291-87e9-efb469dc66be"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
